--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1967" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1967" uniqueCount="395">
   <si>
     <t>50001569 - EUROHINCA</t>
   </si>
@@ -257,6 +257,9 @@
   </si>
   <si>
     <t xml:space="preserve">Reserva produccion,Recepción mono bloque </t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1216208608300141</t>
@@ -2945,7 +2948,7 @@
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46206.67848079861</v>
+        <v>46209.197446886574</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>78</v>
@@ -2992,8 +2995,8 @@
       <c r="S24" s="6">
         <v>0</v>
       </c>
-      <c r="T24" s="7" t="s">
-        <v>46</v>
+      <c r="T24" s="12" t="s">
+        <v>82</v>
       </c>
       <c r="U24" s="12" t="s">
         <v>47</v>
@@ -3001,7 +3004,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B25" s="9">
         <v>46204.786945914355</v>
@@ -3011,7 +3014,7 @@
         <v>46206.769665162035</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>25</v>
@@ -3035,10 +3038,10 @@
         <v>26</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -3048,7 +3051,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B26" s="5">
         <v>46204.78715721065</v>
@@ -3060,7 +3063,7 @@
         <v>46206.76967918982</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
@@ -3087,13 +3090,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>71</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q26" s="5">
         <v>46212</v>
@@ -3113,7 +3116,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B27" s="9">
         <v>46204.78716710648</v>
@@ -3123,7 +3126,7 @@
         <v>46206.673052592596</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
@@ -3150,13 +3153,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>42</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q27" s="9">
         <v>46213</v>
@@ -3176,7 +3179,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B28" s="5">
         <v>46204.787177743056</v>
@@ -3186,16 +3189,16 @@
         <v>46206.76986597222</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I28" s="5">
         <v>46241</v>
@@ -3213,13 +3216,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q28" s="5">
         <v>46244</v>
@@ -3239,7 +3242,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B29" s="9">
         <v>46204.79158200232</v>
@@ -3249,16 +3252,16 @@
         <v>46206.67314619213</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I29" s="9">
         <v>46241</v>
@@ -3276,13 +3279,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q29" s="9">
         <v>46244</v>
@@ -3302,7 +3305,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B30" s="5">
         <v>46204.79163886574</v>
@@ -3312,16 +3315,16 @@
         <v>46206.673139039354</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I30" s="5">
         <v>46241</v>
@@ -3339,13 +3342,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q30" s="5">
         <v>46244</v>
@@ -3365,7 +3368,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B31" s="9">
         <v>46204.7917447338</v>
@@ -3375,16 +3378,16 @@
         <v>46206.67313840278</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I31" s="9">
         <v>46241</v>
@@ -3402,13 +3405,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q31" s="9">
         <v>46244</v>
@@ -3428,7 +3431,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B32" s="5">
         <v>46204.78695173611</v>
@@ -3438,7 +3441,7 @@
         <v>46206.65562592592</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>25</v>
@@ -3462,7 +3465,7 @@
         <v>26</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3475,7 +3478,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B33" s="9">
         <v>46204.78719643518</v>
@@ -3485,16 +3488,16 @@
         <v>46206.67332864583</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I33" s="9">
         <v>46216</v>
@@ -3512,13 +3515,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q33" s="9">
         <v>46273</v>
@@ -3538,7 +3541,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B34" s="5">
         <v>46204.7872006713</v>
@@ -3548,16 +3551,16 @@
         <v>46206.67324984954</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I34" s="5">
         <v>46216</v>
@@ -3575,13 +3578,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3597,7 +3600,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B35" s="9">
         <v>46204.787204837965</v>
@@ -3607,16 +3610,16 @@
         <v>46206.67327987269</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I35" s="9">
         <v>46225</v>
@@ -3634,13 +3637,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3656,7 +3659,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B36" s="5">
         <v>46204.78722327546</v>
@@ -3666,16 +3669,16 @@
         <v>46206.76999994213</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I36" s="5">
         <v>46213</v>
@@ -3693,10 +3696,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3719,7 +3722,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B37" s="9">
         <v>46204.78722760417</v>
@@ -3731,16 +3734,16 @@
         <v>46206.769946203705</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I37" s="9">
         <v>46213</v>
@@ -3758,13 +3761,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3774,7 +3777,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B38" s="5">
         <v>46204.787231689814</v>
@@ -3784,16 +3787,16 @@
         <v>46206.76995223379</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I38" s="5">
         <v>46224</v>
@@ -3811,13 +3814,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3827,7 +3830,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B39" s="9">
         <v>46204.78728243055</v>
@@ -3839,16 +3842,16 @@
         <v>46206.769995821756</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I39" s="9">
         <v>46224</v>
@@ -3866,13 +3869,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -3882,7 +3885,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B40" s="5">
         <v>46204.78728729166</v>
@@ -3892,16 +3895,16 @@
         <v>46206.67363866898</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I40" s="5">
         <v>46245</v>
@@ -3919,13 +3922,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q40" s="5">
         <v>46255</v>
@@ -3945,7 +3948,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B41" s="9">
         <v>46204.787292175926</v>
@@ -3955,16 +3958,16 @@
         <v>46206.67358165509</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I41" s="9">
         <v>46245</v>
@@ -3982,13 +3985,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4004,7 +4007,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B42" s="5">
         <v>46204.78730063657</v>
@@ -4014,16 +4017,16 @@
         <v>46206.673579016206</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I42" s="5">
         <v>46247</v>
@@ -4041,13 +4044,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4063,7 +4066,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B43" s="9">
         <v>46204.793668136575</v>
@@ -4073,16 +4076,16 @@
         <v>46206.67378693287</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I43" s="9">
         <v>46245</v>
@@ -4100,10 +4103,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4126,7 +4129,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B44" s="5">
         <v>46204.794818298615</v>
@@ -4136,16 +4139,16 @@
         <v>46206.673746319444</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I44" s="5">
         <v>46245</v>
@@ -4163,13 +4166,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4179,7 +4182,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B45" s="9">
         <v>46204.794902430556</v>
@@ -4189,16 +4192,16 @@
         <v>46206.673743865744</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I45" s="9">
         <v>46247</v>
@@ -4216,13 +4219,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4232,7 +4235,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B46" s="5">
         <v>46204.7938509375</v>
@@ -4242,16 +4245,16 @@
         <v>46206.67393748843</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I46" s="5">
         <v>46245</v>
@@ -4269,10 +4272,10 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4295,7 +4298,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B47" s="9">
         <v>46204.795001412036</v>
@@ -4305,16 +4308,16 @@
         <v>46206.673880648144</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I47" s="9">
         <v>46245</v>
@@ -4332,13 +4335,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
@@ -4348,7 +4351,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B48" s="5">
         <v>46204.795060543984</v>
@@ -4358,16 +4361,16 @@
         <v>46206.67387746528</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I48" s="5">
         <v>46247</v>
@@ -4385,13 +4388,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4401,7 +4404,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B49" s="9">
         <v>46204.7939687037</v>
@@ -4411,16 +4414,16 @@
         <v>46206.67465699074</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I49" s="9">
         <v>46241</v>
@@ -4438,10 +4441,10 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4464,7 +4467,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B50" s="5">
         <v>46204.795132997686</v>
@@ -4474,16 +4477,16 @@
         <v>46206.67409482639</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4501,13 +4504,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4517,7 +4520,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B51" s="9">
         <v>46204.795219293985</v>
@@ -4527,16 +4530,16 @@
         <v>46206.67409221065</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I51" s="9">
         <v>46246</v>
@@ -4554,13 +4557,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4570,7 +4573,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B52" s="5">
         <v>46206.65895994213</v>
@@ -4580,16 +4583,16 @@
         <v>46206.674336111115</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4605,10 +4608,10 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>26</v>
@@ -4621,7 +4624,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B53" s="9">
         <v>46204.787306770835</v>
@@ -4631,7 +4634,7 @@
         <v>46206.66711462963</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>25</v>
@@ -4655,7 +4658,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>26</v>
@@ -4668,7 +4671,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B54" s="5">
         <v>46204.78731047454</v>
@@ -4678,16 +4681,16 @@
         <v>46206.77015998843</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I54" s="5">
         <v>46212</v>
@@ -4705,13 +4708,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>74</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q54" s="5">
         <v>46218</v>
@@ -4731,7 +4734,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B55" s="9">
         <v>46204.78731518518</v>
@@ -4741,16 +4744,16 @@
         <v>46206.77015964121</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I55" s="9">
         <v>46233</v>
@@ -4768,13 +4771,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q55" s="9">
         <v>46239</v>
@@ -4794,7 +4797,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B56" s="5">
         <v>46204.78732028935</v>
@@ -4804,16 +4807,16 @@
         <v>46206.769866111106</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I56" s="5">
         <v>46240</v>
@@ -4831,13 +4834,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q56" s="5">
         <v>46240</v>
@@ -4857,7 +4860,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B57" s="9">
         <v>46204.787326770835</v>
@@ -4867,16 +4870,16 @@
         <v>46206.67498217593</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I57" s="9">
         <v>46288</v>
@@ -4894,13 +4897,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q57" s="9">
         <v>46288</v>
@@ -4920,7 +4923,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B58" s="5">
         <v>46205.8929956713</v>
@@ -4930,16 +4933,16 @@
         <v>46206.67494384259</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I58" s="5">
         <v>46288</v>
@@ -4957,13 +4960,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4973,7 +4976,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B59" s="9">
         <v>46205.89308850694</v>
@@ -4983,16 +4986,16 @@
         <v>46206.67494135417</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I59" s="9">
         <v>46288</v>
@@ -5010,13 +5013,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5026,7 +5029,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B60" s="5">
         <v>46205.89321678241</v>
@@ -5036,16 +5039,16 @@
         <v>46206.67493778935</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I60" s="5">
         <v>46288</v>
@@ -5063,13 +5066,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5079,7 +5082,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B61" s="9">
         <v>46204.787330555555</v>
@@ -5089,7 +5092,7 @@
         <v>46206.65997969908</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>25</v>
@@ -5113,7 +5116,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5126,7 +5129,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B62" s="5">
         <v>46204.78733380787</v>
@@ -5136,16 +5139,16 @@
         <v>46206.67512555556</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I62" s="5">
         <v>46258</v>
@@ -5163,13 +5166,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q62" s="5">
         <v>46259</v>
@@ -5189,7 +5192,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B63" s="9">
         <v>46204.78733813658</v>
@@ -5199,16 +5202,16 @@
         <v>46206.67526587963</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I63" s="9">
         <v>46260</v>
@@ -5226,13 +5229,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q63" s="9">
         <v>46261</v>
@@ -5252,7 +5255,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B64" s="5">
         <v>46204.79962430555</v>
@@ -5262,16 +5265,16 @@
         <v>46206.67512305555</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I64" s="5">
         <v>46258</v>
@@ -5289,13 +5292,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q64" s="5">
         <v>46259</v>
@@ -5315,7 +5318,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B65" s="9">
         <v>46204.79970230324</v>
@@ -5325,16 +5328,16 @@
         <v>46206.67526299768</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I65" s="9">
         <v>46260</v>
@@ -5352,13 +5355,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q65" s="9">
         <v>46261</v>
@@ -5378,7 +5381,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B66" s="5">
         <v>46204.799834722224</v>
@@ -5388,16 +5391,16 @@
         <v>46206.67512025463</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I66" s="5">
         <v>46258</v>
@@ -5415,13 +5418,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q66" s="5">
         <v>46259</v>
@@ -5441,7 +5444,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B67" s="9">
         <v>46204.80007783565</v>
@@ -5451,16 +5454,16 @@
         <v>46206.67526012732</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I67" s="9">
         <v>46260</v>
@@ -5478,13 +5481,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q67" s="9">
         <v>46261</v>
@@ -5504,7 +5507,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B68" s="5">
         <v>46204.787342662035</v>
@@ -5514,7 +5517,7 @@
         <v>46206.66163074074</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5538,7 +5541,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5551,7 +5554,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B69" s="9">
         <v>46204.78734565972</v>
@@ -5561,16 +5564,16 @@
         <v>46206.67535149306</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I69" s="9">
         <v>46262</v>
@@ -5588,13 +5591,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q69" s="9">
         <v>46266</v>
@@ -5614,7 +5617,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B70" s="5">
         <v>46204.78735021991</v>
@@ -5624,16 +5627,16 @@
         <v>46206.67558131945</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I70" s="5">
         <v>46267</v>
@@ -5651,13 +5654,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q70" s="5">
         <v>46273</v>
@@ -5677,7 +5680,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B71" s="9">
         <v>46204.83329071759</v>
@@ -5687,16 +5690,16 @@
         <v>46206.67551582176</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I71" s="9">
         <v>46267</v>
@@ -5714,13 +5717,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5730,7 +5733,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B72" s="5">
         <v>46204.83348987269</v>
@@ -5740,16 +5743,16 @@
         <v>46206.67551341435</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I72" s="5">
         <v>46267</v>
@@ -5767,13 +5770,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5783,7 +5786,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B73" s="9">
         <v>46204.83350201389</v>
@@ -5793,16 +5796,16 @@
         <v>46206.67551030093</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I73" s="9">
         <v>46267</v>
@@ -5820,13 +5823,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -5836,7 +5839,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B74" s="5">
         <v>46204.787355625</v>
@@ -5846,16 +5849,16 @@
         <v>46206.67580866898</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I74" s="5">
         <v>46274</v>
@@ -5873,13 +5876,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q74" s="5">
         <v>46274</v>
@@ -5899,7 +5902,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B75" s="9">
         <v>46204.83355802084</v>
@@ -5909,16 +5912,16 @@
         <v>46206.67575559027</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I75" s="10"/>
       <c r="J75" s="9">
@@ -5934,13 +5937,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -5950,7 +5953,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B76" s="5">
         <v>46204.833570069444</v>
@@ -5960,16 +5963,16 @@
         <v>46206.67575268519</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I76" s="6"/>
       <c r="J76" s="5">
@@ -5985,13 +5988,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6001,7 +6004,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B77" s="9">
         <v>46204.833579004626</v>
@@ -6011,16 +6014,16 @@
         <v>46206.67574885416</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I77" s="10"/>
       <c r="J77" s="9">
@@ -6036,13 +6039,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6052,7 +6055,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B78" s="5">
         <v>46204.78736071759</v>
@@ -6062,7 +6065,7 @@
         <v>46206.67094998843</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>25</v>
@@ -6086,7 +6089,7 @@
         <v>26</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6099,7 +6102,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B79" s="9">
         <v>46204.78736410879</v>
@@ -6109,16 +6112,16 @@
         <v>46206.6759174537</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I79" s="9">
         <v>46210</v>
@@ -6136,13 +6139,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O79" s="10" t="s">
         <v>78</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q79" s="9">
         <v>46210</v>
@@ -6162,7 +6165,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B80" s="5">
         <v>46204.78737366898</v>
@@ -6172,16 +6175,16 @@
         <v>46206.67591493056</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I80" s="5">
         <v>46253</v>
@@ -6199,13 +6202,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q80" s="5">
         <v>46253</v>
@@ -6225,7 +6228,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B81" s="9">
         <v>46204.78737825232</v>
@@ -6235,16 +6238,16 @@
         <v>46206.67600082176</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I81" s="9">
         <v>46274</v>
@@ -6262,13 +6265,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q81" s="9">
         <v>46274</v>
@@ -6288,7 +6291,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B82" s="5">
         <v>46206.567318657406</v>
@@ -6304,10 +6307,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I82" s="6"/>
       <c r="J82" s="5">
@@ -6323,13 +6326,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6339,7 +6342,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B83" s="9">
         <v>46206.56766555556</v>
@@ -6355,10 +6358,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I83" s="10"/>
       <c r="J83" s="9">
@@ -6374,13 +6377,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6390,7 +6393,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B84" s="5">
         <v>46206.56768260417</v>
@@ -6406,10 +6409,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I84" s="6"/>
       <c r="J84" s="5">
@@ -6425,13 +6428,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6441,7 +6444,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B85" s="9">
         <v>46206.56769806713</v>
@@ -6457,10 +6460,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I85" s="10"/>
       <c r="J85" s="9">
@@ -6476,13 +6479,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6492,7 +6495,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B86" s="5">
         <v>46206.56771423611</v>
@@ -6508,10 +6511,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I86" s="6"/>
       <c r="J86" s="5">
@@ -6527,13 +6530,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6543,7 +6546,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B87" s="9">
         <v>46206.56772880787</v>
@@ -6559,10 +6562,10 @@
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I87" s="10"/>
       <c r="J87" s="9">
@@ -6578,13 +6581,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6594,7 +6597,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B88" s="5">
         <v>46206.567743506945</v>
@@ -6610,10 +6613,10 @@
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I88" s="6"/>
       <c r="J88" s="5">
@@ -6629,13 +6632,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6645,7 +6648,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B89" s="9">
         <v>46206.56775844908</v>
@@ -6661,10 +6664,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I89" s="10"/>
       <c r="J89" s="9">
@@ -6680,13 +6683,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6696,7 +6699,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B90" s="5">
         <v>46206.56777289352</v>
@@ -6712,10 +6715,10 @@
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I90" s="6"/>
       <c r="J90" s="5">
@@ -6731,13 +6734,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6747,7 +6750,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B91" s="9">
         <v>46206.67094809028</v>
@@ -6757,16 +6760,16 @@
         <v>46206.67590806713</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I91" s="9">
         <v>46274</v>
@@ -6784,10 +6787,10 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P91" s="10" t="s">
         <v>26</v>
@@ -6804,7 +6807,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B92" s="5">
         <v>46204.78738409722</v>
@@ -6814,7 +6817,7 @@
         <v>46206.66745490741</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>25</v>
@@ -6838,7 +6841,7 @@
         <v>26</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>26</v>
@@ -6851,7 +6854,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B93" s="9">
         <v>46204.787387268516</v>
@@ -6861,7 +6864,7 @@
         <v>46206.676306875</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -6888,13 +6891,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q93" s="9">
         <v>46281</v>
@@ -6914,7 +6917,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B94" s="5">
         <v>46204.84491833333</v>
@@ -6924,7 +6927,7 @@
         <v>46206.676259513886</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -6951,13 +6954,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -6967,7 +6970,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B95" s="9">
         <v>46204.84493530093</v>
@@ -6977,7 +6980,7 @@
         <v>46206.67625695602</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7004,13 +7007,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7020,7 +7023,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B96" s="5">
         <v>46204.84494427084</v>
@@ -7030,7 +7033,7 @@
         <v>46206.67625305556</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7057,13 +7060,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7073,7 +7076,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B97" s="9">
         <v>46204.78739225694</v>
@@ -7083,7 +7086,7 @@
         <v>46206.67641435185</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7110,13 +7113,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q97" s="9">
         <v>46282</v>
@@ -7136,7 +7139,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B98" s="5">
         <v>46204.84497997686</v>
@@ -7146,7 +7149,7 @@
         <v>46206.67651039352</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7173,13 +7176,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7189,7 +7192,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B99" s="9">
         <v>46204.84498876157</v>
@@ -7199,7 +7202,7 @@
         <v>46206.67650773148</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7226,13 +7229,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7242,7 +7245,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B100" s="5">
         <v>46204.84499563657</v>
@@ -7252,7 +7255,7 @@
         <v>46206.67650460648</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7279,13 +7282,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7295,7 +7298,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B101" s="9">
         <v>46204.78740502315</v>
@@ -7305,7 +7308,7 @@
         <v>46206.676410960645</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7332,13 +7335,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q101" s="9">
         <v>46286</v>
@@ -7358,7 +7361,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B102" s="5">
         <v>46204.84507945602</v>
@@ -7368,7 +7371,7 @@
         <v>46206.67662570602</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7395,13 +7398,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7411,7 +7414,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B103" s="9">
         <v>46204.84508817129</v>
@@ -7421,7 +7424,7 @@
         <v>46206.676623368054</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7448,13 +7451,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7464,7 +7467,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B104" s="5">
         <v>46204.845093854165</v>
@@ -7474,7 +7477,7 @@
         <v>46206.676619756945</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7501,13 +7504,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7517,7 +7520,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B105" s="9">
         <v>46204.78741121528</v>
@@ -7527,7 +7530,7 @@
         <v>46206.67640778935</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7554,13 +7557,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q105" s="9">
         <v>46287</v>
@@ -7580,7 +7583,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B106" s="5">
         <v>46204.84513122685</v>
@@ -7590,7 +7593,7 @@
         <v>46206.67673481481</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7617,13 +7620,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7633,7 +7636,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B107" s="9">
         <v>46204.84513944444</v>
@@ -7643,7 +7646,7 @@
         <v>46206.67673186342</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7670,13 +7673,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7686,7 +7689,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B108" s="5">
         <v>46204.8451466088</v>
@@ -7696,7 +7699,7 @@
         <v>46206.67672797454</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7723,13 +7726,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7739,7 +7742,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B109" s="9">
         <v>46204.787473310185</v>
@@ -7749,7 +7752,7 @@
         <v>46206.676404432874</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -7776,13 +7779,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q109" s="9">
         <v>46289</v>
@@ -7802,7 +7805,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B110" s="5">
         <v>46204.84518325231</v>
@@ -7812,7 +7815,7 @@
         <v>46206.676860590276</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -7839,13 +7842,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -7855,7 +7858,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B111" s="9">
         <v>46204.845191898145</v>
@@ -7865,7 +7868,7 @@
         <v>46206.676858067134</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -7892,13 +7895,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -7908,7 +7911,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B112" s="5">
         <v>46204.84520083333</v>
@@ -7918,7 +7921,7 @@
         <v>46206.676854363424</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -7945,13 +7948,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -7961,7 +7964,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B113" s="9">
         <v>46204.78748032407</v>
@@ -7971,7 +7974,7 @@
         <v>46206.668344247686</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>25</v>
@@ -7995,7 +7998,7 @@
         <v>26</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>
@@ -8008,7 +8011,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B114" s="5">
         <v>46204.787484155095</v>
@@ -8018,16 +8021,16 @@
         <v>46206.677181631945</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I114" s="5">
         <v>46290</v>
@@ -8045,13 +8048,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q114" s="5">
         <v>46290</v>
@@ -8071,7 +8074,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B115" s="9">
         <v>46206.61281571759</v>
@@ -8081,16 +8084,16 @@
         <v>46206.67717564815</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I115" s="9">
         <v>46290</v>
@@ -8108,13 +8111,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8124,7 +8127,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B116" s="5">
         <v>46206.612829722224</v>
@@ -8134,16 +8137,16 @@
         <v>46206.67717299769</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I116" s="5">
         <v>46290</v>
@@ -8161,13 +8164,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8177,7 +8180,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B117" s="9">
         <v>46206.61284180556</v>
@@ -8187,16 +8190,16 @@
         <v>46206.67717023148</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I117" s="9">
         <v>46290</v>
@@ -8214,13 +8217,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8230,7 +8233,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B118" s="5">
         <v>46206.61323981482</v>
@@ -8246,10 +8249,10 @@
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I118" s="5">
         <v>46290</v>
@@ -8267,13 +8270,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>55</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8283,7 +8286,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B119" s="9">
         <v>46206.613256446755</v>
@@ -8299,10 +8302,10 @@
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I119" s="9">
         <v>46290</v>
@@ -8320,13 +8323,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O119" s="10" t="s">
         <v>58</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8336,7 +8339,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B120" s="5">
         <v>46206.61328513889</v>
@@ -8352,10 +8355,10 @@
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I120" s="5">
         <v>46290</v>
@@ -8373,13 +8376,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>55</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8389,7 +8392,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B121" s="9">
         <v>46206.613270925925</v>
@@ -8405,10 +8408,10 @@
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I121" s="9">
         <v>46290</v>
@@ -8426,13 +8429,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O121" s="10" t="s">
         <v>55</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8442,7 +8445,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B122" s="5">
         <v>46206.6133403125</v>
@@ -8458,10 +8461,10 @@
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I122" s="5">
         <v>46290</v>
@@ -8479,13 +8482,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>55</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8495,7 +8498,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B123" s="9">
         <v>46206.613361041665</v>
@@ -8511,10 +8514,10 @@
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I123" s="9">
         <v>46290</v>
@@ -8532,13 +8535,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O123" s="10" t="s">
         <v>55</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8548,7 +8551,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B124" s="5">
         <v>46206.613371493055</v>
@@ -8564,10 +8567,10 @@
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I124" s="5">
         <v>46290</v>
@@ -8585,13 +8588,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>55</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8601,7 +8604,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B125" s="9">
         <v>46206.61338284722</v>
@@ -8617,10 +8620,10 @@
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I125" s="9">
         <v>46290</v>
@@ -8638,13 +8641,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O125" s="10" t="s">
         <v>55</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -8654,7 +8657,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B126" s="5">
         <v>46206.61339653935</v>
@@ -8670,10 +8673,10 @@
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I126" s="5">
         <v>46290</v>
@@ -8691,13 +8694,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>55</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8707,7 +8710,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B127" s="9">
         <v>46204.78748974537</v>
@@ -8717,7 +8720,7 @@
         <v>46206.67743496528</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
@@ -8744,13 +8747,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q127" s="9">
         <v>46293</v>
@@ -8770,7 +8773,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B128" s="5">
         <v>46204.84566665509</v>
@@ -8780,7 +8783,7 @@
         <v>46206.6774368287</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -8807,13 +8810,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -8823,7 +8826,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B129" s="9">
         <v>46204.8456746875</v>
@@ -8833,7 +8836,7 @@
         <v>46206.67743376158</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
@@ -8860,13 +8863,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -8876,7 +8879,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B130" s="5">
         <v>46204.84568395834</v>
@@ -8886,7 +8889,7 @@
         <v>46206.67743099537</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -8913,13 +8916,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -8929,7 +8932,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B131" s="9">
         <v>46204.84577770834</v>
@@ -8939,7 +8942,7 @@
         <v>46206.67742784722</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
@@ -8966,13 +8969,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O131" s="10" t="s">
         <v>55</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -8982,7 +8985,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B132" s="5">
         <v>46204.845803958335</v>
@@ -8992,7 +8995,7 @@
         <v>46206.677424988426</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9019,13 +9022,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O132" s="6" t="s">
         <v>55</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9035,7 +9038,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B133" s="9">
         <v>46204.8458116088</v>
@@ -9045,7 +9048,7 @@
         <v>46206.67742180555</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
@@ -9072,13 +9075,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O133" s="10" t="s">
         <v>55</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9088,7 +9091,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B134" s="5">
         <v>46204.84582686343</v>
@@ -9098,7 +9101,7 @@
         <v>46206.677418680556</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9125,13 +9128,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>55</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9141,7 +9144,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B135" s="9">
         <v>46204.84581974537</v>
@@ -9151,7 +9154,7 @@
         <v>46206.67741584491</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
@@ -9178,13 +9181,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O135" s="10" t="s">
         <v>55</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9194,7 +9197,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B136" s="5">
         <v>46204.84583605324</v>
@@ -9204,7 +9207,7 @@
         <v>46206.67741314815</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9231,13 +9234,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O136" s="6" t="s">
         <v>55</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9247,7 +9250,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B137" s="9">
         <v>46204.84584422453</v>
@@ -9257,7 +9260,7 @@
         <v>46206.67740501158</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
@@ -9284,13 +9287,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O137" s="10" t="s">
         <v>55</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9300,7 +9303,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B138" s="5">
         <v>46204.845850983795</v>
@@ -9310,7 +9313,7 @@
         <v>46206.67740435185</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9337,13 +9340,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O138" s="6" t="s">
         <v>55</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9353,7 +9356,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B139" s="9">
         <v>46204.84585899305</v>
@@ -9363,7 +9366,7 @@
         <v>46206.67740371528</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
@@ -9390,13 +9393,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O139" s="10" t="s">
         <v>55</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q139" s="10"/>
       <c r="R139" s="10"/>
@@ -9406,7 +9409,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B140" s="5">
         <v>46204.78749533565</v>
@@ -9416,16 +9419,16 @@
         <v>46206.67787028935</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I140" s="5">
         <v>46294</v>
@@ -9443,13 +9446,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q140" s="5">
         <v>46294</v>
@@ -9469,7 +9472,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B141" s="9">
         <v>46204.84595449074</v>
@@ -9479,16 +9482,16 @@
         <v>46206.67786329861</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H141" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I141" s="9">
         <v>46294</v>
@@ -9506,13 +9509,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P141" s="10" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q141" s="10"/>
       <c r="R141" s="10"/>
@@ -9522,7 +9525,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B142" s="5">
         <v>46204.845964189815</v>
@@ -9532,16 +9535,16 @@
         <v>46206.677860254626</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I142" s="5">
         <v>46294</v>
@@ -9559,13 +9562,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9575,7 +9578,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B143" s="9">
         <v>46204.84597238426</v>
@@ -9585,16 +9588,16 @@
         <v>46206.67785763889</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H143" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I143" s="9">
         <v>46294</v>
@@ -9612,13 +9615,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q143" s="10"/>
       <c r="R143" s="10"/>
@@ -9628,7 +9631,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B144" s="5">
         <v>46204.846036469906</v>
@@ -9638,16 +9641,16 @@
         <v>46206.67785519676</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I144" s="5">
         <v>46294</v>
@@ -9665,13 +9668,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -9681,7 +9684,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B145" s="9">
         <v>46204.846047893516</v>
@@ -9691,16 +9694,16 @@
         <v>46206.6778525</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H145" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I145" s="9">
         <v>46294</v>
@@ -9718,13 +9721,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -9734,7 +9737,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B146" s="5">
         <v>46204.846056724535</v>
@@ -9744,16 +9747,16 @@
         <v>46206.67784956019</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I146" s="5">
         <v>46294</v>
@@ -9771,13 +9774,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -9787,7 +9790,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B147" s="9">
         <v>46204.846065578706</v>
@@ -9797,16 +9800,16 @@
         <v>46206.677846921295</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H147" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I147" s="9">
         <v>46294</v>
@@ -9824,13 +9827,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O147" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q147" s="10"/>
       <c r="R147" s="10"/>
@@ -9840,7 +9843,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B148" s="5">
         <v>46204.846073252316</v>
@@ -9850,16 +9853,16 @@
         <v>46206.67784445602</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I148" s="5">
         <v>46294</v>
@@ -9877,13 +9880,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -9893,7 +9896,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B149" s="9">
         <v>46204.84608019676</v>
@@ -9903,16 +9906,16 @@
         <v>46206.6778419676</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H149" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I149" s="9">
         <v>46294</v>
@@ -9930,13 +9933,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q149" s="10"/>
       <c r="R149" s="10"/>
@@ -9946,7 +9949,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B150" s="5">
         <v>46204.84608666667</v>
@@ -9956,16 +9959,16 @@
         <v>46206.67783399306</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I150" s="5">
         <v>46294</v>
@@ -9983,13 +9986,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -9999,7 +10002,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B151" s="9">
         <v>46204.84609472222</v>
@@ -10009,16 +10012,16 @@
         <v>46206.677833344904</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G151" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H151" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I151" s="9">
         <v>46294</v>
@@ -10036,13 +10039,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P151" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q151" s="10"/>
       <c r="R151" s="10"/>
@@ -10052,7 +10055,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B152" s="5">
         <v>46204.84610289352</v>
@@ -10062,16 +10065,16 @@
         <v>46206.67783269676</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I152" s="5">
         <v>46294</v>
@@ -10089,13 +10092,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10105,7 +10108,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="8" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B153" s="9">
         <v>46204.78749967593</v>
@@ -10115,16 +10118,16 @@
         <v>46206.67812460648</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G153" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H153" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I153" s="10"/>
       <c r="J153" s="9">
@@ -10140,13 +10143,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O153" s="10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P153" s="10" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q153" s="9">
         <v>46295</v>
@@ -10166,7 +10169,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B154" s="5">
         <v>46204.846246076384</v>
@@ -10176,16 +10179,16 @@
         <v>46206.67812013889</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I154" s="5">
         <v>46295</v>
@@ -10203,13 +10206,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10219,7 +10222,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="8" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B155" s="9">
         <v>46204.84626494213</v>
@@ -10229,16 +10232,16 @@
         <v>46206.678117118056</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G155" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H155" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I155" s="9">
         <v>46295</v>
@@ -10256,13 +10259,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P155" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q155" s="10"/>
       <c r="R155" s="10"/>
@@ -10272,7 +10275,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B156" s="5">
         <v>46204.84627579861</v>
@@ -10282,16 +10285,16 @@
         <v>46206.67810802083</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I156" s="5">
         <v>46295</v>
@@ -10309,13 +10312,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -10325,7 +10328,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B157" s="9">
         <v>46204.846348113424</v>
@@ -10335,16 +10338,16 @@
         <v>46206.67810481481</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H157" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I157" s="9">
         <v>46295</v>
@@ -10362,13 +10365,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P157" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q157" s="10"/>
       <c r="R157" s="10"/>
@@ -10378,7 +10381,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B158" s="5">
         <v>46204.846357789356</v>
@@ -10388,16 +10391,16 @@
         <v>46206.67810172454</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H158" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I158" s="5">
         <v>46295</v>
@@ -10415,13 +10418,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -10431,7 +10434,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B159" s="9">
         <v>46204.846365879624</v>
@@ -10441,16 +10444,16 @@
         <v>46206.67809884259</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G159" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H159" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I159" s="9">
         <v>46295</v>
@@ -10468,13 +10471,13 @@
         <v>26</v>
       </c>
       <c r="N159" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O159" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P159" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q159" s="10"/>
       <c r="R159" s="10"/>
@@ -10484,7 +10487,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B160" s="5">
         <v>46204.846373692126</v>
@@ -10494,16 +10497,16 @@
         <v>46206.678095509254</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H160" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I160" s="5">
         <v>46295</v>
@@ -10521,13 +10524,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -10537,7 +10540,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B161" s="9">
         <v>46204.8463796412</v>
@@ -10547,16 +10550,16 @@
         <v>46206.67809255787</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G161" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H161" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I161" s="9">
         <v>46295</v>
@@ -10574,13 +10577,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O161" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P161" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q161" s="10"/>
       <c r="R161" s="10"/>
@@ -10590,7 +10593,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B162" s="5">
         <v>46204.846388715276</v>
@@ -10600,16 +10603,16 @@
         <v>46206.678089270834</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H162" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I162" s="5">
         <v>46295</v>
@@ -10627,13 +10630,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -10643,7 +10646,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B163" s="9">
         <v>46204.84640113426</v>
@@ -10653,16 +10656,16 @@
         <v>46206.67808063657</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F163" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G163" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H163" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I163" s="9">
         <v>46295</v>
@@ -10680,13 +10683,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O163" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P163" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q163" s="10"/>
       <c r="R163" s="10"/>
@@ -10696,7 +10699,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B164" s="5">
         <v>46204.84641309028</v>
@@ -10706,16 +10709,16 @@
         <v>46206.67807998843</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G164" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H164" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I164" s="5">
         <v>46295</v>
@@ -10733,13 +10736,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -10749,7 +10752,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="8" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B165" s="9">
         <v>46204.846406701385</v>
@@ -10759,16 +10762,16 @@
         <v>46206.67807929398</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G165" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H165" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I165" s="9">
         <v>46295</v>
@@ -10786,13 +10789,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O165" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P165" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q165" s="10"/>
       <c r="R165" s="10"/>
@@ -10802,7 +10805,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B166" s="5">
         <v>46204.7875055787</v>
@@ -10812,7 +10815,7 @@
         <v>46206.66985314815</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>25</v>
@@ -10836,7 +10839,7 @@
         <v>26</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P166" s="6" t="s">
         <v>26</v>
@@ -10855,7 +10858,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="8" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B167" s="9">
         <v>46204.787509016205</v>
@@ -10865,16 +10868,16 @@
         <v>46206.67820732639</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G167" s="10" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H167" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="I167" s="9">
         <v>46296</v>
@@ -10892,13 +10895,13 @@
         <v>26</v>
       </c>
       <c r="N167" s="10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O167" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P167" s="10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q167" s="9">
         <v>46304</v>
@@ -10918,7 +10921,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B168" s="5">
         <v>46204.78751333333</v>
@@ -10928,7 +10931,7 @@
         <v>46206.67824334491</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
@@ -10955,13 +10958,13 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q168" s="5">
         <v>46304</v>
@@ -10981,7 +10984,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B169" s="9">
         <v>46204.787518564815</v>
@@ -10991,7 +10994,7 @@
         <v>46206.67846486111</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>25</v>
@@ -11015,7 +11018,7 @@
         <v>26</v>
       </c>
       <c r="O169" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P169" s="10" t="s">
         <v>26</v>
@@ -11028,7 +11031,7 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B170" s="5">
         <v>46204.78752182871</v>
@@ -11038,7 +11041,7 @@
         <v>46206.67830775463</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
@@ -11065,13 +11068,13 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P170" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q170" s="5">
         <v>46315</v>
@@ -11091,7 +11094,7 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B171" s="9">
         <v>46204.78752627315</v>
@@ -11103,7 +11106,7 @@
         <v>46206.67848190972</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>26</v>
@@ -11130,13 +11133,13 @@
         <v>26</v>
       </c>
       <c r="N171" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O171" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="P171" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q171" s="9">
         <v>46324</v>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1967" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1967" uniqueCount="397">
   <si>
     <t>50001569 - EUROHINCA</t>
   </si>
@@ -118,6 +118,63 @@
     <t>Alcance del proyecto</t>
   </si>
   <si>
+    <t xml:space="preserve">Para el pedido 1569, se tiene 9 ventiladores ZVN 1-6-15/2 y Tablero VDF en Lógica Maestro-Esclavo para Eurohinca:
+    Planos para fabricación:
+        Estacion de ventilación 3xZVN 1-6-15/2 con motor WEG (3 unidades por cada estación)
+        Incluye: Tobera + Rejilla + 2FAR60/100 con bulbo acústico + Tipo C 600-500mm
+hgutierrez@zitron.com, tu apoyo con los planos.
+    Rodete:
+        Rodete monobloque GEL 6-15  
+        Código 300056
+        Plano mecanizado a confirmar.
+benjamin.bustos@zitron.com, favor realizar reserva de 9 unidades.
+    Tratamiento superficial estándar Zitron:
+        Preparación de superficie: Arenado SSPC-SP10
+        1ª capa imprimación 60 micras Hempadur 15570 Color 12430
+        2ª capa intermedia 40 micras Hempathane HS 55610 Color 20450 RAL 9001
+    Datos eléctricos para el motor:
+        Motor WEG 15 KW, 2 Polos, Frame 160L.
+        380 VAC, 50 Hz, IEC-IE3, IP55, FS 1.0.-
+ecarico@zitron.com, tu apoyo con la compra del motor, propuesta en ZPRO.
+    Datos eléctricos para tableros:
+        Tablero VDF  15KW, 380 VAC, 50 HZ.
+        Integrado en envolvente IP54, HMI en puerta, seccionador de entrada, luces piloto presencia de fases, botones marcha, paro, reset y protección de entrada.
+        Configuración Maestro-Esclavo
+ecarico@zitron.com, tu apoyo con la compra del tablero, propuesta en ZPRO.
+    Fecha de entrega:
+        1° Entrega: 29-07-2026 – 1 Estacion 3x ZVN 1-6-15/2 + 3 Tableros VDF M-E
+        2° Entrega: 23-09-2026 – 2 Estaciones 3x ZVN 1-6-15/2 + 6 Tableros VDF M-E
+hugo.isla@zitron.com, favor notar plazos de entrega.
+ Para el pedido 1569, se tiene 9 ventiladores ZVN 1-6-15/2 y Tablero VDF en Lógica Maestro-Esclavo para Eurohinca:
+    Planos para fabricación:
+        Estacion de ventilación 3xZVN 1-6-15/2 con motor WEG (3 unidades por cada estación)
+        Incluye: Tobera + Rejilla + 2FAR60/100 con bulbo acústico + Tipo C 600-500mm
+hgutierrez@zitron.com, tu apoyo con los planos.
+    Rodete:
+        Rodete monobloque GEL 6-15  
+        Código 300056
+        Plano mecanizado a confirmar.
+benjamin.bustos@zitron.com, favor realizar reserva de 9 unidades.
+    Tratamiento superficial estándar Zitron:
+        Preparación de superficie: Arenado SSPC-SP10
+        1ª capa imprimación 60 micras Hempadur 15570 Color 12430
+        2ª capa intermedia 40 micras Hempathane HS 55610 Color 20450 RAL 9001
+    Datos eléctricos para el motor:
+        Motor WEG 15 KW, 2 Polos, Frame 160L.
+        380 VAC, 50 Hz, IEC-IE3, IP55, FS 1.0.-
+ecarico@zitron.com, tu apoyo con la compra del motor, propuesta en ZPRO.
+    Datos eléctricos para tableros:
+        Tablero VDF  15KW, 380 VAC, 50 HZ.
+        Integrado en envolvente IP54, HMI en puerta, seccionador de entrada, luces piloto presencia de fases, botones marcha, paro, reset y protección de entrada.
+        Configuración Maestro-Esclavo
+ecarico@zitron.com, tu apoyo con la compra del tablero, propuesta en ZPRO.
+    Fecha de entrega:
+        1° Entrega: 29-07-2026 – 1 Estacion 3x ZVN 1-6-15/2 + 3 Tableros VDF M-E
+        2° Entrega: 23-09-2026 – 2 Estaciones 3x ZVN 1-6-15/2 + 6 Tableros VDF M-E
+hugo.isla@zitron.com, favor notar plazos de entrega.
+ </t>
+  </si>
+  <si>
     <t>1216218870843919</t>
   </si>
   <si>
@@ -989,6 +1046,11 @@
   </si>
   <si>
     <t>Embalaje</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        1° Entrega: 29-07-2026 – 1 Estacion 3x ZVN 1-6-15/2 + 3 Tableros VDF M-E
+        2° Entrega: 23-09-2026 – 2 Estaciones 3x ZVN 1-6-15/2 + 6 Tableros VDF M-E
+</t>
   </si>
   <si>
     <t>OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C,OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C,OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C,OT 4368 - TABLERO VDF 15 KW LOGICA M-E,OT 4368 - TABLERO VDF 15 KW LOGICA M-E,OT 4368 - TABLERO VDF 15 KW LOGICA M-E,OT 4368 - TABLERO VDF 15 KW LOGICA M-E,OT 4368 - TABLERO VDF 15 KW LOGICA M-E,OT 4368 - TABLERO VDF 15 KW LOGICA M-E,OT 4368 - TABLERO VDF 15 KW LOGICA M-E,OT 4368 - TABLERO VDF 15 KW LOGICA M-E,OT 4368 - TABLERO VDF 15 KW LOGICA M-E</t>
@@ -1944,7 +2006,7 @@
         <v>46206.67845619213</v>
       </c>
       <c r="D6" s="5">
-        <v>46207.196834166665</v>
+        <v>46209.581131099534</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -1966,7 +2028,7 @@
         <v>26</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="M6" s="6" t="s">
         <v>26</v>
@@ -1998,7 +2060,7 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" s="9">
         <v>46204.78710940972</v>
@@ -2010,7 +2072,7 @@
         <v>46207.19683414351</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F7" s="10" t="s">
         <v>26</v>
@@ -2041,7 +2103,7 @@
         <v>26</v>
       </c>
       <c r="P7" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Q7" s="9">
         <v>46206</v>
@@ -2061,7 +2123,7 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8" s="5">
         <v>46204.786935682874</v>
@@ -2071,7 +2133,7 @@
         <v>46206.66434232639</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>25</v>
@@ -2095,7 +2157,7 @@
         <v>26</v>
       </c>
       <c r="O8" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P8" s="6" t="s">
         <v>26</v>
@@ -2108,7 +2170,7 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B9" s="9">
         <v>46204.7871166088</v>
@@ -2118,16 +2180,16 @@
         <v>46206.678481574076</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I9" s="9">
         <v>46209</v>
@@ -2145,13 +2207,13 @@
         <v>26</v>
       </c>
       <c r="N9" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O9" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P9" s="10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q9" s="9">
         <v>46211</v>
@@ -2163,15 +2225,15 @@
         <v>0</v>
       </c>
       <c r="T9" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U9" s="12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B10" s="5">
         <v>46204.78712133101</v>
@@ -2181,16 +2243,16 @@
         <v>46206.67283681713</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I10" s="5">
         <v>46275</v>
@@ -2208,13 +2270,13 @@
         <v>26</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q10" s="5">
         <v>46281</v>
@@ -2226,15 +2288,15 @@
         <v>0</v>
       </c>
       <c r="T10" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U10" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B11" s="9">
         <v>46206.56956019676</v>
@@ -2244,16 +2306,16 @@
         <v>46206.672837025464</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I11" s="9">
         <v>46275</v>
@@ -2271,13 +2333,13 @@
         <v>26</v>
       </c>
       <c r="N11" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O11" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P11" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q11" s="10"/>
       <c r="R11" s="10"/>
@@ -2287,7 +2349,7 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B12" s="5">
         <v>46206.56957760417</v>
@@ -2297,16 +2359,16 @@
         <v>46206.67283768518</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I12" s="5">
         <v>46275</v>
@@ -2324,13 +2386,13 @@
         <v>26</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q12" s="6"/>
       <c r="R12" s="6"/>
@@ -2340,7 +2402,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B13" s="9">
         <v>46206.56959189815</v>
@@ -2350,16 +2412,16 @@
         <v>46206.67283835648</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I13" s="9">
         <v>46275</v>
@@ -2377,13 +2439,13 @@
         <v>26</v>
       </c>
       <c r="N13" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q13" s="10"/>
       <c r="R13" s="10"/>
@@ -2393,7 +2455,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" s="5">
         <v>46206.56960495371</v>
@@ -2403,16 +2465,16 @@
         <v>46206.67283899305</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I14" s="5">
         <v>46275</v>
@@ -2430,13 +2492,13 @@
         <v>26</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
@@ -2446,7 +2508,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B15" s="9">
         <v>46206.569617824076</v>
@@ -2456,16 +2518,16 @@
         <v>46206.67283964121</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I15" s="9">
         <v>46275</v>
@@ -2483,13 +2545,13 @@
         <v>26</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q15" s="10"/>
       <c r="R15" s="10"/>
@@ -2499,7 +2561,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B16" s="5">
         <v>46206.56963048611</v>
@@ -2509,16 +2571,16 @@
         <v>46206.67284035879</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I16" s="5">
         <v>46275</v>
@@ -2536,13 +2598,13 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q16" s="6"/>
       <c r="R16" s="6"/>
@@ -2552,7 +2614,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B17" s="9">
         <v>46206.56964277777</v>
@@ -2562,16 +2624,16 @@
         <v>46206.67284105324</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I17" s="9">
         <v>46275</v>
@@ -2589,13 +2651,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q17" s="10"/>
       <c r="R17" s="10"/>
@@ -2605,7 +2667,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B18" s="5">
         <v>46206.56965513889</v>
@@ -2615,16 +2677,16 @@
         <v>46206.67284175926</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I18" s="5">
         <v>46275</v>
@@ -2642,13 +2704,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q18" s="6"/>
       <c r="R18" s="6"/>
@@ -2658,7 +2720,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B19" s="9">
         <v>46206.569700810185</v>
@@ -2668,16 +2730,16 @@
         <v>46206.67284254629</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I19" s="9">
         <v>46275</v>
@@ -2695,13 +2757,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P19" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q19" s="10"/>
       <c r="R19" s="10"/>
@@ -2711,7 +2773,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B20" s="5">
         <v>46204.78694056713</v>
@@ -2723,7 +2785,7 @@
         <v>46206.76953472222</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>25</v>
@@ -2747,7 +2809,7 @@
         <v>26</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>26</v>
@@ -2764,7 +2826,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B21" s="9">
         <v>46204.787127372685</v>
@@ -2773,10 +2835,10 @@
         <v>46206.769487592595</v>
       </c>
       <c r="D21" s="9">
-        <v>46206.769502615745</v>
+        <v>46209.58127707176</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
@@ -2803,13 +2865,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q21" s="9">
         <v>46217</v>
@@ -2821,7 +2883,7 @@
         <v>1</v>
       </c>
       <c r="T21" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U21" s="7" t="s">
         <v>27</v>
@@ -2829,7 +2891,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B22" s="5">
         <v>46204.787143009264</v>
@@ -2841,7 +2903,7 @@
         <v>46206.76952163194</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -2868,13 +2930,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q22" s="5">
         <v>46211</v>
@@ -2886,7 +2948,7 @@
         <v>1</v>
       </c>
       <c r="T22" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U22" s="7" t="s">
         <v>27</v>
@@ -2894,7 +2956,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B23" s="9">
         <v>46204.78877271991</v>
@@ -2904,7 +2966,7 @@
         <v>46206.64882732639</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>25</v>
@@ -2928,7 +2990,7 @@
         <v>26</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P23" s="10" t="s">
         <v>26</v>
@@ -2941,7 +3003,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B24" s="5">
         <v>46204.788881678236</v>
@@ -2951,16 +3013,16 @@
         <v>46209.197446886574</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I24" s="5">
         <v>46209</v>
@@ -2978,13 +3040,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q24" s="5">
         <v>46216</v>
@@ -2996,15 +3058,15 @@
         <v>0</v>
       </c>
       <c r="T24" s="12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U24" s="12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B25" s="9">
         <v>46204.786945914355</v>
@@ -3014,7 +3076,7 @@
         <v>46206.769665162035</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>25</v>
@@ -3038,10 +3100,10 @@
         <v>26</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -3051,7 +3113,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B26" s="5">
         <v>46204.78715721065</v>
@@ -3063,7 +3125,7 @@
         <v>46206.76967918982</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
@@ -3090,13 +3152,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q26" s="5">
         <v>46212</v>
@@ -3108,7 +3170,7 @@
         <v>1</v>
       </c>
       <c r="T26" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U26" s="7" t="s">
         <v>27</v>
@@ -3116,7 +3178,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B27" s="9">
         <v>46204.78716710648</v>
@@ -3126,7 +3188,7 @@
         <v>46206.673052592596</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
@@ -3153,13 +3215,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q27" s="9">
         <v>46213</v>
@@ -3171,15 +3233,15 @@
         <v>0</v>
       </c>
       <c r="T27" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U27" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B28" s="5">
         <v>46204.787177743056</v>
@@ -3189,16 +3251,16 @@
         <v>46206.76986597222</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I28" s="5">
         <v>46241</v>
@@ -3216,13 +3278,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q28" s="5">
         <v>46244</v>
@@ -3234,15 +3296,15 @@
         <v>0</v>
       </c>
       <c r="T28" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U28" s="12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B29" s="9">
         <v>46204.79158200232</v>
@@ -3252,16 +3314,16 @@
         <v>46206.67314619213</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I29" s="9">
         <v>46241</v>
@@ -3279,13 +3341,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q29" s="9">
         <v>46244</v>
@@ -3297,15 +3359,15 @@
         <v>0</v>
       </c>
       <c r="T29" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B30" s="5">
         <v>46204.79163886574</v>
@@ -3315,16 +3377,16 @@
         <v>46206.673139039354</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I30" s="5">
         <v>46241</v>
@@ -3342,13 +3404,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q30" s="5">
         <v>46244</v>
@@ -3360,15 +3422,15 @@
         <v>0</v>
       </c>
       <c r="T30" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U30" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B31" s="9">
         <v>46204.7917447338</v>
@@ -3378,16 +3440,16 @@
         <v>46206.67313840278</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I31" s="9">
         <v>46241</v>
@@ -3405,13 +3467,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q31" s="9">
         <v>46244</v>
@@ -3423,15 +3485,15 @@
         <v>0</v>
       </c>
       <c r="T31" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B32" s="5">
         <v>46204.78695173611</v>
@@ -3441,7 +3503,7 @@
         <v>46206.65562592592</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>25</v>
@@ -3465,7 +3527,7 @@
         <v>26</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3478,7 +3540,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B33" s="9">
         <v>46204.78719643518</v>
@@ -3488,16 +3550,16 @@
         <v>46206.67332864583</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I33" s="9">
         <v>46216</v>
@@ -3515,13 +3577,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q33" s="9">
         <v>46273</v>
@@ -3533,15 +3595,15 @@
         <v>0</v>
       </c>
       <c r="T33" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B34" s="5">
         <v>46204.7872006713</v>
@@ -3551,16 +3613,16 @@
         <v>46206.67324984954</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I34" s="5">
         <v>46216</v>
@@ -3578,13 +3640,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3592,15 +3654,15 @@
         <v>0</v>
       </c>
       <c r="T34" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B35" s="9">
         <v>46204.787204837965</v>
@@ -3610,16 +3672,16 @@
         <v>46206.67327987269</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I35" s="9">
         <v>46225</v>
@@ -3637,13 +3699,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3651,15 +3713,15 @@
         <v>0</v>
       </c>
       <c r="T35" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B36" s="5">
         <v>46204.78722327546</v>
@@ -3669,16 +3731,16 @@
         <v>46206.76999994213</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I36" s="5">
         <v>46213</v>
@@ -3696,10 +3758,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3714,15 +3776,15 @@
         <v>0</v>
       </c>
       <c r="T36" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U36" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B37" s="9">
         <v>46204.78722760417</v>
@@ -3734,16 +3796,16 @@
         <v>46206.769946203705</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I37" s="9">
         <v>46213</v>
@@ -3761,13 +3823,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3777,7 +3839,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B38" s="5">
         <v>46204.787231689814</v>
@@ -3787,16 +3849,16 @@
         <v>46206.76995223379</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I38" s="5">
         <v>46224</v>
@@ -3814,13 +3876,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3830,7 +3892,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B39" s="9">
         <v>46204.78728243055</v>
@@ -3842,16 +3904,16 @@
         <v>46206.769995821756</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I39" s="9">
         <v>46224</v>
@@ -3869,13 +3931,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -3885,7 +3947,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B40" s="5">
         <v>46204.78728729166</v>
@@ -3895,16 +3957,16 @@
         <v>46206.67363866898</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I40" s="5">
         <v>46245</v>
@@ -3922,13 +3984,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q40" s="5">
         <v>46255</v>
@@ -3940,15 +4002,15 @@
         <v>0</v>
       </c>
       <c r="T40" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U40" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B41" s="9">
         <v>46204.787292175926</v>
@@ -3958,16 +4020,16 @@
         <v>46206.67358165509</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I41" s="9">
         <v>46245</v>
@@ -3985,13 +4047,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3999,15 +4061,15 @@
         <v>0</v>
       </c>
       <c r="T41" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U41" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B42" s="5">
         <v>46204.78730063657</v>
@@ -4017,16 +4079,16 @@
         <v>46206.673579016206</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I42" s="5">
         <v>46247</v>
@@ -4044,13 +4106,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4058,15 +4120,15 @@
         <v>0</v>
       </c>
       <c r="T42" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U42" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B43" s="9">
         <v>46204.793668136575</v>
@@ -4076,16 +4138,16 @@
         <v>46206.67378693287</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I43" s="9">
         <v>46245</v>
@@ -4103,10 +4165,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4121,15 +4183,15 @@
         <v>0</v>
       </c>
       <c r="T43" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U43" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B44" s="5">
         <v>46204.794818298615</v>
@@ -4139,16 +4201,16 @@
         <v>46206.673746319444</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I44" s="5">
         <v>46245</v>
@@ -4166,13 +4228,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4182,7 +4244,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B45" s="9">
         <v>46204.794902430556</v>
@@ -4192,16 +4254,16 @@
         <v>46206.673743865744</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I45" s="9">
         <v>46247</v>
@@ -4219,13 +4281,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4235,7 +4297,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B46" s="5">
         <v>46204.7938509375</v>
@@ -4245,16 +4307,16 @@
         <v>46206.67393748843</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I46" s="5">
         <v>46245</v>
@@ -4272,10 +4334,10 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4290,15 +4352,15 @@
         <v>0</v>
       </c>
       <c r="T46" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U46" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B47" s="9">
         <v>46204.795001412036</v>
@@ -4308,16 +4370,16 @@
         <v>46206.673880648144</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I47" s="9">
         <v>46245</v>
@@ -4335,13 +4397,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
@@ -4351,7 +4413,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B48" s="5">
         <v>46204.795060543984</v>
@@ -4361,16 +4423,16 @@
         <v>46206.67387746528</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I48" s="5">
         <v>46247</v>
@@ -4388,13 +4450,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4404,7 +4466,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B49" s="9">
         <v>46204.7939687037</v>
@@ -4414,16 +4476,16 @@
         <v>46206.67465699074</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I49" s="9">
         <v>46241</v>
@@ -4441,10 +4503,10 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4459,15 +4521,15 @@
         <v>0</v>
       </c>
       <c r="T49" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U49" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B50" s="5">
         <v>46204.795132997686</v>
@@ -4477,16 +4539,16 @@
         <v>46206.67409482639</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4504,13 +4566,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4520,7 +4582,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B51" s="9">
         <v>46204.795219293985</v>
@@ -4530,16 +4592,16 @@
         <v>46206.67409221065</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I51" s="9">
         <v>46246</v>
@@ -4557,13 +4619,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4573,7 +4635,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B52" s="5">
         <v>46206.65895994213</v>
@@ -4583,16 +4645,16 @@
         <v>46206.674336111115</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4608,10 +4670,10 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>26</v>
@@ -4624,7 +4686,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B53" s="9">
         <v>46204.787306770835</v>
@@ -4634,7 +4696,7 @@
         <v>46206.66711462963</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>25</v>
@@ -4658,7 +4720,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>26</v>
@@ -4671,7 +4733,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B54" s="5">
         <v>46204.78731047454</v>
@@ -4681,16 +4743,16 @@
         <v>46206.77015998843</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I54" s="5">
         <v>46212</v>
@@ -4708,13 +4770,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q54" s="5">
         <v>46218</v>
@@ -4726,34 +4788,34 @@
         <v>0</v>
       </c>
       <c r="T54" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U54" s="12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B55" s="9">
         <v>46204.78731518518</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46206.77015964121</v>
+        <v>46209.58031148148</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I55" s="9">
         <v>46233</v>
@@ -4771,13 +4833,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q55" s="9">
         <v>46239</v>
@@ -4789,15 +4851,15 @@
         <v>0</v>
       </c>
       <c r="T55" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U55" s="12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B56" s="5">
         <v>46204.78732028935</v>
@@ -4807,16 +4869,16 @@
         <v>46206.769866111106</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I56" s="5">
         <v>46240</v>
@@ -4834,13 +4896,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q56" s="5">
         <v>46240</v>
@@ -4852,15 +4914,15 @@
         <v>0</v>
       </c>
       <c r="T56" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U56" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B57" s="9">
         <v>46204.787326770835</v>
@@ -4870,16 +4932,16 @@
         <v>46206.67498217593</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I57" s="9">
         <v>46288</v>
@@ -4897,13 +4959,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q57" s="9">
         <v>46288</v>
@@ -4915,15 +4977,15 @@
         <v>0</v>
       </c>
       <c r="T57" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U57" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B58" s="5">
         <v>46205.8929956713</v>
@@ -4933,16 +4995,16 @@
         <v>46206.67494384259</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I58" s="5">
         <v>46288</v>
@@ -4960,13 +5022,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4976,7 +5038,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B59" s="9">
         <v>46205.89308850694</v>
@@ -4986,16 +5048,16 @@
         <v>46206.67494135417</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I59" s="9">
         <v>46288</v>
@@ -5013,13 +5075,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5029,7 +5091,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B60" s="5">
         <v>46205.89321678241</v>
@@ -5039,16 +5101,16 @@
         <v>46206.67493778935</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I60" s="5">
         <v>46288</v>
@@ -5066,13 +5128,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5082,7 +5144,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B61" s="9">
         <v>46204.787330555555</v>
@@ -5092,7 +5154,7 @@
         <v>46206.65997969908</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>25</v>
@@ -5116,7 +5178,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5129,7 +5191,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B62" s="5">
         <v>46204.78733380787</v>
@@ -5139,16 +5201,16 @@
         <v>46206.67512555556</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I62" s="5">
         <v>46258</v>
@@ -5166,13 +5228,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q62" s="5">
         <v>46259</v>
@@ -5184,15 +5246,15 @@
         <v>0</v>
       </c>
       <c r="T62" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U62" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B63" s="9">
         <v>46204.78733813658</v>
@@ -5202,16 +5264,16 @@
         <v>46206.67526587963</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I63" s="9">
         <v>46260</v>
@@ -5229,13 +5291,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q63" s="9">
         <v>46261</v>
@@ -5247,15 +5309,15 @@
         <v>0</v>
       </c>
       <c r="T63" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U63" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B64" s="5">
         <v>46204.79962430555</v>
@@ -5265,16 +5327,16 @@
         <v>46206.67512305555</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I64" s="5">
         <v>46258</v>
@@ -5292,13 +5354,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q64" s="5">
         <v>46259</v>
@@ -5310,15 +5372,15 @@
         <v>0</v>
       </c>
       <c r="T64" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U64" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B65" s="9">
         <v>46204.79970230324</v>
@@ -5328,16 +5390,16 @@
         <v>46206.67526299768</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I65" s="9">
         <v>46260</v>
@@ -5355,13 +5417,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q65" s="9">
         <v>46261</v>
@@ -5373,15 +5435,15 @@
         <v>0</v>
       </c>
       <c r="T65" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U65" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B66" s="5">
         <v>46204.799834722224</v>
@@ -5391,16 +5453,16 @@
         <v>46206.67512025463</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I66" s="5">
         <v>46258</v>
@@ -5418,13 +5480,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q66" s="5">
         <v>46259</v>
@@ -5436,15 +5498,15 @@
         <v>0</v>
       </c>
       <c r="T66" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U66" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B67" s="9">
         <v>46204.80007783565</v>
@@ -5454,16 +5516,16 @@
         <v>46206.67526012732</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I67" s="9">
         <v>46260</v>
@@ -5481,13 +5543,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q67" s="9">
         <v>46261</v>
@@ -5499,15 +5561,15 @@
         <v>0</v>
       </c>
       <c r="T67" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U67" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B68" s="5">
         <v>46204.787342662035</v>
@@ -5517,7 +5579,7 @@
         <v>46206.66163074074</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5541,7 +5603,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5554,7 +5616,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B69" s="9">
         <v>46204.78734565972</v>
@@ -5564,16 +5626,16 @@
         <v>46206.67535149306</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I69" s="9">
         <v>46262</v>
@@ -5591,13 +5653,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q69" s="9">
         <v>46266</v>
@@ -5609,15 +5671,15 @@
         <v>0</v>
       </c>
       <c r="T69" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U69" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B70" s="5">
         <v>46204.78735021991</v>
@@ -5627,16 +5689,16 @@
         <v>46206.67558131945</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I70" s="5">
         <v>46267</v>
@@ -5654,13 +5716,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q70" s="5">
         <v>46273</v>
@@ -5672,15 +5734,15 @@
         <v>0</v>
       </c>
       <c r="T70" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U70" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B71" s="9">
         <v>46204.83329071759</v>
@@ -5690,16 +5752,16 @@
         <v>46206.67551582176</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I71" s="9">
         <v>46267</v>
@@ -5717,13 +5779,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5733,7 +5795,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B72" s="5">
         <v>46204.83348987269</v>
@@ -5743,16 +5805,16 @@
         <v>46206.67551341435</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I72" s="5">
         <v>46267</v>
@@ -5770,13 +5832,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5786,7 +5848,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B73" s="9">
         <v>46204.83350201389</v>
@@ -5796,16 +5858,16 @@
         <v>46206.67551030093</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I73" s="9">
         <v>46267</v>
@@ -5823,13 +5885,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -5839,7 +5901,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B74" s="5">
         <v>46204.787355625</v>
@@ -5849,16 +5911,16 @@
         <v>46206.67580866898</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I74" s="5">
         <v>46274</v>
@@ -5876,13 +5938,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q74" s="5">
         <v>46274</v>
@@ -5894,15 +5956,15 @@
         <v>0</v>
       </c>
       <c r="T74" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U74" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B75" s="9">
         <v>46204.83355802084</v>
@@ -5912,16 +5974,16 @@
         <v>46206.67575559027</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I75" s="10"/>
       <c r="J75" s="9">
@@ -5937,13 +5999,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -5953,7 +6015,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B76" s="5">
         <v>46204.833570069444</v>
@@ -5963,16 +6025,16 @@
         <v>46206.67575268519</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I76" s="6"/>
       <c r="J76" s="5">
@@ -5988,13 +6050,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6004,7 +6066,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B77" s="9">
         <v>46204.833579004626</v>
@@ -6014,16 +6076,16 @@
         <v>46206.67574885416</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I77" s="10"/>
       <c r="J77" s="9">
@@ -6039,13 +6101,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6055,7 +6117,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B78" s="5">
         <v>46204.78736071759</v>
@@ -6065,7 +6127,7 @@
         <v>46206.67094998843</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>25</v>
@@ -6089,7 +6151,7 @@
         <v>26</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6102,7 +6164,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B79" s="9">
         <v>46204.78736410879</v>
@@ -6112,16 +6174,16 @@
         <v>46206.6759174537</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I79" s="9">
         <v>46210</v>
@@ -6139,13 +6201,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q79" s="9">
         <v>46210</v>
@@ -6157,15 +6219,15 @@
         <v>0</v>
       </c>
       <c r="T79" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U79" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B80" s="5">
         <v>46204.78737366898</v>
@@ -6175,16 +6237,16 @@
         <v>46206.67591493056</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I80" s="5">
         <v>46253</v>
@@ -6202,13 +6264,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q80" s="5">
         <v>46253</v>
@@ -6220,15 +6282,15 @@
         <v>0</v>
       </c>
       <c r="T80" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U80" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B81" s="9">
         <v>46204.78737825232</v>
@@ -6238,16 +6300,16 @@
         <v>46206.67600082176</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I81" s="9">
         <v>46274</v>
@@ -6265,13 +6327,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q81" s="9">
         <v>46274</v>
@@ -6283,15 +6345,15 @@
         <v>0</v>
       </c>
       <c r="T81" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U81" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B82" s="5">
         <v>46206.567318657406</v>
@@ -6301,16 +6363,16 @@
         <v>46206.67610053241</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I82" s="6"/>
       <c r="J82" s="5">
@@ -6326,13 +6388,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6342,7 +6404,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B83" s="9">
         <v>46206.56766555556</v>
@@ -6352,16 +6414,16 @@
         <v>46206.676097800926</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I83" s="10"/>
       <c r="J83" s="9">
@@ -6377,13 +6439,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6393,7 +6455,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B84" s="5">
         <v>46206.56768260417</v>
@@ -6403,16 +6465,16 @@
         <v>46206.6760950926</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I84" s="6"/>
       <c r="J84" s="5">
@@ -6428,13 +6490,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6444,7 +6506,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B85" s="9">
         <v>46206.56769806713</v>
@@ -6454,16 +6516,16 @@
         <v>46206.67609248843</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I85" s="10"/>
       <c r="J85" s="9">
@@ -6479,13 +6541,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6495,7 +6557,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B86" s="5">
         <v>46206.56771423611</v>
@@ -6505,16 +6567,16 @@
         <v>46206.67608929398</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I86" s="6"/>
       <c r="J86" s="5">
@@ -6530,13 +6592,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6546,7 +6608,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B87" s="9">
         <v>46206.56772880787</v>
@@ -6556,16 +6618,16 @@
         <v>46206.67608666667</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I87" s="10"/>
       <c r="J87" s="9">
@@ -6581,13 +6643,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6597,7 +6659,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B88" s="5">
         <v>46206.567743506945</v>
@@ -6607,16 +6669,16 @@
         <v>46206.676083935185</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I88" s="6"/>
       <c r="J88" s="5">
@@ -6632,13 +6694,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6648,7 +6710,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B89" s="9">
         <v>46206.56775844908</v>
@@ -6658,16 +6720,16 @@
         <v>46206.676078449076</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I89" s="10"/>
       <c r="J89" s="9">
@@ -6683,13 +6745,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6699,7 +6761,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B90" s="5">
         <v>46206.56777289352</v>
@@ -6709,16 +6771,16 @@
         <v>46206.67607780093</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I90" s="6"/>
       <c r="J90" s="5">
@@ -6734,13 +6796,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6750,7 +6812,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B91" s="9">
         <v>46206.67094809028</v>
@@ -6760,16 +6822,16 @@
         <v>46206.67590806713</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I91" s="9">
         <v>46274</v>
@@ -6787,10 +6849,10 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P91" s="10" t="s">
         <v>26</v>
@@ -6807,7 +6869,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B92" s="5">
         <v>46204.78738409722</v>
@@ -6817,7 +6879,7 @@
         <v>46206.66745490741</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>25</v>
@@ -6841,7 +6903,7 @@
         <v>26</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>26</v>
@@ -6854,7 +6916,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B93" s="9">
         <v>46204.787387268516</v>
@@ -6864,16 +6926,16 @@
         <v>46206.676306875</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I93" s="9">
         <v>46275</v>
@@ -6891,13 +6953,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q93" s="9">
         <v>46281</v>
@@ -6909,15 +6971,15 @@
         <v>0</v>
       </c>
       <c r="T93" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U93" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B94" s="5">
         <v>46204.84491833333</v>
@@ -6927,16 +6989,16 @@
         <v>46206.676259513886</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I94" s="5">
         <v>46275</v>
@@ -6954,13 +7016,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -6970,7 +7032,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B95" s="9">
         <v>46204.84493530093</v>
@@ -6980,16 +7042,16 @@
         <v>46206.67625695602</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I95" s="9">
         <v>46275</v>
@@ -7007,13 +7069,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7023,7 +7085,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B96" s="5">
         <v>46204.84494427084</v>
@@ -7033,16 +7095,16 @@
         <v>46206.67625305556</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I96" s="5">
         <v>46275</v>
@@ -7060,13 +7122,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7076,7 +7138,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B97" s="9">
         <v>46204.78739225694</v>
@@ -7086,16 +7148,16 @@
         <v>46206.67641435185</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I97" s="9">
         <v>46282</v>
@@ -7113,13 +7175,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q97" s="9">
         <v>46282</v>
@@ -7131,15 +7193,15 @@
         <v>0</v>
       </c>
       <c r="T97" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U97" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B98" s="5">
         <v>46204.84497997686</v>
@@ -7149,16 +7211,16 @@
         <v>46206.67651039352</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I98" s="5">
         <v>46282</v>
@@ -7176,13 +7238,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7192,7 +7254,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B99" s="9">
         <v>46204.84498876157</v>
@@ -7202,16 +7264,16 @@
         <v>46206.67650773148</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I99" s="9">
         <v>46282</v>
@@ -7229,13 +7291,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7245,7 +7307,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B100" s="5">
         <v>46204.84499563657</v>
@@ -7255,16 +7317,16 @@
         <v>46206.67650460648</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I100" s="5">
         <v>46282</v>
@@ -7282,13 +7344,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7298,7 +7360,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B101" s="9">
         <v>46204.78740502315</v>
@@ -7308,16 +7370,16 @@
         <v>46206.676410960645</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I101" s="9">
         <v>46286</v>
@@ -7335,13 +7397,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q101" s="9">
         <v>46286</v>
@@ -7353,15 +7415,15 @@
         <v>0</v>
       </c>
       <c r="T101" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U101" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B102" s="5">
         <v>46204.84507945602</v>
@@ -7371,16 +7433,16 @@
         <v>46206.67662570602</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I102" s="5">
         <v>46286</v>
@@ -7398,13 +7460,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7414,7 +7476,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B103" s="9">
         <v>46204.84508817129</v>
@@ -7424,16 +7486,16 @@
         <v>46206.676623368054</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I103" s="9">
         <v>46286</v>
@@ -7451,13 +7513,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7467,7 +7529,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B104" s="5">
         <v>46204.845093854165</v>
@@ -7477,16 +7539,16 @@
         <v>46206.676619756945</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I104" s="5">
         <v>46286</v>
@@ -7504,13 +7566,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7520,7 +7582,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B105" s="9">
         <v>46204.78741121528</v>
@@ -7530,16 +7592,16 @@
         <v>46206.67640778935</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I105" s="9">
         <v>46287</v>
@@ -7557,13 +7619,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q105" s="9">
         <v>46287</v>
@@ -7575,15 +7637,15 @@
         <v>0</v>
       </c>
       <c r="T105" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U105" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B106" s="5">
         <v>46204.84513122685</v>
@@ -7593,16 +7655,16 @@
         <v>46206.67673481481</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I106" s="5">
         <v>46287</v>
@@ -7620,13 +7682,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7636,7 +7698,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B107" s="9">
         <v>46204.84513944444</v>
@@ -7646,16 +7708,16 @@
         <v>46206.67673186342</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I107" s="9">
         <v>46287</v>
@@ -7673,13 +7735,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7689,7 +7751,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B108" s="5">
         <v>46204.8451466088</v>
@@ -7699,16 +7761,16 @@
         <v>46206.67672797454</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I108" s="5">
         <v>46287</v>
@@ -7726,13 +7788,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7742,7 +7804,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B109" s="9">
         <v>46204.787473310185</v>
@@ -7752,16 +7814,16 @@
         <v>46206.676404432874</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I109" s="9">
         <v>46289</v>
@@ -7779,13 +7841,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q109" s="9">
         <v>46289</v>
@@ -7797,15 +7859,15 @@
         <v>0</v>
       </c>
       <c r="T109" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U109" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B110" s="5">
         <v>46204.84518325231</v>
@@ -7815,16 +7877,16 @@
         <v>46206.676860590276</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I110" s="5">
         <v>46289</v>
@@ -7842,13 +7904,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -7858,7 +7920,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B111" s="9">
         <v>46204.845191898145</v>
@@ -7868,16 +7930,16 @@
         <v>46206.676858067134</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I111" s="9">
         <v>46289</v>
@@ -7895,13 +7957,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -7911,7 +7973,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B112" s="5">
         <v>46204.84520083333</v>
@@ -7921,16 +7983,16 @@
         <v>46206.676854363424</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I112" s="5">
         <v>46289</v>
@@ -7948,13 +8010,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -7964,7 +8026,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B113" s="9">
         <v>46204.78748032407</v>
@@ -7974,7 +8036,7 @@
         <v>46206.668344247686</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>25</v>
@@ -7998,7 +8060,7 @@
         <v>26</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>
@@ -8011,7 +8073,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B114" s="5">
         <v>46204.787484155095</v>
@@ -8021,16 +8083,16 @@
         <v>46206.677181631945</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I114" s="5">
         <v>46290</v>
@@ -8048,13 +8110,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q114" s="5">
         <v>46290</v>
@@ -8066,15 +8128,15 @@
         <v>0</v>
       </c>
       <c r="T114" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U114" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B115" s="9">
         <v>46206.61281571759</v>
@@ -8084,16 +8146,16 @@
         <v>46206.67717564815</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I115" s="9">
         <v>46290</v>
@@ -8111,13 +8173,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8127,7 +8189,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B116" s="5">
         <v>46206.612829722224</v>
@@ -8137,16 +8199,16 @@
         <v>46206.67717299769</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I116" s="5">
         <v>46290</v>
@@ -8164,13 +8226,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8180,7 +8242,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B117" s="9">
         <v>46206.61284180556</v>
@@ -8190,16 +8252,16 @@
         <v>46206.67717023148</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I117" s="9">
         <v>46290</v>
@@ -8217,13 +8279,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8233,7 +8295,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B118" s="5">
         <v>46206.61323981482</v>
@@ -8243,16 +8305,16 @@
         <v>46206.677167546295</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I118" s="5">
         <v>46290</v>
@@ -8270,13 +8332,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8286,7 +8348,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B119" s="9">
         <v>46206.613256446755</v>
@@ -8296,16 +8358,16 @@
         <v>46206.677164733796</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I119" s="9">
         <v>46290</v>
@@ -8323,13 +8385,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8339,7 +8401,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B120" s="5">
         <v>46206.61328513889</v>
@@ -8349,16 +8411,16 @@
         <v>46206.67716196759</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I120" s="5">
         <v>46290</v>
@@ -8376,13 +8438,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8392,7 +8454,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B121" s="9">
         <v>46206.613270925925</v>
@@ -8402,16 +8464,16 @@
         <v>46206.677158935185</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I121" s="9">
         <v>46290</v>
@@ -8429,13 +8491,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8445,7 +8507,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B122" s="5">
         <v>46206.6133403125</v>
@@ -8455,16 +8517,16 @@
         <v>46206.677155868056</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I122" s="5">
         <v>46290</v>
@@ -8482,13 +8544,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8498,7 +8560,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B123" s="9">
         <v>46206.613361041665</v>
@@ -8508,16 +8570,16 @@
         <v>46206.67715351852</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I123" s="9">
         <v>46290</v>
@@ -8535,13 +8597,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8551,7 +8613,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B124" s="5">
         <v>46206.613371493055</v>
@@ -8561,16 +8623,16 @@
         <v>46206.67715042824</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I124" s="5">
         <v>46290</v>
@@ -8588,13 +8650,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8604,7 +8666,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B125" s="9">
         <v>46206.61338284722</v>
@@ -8614,16 +8676,16 @@
         <v>46206.677144120375</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I125" s="9">
         <v>46290</v>
@@ -8641,13 +8703,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -8657,7 +8719,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B126" s="5">
         <v>46206.61339653935</v>
@@ -8667,16 +8729,16 @@
         <v>46206.67714356481</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I126" s="5">
         <v>46290</v>
@@ -8694,13 +8756,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8710,26 +8772,26 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B127" s="9">
         <v>46204.78748974537</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46206.67743496528</v>
+        <v>46209.580981481486</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I127" s="9">
         <v>46293</v>
@@ -8741,19 +8803,19 @@
         <v>26</v>
       </c>
       <c r="L127" s="10" t="s">
-        <v>26</v>
+        <v>327</v>
       </c>
       <c r="M127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q127" s="9">
         <v>46293</v>
@@ -8765,15 +8827,15 @@
         <v>0</v>
       </c>
       <c r="T127" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U127" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B128" s="5">
         <v>46204.84566665509</v>
@@ -8783,16 +8845,16 @@
         <v>46206.6774368287</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I128" s="5">
         <v>46293</v>
@@ -8810,13 +8872,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -8826,7 +8888,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B129" s="9">
         <v>46204.8456746875</v>
@@ -8836,16 +8898,16 @@
         <v>46206.67743376158</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I129" s="9">
         <v>46293</v>
@@ -8863,13 +8925,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -8879,7 +8941,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B130" s="5">
         <v>46204.84568395834</v>
@@ -8889,16 +8951,16 @@
         <v>46206.67743099537</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I130" s="5">
         <v>46293</v>
@@ -8916,13 +8978,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -8932,7 +8994,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B131" s="9">
         <v>46204.84577770834</v>
@@ -8942,16 +9004,16 @@
         <v>46206.67742784722</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I131" s="9">
         <v>46293</v>
@@ -8969,13 +9031,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -8985,7 +9047,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B132" s="5">
         <v>46204.845803958335</v>
@@ -8995,16 +9057,16 @@
         <v>46206.677424988426</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I132" s="5">
         <v>46293</v>
@@ -9022,13 +9084,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9038,7 +9100,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B133" s="9">
         <v>46204.8458116088</v>
@@ -9048,16 +9110,16 @@
         <v>46206.67742180555</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I133" s="9">
         <v>46293</v>
@@ -9075,13 +9137,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9091,7 +9153,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B134" s="5">
         <v>46204.84582686343</v>
@@ -9101,16 +9163,16 @@
         <v>46206.677418680556</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I134" s="5">
         <v>46293</v>
@@ -9128,13 +9190,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9144,7 +9206,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B135" s="9">
         <v>46204.84581974537</v>
@@ -9154,16 +9216,16 @@
         <v>46206.67741584491</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H135" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I135" s="9">
         <v>46293</v>
@@ -9181,13 +9243,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9197,7 +9259,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B136" s="5">
         <v>46204.84583605324</v>
@@ -9207,16 +9269,16 @@
         <v>46206.67741314815</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I136" s="5">
         <v>46293</v>
@@ -9234,13 +9296,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9250,7 +9312,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B137" s="9">
         <v>46204.84584422453</v>
@@ -9260,16 +9322,16 @@
         <v>46206.67740501158</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H137" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I137" s="9">
         <v>46293</v>
@@ -9287,13 +9349,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9303,7 +9365,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B138" s="5">
         <v>46204.845850983795</v>
@@ -9313,16 +9375,16 @@
         <v>46206.67740435185</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I138" s="5">
         <v>46293</v>
@@ -9340,13 +9402,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9356,7 +9418,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B139" s="9">
         <v>46204.84585899305</v>
@@ -9366,16 +9428,16 @@
         <v>46206.67740371528</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H139" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I139" s="9">
         <v>46293</v>
@@ -9393,13 +9455,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q139" s="10"/>
       <c r="R139" s="10"/>
@@ -9409,7 +9471,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B140" s="5">
         <v>46204.78749533565</v>
@@ -9419,16 +9481,16 @@
         <v>46206.67787028935</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I140" s="5">
         <v>46294</v>
@@ -9446,13 +9508,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q140" s="5">
         <v>46294</v>
@@ -9464,15 +9526,15 @@
         <v>0</v>
       </c>
       <c r="T140" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U140" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B141" s="9">
         <v>46204.84595449074</v>
@@ -9482,16 +9544,16 @@
         <v>46206.67786329861</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H141" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I141" s="9">
         <v>46294</v>
@@ -9509,13 +9571,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P141" s="10" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q141" s="10"/>
       <c r="R141" s="10"/>
@@ -9525,7 +9587,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B142" s="5">
         <v>46204.845964189815</v>
@@ -9535,16 +9597,16 @@
         <v>46206.677860254626</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I142" s="5">
         <v>46294</v>
@@ -9562,13 +9624,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9578,7 +9640,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B143" s="9">
         <v>46204.84597238426</v>
@@ -9588,16 +9650,16 @@
         <v>46206.67785763889</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H143" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I143" s="9">
         <v>46294</v>
@@ -9615,13 +9677,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q143" s="10"/>
       <c r="R143" s="10"/>
@@ -9631,7 +9693,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B144" s="5">
         <v>46204.846036469906</v>
@@ -9641,16 +9703,16 @@
         <v>46206.67785519676</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I144" s="5">
         <v>46294</v>
@@ -9668,13 +9730,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -9684,7 +9746,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B145" s="9">
         <v>46204.846047893516</v>
@@ -9694,16 +9756,16 @@
         <v>46206.6778525</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H145" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I145" s="9">
         <v>46294</v>
@@ -9721,13 +9783,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -9737,7 +9799,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B146" s="5">
         <v>46204.846056724535</v>
@@ -9747,16 +9809,16 @@
         <v>46206.67784956019</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I146" s="5">
         <v>46294</v>
@@ -9774,13 +9836,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -9790,7 +9852,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B147" s="9">
         <v>46204.846065578706</v>
@@ -9800,16 +9862,16 @@
         <v>46206.677846921295</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H147" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I147" s="9">
         <v>46294</v>
@@ -9827,13 +9889,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="10" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="O147" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q147" s="10"/>
       <c r="R147" s="10"/>
@@ -9843,7 +9905,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B148" s="5">
         <v>46204.846073252316</v>
@@ -9853,16 +9915,16 @@
         <v>46206.67784445602</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I148" s="5">
         <v>46294</v>
@@ -9880,13 +9942,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -9896,7 +9958,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B149" s="9">
         <v>46204.84608019676</v>
@@ -9906,16 +9968,16 @@
         <v>46206.6778419676</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H149" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I149" s="9">
         <v>46294</v>
@@ -9933,13 +9995,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="10" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q149" s="10"/>
       <c r="R149" s="10"/>
@@ -9949,7 +10011,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B150" s="5">
         <v>46204.84608666667</v>
@@ -9959,16 +10021,16 @@
         <v>46206.67783399306</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I150" s="5">
         <v>46294</v>
@@ -9986,13 +10048,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10002,7 +10064,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B151" s="9">
         <v>46204.84609472222</v>
@@ -10012,16 +10074,16 @@
         <v>46206.677833344904</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G151" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H151" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I151" s="9">
         <v>46294</v>
@@ -10039,13 +10101,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="10" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P151" s="10" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q151" s="10"/>
       <c r="R151" s="10"/>
@@ -10055,7 +10117,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B152" s="5">
         <v>46204.84610289352</v>
@@ -10065,16 +10127,16 @@
         <v>46206.67783269676</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I152" s="5">
         <v>46294</v>
@@ -10092,13 +10154,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10108,7 +10170,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="8" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B153" s="9">
         <v>46204.78749967593</v>
@@ -10118,16 +10180,16 @@
         <v>46206.67812460648</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G153" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H153" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I153" s="10"/>
       <c r="J153" s="9">
@@ -10143,13 +10205,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O153" s="10" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="P153" s="10" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q153" s="9">
         <v>46295</v>
@@ -10161,15 +10223,15 @@
         <v>0</v>
       </c>
       <c r="T153" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U153" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B154" s="5">
         <v>46204.846246076384</v>
@@ -10179,16 +10241,16 @@
         <v>46206.67812013889</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I154" s="5">
         <v>46295</v>
@@ -10206,13 +10268,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10222,7 +10284,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="8" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B155" s="9">
         <v>46204.84626494213</v>
@@ -10232,16 +10294,16 @@
         <v>46206.678117118056</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G155" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H155" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I155" s="9">
         <v>46295</v>
@@ -10259,13 +10321,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="10" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="P155" s="10" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q155" s="10"/>
       <c r="R155" s="10"/>
@@ -10275,7 +10337,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B156" s="5">
         <v>46204.84627579861</v>
@@ -10285,16 +10347,16 @@
         <v>46206.67810802083</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I156" s="5">
         <v>46295</v>
@@ -10312,13 +10374,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -10328,7 +10390,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B157" s="9">
         <v>46204.846348113424</v>
@@ -10338,16 +10400,16 @@
         <v>46206.67810481481</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H157" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I157" s="9">
         <v>46295</v>
@@ -10365,13 +10427,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="10" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="P157" s="10" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q157" s="10"/>
       <c r="R157" s="10"/>
@@ -10381,7 +10443,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B158" s="5">
         <v>46204.846357789356</v>
@@ -10391,16 +10453,16 @@
         <v>46206.67810172454</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H158" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I158" s="5">
         <v>46295</v>
@@ -10418,13 +10480,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -10434,7 +10496,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B159" s="9">
         <v>46204.846365879624</v>
@@ -10444,16 +10506,16 @@
         <v>46206.67809884259</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G159" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H159" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I159" s="9">
         <v>46295</v>
@@ -10471,13 +10533,13 @@
         <v>26</v>
       </c>
       <c r="N159" s="10" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O159" s="10" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="P159" s="10" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q159" s="10"/>
       <c r="R159" s="10"/>
@@ -10487,7 +10549,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B160" s="5">
         <v>46204.846373692126</v>
@@ -10497,16 +10559,16 @@
         <v>46206.678095509254</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H160" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I160" s="5">
         <v>46295</v>
@@ -10524,13 +10586,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -10540,7 +10602,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B161" s="9">
         <v>46204.8463796412</v>
@@ -10550,16 +10612,16 @@
         <v>46206.67809255787</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G161" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H161" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I161" s="9">
         <v>46295</v>
@@ -10577,13 +10639,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="10" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O161" s="10" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="P161" s="10" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q161" s="10"/>
       <c r="R161" s="10"/>
@@ -10593,7 +10655,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B162" s="5">
         <v>46204.846388715276</v>
@@ -10603,16 +10665,16 @@
         <v>46206.678089270834</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H162" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I162" s="5">
         <v>46295</v>
@@ -10630,13 +10692,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -10646,7 +10708,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B163" s="9">
         <v>46204.84640113426</v>
@@ -10656,16 +10718,16 @@
         <v>46206.67808063657</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F163" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G163" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H163" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I163" s="9">
         <v>46295</v>
@@ -10683,13 +10745,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="10" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O163" s="10" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="P163" s="10" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q163" s="10"/>
       <c r="R163" s="10"/>
@@ -10699,7 +10761,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B164" s="5">
         <v>46204.84641309028</v>
@@ -10709,16 +10771,16 @@
         <v>46206.67807998843</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G164" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H164" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I164" s="5">
         <v>46295</v>
@@ -10736,13 +10798,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -10752,7 +10814,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="8" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B165" s="9">
         <v>46204.846406701385</v>
@@ -10762,16 +10824,16 @@
         <v>46206.67807929398</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G165" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H165" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I165" s="9">
         <v>46295</v>
@@ -10789,13 +10851,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="10" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O165" s="10" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="P165" s="10" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q165" s="10"/>
       <c r="R165" s="10"/>
@@ -10805,7 +10867,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B166" s="5">
         <v>46204.7875055787</v>
@@ -10815,7 +10877,7 @@
         <v>46206.66985314815</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>25</v>
@@ -10839,7 +10901,7 @@
         <v>26</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="P166" s="6" t="s">
         <v>26</v>
@@ -10850,15 +10912,15 @@
         <v>0</v>
       </c>
       <c r="T166" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U166" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="8" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B167" s="9">
         <v>46204.787509016205</v>
@@ -10868,16 +10930,16 @@
         <v>46206.67820732639</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G167" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="H167" s="10" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="I167" s="9">
         <v>46296</v>
@@ -10895,13 +10957,13 @@
         <v>26</v>
       </c>
       <c r="N167" s="10" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="O167" s="10" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="P167" s="10" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Q167" s="9">
         <v>46304</v>
@@ -10913,15 +10975,15 @@
         <v>0</v>
       </c>
       <c r="T167" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U167" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B168" s="5">
         <v>46204.78751333333</v>
@@ -10931,7 +10993,7 @@
         <v>46206.67824334491</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
@@ -10958,13 +11020,13 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Q168" s="5">
         <v>46304</v>
@@ -10976,15 +11038,15 @@
         <v>0</v>
       </c>
       <c r="T168" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U168" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B169" s="9">
         <v>46204.787518564815</v>
@@ -10994,7 +11056,7 @@
         <v>46206.67846486111</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>25</v>
@@ -11018,7 +11080,7 @@
         <v>26</v>
       </c>
       <c r="O169" s="10" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="P169" s="10" t="s">
         <v>26</v>
@@ -11031,7 +11093,7 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B170" s="5">
         <v>46204.78752182871</v>
@@ -11041,16 +11103,16 @@
         <v>46206.67830775463</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G170" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H170" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I170" s="5">
         <v>46307</v>
@@ -11068,13 +11130,13 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="P170" s="6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="Q170" s="5">
         <v>46315</v>
@@ -11086,15 +11148,15 @@
         <v>0</v>
       </c>
       <c r="T170" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U170" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B171" s="9">
         <v>46204.78752627315</v>
@@ -11106,16 +11168,16 @@
         <v>46206.67848190972</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G171" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H171" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I171" s="9">
         <v>46316</v>
@@ -11133,13 +11195,13 @@
         <v>26</v>
       </c>
       <c r="N171" s="10" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="O171" s="10" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="P171" s="10" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="Q171" s="9">
         <v>46324</v>
@@ -11151,7 +11213,7 @@
         <v>1</v>
       </c>
       <c r="T171" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U171" s="7" t="s">
         <v>27</v>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -3010,7 +3010,7 @@
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46209.197446886574</v>
+        <v>46209.812545775465</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>79</v>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46206.769665162035</v>
+        <v>46209.79230103009</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>85</v>
@@ -3183,9 +3183,11 @@
       <c r="B27" s="9">
         <v>46204.78716710648</v>
       </c>
-      <c r="C27" s="10"/>
+      <c r="C27" s="9">
+        <v>46209.792292743055</v>
+      </c>
       <c r="D27" s="9">
-        <v>46206.673052592596</v>
+        <v>46209.792473298614</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>92</v>
@@ -3230,13 +3232,13 @@
         <v>46212</v>
       </c>
       <c r="S27" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T27" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="U27" s="11" t="s">
-        <v>54</v>
+      <c r="U27" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -3610,7 +3612,7 @@
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46206.67324984954</v>
+        <v>46209.792300393514</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>118</v>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -508,7 +508,7 @@
     <t xml:space="preserve">Corte plasma 4367 </t>
   </si>
   <si>
-    <t xml:space="preserve">Generacion Oc Corte Plasma ,Fabricación corte plasma </t>
+    <t xml:space="preserve">Generacion Oc Corte Plasma ,Fabricación corte plasma ,Generacion Oc Corte Plasma </t>
   </si>
   <si>
     <t>1216208498022071</t>
@@ -4137,7 +4137,7 @@
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46206.67378693287</v>
+        <v>46209.87015284722</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>146</v>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -289,6 +289,9 @@
     <t>Ingenieria Jefe de proyecto:,Planos Definitivos,propuesta motor</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1216219007060429</t>
   </si>
   <si>
@@ -314,9 +317,6 @@
   </si>
   <si>
     <t xml:space="preserve">Reserva produccion,Recepción mono bloque </t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1216208608300141</t>
@@ -2835,7 +2835,7 @@
         <v>46206.769487592595</v>
       </c>
       <c r="D21" s="9">
-        <v>46209.58127707176</v>
+        <v>46210.205320381945</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>72</v>
@@ -2882,8 +2882,8 @@
       <c r="S21" s="10">
         <v>1</v>
       </c>
-      <c r="T21" s="7" t="s">
-        <v>47</v>
+      <c r="T21" s="12" t="s">
+        <v>74</v>
       </c>
       <c r="U21" s="7" t="s">
         <v>27</v>
@@ -2891,7 +2891,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B22" s="5">
         <v>46204.787143009264</v>
@@ -2903,7 +2903,7 @@
         <v>46206.76952163194</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -2936,7 +2936,7 @@
         <v>37</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q22" s="5">
         <v>46211</v>
@@ -2956,7 +2956,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B23" s="9">
         <v>46204.78877271991</v>
@@ -2966,7 +2966,7 @@
         <v>46206.64882732639</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>25</v>
@@ -2990,7 +2990,7 @@
         <v>26</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P23" s="10" t="s">
         <v>26</v>
@@ -3003,7 +3003,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B24" s="5">
         <v>46204.788881678236</v>
@@ -3013,16 +3013,16 @@
         <v>46209.812545775465</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I24" s="5">
         <v>46209</v>
@@ -3040,13 +3040,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>37</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q24" s="5">
         <v>46216</v>
@@ -3058,7 +3058,7 @@
         <v>0</v>
       </c>
       <c r="T24" s="12" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="U24" s="12" t="s">
         <v>48</v>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46206.66711462963</v>
+        <v>46210.52590918982</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>175</v>
@@ -4740,9 +4740,11 @@
       <c r="B54" s="5">
         <v>46204.78731047454</v>
       </c>
-      <c r="C54" s="6"/>
+      <c r="C54" s="5">
+        <v>46210.52590148148</v>
+      </c>
       <c r="D54" s="5">
-        <v>46206.77015998843</v>
+        <v>46210.525921354165</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>178</v>
@@ -4775,7 +4777,7 @@
         <v>175</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>181</v>
@@ -4787,13 +4789,13 @@
         <v>46212</v>
       </c>
       <c r="S54" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T54" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="U54" s="12" t="s">
-        <v>48</v>
+      <c r="U54" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
@@ -4805,7 +4807,7 @@
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46209.58031148148</v>
+        <v>46210.53586592592</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>183</v>
@@ -4868,7 +4870,7 @@
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46206.769866111106</v>
+        <v>46210.52590861111</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>101</v>
@@ -6173,7 +6175,7 @@
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46206.6759174537</v>
+        <v>46210.173701493055</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>244</v>
@@ -6206,7 +6208,7 @@
         <v>201</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P79" s="10" t="s">
         <v>245</v>
@@ -6934,10 +6936,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I93" s="9">
         <v>46275</v>
@@ -6997,10 +6999,10 @@
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I94" s="5">
         <v>46275</v>
@@ -7050,10 +7052,10 @@
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I95" s="9">
         <v>46275</v>
@@ -7103,10 +7105,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I96" s="5">
         <v>46275</v>
@@ -7156,10 +7158,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I97" s="9">
         <v>46282</v>
@@ -7219,10 +7221,10 @@
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I98" s="5">
         <v>46282</v>
@@ -7272,10 +7274,10 @@
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I99" s="9">
         <v>46282</v>
@@ -7325,10 +7327,10 @@
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I100" s="5">
         <v>46282</v>
@@ -7378,10 +7380,10 @@
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I101" s="9">
         <v>46286</v>
@@ -7441,10 +7443,10 @@
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I102" s="5">
         <v>46286</v>
@@ -7494,10 +7496,10 @@
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I103" s="9">
         <v>46286</v>
@@ -7547,10 +7549,10 @@
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I104" s="5">
         <v>46286</v>
@@ -7600,10 +7602,10 @@
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I105" s="9">
         <v>46287</v>
@@ -7663,10 +7665,10 @@
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I106" s="5">
         <v>46287</v>
@@ -7716,10 +7718,10 @@
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I107" s="9">
         <v>46287</v>
@@ -7769,10 +7771,10 @@
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I108" s="5">
         <v>46287</v>
@@ -7822,10 +7824,10 @@
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I109" s="9">
         <v>46289</v>
@@ -7885,10 +7887,10 @@
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I110" s="5">
         <v>46289</v>
@@ -7938,10 +7940,10 @@
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I111" s="9">
         <v>46289</v>
@@ -7991,10 +7993,10 @@
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I112" s="5">
         <v>46289</v>
@@ -8790,10 +8792,10 @@
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I127" s="9">
         <v>46293</v>
@@ -8853,10 +8855,10 @@
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I128" s="5">
         <v>46293</v>
@@ -8906,10 +8908,10 @@
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I129" s="9">
         <v>46293</v>
@@ -8959,10 +8961,10 @@
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I130" s="5">
         <v>46293</v>
@@ -9012,10 +9014,10 @@
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I131" s="9">
         <v>46293</v>
@@ -9065,10 +9067,10 @@
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I132" s="5">
         <v>46293</v>
@@ -9118,10 +9120,10 @@
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I133" s="9">
         <v>46293</v>
@@ -9171,10 +9173,10 @@
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I134" s="5">
         <v>46293</v>
@@ -9224,10 +9226,10 @@
         <v>26</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H135" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I135" s="9">
         <v>46293</v>
@@ -9277,10 +9279,10 @@
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I136" s="5">
         <v>46293</v>
@@ -9330,10 +9332,10 @@
         <v>26</v>
       </c>
       <c r="G137" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H137" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I137" s="9">
         <v>46293</v>
@@ -9383,10 +9385,10 @@
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I138" s="5">
         <v>46293</v>
@@ -9436,10 +9438,10 @@
         <v>26</v>
       </c>
       <c r="G139" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H139" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I139" s="9">
         <v>46293</v>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -2177,7 +2177,7 @@
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="9">
-        <v>46206.678481574076</v>
+        <v>46211.17328768519</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>43</v>
@@ -4744,7 +4744,7 @@
         <v>46210.52590148148</v>
       </c>
       <c r="D54" s="5">
-        <v>46210.525921354165</v>
+        <v>46211.18996762732</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>178</v>
@@ -4791,8 +4791,8 @@
       <c r="S54" s="6">
         <v>1</v>
       </c>
-      <c r="T54" s="7" t="s">
-        <v>47</v>
+      <c r="T54" s="12" t="s">
+        <v>74</v>
       </c>
       <c r="U54" s="7" t="s">
         <v>27</v>
@@ -4807,7 +4807,7 @@
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46210.53586592592</v>
+        <v>46211.53746420139</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>183</v>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46210.173701493055</v>
+        <v>46211.203985914355</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>244</v>
@@ -6222,8 +6222,8 @@
       <c r="S79" s="10">
         <v>0</v>
       </c>
-      <c r="T79" s="7" t="s">
-        <v>47</v>
+      <c r="T79" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="U79" s="11" t="s">
         <v>54</v>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -1884,13 +1884,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46204.620263923614</v>
+        <v>46204.78693059028</v>
       </c>
       <c r="C4" s="5">
-        <v>46206.51181327546</v>
+        <v>46206.67847994213</v>
       </c>
       <c r="D4" s="5">
-        <v>46206.51182484954</v>
+        <v>46206.6784915162</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1937,13 +1937,13 @@
         <v>28</v>
       </c>
       <c r="B5" s="9">
-        <v>46204.620437233796</v>
+        <v>46204.78710390047</v>
       </c>
       <c r="C5" s="9">
-        <v>46206.51178869213</v>
+        <v>46206.67845535879</v>
       </c>
       <c r="D5" s="9">
-        <v>46207.030167476856</v>
+        <v>46207.19683414351</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>29</v>
@@ -2000,13 +2000,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46204.62044003472</v>
+        <v>46204.78710670139</v>
       </c>
       <c r="C6" s="5">
-        <v>46206.511789525466</v>
+        <v>46206.67845619213</v>
       </c>
       <c r="D6" s="5">
-        <v>46209.41446443287</v>
+        <v>46209.581131099534</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -2063,13 +2063,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="9">
-        <v>46204.62044274306</v>
+        <v>46204.78710940972</v>
       </c>
       <c r="C7" s="9">
-        <v>46206.51179020833</v>
+        <v>46206.678456875</v>
       </c>
       <c r="D7" s="9">
-        <v>46207.030167476856</v>
+        <v>46207.19683414351</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>37</v>
@@ -2126,11 +2126,11 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46204.6202690162</v>
+        <v>46204.786935682874</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="5">
-        <v>46206.49767565972</v>
+        <v>46206.66434232639</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -2173,11 +2173,11 @@
         <v>42</v>
       </c>
       <c r="B9" s="9">
-        <v>46204.62044994213</v>
+        <v>46204.7871166088</v>
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="9">
-        <v>46211.00662101852</v>
+        <v>46211.17328768519</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>43</v>
@@ -2236,11 +2236,11 @@
         <v>49</v>
       </c>
       <c r="B10" s="5">
-        <v>46204.62045466436</v>
+        <v>46204.78712133101</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46206.50617015046</v>
+        <v>46206.67283681713</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>50</v>
@@ -2299,11 +2299,11 @@
         <v>55</v>
       </c>
       <c r="B11" s="9">
-        <v>46206.40289353009</v>
+        <v>46206.56956019676</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="9">
-        <v>46206.5061703588</v>
+        <v>46206.672837025464</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>56</v>
@@ -2352,11 +2352,11 @@
         <v>58</v>
       </c>
       <c r="B12" s="5">
-        <v>46206.4029109375</v>
+        <v>46206.56957760417</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46206.50617101852</v>
+        <v>46206.67283768518</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>59</v>
@@ -2405,11 +2405,11 @@
         <v>60</v>
       </c>
       <c r="B13" s="9">
-        <v>46206.40292523148</v>
+        <v>46206.56959189815</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="9">
-        <v>46206.50617168982</v>
+        <v>46206.67283835648</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>56</v>
@@ -2458,11 +2458,11 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46206.402938287036</v>
+        <v>46206.56960495371</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46206.50617232639</v>
+        <v>46206.67283899305</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>56</v>
@@ -2511,11 +2511,11 @@
         <v>63</v>
       </c>
       <c r="B15" s="9">
-        <v>46206.402951157404</v>
+        <v>46206.569617824076</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46206.506172974536</v>
+        <v>46206.67283964121</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>56</v>
@@ -2564,11 +2564,11 @@
         <v>64</v>
       </c>
       <c r="B16" s="5">
-        <v>46206.40296381945</v>
+        <v>46206.56963048611</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46206.506173692134</v>
+        <v>46206.67284035879</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>56</v>
@@ -2617,11 +2617,11 @@
         <v>65</v>
       </c>
       <c r="B17" s="9">
-        <v>46206.402976111116</v>
+        <v>46206.56964277777</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="9">
-        <v>46206.50617438657</v>
+        <v>46206.67284105324</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>56</v>
@@ -2670,11 +2670,11 @@
         <v>66</v>
       </c>
       <c r="B18" s="5">
-        <v>46206.402988472226</v>
+        <v>46206.56965513889</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46206.506175092596</v>
+        <v>46206.67284175926</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>56</v>
@@ -2723,11 +2723,11 @@
         <v>67</v>
       </c>
       <c r="B19" s="9">
-        <v>46206.403034143514</v>
+        <v>46206.569700810185</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="9">
-        <v>46206.50617587963</v>
+        <v>46206.67284254629</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>56</v>
@@ -2776,13 +2776,13 @@
         <v>68</v>
       </c>
       <c r="B20" s="5">
-        <v>46204.620273900466</v>
+        <v>46204.78694056713</v>
       </c>
       <c r="C20" s="5">
-        <v>46206.60285498842</v>
+        <v>46206.76952165509</v>
       </c>
       <c r="D20" s="5">
-        <v>46206.60286805556</v>
+        <v>46206.76953472222</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>69</v>
@@ -2829,13 +2829,13 @@
         <v>71</v>
       </c>
       <c r="B21" s="9">
-        <v>46204.62046070602</v>
+        <v>46204.787127372685</v>
       </c>
       <c r="C21" s="9">
-        <v>46206.602820925924</v>
+        <v>46206.769487592595</v>
       </c>
       <c r="D21" s="9">
-        <v>46210.03865371528</v>
+        <v>46210.205320381945</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>72</v>
@@ -2894,13 +2894,13 @@
         <v>75</v>
       </c>
       <c r="B22" s="5">
-        <v>46204.62047634259</v>
+        <v>46204.787143009264</v>
       </c>
       <c r="C22" s="5">
-        <v>46206.60283923611</v>
+        <v>46206.769505902776</v>
       </c>
       <c r="D22" s="5">
-        <v>46206.60285496528</v>
+        <v>46206.76952163194</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>76</v>
@@ -2959,11 +2959,11 @@
         <v>78</v>
       </c>
       <c r="B23" s="9">
-        <v>46204.62210605324</v>
+        <v>46204.78877271991</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46206.482160659725</v>
+        <v>46206.64882732639</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>79</v>
@@ -3006,11 +3006,11 @@
         <v>81</v>
       </c>
       <c r="B24" s="5">
-        <v>46204.62221501158</v>
+        <v>46204.788881678236</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46209.64587910879</v>
+        <v>46209.812545775465</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>80</v>
@@ -3069,11 +3069,11 @@
         <v>84</v>
       </c>
       <c r="B25" s="9">
-        <v>46204.62027924768</v>
+        <v>46204.786945914355</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46209.62563436343</v>
+        <v>46209.79230103009</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>85</v>
@@ -3116,13 +3116,13 @@
         <v>88</v>
       </c>
       <c r="B26" s="5">
-        <v>46204.62049054398</v>
+        <v>46204.78715721065</v>
       </c>
       <c r="C26" s="5">
-        <v>46206.602994560184</v>
+        <v>46206.76966122685</v>
       </c>
       <c r="D26" s="5">
-        <v>46206.60301252315</v>
+        <v>46206.76967918982</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>89</v>
@@ -3181,13 +3181,13 @@
         <v>91</v>
       </c>
       <c r="B27" s="9">
-        <v>46204.620500439814</v>
+        <v>46204.78716710648</v>
       </c>
       <c r="C27" s="9">
-        <v>46209.62562607639</v>
+        <v>46209.792292743055</v>
       </c>
       <c r="D27" s="9">
-        <v>46209.62580663194</v>
+        <v>46209.792473298614</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>92</v>
@@ -3246,11 +3246,11 @@
         <v>94</v>
       </c>
       <c r="B28" s="5">
-        <v>46204.620511076384</v>
+        <v>46204.787177743056</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46206.60319930555</v>
+        <v>46206.76986597222</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>95</v>
@@ -3309,11 +3309,11 @@
         <v>99</v>
       </c>
       <c r="B29" s="9">
-        <v>46204.62491533565</v>
+        <v>46204.79158200232</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46206.50647952546</v>
+        <v>46206.67314619213</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>100</v>
@@ -3372,11 +3372,11 @@
         <v>103</v>
       </c>
       <c r="B30" s="5">
-        <v>46204.624972199075</v>
+        <v>46204.79163886574</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46206.50647237268</v>
+        <v>46206.673139039354</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>104</v>
@@ -3435,11 +3435,11 @@
         <v>106</v>
       </c>
       <c r="B31" s="9">
-        <v>46204.625078067125</v>
+        <v>46204.7917447338</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46206.50647173611</v>
+        <v>46206.67313840278</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>107</v>
@@ -3498,11 +3498,11 @@
         <v>109</v>
       </c>
       <c r="B32" s="5">
-        <v>46204.620285069446</v>
+        <v>46204.78695173611</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46206.48895925926</v>
+        <v>46206.65562592592</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>110</v>
@@ -3545,11 +3545,11 @@
         <v>112</v>
       </c>
       <c r="B33" s="9">
-        <v>46204.62052976852</v>
+        <v>46204.78719643518</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46206.50666197916</v>
+        <v>46206.67332864583</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>113</v>
@@ -3608,11 +3608,11 @@
         <v>117</v>
       </c>
       <c r="B34" s="5">
-        <v>46204.62053400463</v>
+        <v>46204.7872006713</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46209.62563372686</v>
+        <v>46209.792300393514</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>118</v>
@@ -3667,11 +3667,11 @@
         <v>120</v>
       </c>
       <c r="B35" s="9">
-        <v>46204.62053817129</v>
+        <v>46204.787204837965</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46206.50661320602</v>
+        <v>46206.67327987269</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>121</v>
@@ -3726,11 +3726,11 @@
         <v>123</v>
       </c>
       <c r="B36" s="5">
-        <v>46204.620556608796</v>
+        <v>46204.78722327546</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46206.60333327546</v>
+        <v>46206.76999994213</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>124</v>
@@ -3789,13 +3789,13 @@
         <v>126</v>
       </c>
       <c r="B37" s="9">
-        <v>46204.6205609375</v>
+        <v>46204.78722760417</v>
       </c>
       <c r="C37" s="9">
-        <v>46206.603278310184</v>
+        <v>46206.769944976855</v>
       </c>
       <c r="D37" s="9">
-        <v>46206.60327953704</v>
+        <v>46206.769946203705</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>127</v>
@@ -3844,11 +3844,11 @@
         <v>129</v>
       </c>
       <c r="B38" s="5">
-        <v>46204.62056502315</v>
+        <v>46204.787231689814</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46206.60328556713</v>
+        <v>46206.76995223379</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>130</v>
@@ -3897,13 +3897,13 @@
         <v>132</v>
       </c>
       <c r="B39" s="9">
-        <v>46204.62061576389</v>
+        <v>46204.78728243055</v>
       </c>
       <c r="C39" s="9">
-        <v>46206.603327731485</v>
+        <v>46206.76999439815</v>
       </c>
       <c r="D39" s="9">
-        <v>46206.60332915509</v>
+        <v>46206.769995821756</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>133</v>
@@ -3952,11 +3952,11 @@
         <v>135</v>
       </c>
       <c r="B40" s="5">
-        <v>46204.620620625</v>
+        <v>46204.78728729166</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46206.50697200232</v>
+        <v>46206.67363866898</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>136</v>
@@ -4015,11 +4015,11 @@
         <v>140</v>
       </c>
       <c r="B41" s="9">
-        <v>46204.620625509255</v>
+        <v>46204.787292175926</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46206.50691498842</v>
+        <v>46206.67358165509</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>87</v>
@@ -4074,11 +4074,11 @@
         <v>142</v>
       </c>
       <c r="B42" s="5">
-        <v>46204.620633969906</v>
+        <v>46204.78730063657</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46206.506912349534</v>
+        <v>46206.673579016206</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>143</v>
@@ -4133,11 +4133,11 @@
         <v>145</v>
       </c>
       <c r="B43" s="9">
-        <v>46204.62700146991</v>
+        <v>46204.793668136575</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46209.70348618056</v>
+        <v>46209.87015284722</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>146</v>
@@ -4196,11 +4196,11 @@
         <v>148</v>
       </c>
       <c r="B44" s="5">
-        <v>46204.62815163194</v>
+        <v>46204.794818298615</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46206.50707965277</v>
+        <v>46206.673746319444</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>102</v>
@@ -4249,11 +4249,11 @@
         <v>150</v>
       </c>
       <c r="B45" s="9">
-        <v>46204.628235763885</v>
+        <v>46204.794902430556</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46206.50707719907</v>
+        <v>46206.673743865744</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>149</v>
@@ -4302,11 +4302,11 @@
         <v>152</v>
       </c>
       <c r="B46" s="5">
-        <v>46204.62718427084</v>
+        <v>46204.7938509375</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46206.50727082176</v>
+        <v>46206.67393748843</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>153</v>
@@ -4365,11 +4365,11 @@
         <v>155</v>
       </c>
       <c r="B47" s="9">
-        <v>46204.62833474537</v>
+        <v>46204.795001412036</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46206.50721398148</v>
+        <v>46206.673880648144</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>105</v>
@@ -4418,11 +4418,11 @@
         <v>157</v>
       </c>
       <c r="B48" s="5">
-        <v>46204.62839387731</v>
+        <v>46204.795060543984</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46206.50721079861</v>
+        <v>46206.67387746528</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>158</v>
@@ -4471,11 +4471,11 @@
         <v>160</v>
       </c>
       <c r="B49" s="9">
-        <v>46204.627302037035</v>
+        <v>46204.7939687037</v>
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46206.50799032407</v>
+        <v>46206.67465699074</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>161</v>
@@ -4534,11 +4534,11 @@
         <v>165</v>
       </c>
       <c r="B50" s="5">
-        <v>46204.62846633102</v>
+        <v>46204.795132997686</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46206.50742815972</v>
+        <v>46206.67409482639</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>108</v>
@@ -4587,11 +4587,11 @@
         <v>167</v>
       </c>
       <c r="B51" s="9">
-        <v>46204.62855262731</v>
+        <v>46204.795219293985</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46206.50742554398</v>
+        <v>46206.67409221065</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>168</v>
@@ -4640,11 +4640,11 @@
         <v>170</v>
       </c>
       <c r="B52" s="5">
-        <v>46206.49229327546</v>
+        <v>46206.65895994213</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46206.50766944444</v>
+        <v>46206.674336111115</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>171</v>
@@ -4691,11 +4691,11 @@
         <v>174</v>
       </c>
       <c r="B53" s="9">
-        <v>46204.62064010417</v>
+        <v>46204.787306770835</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46210.35924252315</v>
+        <v>46210.52590918982</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>175</v>
@@ -4738,13 +4738,13 @@
         <v>177</v>
       </c>
       <c r="B54" s="5">
-        <v>46204.620643807866</v>
+        <v>46204.78731047454</v>
       </c>
       <c r="C54" s="5">
-        <v>46210.359234814816</v>
+        <v>46210.52590148148</v>
       </c>
       <c r="D54" s="5">
-        <v>46211.023300960645</v>
+        <v>46211.18996762732</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>178</v>
@@ -4803,11 +4803,11 @@
         <v>182</v>
       </c>
       <c r="B55" s="9">
-        <v>46204.62064851852</v>
+        <v>46204.78731518518</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46211.37079753472</v>
+        <v>46211.53746420139</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>183</v>
@@ -4866,11 +4866,11 @@
         <v>186</v>
       </c>
       <c r="B56" s="5">
-        <v>46204.62065362268</v>
+        <v>46204.78732028935</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46210.35924194445</v>
+        <v>46210.52590861111</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>101</v>
@@ -4929,11 +4929,11 @@
         <v>189</v>
       </c>
       <c r="B57" s="9">
-        <v>46204.62066010416</v>
+        <v>46204.787326770835</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="9">
-        <v>46206.50831550926</v>
+        <v>46206.67498217593</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>190</v>
@@ -4992,11 +4992,11 @@
         <v>194</v>
       </c>
       <c r="B58" s="5">
-        <v>46205.726329004625</v>
+        <v>46205.8929956713</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46206.508277175926</v>
+        <v>46206.67494384259</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>195</v>
@@ -5045,11 +5045,11 @@
         <v>197</v>
       </c>
       <c r="B59" s="9">
-        <v>46205.72642184028</v>
+        <v>46205.89308850694</v>
       </c>
       <c r="C59" s="10"/>
       <c r="D59" s="9">
-        <v>46206.5082746875</v>
+        <v>46206.67494135417</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>195</v>
@@ -5098,11 +5098,11 @@
         <v>199</v>
       </c>
       <c r="B60" s="5">
-        <v>46205.72655011574</v>
+        <v>46205.89321678241</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46206.508271122686</v>
+        <v>46206.67493778935</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>195</v>
@@ -5151,11 +5151,11 @@
         <v>200</v>
       </c>
       <c r="B61" s="9">
-        <v>46204.62066388889</v>
+        <v>46204.787330555555</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46206.493313032406</v>
+        <v>46206.65997969908</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>201</v>
@@ -5198,11 +5198,11 @@
         <v>203</v>
       </c>
       <c r="B62" s="5">
-        <v>46204.62066714121</v>
+        <v>46204.78733380787</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46206.508458888886</v>
+        <v>46206.67512555556</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>204</v>
@@ -5261,11 +5261,11 @@
         <v>208</v>
       </c>
       <c r="B63" s="9">
-        <v>46204.62067146991</v>
+        <v>46204.78733813658</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46206.50859921296</v>
+        <v>46206.67526587963</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>209</v>
@@ -5324,11 +5324,11 @@
         <v>211</v>
       </c>
       <c r="B64" s="5">
-        <v>46204.63295763889</v>
+        <v>46204.79962430555</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46206.50845638889</v>
+        <v>46206.67512305555</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>212</v>
@@ -5387,11 +5387,11 @@
         <v>214</v>
       </c>
       <c r="B65" s="9">
-        <v>46204.63303563657</v>
+        <v>46204.79970230324</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46206.50859633102</v>
+        <v>46206.67526299768</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>213</v>
@@ -5450,11 +5450,11 @@
         <v>216</v>
       </c>
       <c r="B66" s="5">
-        <v>46204.63316805556</v>
+        <v>46204.799834722224</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46206.50845358796</v>
+        <v>46206.67512025463</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>217</v>
@@ -5513,11 +5513,11 @@
         <v>219</v>
       </c>
       <c r="B67" s="9">
-        <v>46204.63341116898</v>
+        <v>46204.80007783565</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46206.50859346065</v>
+        <v>46206.67526012732</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>218</v>
@@ -5576,11 +5576,11 @@
         <v>220</v>
       </c>
       <c r="B68" s="5">
-        <v>46204.62067599537</v>
+        <v>46204.787342662035</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46206.494964074074</v>
+        <v>46206.66163074074</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>221</v>
@@ -5623,11 +5623,11 @@
         <v>223</v>
       </c>
       <c r="B69" s="9">
-        <v>46204.62067899306</v>
+        <v>46204.78734565972</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46206.50868482639</v>
+        <v>46206.67535149306</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>215</v>
@@ -5686,11 +5686,11 @@
         <v>228</v>
       </c>
       <c r="B70" s="5">
-        <v>46204.620683553236</v>
+        <v>46204.78735021991</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46206.508914652775</v>
+        <v>46206.67558131945</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>229</v>
@@ -5749,11 +5749,11 @@
         <v>230</v>
       </c>
       <c r="B71" s="9">
-        <v>46204.66662405092</v>
+        <v>46204.83329071759</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46206.50884915509</v>
+        <v>46206.67551582176</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>195</v>
@@ -5802,11 +5802,11 @@
         <v>233</v>
       </c>
       <c r="B72" s="5">
-        <v>46204.66682320602</v>
+        <v>46204.83348987269</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46206.50884674769</v>
+        <v>46206.67551341435</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>195</v>
@@ -5855,11 +5855,11 @@
         <v>234</v>
       </c>
       <c r="B73" s="9">
-        <v>46204.66683534722</v>
+        <v>46204.83350201389</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46206.50884363426</v>
+        <v>46206.67551030093</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>195</v>
@@ -5908,11 +5908,11 @@
         <v>235</v>
       </c>
       <c r="B74" s="5">
-        <v>46204.62068895833</v>
+        <v>46204.787355625</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46206.50914200232</v>
+        <v>46206.67580866898</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>236</v>
@@ -5971,11 +5971,11 @@
         <v>237</v>
       </c>
       <c r="B75" s="9">
-        <v>46204.666891354165</v>
+        <v>46204.83355802084</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46206.509088923616</v>
+        <v>46206.67575559027</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>195</v>
@@ -6022,11 +6022,11 @@
         <v>239</v>
       </c>
       <c r="B76" s="5">
-        <v>46204.66690340277</v>
+        <v>46204.833570069444</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46206.509086018516</v>
+        <v>46206.67575268519</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>195</v>
@@ -6073,11 +6073,11 @@
         <v>240</v>
       </c>
       <c r="B77" s="9">
-        <v>46204.66691233796</v>
+        <v>46204.833579004626</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46206.5090821875</v>
+        <v>46206.67574885416</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>195</v>
@@ -6124,11 +6124,11 @@
         <v>241</v>
       </c>
       <c r="B78" s="5">
-        <v>46204.62069405093</v>
+        <v>46204.78736071759</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46206.50428332176</v>
+        <v>46206.67094998843</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>201</v>
@@ -6171,11 +6171,11 @@
         <v>243</v>
       </c>
       <c r="B79" s="9">
-        <v>46204.62069744213</v>
+        <v>46204.78736410879</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46211.03731924768</v>
+        <v>46211.203985914355</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>244</v>
@@ -6234,11 +6234,11 @@
         <v>246</v>
       </c>
       <c r="B80" s="5">
-        <v>46204.620707002316</v>
+        <v>46204.78737366898</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46206.50924826389</v>
+        <v>46206.67591493056</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>247</v>
@@ -6297,11 +6297,11 @@
         <v>248</v>
       </c>
       <c r="B81" s="9">
-        <v>46204.62071158565</v>
+        <v>46204.78737825232</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46206.5093341551</v>
+        <v>46206.67600082176</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>249</v>
@@ -6360,11 +6360,11 @@
         <v>251</v>
       </c>
       <c r="B82" s="5">
-        <v>46206.40065199074</v>
+        <v>46206.567318657406</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46206.509433865736</v>
+        <v>46206.67610053241</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>56</v>
@@ -6411,11 +6411,11 @@
         <v>253</v>
       </c>
       <c r="B83" s="9">
-        <v>46206.40099888889</v>
+        <v>46206.56766555556</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46206.509431134255</v>
+        <v>46206.676097800926</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>56</v>
@@ -6462,11 +6462,11 @@
         <v>255</v>
       </c>
       <c r="B84" s="5">
-        <v>46206.4010159375</v>
+        <v>46206.56768260417</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46206.509428425925</v>
+        <v>46206.6760950926</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>61</v>
@@ -6513,11 +6513,11 @@
         <v>256</v>
       </c>
       <c r="B85" s="9">
-        <v>46206.40103140046</v>
+        <v>46206.56769806713</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46206.50942582176</v>
+        <v>46206.67609248843</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>56</v>
@@ -6564,11 +6564,11 @@
         <v>257</v>
       </c>
       <c r="B86" s="5">
-        <v>46206.401047569445</v>
+        <v>46206.56771423611</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46206.509422627314</v>
+        <v>46206.67608929398</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>56</v>
@@ -6615,11 +6615,11 @@
         <v>258</v>
       </c>
       <c r="B87" s="9">
-        <v>46206.4010621412</v>
+        <v>46206.56772880787</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46206.50942</v>
+        <v>46206.67608666667</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>56</v>
@@ -6666,11 +6666,11 @@
         <v>259</v>
       </c>
       <c r="B88" s="5">
-        <v>46206.40107684028</v>
+        <v>46206.567743506945</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46206.50941726852</v>
+        <v>46206.676083935185</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>56</v>
@@ -6717,11 +6717,11 @@
         <v>260</v>
       </c>
       <c r="B89" s="9">
-        <v>46206.401091782405</v>
+        <v>46206.56775844908</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46206.509411782405</v>
+        <v>46206.676078449076</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>56</v>
@@ -6768,11 +6768,11 @@
         <v>261</v>
       </c>
       <c r="B90" s="5">
-        <v>46206.401106226855</v>
+        <v>46206.56777289352</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46206.50941113426</v>
+        <v>46206.67607780093</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>56</v>
@@ -6819,11 +6819,11 @@
         <v>262</v>
       </c>
       <c r="B91" s="9">
-        <v>46206.50428142361</v>
+        <v>46206.67094809028</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46206.50924140046</v>
+        <v>46206.67590806713</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>263</v>
@@ -6876,11 +6876,11 @@
         <v>264</v>
       </c>
       <c r="B92" s="5">
-        <v>46204.62071743056</v>
+        <v>46204.78738409722</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46206.50078824074</v>
+        <v>46206.66745490741</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>265</v>
@@ -6923,11 +6923,11 @@
         <v>267</v>
       </c>
       <c r="B93" s="9">
-        <v>46204.62072060185</v>
+        <v>46204.787387268516</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46206.50964020833</v>
+        <v>46206.676306875</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>268</v>
@@ -6986,11 +6986,11 @@
         <v>269</v>
       </c>
       <c r="B94" s="5">
-        <v>46204.67825166667</v>
+        <v>46204.84491833333</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46206.50959284722</v>
+        <v>46206.676259513886</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>195</v>
@@ -7039,11 +7039,11 @@
         <v>271</v>
       </c>
       <c r="B95" s="9">
-        <v>46204.67826863426</v>
+        <v>46204.84493530093</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46206.50959028935</v>
+        <v>46206.67625695602</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>195</v>
@@ -7092,11 +7092,11 @@
         <v>272</v>
       </c>
       <c r="B96" s="5">
-        <v>46204.678277604165</v>
+        <v>46204.84494427084</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46206.509586388886</v>
+        <v>46206.67625305556</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>195</v>
@@ -7145,11 +7145,11 @@
         <v>274</v>
       </c>
       <c r="B97" s="9">
-        <v>46204.62072559028</v>
+        <v>46204.78739225694</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46206.50974768518</v>
+        <v>46206.67641435185</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>275</v>
@@ -7208,11 +7208,11 @@
         <v>276</v>
       </c>
       <c r="B98" s="5">
-        <v>46204.678313310185</v>
+        <v>46204.84497997686</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46206.50984372685</v>
+        <v>46206.67651039352</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>195</v>
@@ -7261,11 +7261,11 @@
         <v>279</v>
       </c>
       <c r="B99" s="9">
-        <v>46204.67832209491</v>
+        <v>46204.84498876157</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46206.50984106481</v>
+        <v>46206.67650773148</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>195</v>
@@ -7314,11 +7314,11 @@
         <v>280</v>
       </c>
       <c r="B100" s="5">
-        <v>46204.67832896991</v>
+        <v>46204.84499563657</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46206.50983793981</v>
+        <v>46206.67650460648</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>195</v>
@@ -7367,11 +7367,11 @@
         <v>281</v>
       </c>
       <c r="B101" s="9">
-        <v>46204.620738356476</v>
+        <v>46204.78740502315</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46206.50974429398</v>
+        <v>46206.676410960645</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>282</v>
@@ -7430,11 +7430,11 @@
         <v>283</v>
       </c>
       <c r="B102" s="5">
-        <v>46204.67841278935</v>
+        <v>46204.84507945602</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46206.50995903935</v>
+        <v>46206.67662570602</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>195</v>
@@ -7483,11 +7483,11 @@
         <v>286</v>
       </c>
       <c r="B103" s="9">
-        <v>46204.67842150463</v>
+        <v>46204.84508817129</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46206.50995670139</v>
+        <v>46206.676623368054</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>195</v>
@@ -7536,11 +7536,11 @@
         <v>287</v>
       </c>
       <c r="B104" s="5">
-        <v>46204.6784271875</v>
+        <v>46204.845093854165</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46206.50995309028</v>
+        <v>46206.676619756945</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>195</v>
@@ -7589,11 +7589,11 @@
         <v>288</v>
       </c>
       <c r="B105" s="9">
-        <v>46204.62074454861</v>
+        <v>46204.78741121528</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46206.50974112269</v>
+        <v>46206.67640778935</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>289</v>
@@ -7652,11 +7652,11 @@
         <v>290</v>
       </c>
       <c r="B106" s="5">
-        <v>46204.67846456019</v>
+        <v>46204.84513122685</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46206.51006814815</v>
+        <v>46206.67673481481</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>195</v>
@@ -7705,11 +7705,11 @@
         <v>293</v>
       </c>
       <c r="B107" s="9">
-        <v>46204.67847277778</v>
+        <v>46204.84513944444</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46206.51006519676</v>
+        <v>46206.67673186342</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>195</v>
@@ -7758,11 +7758,11 @@
         <v>294</v>
       </c>
       <c r="B108" s="5">
-        <v>46204.67847994213</v>
+        <v>46204.8451466088</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46206.51006130787</v>
+        <v>46206.67672797454</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>195</v>
@@ -7811,11 +7811,11 @@
         <v>295</v>
       </c>
       <c r="B109" s="9">
-        <v>46204.62080664352</v>
+        <v>46204.787473310185</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46206.5097377662</v>
+        <v>46206.676404432874</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>296</v>
@@ -7874,11 +7874,11 @@
         <v>298</v>
       </c>
       <c r="B110" s="5">
-        <v>46204.67851658565</v>
+        <v>46204.84518325231</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46206.51019392361</v>
+        <v>46206.676860590276</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>195</v>
@@ -7927,11 +7927,11 @@
         <v>300</v>
       </c>
       <c r="B111" s="9">
-        <v>46204.67852523148</v>
+        <v>46204.845191898145</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46206.51019140046</v>
+        <v>46206.676858067134</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>301</v>
@@ -7980,11 +7980,11 @@
         <v>302</v>
       </c>
       <c r="B112" s="5">
-        <v>46204.67853416667</v>
+        <v>46204.84520083333</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46206.51018769676</v>
+        <v>46206.676854363424</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>195</v>
@@ -8033,11 +8033,11 @@
         <v>303</v>
       </c>
       <c r="B113" s="9">
-        <v>46204.620813657406</v>
+        <v>46204.78748032407</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46206.50167758102</v>
+        <v>46206.668344247686</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>304</v>
@@ -8080,11 +8080,11 @@
         <v>306</v>
       </c>
       <c r="B114" s="5">
-        <v>46204.62081748842</v>
+        <v>46204.787484155095</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46206.51051496528</v>
+        <v>46206.677181631945</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>307</v>
@@ -8143,11 +8143,11 @@
         <v>311</v>
       </c>
       <c r="B115" s="9">
-        <v>46206.44614905093</v>
+        <v>46206.61281571759</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46206.51050898148</v>
+        <v>46206.67717564815</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>195</v>
@@ -8196,11 +8196,11 @@
         <v>313</v>
       </c>
       <c r="B116" s="5">
-        <v>46206.44616305556</v>
+        <v>46206.612829722224</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46206.51050633102</v>
+        <v>46206.67717299769</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>195</v>
@@ -8249,11 +8249,11 @@
         <v>314</v>
       </c>
       <c r="B117" s="9">
-        <v>46206.44617513889</v>
+        <v>46206.61284180556</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46206.510503564816</v>
+        <v>46206.67717023148</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>195</v>
@@ -8302,11 +8302,11 @@
         <v>315</v>
       </c>
       <c r="B118" s="5">
-        <v>46206.44657314815</v>
+        <v>46206.61323981482</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46206.51050087963</v>
+        <v>46206.677167546295</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>56</v>
@@ -8355,11 +8355,11 @@
         <v>317</v>
       </c>
       <c r="B119" s="9">
-        <v>46206.44658978009</v>
+        <v>46206.613256446755</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46206.51049806713</v>
+        <v>46206.677164733796</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>56</v>
@@ -8408,11 +8408,11 @@
         <v>318</v>
       </c>
       <c r="B120" s="5">
-        <v>46206.446618472226</v>
+        <v>46206.61328513889</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46206.51049530093</v>
+        <v>46206.67716196759</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>56</v>
@@ -8461,11 +8461,11 @@
         <v>319</v>
       </c>
       <c r="B121" s="9">
-        <v>46206.446604259254</v>
+        <v>46206.613270925925</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46206.51049226851</v>
+        <v>46206.677158935185</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>56</v>
@@ -8514,11 +8514,11 @@
         <v>320</v>
       </c>
       <c r="B122" s="5">
-        <v>46206.446673645834</v>
+        <v>46206.6133403125</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46206.51048920139</v>
+        <v>46206.677155868056</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>56</v>
@@ -8567,11 +8567,11 @@
         <v>321</v>
       </c>
       <c r="B123" s="9">
-        <v>46206.446694375</v>
+        <v>46206.613361041665</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46206.510486851854</v>
+        <v>46206.67715351852</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>56</v>
@@ -8620,11 +8620,11 @@
         <v>322</v>
       </c>
       <c r="B124" s="5">
-        <v>46206.44670482639</v>
+        <v>46206.613371493055</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46206.51048376157</v>
+        <v>46206.67715042824</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>56</v>
@@ -8673,11 +8673,11 @@
         <v>323</v>
       </c>
       <c r="B125" s="9">
-        <v>46206.44671618055</v>
+        <v>46206.61338284722</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46206.5104774537</v>
+        <v>46206.677144120375</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>56</v>
@@ -8726,11 +8726,11 @@
         <v>324</v>
       </c>
       <c r="B126" s="5">
-        <v>46206.44672987268</v>
+        <v>46206.61339653935</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46206.51047689815</v>
+        <v>46206.67714356481</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>56</v>
@@ -8779,11 +8779,11 @@
         <v>325</v>
       </c>
       <c r="B127" s="9">
-        <v>46204.6208230787</v>
+        <v>46204.78748974537</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46209.414314814814</v>
+        <v>46209.580981481486</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>326</v>
@@ -8842,11 +8842,11 @@
         <v>329</v>
       </c>
       <c r="B128" s="5">
-        <v>46204.67899998843</v>
+        <v>46204.84566665509</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46206.510770162036</v>
+        <v>46206.6774368287</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>195</v>
@@ -8895,11 +8895,11 @@
         <v>331</v>
       </c>
       <c r="B129" s="9">
-        <v>46204.67900802083</v>
+        <v>46204.8456746875</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46206.51076709491</v>
+        <v>46206.67743376158</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>195</v>
@@ -8948,11 +8948,11 @@
         <v>332</v>
       </c>
       <c r="B130" s="5">
-        <v>46204.679017291666</v>
+        <v>46204.84568395834</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46206.510764328705</v>
+        <v>46206.67743099537</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>195</v>
@@ -9001,11 +9001,11 @@
         <v>333</v>
       </c>
       <c r="B131" s="9">
-        <v>46204.67911104167</v>
+        <v>46204.84577770834</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46206.51076118056</v>
+        <v>46206.67742784722</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>334</v>
@@ -9054,11 +9054,11 @@
         <v>336</v>
       </c>
       <c r="B132" s="5">
-        <v>46204.67913729166</v>
+        <v>46204.845803958335</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46206.51075832176</v>
+        <v>46206.677424988426</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>334</v>
@@ -9107,11 +9107,11 @@
         <v>337</v>
       </c>
       <c r="B133" s="9">
-        <v>46204.67914494213</v>
+        <v>46204.8458116088</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46206.510755138894</v>
+        <v>46206.67742180555</v>
       </c>
       <c r="E133" s="10" t="s">
         <v>334</v>
@@ -9160,11 +9160,11 @@
         <v>338</v>
       </c>
       <c r="B134" s="5">
-        <v>46204.679160196756</v>
+        <v>46204.84582686343</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46206.510752013884</v>
+        <v>46206.677418680556</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>334</v>
@@ -9213,11 +9213,11 @@
         <v>339</v>
       </c>
       <c r="B135" s="9">
-        <v>46204.6791530787</v>
+        <v>46204.84581974537</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46206.51074917824</v>
+        <v>46206.67741584491</v>
       </c>
       <c r="E135" s="10" t="s">
         <v>334</v>
@@ -9266,11 +9266,11 @@
         <v>340</v>
       </c>
       <c r="B136" s="5">
-        <v>46204.679169386574</v>
+        <v>46204.84583605324</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46206.51074648148</v>
+        <v>46206.67741314815</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>334</v>
@@ -9319,11 +9319,11 @@
         <v>341</v>
       </c>
       <c r="B137" s="9">
-        <v>46204.679177557875</v>
+        <v>46204.84584422453</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46206.51073834491</v>
+        <v>46206.67740501158</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>334</v>
@@ -9372,11 +9372,11 @@
         <v>342</v>
       </c>
       <c r="B138" s="5">
-        <v>46204.67918431713</v>
+        <v>46204.845850983795</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46206.51073768518</v>
+        <v>46206.67740435185</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>334</v>
@@ -9425,11 +9425,11 @@
         <v>343</v>
       </c>
       <c r="B139" s="9">
-        <v>46204.67919232639</v>
+        <v>46204.84585899305</v>
       </c>
       <c r="C139" s="10"/>
       <c r="D139" s="9">
-        <v>46206.51073704861</v>
+        <v>46206.67740371528</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>334</v>
@@ -9478,11 +9478,11 @@
         <v>344</v>
       </c>
       <c r="B140" s="5">
-        <v>46204.62082866898</v>
+        <v>46204.78749533565</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46206.511203622686</v>
+        <v>46206.67787028935</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>345</v>
@@ -9541,11 +9541,11 @@
         <v>348</v>
       </c>
       <c r="B141" s="9">
-        <v>46204.679287824074</v>
+        <v>46204.84595449074</v>
       </c>
       <c r="C141" s="10"/>
       <c r="D141" s="9">
-        <v>46206.511196631945</v>
+        <v>46206.67786329861</v>
       </c>
       <c r="E141" s="10" t="s">
         <v>349</v>
@@ -9594,11 +9594,11 @@
         <v>351</v>
       </c>
       <c r="B142" s="5">
-        <v>46204.67929752315</v>
+        <v>46204.845964189815</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46206.51119358796</v>
+        <v>46206.677860254626</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>349</v>
@@ -9647,11 +9647,11 @@
         <v>352</v>
       </c>
       <c r="B143" s="9">
-        <v>46204.6793057176</v>
+        <v>46204.84597238426</v>
       </c>
       <c r="C143" s="10"/>
       <c r="D143" s="9">
-        <v>46206.51119097222</v>
+        <v>46206.67785763889</v>
       </c>
       <c r="E143" s="10" t="s">
         <v>349</v>
@@ -9700,11 +9700,11 @@
         <v>353</v>
       </c>
       <c r="B144" s="5">
-        <v>46204.67936980324</v>
+        <v>46204.846036469906</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46206.511188530094</v>
+        <v>46206.67785519676</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>354</v>
@@ -9753,11 +9753,11 @@
         <v>356</v>
       </c>
       <c r="B145" s="9">
-        <v>46204.67938122685</v>
+        <v>46204.846047893516</v>
       </c>
       <c r="C145" s="10"/>
       <c r="D145" s="9">
-        <v>46206.51118583333</v>
+        <v>46206.6778525</v>
       </c>
       <c r="E145" s="10" t="s">
         <v>354</v>
@@ -9806,11 +9806,11 @@
         <v>357</v>
       </c>
       <c r="B146" s="5">
-        <v>46204.67939005787</v>
+        <v>46204.846056724535</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46206.51118289352</v>
+        <v>46206.67784956019</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>354</v>
@@ -9859,11 +9859,11 @@
         <v>358</v>
       </c>
       <c r="B147" s="9">
-        <v>46204.679398912034</v>
+        <v>46204.846065578706</v>
       </c>
       <c r="C147" s="10"/>
       <c r="D147" s="9">
-        <v>46206.51118025463</v>
+        <v>46206.677846921295</v>
       </c>
       <c r="E147" s="10" t="s">
         <v>354</v>
@@ -9912,11 +9912,11 @@
         <v>359</v>
       </c>
       <c r="B148" s="5">
-        <v>46204.67940658565</v>
+        <v>46204.846073252316</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46206.51117778935</v>
+        <v>46206.67784445602</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>354</v>
@@ -9965,11 +9965,11 @@
         <v>360</v>
       </c>
       <c r="B149" s="9">
-        <v>46204.67941353009</v>
+        <v>46204.84608019676</v>
       </c>
       <c r="C149" s="10"/>
       <c r="D149" s="9">
-        <v>46206.511175300926</v>
+        <v>46206.6778419676</v>
       </c>
       <c r="E149" s="10" t="s">
         <v>354</v>
@@ -10018,11 +10018,11 @@
         <v>361</v>
       </c>
       <c r="B150" s="5">
-        <v>46204.67942</v>
+        <v>46204.84608666667</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46206.51116732639</v>
+        <v>46206.67783399306</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>354</v>
@@ -10071,11 +10071,11 @@
         <v>362</v>
       </c>
       <c r="B151" s="9">
-        <v>46204.679428055555</v>
+        <v>46204.84609472222</v>
       </c>
       <c r="C151" s="10"/>
       <c r="D151" s="9">
-        <v>46206.51116667824</v>
+        <v>46206.677833344904</v>
       </c>
       <c r="E151" s="10" t="s">
         <v>354</v>
@@ -10124,11 +10124,11 @@
         <v>363</v>
       </c>
       <c r="B152" s="5">
-        <v>46204.679436226856</v>
+        <v>46204.84610289352</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46206.51116603009</v>
+        <v>46206.67783269676</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>354</v>
@@ -10177,11 +10177,11 @@
         <v>364</v>
       </c>
       <c r="B153" s="9">
-        <v>46204.62083300926</v>
+        <v>46204.78749967593</v>
       </c>
       <c r="C153" s="10"/>
       <c r="D153" s="9">
-        <v>46206.511457939814</v>
+        <v>46206.67812460648</v>
       </c>
       <c r="E153" s="10" t="s">
         <v>365</v>
@@ -10238,11 +10238,11 @@
         <v>368</v>
       </c>
       <c r="B154" s="5">
-        <v>46204.67957940973</v>
+        <v>46204.846246076384</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46206.51145347222</v>
+        <v>46206.67812013889</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>349</v>
@@ -10291,11 +10291,11 @@
         <v>369</v>
       </c>
       <c r="B155" s="9">
-        <v>46204.67959827546</v>
+        <v>46204.84626494213</v>
       </c>
       <c r="C155" s="10"/>
       <c r="D155" s="9">
-        <v>46206.51145045139</v>
+        <v>46206.678117118056</v>
       </c>
       <c r="E155" s="10" t="s">
         <v>349</v>
@@ -10344,11 +10344,11 @@
         <v>370</v>
       </c>
       <c r="B156" s="5">
-        <v>46204.67960913194</v>
+        <v>46204.84627579861</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46206.51144135417</v>
+        <v>46206.67810802083</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>349</v>
@@ -10397,11 +10397,11 @@
         <v>371</v>
       </c>
       <c r="B157" s="9">
-        <v>46204.67968144676</v>
+        <v>46204.846348113424</v>
       </c>
       <c r="C157" s="10"/>
       <c r="D157" s="9">
-        <v>46206.51143814815</v>
+        <v>46206.67810481481</v>
       </c>
       <c r="E157" s="10" t="s">
         <v>354</v>
@@ -10450,11 +10450,11 @@
         <v>372</v>
       </c>
       <c r="B158" s="5">
-        <v>46204.679691122685</v>
+        <v>46204.846357789356</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46206.511435057866</v>
+        <v>46206.67810172454</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>354</v>
@@ -10503,11 +10503,11 @@
         <v>373</v>
       </c>
       <c r="B159" s="9">
-        <v>46204.67969921297</v>
+        <v>46204.846365879624</v>
       </c>
       <c r="C159" s="10"/>
       <c r="D159" s="9">
-        <v>46206.511432175925</v>
+        <v>46206.67809884259</v>
       </c>
       <c r="E159" s="10" t="s">
         <v>354</v>
@@ -10556,11 +10556,11 @@
         <v>374</v>
       </c>
       <c r="B160" s="5">
-        <v>46204.67970702546</v>
+        <v>46204.846373692126</v>
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46206.5114288426</v>
+        <v>46206.678095509254</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>354</v>
@@ -10609,11 +10609,11 @@
         <v>375</v>
       </c>
       <c r="B161" s="9">
-        <v>46204.67971297454</v>
+        <v>46204.8463796412</v>
       </c>
       <c r="C161" s="10"/>
       <c r="D161" s="9">
-        <v>46206.51142589121</v>
+        <v>46206.67809255787</v>
       </c>
       <c r="E161" s="10" t="s">
         <v>354</v>
@@ -10662,11 +10662,11 @@
         <v>376</v>
       </c>
       <c r="B162" s="5">
-        <v>46204.67972204861</v>
+        <v>46204.846388715276</v>
       </c>
       <c r="C162" s="6"/>
       <c r="D162" s="5">
-        <v>46206.51142260416</v>
+        <v>46206.678089270834</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>354</v>
@@ -10715,11 +10715,11 @@
         <v>377</v>
       </c>
       <c r="B163" s="9">
-        <v>46204.679734467594</v>
+        <v>46204.84640113426</v>
       </c>
       <c r="C163" s="10"/>
       <c r="D163" s="9">
-        <v>46206.51141396991</v>
+        <v>46206.67808063657</v>
       </c>
       <c r="E163" s="10" t="s">
         <v>354</v>
@@ -10768,11 +10768,11 @@
         <v>378</v>
       </c>
       <c r="B164" s="5">
-        <v>46204.679746423615</v>
+        <v>46204.84641309028</v>
       </c>
       <c r="C164" s="6"/>
       <c r="D164" s="5">
-        <v>46206.51141332176</v>
+        <v>46206.67807998843</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>354</v>
@@ -10821,11 +10821,11 @@
         <v>379</v>
       </c>
       <c r="B165" s="9">
-        <v>46204.67974003472</v>
+        <v>46204.846406701385</v>
       </c>
       <c r="C165" s="10"/>
       <c r="D165" s="9">
-        <v>46206.51141262731</v>
+        <v>46206.67807929398</v>
       </c>
       <c r="E165" s="10" t="s">
         <v>354</v>
@@ -10874,11 +10874,11 @@
         <v>380</v>
       </c>
       <c r="B166" s="5">
-        <v>46204.62083891204</v>
+        <v>46204.7875055787</v>
       </c>
       <c r="C166" s="6"/>
       <c r="D166" s="5">
-        <v>46206.50318648148</v>
+        <v>46206.66985314815</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>381</v>
@@ -10927,11 +10927,11 @@
         <v>383</v>
       </c>
       <c r="B167" s="9">
-        <v>46204.62084234954</v>
+        <v>46204.787509016205</v>
       </c>
       <c r="C167" s="10"/>
       <c r="D167" s="9">
-        <v>46206.51154065972</v>
+        <v>46206.67820732639</v>
       </c>
       <c r="E167" s="10" t="s">
         <v>384</v>
@@ -10990,11 +10990,11 @@
         <v>387</v>
       </c>
       <c r="B168" s="5">
-        <v>46204.620846666665</v>
+        <v>46204.78751333333</v>
       </c>
       <c r="C168" s="6"/>
       <c r="D168" s="5">
-        <v>46206.51157667824</v>
+        <v>46206.67824334491</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>388</v>
@@ -11053,11 +11053,11 @@
         <v>389</v>
       </c>
       <c r="B169" s="9">
-        <v>46204.620851898144</v>
+        <v>46204.787518564815</v>
       </c>
       <c r="C169" s="10"/>
       <c r="D169" s="9">
-        <v>46206.51179819445</v>
+        <v>46206.67846486111</v>
       </c>
       <c r="E169" s="10" t="s">
         <v>390</v>
@@ -11100,11 +11100,11 @@
         <v>392</v>
       </c>
       <c r="B170" s="5">
-        <v>46204.62085516204</v>
+        <v>46204.78752182871</v>
       </c>
       <c r="C170" s="6"/>
       <c r="D170" s="5">
-        <v>46206.511641087964</v>
+        <v>46206.67830775463</v>
       </c>
       <c r="E170" s="6" t="s">
         <v>393</v>
@@ -11163,13 +11163,13 @@
         <v>395</v>
       </c>
       <c r="B171" s="9">
-        <v>46204.62085960648</v>
+        <v>46204.78752627315</v>
       </c>
       <c r="C171" s="9">
-        <v>46206.511790868055</v>
+        <v>46206.67845753473</v>
       </c>
       <c r="D171" s="9">
-        <v>46206.51181524305</v>
+        <v>46206.67848190972</v>
       </c>
       <c r="E171" s="10" t="s">
         <v>396</v>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -208,25 +208,25 @@
     <t>Ingenieria Servicios:,propuesta tableros</t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
+    <t>1216218963027994</t>
+  </si>
+  <si>
+    <t>Revision tableros pruebas</t>
+  </si>
+  <si>
+    <t>sergio saavedra fernandez</t>
+  </si>
+  <si>
+    <t>sergio.saavedra@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT' 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E</t>
+  </si>
+  <si>
     <t>Baja</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1216218963027994</t>
-  </si>
-  <si>
-    <t>Revision tableros pruebas</t>
-  </si>
-  <si>
-    <t>sergio saavedra fernandez</t>
-  </si>
-  <si>
-    <t>sergio.saavedra@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT' 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E</t>
   </si>
   <si>
     <t>Tarea sin iniciar</t>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="9">
-        <v>46211.17328768519</v>
+        <v>46212.19074954861</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>43</v>
@@ -2224,16 +2224,16 @@
       <c r="S9" s="10">
         <v>0</v>
       </c>
-      <c r="T9" s="7" t="s">
+      <c r="T9" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="U9" s="12" t="s">
         <v>47</v>
-      </c>
-      <c r="U9" s="12" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B10" s="5">
         <v>46204.78712133101</v>
@@ -2243,16 +2243,16 @@
         <v>46206.67283681713</v>
       </c>
       <c r="E10" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="F10" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="6" t="s">
+      <c r="H10" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>52</v>
       </c>
       <c r="I10" s="5">
         <v>46275</v>
@@ -2273,7 +2273,7 @@
         <v>40</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="P10" s="6" t="s">
         <v>40</v>
@@ -2288,7 +2288,7 @@
         <v>0</v>
       </c>
       <c r="T10" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U10" s="11" t="s">
         <v>54</v>
@@ -2312,10 +2312,10 @@
         <v>26</v>
       </c>
       <c r="G11" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H11" s="10" t="s">
         <v>51</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>52</v>
       </c>
       <c r="I11" s="9">
         <v>46275</v>
@@ -2333,7 +2333,7 @@
         <v>26</v>
       </c>
       <c r="N11" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O11" s="10" t="s">
         <v>56</v>
@@ -2365,10 +2365,10 @@
         <v>26</v>
       </c>
       <c r="G12" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H12" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>52</v>
       </c>
       <c r="I12" s="5">
         <v>46275</v>
@@ -2386,7 +2386,7 @@
         <v>26</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>56</v>
@@ -2418,10 +2418,10 @@
         <v>26</v>
       </c>
       <c r="G13" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13" s="10" t="s">
         <v>51</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>52</v>
       </c>
       <c r="I13" s="9">
         <v>46275</v>
@@ -2439,7 +2439,7 @@
         <v>26</v>
       </c>
       <c r="N13" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O13" s="10" t="s">
         <v>61</v>
@@ -2471,10 +2471,10 @@
         <v>26</v>
       </c>
       <c r="G14" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H14" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>52</v>
       </c>
       <c r="I14" s="5">
         <v>46275</v>
@@ -2492,7 +2492,7 @@
         <v>26</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>56</v>
@@ -2524,10 +2524,10 @@
         <v>26</v>
       </c>
       <c r="G15" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H15" s="10" t="s">
         <v>51</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>52</v>
       </c>
       <c r="I15" s="9">
         <v>46275</v>
@@ -2545,7 +2545,7 @@
         <v>26</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O15" s="10" t="s">
         <v>56</v>
@@ -2577,10 +2577,10 @@
         <v>26</v>
       </c>
       <c r="G16" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>52</v>
       </c>
       <c r="I16" s="5">
         <v>46275</v>
@@ -2598,7 +2598,7 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>56</v>
@@ -2630,10 +2630,10 @@
         <v>26</v>
       </c>
       <c r="G17" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H17" s="10" t="s">
         <v>51</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>52</v>
       </c>
       <c r="I17" s="9">
         <v>46275</v>
@@ -2651,7 +2651,7 @@
         <v>26</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O17" s="10" t="s">
         <v>56</v>
@@ -2683,10 +2683,10 @@
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H18" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>52</v>
       </c>
       <c r="I18" s="5">
         <v>46275</v>
@@ -2704,7 +2704,7 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>56</v>
@@ -2736,10 +2736,10 @@
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H19" s="10" t="s">
         <v>51</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>52</v>
       </c>
       <c r="I19" s="9">
         <v>46275</v>
@@ -2757,7 +2757,7 @@
         <v>26</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O19" s="10" t="s">
         <v>56</v>
@@ -2900,7 +2900,7 @@
         <v>46206.769505902776</v>
       </c>
       <c r="D22" s="5">
-        <v>46206.76952163194</v>
+        <v>46212.19074947917</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>76</v>
@@ -2947,8 +2947,8 @@
       <c r="S22" s="6">
         <v>1</v>
       </c>
-      <c r="T22" s="7" t="s">
-        <v>47</v>
+      <c r="T22" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="U22" s="7" t="s">
         <v>27</v>
@@ -3061,7 +3061,7 @@
         <v>74</v>
       </c>
       <c r="U24" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -3170,7 +3170,7 @@
         <v>1</v>
       </c>
       <c r="T26" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U26" s="7" t="s">
         <v>27</v>
@@ -3235,7 +3235,7 @@
         <v>1</v>
       </c>
       <c r="T27" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U27" s="7" t="s">
         <v>27</v>
@@ -3298,10 +3298,10 @@
         <v>0</v>
       </c>
       <c r="T28" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="U28" s="12" t="s">
         <v>47</v>
-      </c>
-      <c r="U28" s="12" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -3361,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="T29" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U29" s="11" t="s">
         <v>54</v>
@@ -3424,7 +3424,7 @@
         <v>0</v>
       </c>
       <c r="T30" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U30" s="11" t="s">
         <v>54</v>
@@ -3487,7 +3487,7 @@
         <v>0</v>
       </c>
       <c r="T31" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U31" s="11" t="s">
         <v>54</v>
@@ -3597,7 +3597,7 @@
         <v>0</v>
       </c>
       <c r="T33" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U33" s="11" t="s">
         <v>54</v>
@@ -3656,7 +3656,7 @@
         <v>0</v>
       </c>
       <c r="T34" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U34" s="11" t="s">
         <v>54</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="T35" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U35" s="11" t="s">
         <v>54</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="T36" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U36" s="11" t="s">
         <v>54</v>
@@ -4004,7 +4004,7 @@
         <v>0</v>
       </c>
       <c r="T40" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U40" s="11" t="s">
         <v>54</v>
@@ -4063,7 +4063,7 @@
         <v>0</v>
       </c>
       <c r="T41" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U41" s="11" t="s">
         <v>54</v>
@@ -4122,7 +4122,7 @@
         <v>0</v>
       </c>
       <c r="T42" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U42" s="11" t="s">
         <v>54</v>
@@ -4185,7 +4185,7 @@
         <v>0</v>
       </c>
       <c r="T43" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U43" s="11" t="s">
         <v>54</v>
@@ -4354,7 +4354,7 @@
         <v>0</v>
       </c>
       <c r="T46" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U46" s="11" t="s">
         <v>54</v>
@@ -4523,7 +4523,7 @@
         <v>0</v>
       </c>
       <c r="T49" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U49" s="11" t="s">
         <v>54</v>
@@ -4855,10 +4855,10 @@
         <v>0</v>
       </c>
       <c r="T55" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="U55" s="12" t="s">
         <v>47</v>
-      </c>
-      <c r="U55" s="12" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
@@ -4918,7 +4918,7 @@
         <v>0</v>
       </c>
       <c r="T56" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U56" s="11" t="s">
         <v>54</v>
@@ -4981,7 +4981,7 @@
         <v>0</v>
       </c>
       <c r="T57" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U57" s="11" t="s">
         <v>54</v>
@@ -5250,7 +5250,7 @@
         <v>0</v>
       </c>
       <c r="T62" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U62" s="11" t="s">
         <v>54</v>
@@ -5313,7 +5313,7 @@
         <v>0</v>
       </c>
       <c r="T63" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U63" s="11" t="s">
         <v>54</v>
@@ -5376,7 +5376,7 @@
         <v>0</v>
       </c>
       <c r="T64" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U64" s="11" t="s">
         <v>54</v>
@@ -5439,7 +5439,7 @@
         <v>0</v>
       </c>
       <c r="T65" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U65" s="11" t="s">
         <v>54</v>
@@ -5502,7 +5502,7 @@
         <v>0</v>
       </c>
       <c r="T66" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U66" s="11" t="s">
         <v>54</v>
@@ -5565,7 +5565,7 @@
         <v>0</v>
       </c>
       <c r="T67" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U67" s="11" t="s">
         <v>54</v>
@@ -5675,7 +5675,7 @@
         <v>0</v>
       </c>
       <c r="T69" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U69" s="11" t="s">
         <v>54</v>
@@ -5738,7 +5738,7 @@
         <v>0</v>
       </c>
       <c r="T70" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U70" s="11" t="s">
         <v>54</v>
@@ -5960,7 +5960,7 @@
         <v>0</v>
       </c>
       <c r="T74" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U74" s="11" t="s">
         <v>54</v>
@@ -6286,7 +6286,7 @@
         <v>0</v>
       </c>
       <c r="T80" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U80" s="11" t="s">
         <v>54</v>
@@ -6349,7 +6349,7 @@
         <v>0</v>
       </c>
       <c r="T81" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U81" s="11" t="s">
         <v>54</v>
@@ -6975,7 +6975,7 @@
         <v>0</v>
       </c>
       <c r="T93" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U93" s="11" t="s">
         <v>54</v>
@@ -7197,7 +7197,7 @@
         <v>0</v>
       </c>
       <c r="T97" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U97" s="11" t="s">
         <v>54</v>
@@ -7419,7 +7419,7 @@
         <v>0</v>
       </c>
       <c r="T101" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U101" s="11" t="s">
         <v>54</v>
@@ -7641,7 +7641,7 @@
         <v>0</v>
       </c>
       <c r="T105" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U105" s="11" t="s">
         <v>54</v>
@@ -7863,7 +7863,7 @@
         <v>0</v>
       </c>
       <c r="T109" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U109" s="11" t="s">
         <v>54</v>
@@ -8132,7 +8132,7 @@
         <v>0</v>
       </c>
       <c r="T114" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U114" s="11" t="s">
         <v>54</v>
@@ -8831,7 +8831,7 @@
         <v>0</v>
       </c>
       <c r="T127" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U127" s="11" t="s">
         <v>54</v>
@@ -9530,7 +9530,7 @@
         <v>0</v>
       </c>
       <c r="T140" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U140" s="11" t="s">
         <v>54</v>
@@ -10227,7 +10227,7 @@
         <v>0</v>
       </c>
       <c r="T153" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U153" s="11" t="s">
         <v>54</v>
@@ -10916,7 +10916,7 @@
         <v>0</v>
       </c>
       <c r="T166" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U166" s="11" t="s">
         <v>54</v>
@@ -10979,7 +10979,7 @@
         <v>0</v>
       </c>
       <c r="T167" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U167" s="11" t="s">
         <v>54</v>
@@ -11042,7 +11042,7 @@
         <v>0</v>
       </c>
       <c r="T168" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U168" s="11" t="s">
         <v>54</v>
@@ -11152,7 +11152,7 @@
         <v>0</v>
       </c>
       <c r="T170" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U170" s="11" t="s">
         <v>54</v>
@@ -11217,7 +11217,7 @@
         <v>1</v>
       </c>
       <c r="T171" s="7" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="U171" s="7" t="s">
         <v>27</v>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -208,115 +208,115 @@
     <t>Ingenieria Servicios:,propuesta tableros</t>
   </si>
   <si>
+    <t>1216218963027994</t>
+  </si>
+  <si>
+    <t>Revision tableros pruebas</t>
+  </si>
+  <si>
+    <t>sergio saavedra fernandez</t>
+  </si>
+  <si>
+    <t>sergio.saavedra@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT' 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E</t>
+  </si>
+  <si>
+    <t>Baja</t>
+  </si>
+  <si>
+    <t>Tarea sin iniciar</t>
+  </si>
+  <si>
+    <t>1216265318483681</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OT 4368 - TABLERO VDF 15 KW LOGICA M-E</t>
+  </si>
+  <si>
+    <t>Revision tableros pruebas, OT 4368 - TABLERO VDF 15 KW LOGICA M-E</t>
+  </si>
+  <si>
+    <t>1216265318483682</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OT' 4368 - TABLERO VDF 15 KW LOGICA M-E</t>
+  </si>
+  <si>
+    <t>1216265318483683</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OT 34368 - TABLERO VDF 15 KW LOGICA M-E</t>
+  </si>
+  <si>
+    <t>1216265318483684</t>
+  </si>
+  <si>
+    <t>1216265318483685</t>
+  </si>
+  <si>
+    <t>1216265318483686</t>
+  </si>
+  <si>
+    <t>1216265318483687</t>
+  </si>
+  <si>
+    <t>1216265318483688</t>
+  </si>
+  <si>
+    <t>1216265318483689</t>
+  </si>
+  <si>
+    <t>1216208608300139</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:</t>
+  </si>
+  <si>
+    <t>Ingenieria Basica Motor,Ingenieria Detalle</t>
+  </si>
+  <si>
+    <t>1216218870853526</t>
+  </si>
+  <si>
+    <t>Ingenieria Basica Motor</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:,Planos Definitivos,propuesta motor</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>1216219007060429</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:,propuesta corte laser,Planos Preliminar</t>
+  </si>
+  <si>
+    <t>1216208498022053</t>
+  </si>
+  <si>
+    <t>Reserva produccion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserva mono bloque </t>
+  </si>
+  <si>
+    <t>1216208498022055</t>
+  </si>
+  <si>
+    <t>benjamin.bustos@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserva produccion,Recepción mono bloque </t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1216218963027994</t>
-  </si>
-  <si>
-    <t>Revision tableros pruebas</t>
-  </si>
-  <si>
-    <t>sergio saavedra fernandez</t>
-  </si>
-  <si>
-    <t>sergio.saavedra@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT' 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E</t>
-  </si>
-  <si>
-    <t>Baja</t>
-  </si>
-  <si>
-    <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1216265318483681</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OT 4368 - TABLERO VDF 15 KW LOGICA M-E</t>
-  </si>
-  <si>
-    <t>Revision tableros pruebas, OT 4368 - TABLERO VDF 15 KW LOGICA M-E</t>
-  </si>
-  <si>
-    <t>1216265318483682</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OT' 4368 - TABLERO VDF 15 KW LOGICA M-E</t>
-  </si>
-  <si>
-    <t>1216265318483683</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OT 34368 - TABLERO VDF 15 KW LOGICA M-E</t>
-  </si>
-  <si>
-    <t>1216265318483684</t>
-  </si>
-  <si>
-    <t>1216265318483685</t>
-  </si>
-  <si>
-    <t>1216265318483686</t>
-  </si>
-  <si>
-    <t>1216265318483687</t>
-  </si>
-  <si>
-    <t>1216265318483688</t>
-  </si>
-  <si>
-    <t>1216265318483689</t>
-  </si>
-  <si>
-    <t>1216208608300139</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:</t>
-  </si>
-  <si>
-    <t>Ingenieria Basica Motor,Ingenieria Detalle</t>
-  </si>
-  <si>
-    <t>1216218870853526</t>
-  </si>
-  <si>
-    <t>Ingenieria Basica Motor</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,Planos Definitivos,propuesta motor</t>
-  </si>
-  <si>
-    <t>Media</t>
-  </si>
-  <si>
-    <t>1216219007060429</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,propuesta corte laser,Planos Preliminar</t>
-  </si>
-  <si>
-    <t>1216208498022053</t>
-  </si>
-  <si>
-    <t>Reserva produccion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserva mono bloque </t>
-  </si>
-  <si>
-    <t>1216208498022055</t>
-  </si>
-  <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserva produccion,Recepción mono bloque </t>
   </si>
   <si>
     <t>1216208608300141</t>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="5">
-        <v>46206.66434232639</v>
+        <v>46212.646741226854</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -2175,9 +2175,11 @@
       <c r="B9" s="9">
         <v>46204.7871166088</v>
       </c>
-      <c r="C9" s="10"/>
+      <c r="C9" s="9">
+        <v>46212.64673310185</v>
+      </c>
       <c r="D9" s="9">
-        <v>46212.19074954861</v>
+        <v>46212.64675215278</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>43</v>
@@ -2222,18 +2224,18 @@
         <v>46209</v>
       </c>
       <c r="S9" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T9" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="U9" s="12" t="s">
-        <v>47</v>
+      <c r="U9" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B10" s="5">
         <v>46204.78712133101</v>
@@ -2243,16 +2245,16 @@
         <v>46206.67283681713</v>
       </c>
       <c r="E10" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="6" t="s">
+      <c r="H10" s="6" t="s">
         <v>50</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>51</v>
       </c>
       <c r="I10" s="5">
         <v>46275</v>
@@ -2273,7 +2275,7 @@
         <v>40</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P10" s="6" t="s">
         <v>40</v>
@@ -2288,15 +2290,15 @@
         <v>0</v>
       </c>
       <c r="T10" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U10" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="U10" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B11" s="9">
         <v>46206.56956019676</v>
@@ -2306,16 +2308,16 @@
         <v>46206.672837025464</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G11" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="H11" s="10" t="s">
         <v>50</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>51</v>
       </c>
       <c r="I11" s="9">
         <v>46275</v>
@@ -2333,13 +2335,13 @@
         <v>26</v>
       </c>
       <c r="N11" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O11" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="P11" s="10" t="s">
         <v>56</v>
-      </c>
-      <c r="P11" s="10" t="s">
-        <v>57</v>
       </c>
       <c r="Q11" s="10"/>
       <c r="R11" s="10"/>
@@ -2349,7 +2351,7 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B12" s="5">
         <v>46206.56957760417</v>
@@ -2359,16 +2361,16 @@
         <v>46206.67283768518</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G12" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H12" s="6" t="s">
         <v>50</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>51</v>
       </c>
       <c r="I12" s="5">
         <v>46275</v>
@@ -2386,13 +2388,13 @@
         <v>26</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O12" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="P12" s="6" t="s">
         <v>56</v>
-      </c>
-      <c r="P12" s="6" t="s">
-        <v>57</v>
       </c>
       <c r="Q12" s="6"/>
       <c r="R12" s="6"/>
@@ -2402,7 +2404,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B13" s="9">
         <v>46206.56959189815</v>
@@ -2412,16 +2414,16 @@
         <v>46206.67283835648</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G13" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="H13" s="10" t="s">
         <v>50</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>51</v>
       </c>
       <c r="I13" s="9">
         <v>46275</v>
@@ -2439,13 +2441,13 @@
         <v>26</v>
       </c>
       <c r="N13" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Q13" s="10"/>
       <c r="R13" s="10"/>
@@ -2455,7 +2457,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B14" s="5">
         <v>46206.56960495371</v>
@@ -2465,16 +2467,16 @@
         <v>46206.67283899305</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G14" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H14" s="6" t="s">
         <v>50</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>51</v>
       </c>
       <c r="I14" s="5">
         <v>46275</v>
@@ -2492,13 +2494,13 @@
         <v>26</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O14" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="P14" s="6" t="s">
         <v>56</v>
-      </c>
-      <c r="P14" s="6" t="s">
-        <v>57</v>
       </c>
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
@@ -2508,7 +2510,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B15" s="9">
         <v>46206.569617824076</v>
@@ -2518,16 +2520,16 @@
         <v>46206.67283964121</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G15" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="H15" s="10" t="s">
         <v>50</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>51</v>
       </c>
       <c r="I15" s="9">
         <v>46275</v>
@@ -2545,13 +2547,13 @@
         <v>26</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O15" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="P15" s="10" t="s">
         <v>56</v>
-      </c>
-      <c r="P15" s="10" t="s">
-        <v>57</v>
       </c>
       <c r="Q15" s="10"/>
       <c r="R15" s="10"/>
@@ -2561,7 +2563,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B16" s="5">
         <v>46206.56963048611</v>
@@ -2571,16 +2573,16 @@
         <v>46206.67284035879</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G16" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>50</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>51</v>
       </c>
       <c r="I16" s="5">
         <v>46275</v>
@@ -2598,13 +2600,13 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O16" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="P16" s="6" t="s">
         <v>56</v>
-      </c>
-      <c r="P16" s="6" t="s">
-        <v>57</v>
       </c>
       <c r="Q16" s="6"/>
       <c r="R16" s="6"/>
@@ -2614,7 +2616,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B17" s="9">
         <v>46206.56964277777</v>
@@ -2624,16 +2626,16 @@
         <v>46206.67284105324</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="H17" s="10" t="s">
         <v>50</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>51</v>
       </c>
       <c r="I17" s="9">
         <v>46275</v>
@@ -2651,13 +2653,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O17" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="P17" s="10" t="s">
         <v>56</v>
-      </c>
-      <c r="P17" s="10" t="s">
-        <v>57</v>
       </c>
       <c r="Q17" s="10"/>
       <c r="R17" s="10"/>
@@ -2667,7 +2669,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B18" s="5">
         <v>46206.56965513889</v>
@@ -2677,16 +2679,16 @@
         <v>46206.67284175926</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H18" s="6" t="s">
         <v>50</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>51</v>
       </c>
       <c r="I18" s="5">
         <v>46275</v>
@@ -2704,13 +2706,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O18" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="P18" s="6" t="s">
         <v>56</v>
-      </c>
-      <c r="P18" s="6" t="s">
-        <v>57</v>
       </c>
       <c r="Q18" s="6"/>
       <c r="R18" s="6"/>
@@ -2720,7 +2722,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B19" s="9">
         <v>46206.569700810185</v>
@@ -2730,16 +2732,16 @@
         <v>46206.67284254629</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G19" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="H19" s="10" t="s">
         <v>50</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>51</v>
       </c>
       <c r="I19" s="9">
         <v>46275</v>
@@ -2757,13 +2759,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O19" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="P19" s="10" t="s">
         <v>56</v>
-      </c>
-      <c r="P19" s="10" t="s">
-        <v>57</v>
       </c>
       <c r="Q19" s="10"/>
       <c r="R19" s="10"/>
@@ -2773,7 +2775,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B20" s="5">
         <v>46204.78694056713</v>
@@ -2785,7 +2787,7 @@
         <v>46206.76953472222</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>25</v>
@@ -2809,7 +2811,7 @@
         <v>26</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>26</v>
@@ -2826,7 +2828,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B21" s="9">
         <v>46204.787127372685</v>
@@ -2838,7 +2840,7 @@
         <v>46210.205320381945</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
@@ -2865,13 +2867,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O21" s="10" t="s">
         <v>37</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q21" s="9">
         <v>46217</v>
@@ -2883,7 +2885,7 @@
         <v>1</v>
       </c>
       <c r="T21" s="12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="U21" s="7" t="s">
         <v>27</v>
@@ -2891,7 +2893,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B22" s="5">
         <v>46204.787143009264</v>
@@ -2903,7 +2905,7 @@
         <v>46212.19074947917</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -2930,13 +2932,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>37</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q22" s="5">
         <v>46211</v>
@@ -2956,7 +2958,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B23" s="9">
         <v>46204.78877271991</v>
@@ -2966,7 +2968,7 @@
         <v>46206.64882732639</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>25</v>
@@ -2990,7 +2992,7 @@
         <v>26</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P23" s="10" t="s">
         <v>26</v>
@@ -3003,7 +3005,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B24" s="5">
         <v>46204.788881678236</v>
@@ -3013,16 +3015,16 @@
         <v>46209.812545775465</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I24" s="5">
         <v>46209</v>
@@ -3040,13 +3042,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>37</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q24" s="5">
         <v>46216</v>
@@ -3058,10 +3060,10 @@
         <v>0</v>
       </c>
       <c r="T24" s="12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="U24" s="12" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -3155,7 +3157,7 @@
         <v>85</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>90</v>
@@ -3170,7 +3172,7 @@
         <v>1</v>
       </c>
       <c r="T26" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U26" s="7" t="s">
         <v>27</v>
@@ -3187,7 +3189,7 @@
         <v>46209.792292743055</v>
       </c>
       <c r="D27" s="9">
-        <v>46209.792473298614</v>
+        <v>46212.64675210648</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>92</v>
@@ -3235,10 +3237,10 @@
         <v>1</v>
       </c>
       <c r="T27" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="U27" s="7" t="s">
-        <v>27</v>
+        <v>52</v>
+      </c>
+      <c r="U27" s="12" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -3298,10 +3300,10 @@
         <v>0</v>
       </c>
       <c r="T28" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U28" s="12" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -3361,10 +3363,10 @@
         <v>0</v>
       </c>
       <c r="T29" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U29" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="U29" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -3424,10 +3426,10 @@
         <v>0</v>
       </c>
       <c r="T30" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U30" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="U30" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -3487,10 +3489,10 @@
         <v>0</v>
       </c>
       <c r="T31" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U31" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="U31" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
@@ -3597,10 +3599,10 @@
         <v>0</v>
       </c>
       <c r="T33" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U33" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="U33" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -3656,10 +3658,10 @@
         <v>0</v>
       </c>
       <c r="T34" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U34" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="U34" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
@@ -3715,10 +3717,10 @@
         <v>0</v>
       </c>
       <c r="T35" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U35" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="U35" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
@@ -3778,10 +3780,10 @@
         <v>0</v>
       </c>
       <c r="T36" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U36" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="U36" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -4004,10 +4006,10 @@
         <v>0</v>
       </c>
       <c r="T40" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U40" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="U40" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
@@ -4063,10 +4065,10 @@
         <v>0</v>
       </c>
       <c r="T41" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U41" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="U41" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
@@ -4122,10 +4124,10 @@
         <v>0</v>
       </c>
       <c r="T42" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U42" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="U42" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
@@ -4185,10 +4187,10 @@
         <v>0</v>
       </c>
       <c r="T43" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U43" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="U43" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -4354,10 +4356,10 @@
         <v>0</v>
       </c>
       <c r="T46" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U46" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="U46" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
@@ -4523,10 +4525,10 @@
         <v>0</v>
       </c>
       <c r="T49" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U49" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="U49" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -4777,7 +4779,7 @@
         <v>175</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>181</v>
@@ -4792,7 +4794,7 @@
         <v>1</v>
       </c>
       <c r="T54" s="12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="U54" s="7" t="s">
         <v>27</v>
@@ -4855,10 +4857,10 @@
         <v>0</v>
       </c>
       <c r="T55" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U55" s="12" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
@@ -4918,10 +4920,10 @@
         <v>0</v>
       </c>
       <c r="T56" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U56" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="U56" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
@@ -4981,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="T57" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U57" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="U57" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -5250,10 +5252,10 @@
         <v>0</v>
       </c>
       <c r="T62" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U62" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="U62" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
@@ -5313,10 +5315,10 @@
         <v>0</v>
       </c>
       <c r="T63" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U63" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="U63" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
@@ -5376,10 +5378,10 @@
         <v>0</v>
       </c>
       <c r="T64" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U64" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="U64" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5439,10 +5441,10 @@
         <v>0</v>
       </c>
       <c r="T65" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U65" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="U65" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5502,10 +5504,10 @@
         <v>0</v>
       </c>
       <c r="T66" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U66" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="U66" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5565,10 +5567,10 @@
         <v>0</v>
       </c>
       <c r="T67" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U67" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="U67" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5675,10 +5677,10 @@
         <v>0</v>
       </c>
       <c r="T69" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U69" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="U69" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5738,10 +5740,10 @@
         <v>0</v>
       </c>
       <c r="T70" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U70" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="U70" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -5960,10 +5962,10 @@
         <v>0</v>
       </c>
       <c r="T74" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U74" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="U74" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -6208,7 +6210,7 @@
         <v>201</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P79" s="10" t="s">
         <v>245</v>
@@ -6226,7 +6228,7 @@
         <v>32</v>
       </c>
       <c r="U79" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
@@ -6286,10 +6288,10 @@
         <v>0</v>
       </c>
       <c r="T80" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U80" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="U80" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
@@ -6349,10 +6351,10 @@
         <v>0</v>
       </c>
       <c r="T81" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U81" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="U81" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6367,7 +6369,7 @@
         <v>46206.67610053241</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6418,7 +6420,7 @@
         <v>46206.676097800926</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6469,7 +6471,7 @@
         <v>46206.6760950926</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6520,7 +6522,7 @@
         <v>46206.67609248843</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6571,7 +6573,7 @@
         <v>46206.67608929398</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6622,7 +6624,7 @@
         <v>46206.67608666667</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6673,7 +6675,7 @@
         <v>46206.676083935185</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6724,7 +6726,7 @@
         <v>46206.676078449076</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6775,7 +6777,7 @@
         <v>46206.67607780093</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6936,10 +6938,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I93" s="9">
         <v>46275</v>
@@ -6975,10 +6977,10 @@
         <v>0</v>
       </c>
       <c r="T93" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U93" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="U93" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
@@ -6999,10 +7001,10 @@
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I94" s="5">
         <v>46275</v>
@@ -7052,10 +7054,10 @@
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I95" s="9">
         <v>46275</v>
@@ -7105,10 +7107,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I96" s="5">
         <v>46275</v>
@@ -7158,10 +7160,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I97" s="9">
         <v>46282</v>
@@ -7197,10 +7199,10 @@
         <v>0</v>
       </c>
       <c r="T97" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U97" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="U97" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
@@ -7221,10 +7223,10 @@
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I98" s="5">
         <v>46282</v>
@@ -7274,10 +7276,10 @@
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I99" s="9">
         <v>46282</v>
@@ -7327,10 +7329,10 @@
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I100" s="5">
         <v>46282</v>
@@ -7380,10 +7382,10 @@
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I101" s="9">
         <v>46286</v>
@@ -7419,10 +7421,10 @@
         <v>0</v>
       </c>
       <c r="T101" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U101" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="U101" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
@@ -7443,10 +7445,10 @@
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I102" s="5">
         <v>46286</v>
@@ -7496,10 +7498,10 @@
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I103" s="9">
         <v>46286</v>
@@ -7549,10 +7551,10 @@
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I104" s="5">
         <v>46286</v>
@@ -7602,10 +7604,10 @@
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I105" s="9">
         <v>46287</v>
@@ -7641,10 +7643,10 @@
         <v>0</v>
       </c>
       <c r="T105" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U105" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="U105" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
@@ -7665,10 +7667,10 @@
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I106" s="5">
         <v>46287</v>
@@ -7718,10 +7720,10 @@
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I107" s="9">
         <v>46287</v>
@@ -7771,10 +7773,10 @@
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I108" s="5">
         <v>46287</v>
@@ -7824,10 +7826,10 @@
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I109" s="9">
         <v>46289</v>
@@ -7863,10 +7865,10 @@
         <v>0</v>
       </c>
       <c r="T109" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U109" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="U109" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
@@ -7887,10 +7889,10 @@
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I110" s="5">
         <v>46289</v>
@@ -7940,10 +7942,10 @@
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I111" s="9">
         <v>46289</v>
@@ -7993,10 +7995,10 @@
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I112" s="5">
         <v>46289</v>
@@ -8132,10 +8134,10 @@
         <v>0</v>
       </c>
       <c r="T114" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U114" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="U114" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
@@ -8309,7 +8311,7 @@
         <v>46206.677167546295</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8339,7 +8341,7 @@
         <v>307</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>316</v>
@@ -8362,7 +8364,7 @@
         <v>46206.677164733796</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
@@ -8392,7 +8394,7 @@
         <v>307</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P119" s="10" t="s">
         <v>316</v>
@@ -8415,7 +8417,7 @@
         <v>46206.67716196759</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8445,7 +8447,7 @@
         <v>307</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>316</v>
@@ -8468,7 +8470,7 @@
         <v>46206.677158935185</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
@@ -8498,7 +8500,7 @@
         <v>307</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P121" s="10" t="s">
         <v>316</v>
@@ -8521,7 +8523,7 @@
         <v>46206.677155868056</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8551,7 +8553,7 @@
         <v>307</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>316</v>
@@ -8574,7 +8576,7 @@
         <v>46206.67715351852</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>26</v>
@@ -8604,7 +8606,7 @@
         <v>307</v>
       </c>
       <c r="O123" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P123" s="10" t="s">
         <v>316</v>
@@ -8627,7 +8629,7 @@
         <v>46206.67715042824</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8657,7 +8659,7 @@
         <v>307</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>316</v>
@@ -8680,7 +8682,7 @@
         <v>46206.677144120375</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
@@ -8710,7 +8712,7 @@
         <v>307</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P125" s="10" t="s">
         <v>316</v>
@@ -8733,7 +8735,7 @@
         <v>46206.67714356481</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -8763,7 +8765,7 @@
         <v>307</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>316</v>
@@ -8792,10 +8794,10 @@
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I127" s="9">
         <v>46293</v>
@@ -8831,10 +8833,10 @@
         <v>0</v>
       </c>
       <c r="T127" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U127" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="U127" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
@@ -8855,10 +8857,10 @@
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I128" s="5">
         <v>46293</v>
@@ -8908,10 +8910,10 @@
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I129" s="9">
         <v>46293</v>
@@ -8961,10 +8963,10 @@
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I130" s="5">
         <v>46293</v>
@@ -9014,10 +9016,10 @@
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I131" s="9">
         <v>46293</v>
@@ -9038,7 +9040,7 @@
         <v>326</v>
       </c>
       <c r="O131" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P131" s="10" t="s">
         <v>335</v>
@@ -9067,10 +9069,10 @@
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I132" s="5">
         <v>46293</v>
@@ -9091,7 +9093,7 @@
         <v>326</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P132" s="6" t="s">
         <v>335</v>
@@ -9120,10 +9122,10 @@
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I133" s="9">
         <v>46293</v>
@@ -9144,7 +9146,7 @@
         <v>326</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P133" s="10" t="s">
         <v>335</v>
@@ -9173,10 +9175,10 @@
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I134" s="5">
         <v>46293</v>
@@ -9197,7 +9199,7 @@
         <v>326</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P134" s="6" t="s">
         <v>335</v>
@@ -9226,10 +9228,10 @@
         <v>26</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H135" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I135" s="9">
         <v>46293</v>
@@ -9250,7 +9252,7 @@
         <v>326</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P135" s="10" t="s">
         <v>335</v>
@@ -9279,10 +9281,10 @@
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I136" s="5">
         <v>46293</v>
@@ -9303,7 +9305,7 @@
         <v>326</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P136" s="6" t="s">
         <v>335</v>
@@ -9332,10 +9334,10 @@
         <v>26</v>
       </c>
       <c r="G137" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H137" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I137" s="9">
         <v>46293</v>
@@ -9356,7 +9358,7 @@
         <v>326</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P137" s="10" t="s">
         <v>335</v>
@@ -9385,10 +9387,10 @@
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I138" s="5">
         <v>46293</v>
@@ -9409,7 +9411,7 @@
         <v>326</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P138" s="6" t="s">
         <v>335</v>
@@ -9438,10 +9440,10 @@
         <v>26</v>
       </c>
       <c r="G139" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H139" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I139" s="9">
         <v>46293</v>
@@ -9462,7 +9464,7 @@
         <v>326</v>
       </c>
       <c r="O139" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P139" s="10" t="s">
         <v>335</v>
@@ -9530,10 +9532,10 @@
         <v>0</v>
       </c>
       <c r="T140" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U140" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="U140" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
@@ -10227,10 +10229,10 @@
         <v>0</v>
       </c>
       <c r="T153" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U153" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="U153" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
@@ -10916,10 +10918,10 @@
         <v>0</v>
       </c>
       <c r="T166" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U166" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="U166" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
@@ -10979,10 +10981,10 @@
         <v>0</v>
       </c>
       <c r="T167" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U167" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="U167" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
@@ -11042,10 +11044,10 @@
         <v>0</v>
       </c>
       <c r="T168" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U168" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="U168" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
@@ -11152,10 +11154,10 @@
         <v>0</v>
       </c>
       <c r="T170" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="U170" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="U170" s="11" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
@@ -11217,7 +11219,7 @@
         <v>1</v>
       </c>
       <c r="T171" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U171" s="7" t="s">
         <v>27</v>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -11059,7 +11059,7 @@
       </c>
       <c r="C169" s="10"/>
       <c r="D169" s="9">
-        <v>46206.67846486111</v>
+        <v>46212.76788890046</v>
       </c>
       <c r="E169" s="10" t="s">
         <v>390</v>
@@ -11167,11 +11167,9 @@
       <c r="B171" s="9">
         <v>46204.78752627315</v>
       </c>
-      <c r="C171" s="9">
-        <v>46206.67845753473</v>
-      </c>
+      <c r="C171" s="10"/>
       <c r="D171" s="9">
-        <v>46206.67848190972</v>
+        <v>46212.767965266205</v>
       </c>
       <c r="E171" s="10" t="s">
         <v>396</v>
@@ -11216,13 +11214,13 @@
         <v>46316</v>
       </c>
       <c r="S171" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T171" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="U171" s="7" t="s">
-        <v>27</v>
+      <c r="U171" s="11" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1967" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1968" uniqueCount="397">
   <si>
     <t>50001569 - EUROHINCA</t>
   </si>
@@ -316,37 +316,37 @@
     <t xml:space="preserve">Reserva produccion,Recepción mono bloque </t>
   </si>
   <si>
+    <t>1216208608300141</t>
+  </si>
+  <si>
+    <t>Propuesta compras:</t>
+  </si>
+  <si>
+    <t>propuesta corte laser,propuesta motor,propuesta tableros</t>
+  </si>
+  <si>
+    <t>Generación OC corte laser</t>
+  </si>
+  <si>
+    <t>1216219007082142</t>
+  </si>
+  <si>
+    <t>propuesta motor</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación oc Motor</t>
+  </si>
+  <si>
+    <t>1216219007089965</t>
+  </si>
+  <si>
+    <t>propuesta tableros</t>
+  </si>
+  <si>
+    <t>Generación OC Tableros,Propuesta compras:</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1216208608300141</t>
-  </si>
-  <si>
-    <t>Propuesta compras:</t>
-  </si>
-  <si>
-    <t>propuesta corte laser,propuesta motor,propuesta tableros</t>
-  </si>
-  <si>
-    <t>Generación OC corte laser</t>
-  </si>
-  <si>
-    <t>1216219007082142</t>
-  </si>
-  <si>
-    <t>propuesta motor</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación oc Motor</t>
-  </si>
-  <si>
-    <t>1216219007089965</t>
-  </si>
-  <si>
-    <t>propuesta tableros</t>
-  </si>
-  <si>
-    <t>Generación OC Tableros,Propuesta compras:</t>
   </si>
   <si>
     <t>1216218870903024</t>
@@ -2963,9 +2963,11 @@
       <c r="B23" s="9">
         <v>46204.78877271991</v>
       </c>
-      <c r="C23" s="10"/>
+      <c r="C23" s="9">
+        <v>46213.50330829861</v>
+      </c>
       <c r="D23" s="9">
-        <v>46206.64882732639</v>
+        <v>46213.50331935185</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>78</v>
@@ -2999,9 +3001,13 @@
       </c>
       <c r="Q23" s="10"/>
       <c r="R23" s="10"/>
-      <c r="S23" s="10"/>
+      <c r="S23" s="10">
+        <v>1</v>
+      </c>
       <c r="T23" s="10"/>
-      <c r="U23" s="10"/>
+      <c r="U23" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
@@ -3010,9 +3016,11 @@
       <c r="B24" s="5">
         <v>46204.788881678236</v>
       </c>
-      <c r="C24" s="6"/>
+      <c r="C24" s="5">
+        <v>46213.50328878472</v>
+      </c>
       <c r="D24" s="5">
-        <v>46209.812545775465</v>
+        <v>46213.5033090162</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>79</v>
@@ -3057,18 +3065,18 @@
         <v>46209</v>
       </c>
       <c r="S24" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T24" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="U24" s="12" t="s">
-        <v>83</v>
+      <c r="U24" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B25" s="9">
         <v>46204.786945914355</v>
@@ -3078,7 +3086,7 @@
         <v>46209.79230103009</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>25</v>
@@ -3102,10 +3110,10 @@
         <v>26</v>
       </c>
       <c r="O25" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="P25" s="10" t="s">
         <v>86</v>
-      </c>
-      <c r="P25" s="10" t="s">
-        <v>87</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -3115,7 +3123,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B26" s="5">
         <v>46204.78715721065</v>
@@ -3124,10 +3132,10 @@
         <v>46206.76966122685</v>
       </c>
       <c r="D26" s="5">
-        <v>46206.76967918982</v>
+        <v>46213.19381935185</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
@@ -3154,13 +3162,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>71</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q26" s="5">
         <v>46212</v>
@@ -3171,8 +3179,8 @@
       <c r="S26" s="6">
         <v>1</v>
       </c>
-      <c r="T26" s="7" t="s">
-        <v>52</v>
+      <c r="T26" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="U26" s="7" t="s">
         <v>27</v>
@@ -3180,7 +3188,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B27" s="9">
         <v>46204.78716710648</v>
@@ -3192,7 +3200,7 @@
         <v>46212.64675210648</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
@@ -3219,13 +3227,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>43</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q27" s="9">
         <v>46213</v>
@@ -3240,7 +3248,7 @@
         <v>52</v>
       </c>
       <c r="U27" s="12" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -3282,13 +3290,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>98</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q28" s="5">
         <v>46244</v>
@@ -3303,7 +3311,7 @@
         <v>52</v>
       </c>
       <c r="U28" s="12" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -3345,7 +3353,7 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O29" s="10" t="s">
         <v>101</v>
@@ -3408,7 +3416,7 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>101</v>
@@ -3471,7 +3479,7 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O31" s="10" t="s">
         <v>101</v>
@@ -3647,7 +3655,7 @@
         <v>113</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>119</v>
@@ -3830,7 +3838,7 @@
         <v>124</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P37" s="10" t="s">
         <v>128</v>
@@ -4024,7 +4032,7 @@
         <v>46206.67358165509</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
@@ -4054,7 +4062,7 @@
         <v>136</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P41" s="10" t="s">
         <v>141</v>
@@ -4113,7 +4121,7 @@
         <v>136</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>144</v>
@@ -4860,7 +4868,7 @@
         <v>52</v>
       </c>
       <c r="U55" s="12" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
@@ -6177,7 +6185,7 @@
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46211.203985914355</v>
+        <v>46213.50330894676</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>244</v>
@@ -6227,8 +6235,8 @@
       <c r="T79" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="U79" s="11" t="s">
-        <v>53</v>
+      <c r="U79" s="12" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -3797,9 +3797,11 @@
       <c r="B36" s="5">
         <v>46204.78722327546</v>
       </c>
-      <c r="C36" s="6"/>
+      <c r="C36" s="5">
+        <v>46217.69453972222</v>
+      </c>
       <c r="D36" s="5">
-        <v>46206.76999994213</v>
+        <v>46217.69515425926</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>125</v>
@@ -3844,13 +3846,13 @@
         <v>46213</v>
       </c>
       <c r="S36" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T36" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="U36" s="11" t="s">
-        <v>54</v>
+      <c r="U36" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -3915,9 +3917,11 @@
       <c r="B38" s="5">
         <v>46204.787231689814</v>
       </c>
-      <c r="C38" s="6"/>
+      <c r="C38" s="5">
+        <v>46217.69452263889</v>
+      </c>
       <c r="D38" s="5">
-        <v>46206.76995223379</v>
+        <v>46217.69452489584</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>131</v>
@@ -4764,7 +4768,7 @@
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46210.52590918982</v>
+        <v>46217.8575847801</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>176</v>
@@ -4874,9 +4878,11 @@
       <c r="B55" s="9">
         <v>46204.78731518518</v>
       </c>
-      <c r="C55" s="10"/>
+      <c r="C55" s="9">
+        <v>46217.85757222222</v>
+      </c>
       <c r="D55" s="9">
-        <v>46213.90764578704</v>
+        <v>46217.85759137732</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>184</v>
@@ -4921,13 +4927,13 @@
         <v>46233</v>
       </c>
       <c r="S55" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T55" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="U55" s="12" t="s">
-        <v>94</v>
+      <c r="U55" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
@@ -4939,7 +4945,7 @@
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46210.52590861111</v>
+        <v>46217.857591875</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>102</v>
@@ -4989,8 +4995,8 @@
       <c r="T56" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="U56" s="11" t="s">
-        <v>54</v>
+      <c r="U56" s="12" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
@@ -6307,7 +6313,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46206.67591493056</v>
+        <v>46217.69454351852</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>248</v>
@@ -6357,8 +6363,8 @@
       <c r="T80" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="U80" s="11" t="s">
-        <v>54</v>
+      <c r="U80" s="12" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -345,331 +345,331 @@
     <t>Ingenieria Jefe de proyecto:,Planos Definitivos,propuesta motor</t>
   </si>
   <si>
+    <t>1216219007060429</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:,propuesta corte laser,Planos Preliminar</t>
+  </si>
+  <si>
+    <t>1216208498022053</t>
+  </si>
+  <si>
+    <t>Reserva produccion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserva mono bloque </t>
+  </si>
+  <si>
+    <t>1216208498022055</t>
+  </si>
+  <si>
+    <t>benjamin.bustos@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserva produccion,Recepción mono bloque </t>
+  </si>
+  <si>
+    <t>1216208608300141</t>
+  </si>
+  <si>
+    <t>Propuesta compras:</t>
+  </si>
+  <si>
+    <t>propuesta corte laser,propuesta motor,propuesta tableros</t>
+  </si>
+  <si>
+    <t>Generación OC corte laser</t>
+  </si>
+  <si>
+    <t>1216219007082142</t>
+  </si>
+  <si>
+    <t>propuesta motor</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación oc Motor</t>
+  </si>
+  <si>
+    <t>1216219007089965</t>
+  </si>
+  <si>
+    <t>propuesta tableros</t>
+  </si>
+  <si>
+    <t>Generación OC Tableros,Propuesta compras:</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
+    <t>1216218870903024</t>
+  </si>
+  <si>
+    <t>propuesta corte laser</t>
+  </si>
+  <si>
+    <t>hugo isla martinez</t>
+  </si>
+  <si>
+    <t>hugo.isla@zitron.com</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle,Check Planos</t>
+  </si>
+  <si>
+    <t>1216208498022062</t>
+  </si>
+  <si>
+    <t>propuesta corte plasma</t>
+  </si>
+  <si>
+    <t>Check Planos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación  oc corte plasma </t>
+  </si>
+  <si>
+    <t>1216208498022063</t>
+  </si>
+  <si>
+    <t>propuesta mecanizado</t>
+  </si>
+  <si>
+    <t>generación oc mecanizado</t>
+  </si>
+  <si>
+    <t>1216208498022064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">propuesta fabricación externa </t>
+  </si>
+  <si>
+    <t xml:space="preserve">generacion oc fabricación externa </t>
+  </si>
+  <si>
+    <t>1216208498022048</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tableros 4368,Corte laser 4367 </t>
+  </si>
+  <si>
+    <t>1216219007108859</t>
+  </si>
+  <si>
+    <t>Tableros 4368</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC Tableros,Fabricación Tablero</t>
+  </si>
+  <si>
+    <t>1216218896994060</t>
+  </si>
+  <si>
+    <t>Generación OC Tableros</t>
+  </si>
+  <si>
+    <t>Tableros 4368,Fabricación Tablero</t>
+  </si>
+  <si>
+    <t>1216218897008580</t>
+  </si>
+  <si>
+    <t>Fabricación Tablero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tableros 4368, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 34368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E,RECEPCION FABRICACIÓN EXTERNA </t>
+  </si>
+  <si>
+    <t>1216219007123932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motor 4367 </t>
+  </si>
+  <si>
+    <t>Generación oc Motor,Fabricación motor,Planos motor proveedor</t>
+  </si>
+  <si>
+    <t>1216219007123944</t>
+  </si>
+  <si>
+    <t>Generación oc Motor</t>
+  </si>
+  <si>
+    <t>Motor 4367 ,Fabricación motor,Planos motor proveedor</t>
+  </si>
+  <si>
+    <t>1216218870925196</t>
+  </si>
+  <si>
+    <t>Fabricación motor</t>
+  </si>
+  <si>
+    <t>Motor 4367 ,Recepcion Motor</t>
+  </si>
+  <si>
+    <t>1216218896926045</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor</t>
+  </si>
+  <si>
+    <t>Motor 4367 ,Planos Definitivos</t>
+  </si>
+  <si>
+    <t>1216218897037029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corte laser 4367 </t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC corte laser,Fabricacion  corte laser</t>
+  </si>
+  <si>
+    <t>1216218897037046</t>
+  </si>
+  <si>
+    <t>Corte laser 4367 ,Fabricacion  corte laser</t>
+  </si>
+  <si>
+    <t>1216218897038301</t>
+  </si>
+  <si>
+    <t>Fabricacion  corte laser</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corte laser 4367 ,Recepcion corte laser </t>
+  </si>
+  <si>
+    <t>1216208498022065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corte plasma 4367 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generacion Oc Corte Plasma ,Fabricación corte plasma ,Generacion Oc Corte Plasma </t>
+  </si>
+  <si>
+    <t>1216208498022071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación corte plasma </t>
+  </si>
+  <si>
+    <t>1216208498022072</t>
+  </si>
+  <si>
+    <t>Corte plasma 4367 ,Recepcion corte plasma</t>
+  </si>
+  <si>
+    <t>1216208498022066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mecanizado 4367 </t>
+  </si>
+  <si>
+    <t>generación oc mecanizado,fabricacion mecanizado</t>
+  </si>
+  <si>
+    <t>1216208498022073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fabricacion mecanizado,Mecanizado 4367 </t>
+  </si>
+  <si>
+    <t>1216208498022074</t>
+  </si>
+  <si>
+    <t>fabricacion mecanizado</t>
+  </si>
+  <si>
+    <t>Mecanizado 4367 ,Recepción mecanizado</t>
+  </si>
+  <si>
+    <t>1216208498022067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación externa 4367 </t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">generacion oc fabricación externa ,fabricación material con proveedor externo </t>
+  </si>
+  <si>
+    <t>1216208498022075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fabricación material con proveedor externo ,Fabricación externa 4367 </t>
+  </si>
+  <si>
+    <t>1216208498022076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fabricación material con proveedor externo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación externa 4367 ,CONTROL DE CALIDAD FABRICACIONE XTERNA </t>
+  </si>
+  <si>
+    <t>1216265318483734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTROL DE CALIDAD FABRICACIONE XTERNA </t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1216219007170836</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:</t>
+  </si>
+  <si>
+    <t>Check Planos,Planos Preliminar,Planos Definitivos,Check pruebas FAT</t>
+  </si>
+  <si>
+    <t>1216219007170850</t>
+  </si>
+  <si>
+    <t>Planos Preliminar</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>Check Planos,Ingenieria y diseño:,Planos Definitivos</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216219007060429</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,propuesta corte laser,Planos Preliminar</t>
-  </si>
-  <si>
-    <t>1216208498022053</t>
-  </si>
-  <si>
-    <t>Reserva produccion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserva mono bloque </t>
-  </si>
-  <si>
-    <t>1216208498022055</t>
-  </si>
-  <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserva produccion,Recepción mono bloque </t>
-  </si>
-  <si>
-    <t>1216208608300141</t>
-  </si>
-  <si>
-    <t>Propuesta compras:</t>
-  </si>
-  <si>
-    <t>propuesta corte laser,propuesta motor,propuesta tableros</t>
-  </si>
-  <si>
-    <t>Generación OC corte laser</t>
-  </si>
-  <si>
-    <t>1216219007082142</t>
-  </si>
-  <si>
-    <t>propuesta motor</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación oc Motor</t>
-  </si>
-  <si>
-    <t>1216219007089965</t>
-  </si>
-  <si>
-    <t>propuesta tableros</t>
-  </si>
-  <si>
-    <t>Generación OC Tableros,Propuesta compras:</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1216218870903024</t>
-  </si>
-  <si>
-    <t>propuesta corte laser</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle,Check Planos</t>
-  </si>
-  <si>
-    <t>1216208498022062</t>
-  </si>
-  <si>
-    <t>propuesta corte plasma</t>
-  </si>
-  <si>
-    <t>Check Planos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación  oc corte plasma </t>
-  </si>
-  <si>
-    <t>1216208498022063</t>
-  </si>
-  <si>
-    <t>propuesta mecanizado</t>
-  </si>
-  <si>
-    <t>generación oc mecanizado</t>
-  </si>
-  <si>
-    <t>1216208498022064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">propuesta fabricación externa </t>
-  </si>
-  <si>
-    <t xml:space="preserve">generacion oc fabricación externa </t>
-  </si>
-  <si>
-    <t>1216208498022048</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tableros 4368,Corte laser 4367 </t>
-  </si>
-  <si>
-    <t>1216219007108859</t>
-  </si>
-  <si>
-    <t>Tableros 4368</t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC Tableros,Fabricación Tablero</t>
-  </si>
-  <si>
-    <t>1216218896994060</t>
-  </si>
-  <si>
-    <t>Generación OC Tableros</t>
-  </si>
-  <si>
-    <t>Tableros 4368,Fabricación Tablero</t>
-  </si>
-  <si>
-    <t>1216218897008580</t>
-  </si>
-  <si>
-    <t>Fabricación Tablero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tableros 4368, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 34368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E,RECEPCION FABRICACIÓN EXTERNA </t>
-  </si>
-  <si>
-    <t>1216219007123932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motor 4367 </t>
-  </si>
-  <si>
-    <t>Generación oc Motor,Fabricación motor,Planos motor proveedor</t>
-  </si>
-  <si>
-    <t>1216219007123944</t>
-  </si>
-  <si>
-    <t>Generación oc Motor</t>
-  </si>
-  <si>
-    <t>Motor 4367 ,Fabricación motor,Planos motor proveedor</t>
-  </si>
-  <si>
-    <t>1216218870925196</t>
-  </si>
-  <si>
-    <t>Fabricación motor</t>
-  </si>
-  <si>
-    <t>Motor 4367 ,Recepcion Motor</t>
-  </si>
-  <si>
-    <t>1216218896926045</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor</t>
-  </si>
-  <si>
-    <t>Motor 4367 ,Planos Definitivos</t>
-  </si>
-  <si>
-    <t>1216218897037029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corte laser 4367 </t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC corte laser,Fabricacion  corte laser</t>
-  </si>
-  <si>
-    <t>1216218897037046</t>
-  </si>
-  <si>
-    <t>Corte laser 4367 ,Fabricacion  corte laser</t>
-  </si>
-  <si>
-    <t>1216218897038301</t>
-  </si>
-  <si>
-    <t>Fabricacion  corte laser</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corte laser 4367 ,Recepcion corte laser </t>
-  </si>
-  <si>
-    <t>1216208498022065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corte plasma 4367 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generacion Oc Corte Plasma ,Fabricación corte plasma ,Generacion Oc Corte Plasma </t>
-  </si>
-  <si>
-    <t>1216208498022071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación corte plasma </t>
-  </si>
-  <si>
-    <t>1216208498022072</t>
-  </si>
-  <si>
-    <t>Corte plasma 4367 ,Recepcion corte plasma</t>
-  </si>
-  <si>
-    <t>1216208498022066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mecanizado 4367 </t>
-  </si>
-  <si>
-    <t>generación oc mecanizado,fabricacion mecanizado</t>
-  </si>
-  <si>
-    <t>1216208498022073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fabricacion mecanizado,Mecanizado 4367 </t>
-  </si>
-  <si>
-    <t>1216208498022074</t>
-  </si>
-  <si>
-    <t>fabricacion mecanizado</t>
-  </si>
-  <si>
-    <t>Mecanizado 4367 ,Recepción mecanizado</t>
-  </si>
-  <si>
-    <t>1216208498022067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación externa 4367 </t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">generacion oc fabricación externa ,fabricación material con proveedor externo </t>
-  </si>
-  <si>
-    <t>1216208498022075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fabricación material con proveedor externo ,Fabricación externa 4367 </t>
-  </si>
-  <si>
-    <t>1216208498022076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fabricación material con proveedor externo </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación externa 4367 ,CONTROL DE CALIDAD FABRICACIONE XTERNA </t>
-  </si>
-  <si>
-    <t>1216265318483734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTROL DE CALIDAD FABRICACIONE XTERNA </t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1216219007170836</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:</t>
-  </si>
-  <si>
-    <t>Check Planos,Planos Preliminar,Planos Definitivos,Check pruebas FAT</t>
-  </si>
-  <si>
-    <t>1216219007170850</t>
-  </si>
-  <si>
-    <t>Planos Preliminar</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Check Planos,Ingenieria y diseño:,Planos Definitivos</t>
   </si>
   <si>
     <t>1216218897067253</t>
@@ -2896,7 +2896,7 @@
         <v>46206.769487592595</v>
       </c>
       <c r="D21" s="9">
-        <v>46210.205320381945</v>
+        <v>46218.18071489583</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>72</v>
@@ -2943,8 +2943,8 @@
       <c r="S21" s="10">
         <v>1</v>
       </c>
-      <c r="T21" s="12" t="s">
-        <v>74</v>
+      <c r="T21" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="U21" s="7" t="s">
         <v>27</v>
@@ -2952,7 +2952,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B22" s="5">
         <v>46204.787143009264</v>
@@ -2964,7 +2964,7 @@
         <v>46212.19074947917</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -2997,7 +2997,7 @@
         <v>38</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q22" s="5">
         <v>46211</v>
@@ -3017,7 +3017,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B23" s="9">
         <v>46204.78877271991</v>
@@ -3029,7 +3029,7 @@
         <v>46213.50331935185</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>25</v>
@@ -3053,7 +3053,7 @@
         <v>26</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P23" s="10" t="s">
         <v>26</v>
@@ -3070,7 +3070,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B24" s="5">
         <v>46204.788881678236</v>
@@ -3082,16 +3082,16 @@
         <v>46217.187861597224</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I24" s="5">
         <v>46209</v>
@@ -3109,13 +3109,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>38</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q24" s="5">
         <v>46216</v>
@@ -3135,7 +3135,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B25" s="9">
         <v>46204.786945914355</v>
@@ -3145,7 +3145,7 @@
         <v>46209.79230103009</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>25</v>
@@ -3169,10 +3169,10 @@
         <v>26</v>
       </c>
       <c r="O25" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="P25" s="10" t="s">
         <v>86</v>
-      </c>
-      <c r="P25" s="10" t="s">
-        <v>87</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -3182,7 +3182,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B26" s="5">
         <v>46204.78715721065</v>
@@ -3194,7 +3194,7 @@
         <v>46213.19381935185</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
@@ -3221,13 +3221,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>72</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q26" s="5">
         <v>46212</v>
@@ -3247,7 +3247,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B27" s="9">
         <v>46204.78716710648</v>
@@ -3259,7 +3259,7 @@
         <v>46214.18292518519</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
@@ -3286,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>44</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q27" s="9">
         <v>46213</v>
@@ -3307,12 +3307,12 @@
         <v>33</v>
       </c>
       <c r="U27" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B28" s="5">
         <v>46204.787177743056</v>
@@ -3322,16 +3322,16 @@
         <v>46206.76986597222</v>
       </c>
       <c r="E28" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G28" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="F28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G28" s="6" t="s">
+      <c r="H28" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="I28" s="5">
         <v>46241</v>
@@ -3349,13 +3349,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q28" s="5">
         <v>46244</v>
@@ -3370,12 +3370,12 @@
         <v>53</v>
       </c>
       <c r="U28" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B29" s="9">
         <v>46204.79158200232</v>
@@ -3385,16 +3385,16 @@
         <v>46206.67314619213</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H29" s="10" t="s">
         <v>97</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>98</v>
       </c>
       <c r="I29" s="9">
         <v>46241</v>
@@ -3412,13 +3412,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O29" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="P29" s="10" t="s">
         <v>102</v>
-      </c>
-      <c r="P29" s="10" t="s">
-        <v>103</v>
       </c>
       <c r="Q29" s="9">
         <v>46244</v>
@@ -3438,7 +3438,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B30" s="5">
         <v>46204.79163886574</v>
@@ -3448,16 +3448,16 @@
         <v>46206.673139039354</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="I30" s="5">
         <v>46241</v>
@@ -3475,13 +3475,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q30" s="5">
         <v>46244</v>
@@ -3501,7 +3501,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B31" s="9">
         <v>46204.7917447338</v>
@@ -3511,16 +3511,16 @@
         <v>46206.67313840278</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H31" s="10" t="s">
         <v>97</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>98</v>
       </c>
       <c r="I31" s="9">
         <v>46241</v>
@@ -3538,13 +3538,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q31" s="9">
         <v>46244</v>
@@ -3564,7 +3564,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B32" s="5">
         <v>46204.78695173611</v>
@@ -3574,7 +3574,7 @@
         <v>46206.65562592592</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>25</v>
@@ -3598,7 +3598,7 @@
         <v>26</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3611,7 +3611,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B33" s="9">
         <v>46204.78719643518</v>
@@ -3621,16 +3621,16 @@
         <v>46206.67332864583</v>
       </c>
       <c r="E33" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="F33" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="10" t="s">
+      <c r="H33" s="10" t="s">
         <v>115</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>116</v>
       </c>
       <c r="I33" s="9">
         <v>46216</v>
@@ -3648,13 +3648,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Q33" s="9">
         <v>46273</v>
@@ -3674,7 +3674,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B34" s="5">
         <v>46204.7872006713</v>
@@ -3684,16 +3684,16 @@
         <v>46209.792300393514</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>115</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>116</v>
       </c>
       <c r="I34" s="5">
         <v>46216</v>
@@ -3711,13 +3711,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3733,7 +3733,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B35" s="9">
         <v>46204.787204837965</v>
@@ -3743,16 +3743,16 @@
         <v>46206.67327987269</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="H35" s="10" t="s">
         <v>115</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>116</v>
       </c>
       <c r="I35" s="9">
         <v>46225</v>
@@ -3770,13 +3770,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3792,7 +3792,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B36" s="5">
         <v>46204.78722327546</v>
@@ -3804,16 +3804,16 @@
         <v>46217.69515425926</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>115</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>116</v>
       </c>
       <c r="I36" s="5">
         <v>46213</v>
@@ -3831,10 +3831,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3857,7 +3857,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B37" s="9">
         <v>46204.78722760417</v>
@@ -3869,16 +3869,16 @@
         <v>46206.769946203705</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>115</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>116</v>
       </c>
       <c r="I37" s="9">
         <v>46213</v>
@@ -3896,13 +3896,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3912,7 +3912,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B38" s="5">
         <v>46204.787231689814</v>
@@ -3924,16 +3924,16 @@
         <v>46217.69452489584</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>115</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>116</v>
       </c>
       <c r="I38" s="5">
         <v>46224</v>
@@ -3951,13 +3951,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3967,7 +3967,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B39" s="9">
         <v>46204.78728243055</v>
@@ -3979,16 +3979,16 @@
         <v>46206.769995821756</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="H39" s="10" t="s">
         <v>115</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>116</v>
       </c>
       <c r="I39" s="9">
         <v>46224</v>
@@ -4006,13 +4006,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -4022,7 +4022,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B40" s="5">
         <v>46204.78728729166</v>
@@ -4032,16 +4032,16 @@
         <v>46206.67363866898</v>
       </c>
       <c r="E40" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G40" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="F40" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G40" s="6" t="s">
+      <c r="H40" s="6" t="s">
         <v>138</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>139</v>
       </c>
       <c r="I40" s="5">
         <v>46245</v>
@@ -4059,13 +4059,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Q40" s="5">
         <v>46255</v>
@@ -4085,7 +4085,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B41" s="9">
         <v>46204.787292175926</v>
@@ -4095,16 +4095,16 @@
         <v>46206.67358165509</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>138</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>139</v>
       </c>
       <c r="I41" s="9">
         <v>46245</v>
@@ -4122,13 +4122,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4144,7 +4144,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B42" s="5">
         <v>46204.78730063657</v>
@@ -4154,16 +4154,16 @@
         <v>46206.673579016206</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>138</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>139</v>
       </c>
       <c r="I42" s="5">
         <v>46247</v>
@@ -4181,13 +4181,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4203,7 +4203,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B43" s="9">
         <v>46204.793668136575</v>
@@ -4213,16 +4213,16 @@
         <v>46209.87015284722</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="H43" s="10" t="s">
         <v>138</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>139</v>
       </c>
       <c r="I43" s="9">
         <v>46245</v>
@@ -4240,10 +4240,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B44" s="5">
         <v>46204.794818298615</v>
@@ -4276,16 +4276,16 @@
         <v>46206.673746319444</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>138</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>139</v>
       </c>
       <c r="I44" s="5">
         <v>46245</v>
@@ -4303,13 +4303,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4319,7 +4319,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B45" s="9">
         <v>46204.794902430556</v>
@@ -4329,16 +4329,16 @@
         <v>46206.673743865744</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>138</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>139</v>
       </c>
       <c r="I45" s="9">
         <v>46247</v>
@@ -4356,13 +4356,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4372,7 +4372,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B46" s="5">
         <v>46204.7938509375</v>
@@ -4382,16 +4382,16 @@
         <v>46206.67393748843</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>138</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>139</v>
       </c>
       <c r="I46" s="5">
         <v>46245</v>
@@ -4409,10 +4409,10 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4435,7 +4435,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B47" s="9">
         <v>46204.795001412036</v>
@@ -4445,16 +4445,16 @@
         <v>46206.673880648144</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="H47" s="10" t="s">
         <v>138</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>139</v>
       </c>
       <c r="I47" s="9">
         <v>46245</v>
@@ -4472,13 +4472,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
@@ -4488,7 +4488,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B48" s="5">
         <v>46204.795060543984</v>
@@ -4498,16 +4498,16 @@
         <v>46206.67387746528</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>138</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>139</v>
       </c>
       <c r="I48" s="5">
         <v>46247</v>
@@ -4525,13 +4525,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4541,7 +4541,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B49" s="9">
         <v>46204.7939687037</v>
@@ -4551,16 +4551,16 @@
         <v>46206.67465699074</v>
       </c>
       <c r="E49" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G49" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="F49" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G49" s="10" t="s">
+      <c r="H49" s="10" t="s">
         <v>163</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>164</v>
       </c>
       <c r="I49" s="9">
         <v>46241</v>
@@ -4578,10 +4578,10 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4604,7 +4604,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B50" s="5">
         <v>46204.795132997686</v>
@@ -4614,16 +4614,16 @@
         <v>46206.67409482639</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>163</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>164</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4641,13 +4641,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4657,7 +4657,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B51" s="9">
         <v>46204.795219293985</v>
@@ -4667,16 +4667,16 @@
         <v>46206.67409221065</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>163</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>164</v>
       </c>
       <c r="I51" s="9">
         <v>46246</v>
@@ -4694,13 +4694,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4710,7 +4710,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B52" s="5">
         <v>46206.65895994213</v>
@@ -4720,16 +4720,16 @@
         <v>46206.674336111115</v>
       </c>
       <c r="E52" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="F52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G52" s="6" t="s">
+      <c r="H52" s="6" t="s">
         <v>173</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>174</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4745,10 +4745,10 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>26</v>
@@ -4761,7 +4761,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B53" s="9">
         <v>46204.787306770835</v>
@@ -4771,7 +4771,7 @@
         <v>46217.8575847801</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>25</v>
@@ -4795,7 +4795,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>26</v>
@@ -4808,7 +4808,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B54" s="5">
         <v>46204.78731047454</v>
@@ -4820,16 +4820,16 @@
         <v>46211.18996762732</v>
       </c>
       <c r="E54" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G54" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="F54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G54" s="6" t="s">
+      <c r="H54" s="6" t="s">
         <v>180</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>181</v>
       </c>
       <c r="I54" s="5">
         <v>46212</v>
@@ -4847,13 +4847,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q54" s="5">
         <v>46218</v>
@@ -4865,7 +4865,7 @@
         <v>1</v>
       </c>
       <c r="T54" s="12" t="s">
-        <v>74</v>
+        <v>182</v>
       </c>
       <c r="U54" s="7" t="s">
         <v>27</v>
@@ -4891,10 +4891,10 @@
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="I55" s="9">
         <v>46233</v>
@@ -4912,7 +4912,7 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O55" s="10" t="s">
         <v>185</v>
@@ -4948,16 +4948,16 @@
         <v>46217.857591875</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>180</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>181</v>
       </c>
       <c r="I56" s="5">
         <v>46240</v>
@@ -4975,7 +4975,7 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>188</v>
@@ -4996,7 +4996,7 @@
         <v>53</v>
       </c>
       <c r="U56" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
@@ -5038,13 +5038,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O57" s="10" t="s">
         <v>194</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q57" s="9">
         <v>46288</v>
@@ -5310,7 +5310,7 @@
         <v>202</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>208</v>
@@ -5349,10 +5349,10 @@
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="I63" s="9">
         <v>46260</v>
@@ -5436,7 +5436,7 @@
         <v>202</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>214</v>
@@ -5475,10 +5475,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="I65" s="9">
         <v>46260</v>
@@ -5562,7 +5562,7 @@
         <v>202</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>219</v>
@@ -5601,10 +5601,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="I67" s="9">
         <v>46260</v>
@@ -5996,10 +5996,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>173</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>174</v>
       </c>
       <c r="I74" s="5">
         <v>46274</v>
@@ -6059,10 +6059,10 @@
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="H75" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="I75" s="10"/>
       <c r="J75" s="9">
@@ -6110,10 +6110,10 @@
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>173</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>174</v>
       </c>
       <c r="I76" s="6"/>
       <c r="J76" s="5">
@@ -6161,10 +6161,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="H77" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="I77" s="10"/>
       <c r="J77" s="9">
@@ -6283,7 +6283,7 @@
         <v>202</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P79" s="10" t="s">
         <v>246</v>
@@ -6301,7 +6301,7 @@
         <v>33</v>
       </c>
       <c r="U79" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
@@ -6346,7 +6346,7 @@
         <v>202</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>246</v>
@@ -6364,7 +6364,7 @@
         <v>53</v>
       </c>
       <c r="U80" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
@@ -6470,7 +6470,7 @@
         <v>250</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>253</v>
@@ -6521,7 +6521,7 @@
         <v>250</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P83" s="10" t="s">
         <v>255</v>
@@ -6572,7 +6572,7 @@
         <v>250</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>253</v>
@@ -6623,7 +6623,7 @@
         <v>250</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>253</v>
@@ -6674,7 +6674,7 @@
         <v>250</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>253</v>
@@ -6725,7 +6725,7 @@
         <v>250</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P87" s="10" t="s">
         <v>253</v>
@@ -6776,7 +6776,7 @@
         <v>250</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>253</v>
@@ -6827,7 +6827,7 @@
         <v>250</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P89" s="10" t="s">
         <v>253</v>
@@ -6878,7 +6878,7 @@
         <v>250</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>253</v>
@@ -6931,7 +6931,7 @@
         <v>202</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P91" s="10" t="s">
         <v>26</v>
@@ -7011,10 +7011,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I93" s="9">
         <v>46275</v>
@@ -7074,10 +7074,10 @@
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I94" s="5">
         <v>46275</v>
@@ -7127,10 +7127,10 @@
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I95" s="9">
         <v>46275</v>
@@ -7180,10 +7180,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I96" s="5">
         <v>46275</v>
@@ -7233,10 +7233,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I97" s="9">
         <v>46282</v>
@@ -7296,10 +7296,10 @@
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I98" s="5">
         <v>46282</v>
@@ -7349,10 +7349,10 @@
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I99" s="9">
         <v>46282</v>
@@ -7402,10 +7402,10 @@
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I100" s="5">
         <v>46282</v>
@@ -7455,10 +7455,10 @@
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I101" s="9">
         <v>46286</v>
@@ -7518,10 +7518,10 @@
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I102" s="5">
         <v>46286</v>
@@ -7571,10 +7571,10 @@
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I103" s="9">
         <v>46286</v>
@@ -7624,10 +7624,10 @@
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I104" s="5">
         <v>46286</v>
@@ -7677,10 +7677,10 @@
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I105" s="9">
         <v>46287</v>
@@ -7740,10 +7740,10 @@
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I106" s="5">
         <v>46287</v>
@@ -7793,10 +7793,10 @@
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I107" s="9">
         <v>46287</v>
@@ -7846,10 +7846,10 @@
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I108" s="5">
         <v>46287</v>
@@ -7899,10 +7899,10 @@
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I109" s="9">
         <v>46289</v>
@@ -7962,10 +7962,10 @@
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I110" s="5">
         <v>46289</v>
@@ -8015,10 +8015,10 @@
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I111" s="9">
         <v>46289</v>
@@ -8068,10 +8068,10 @@
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I112" s="5">
         <v>46289</v>
@@ -8867,10 +8867,10 @@
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I127" s="9">
         <v>46293</v>
@@ -8930,10 +8930,10 @@
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I128" s="5">
         <v>46293</v>
@@ -8983,10 +8983,10 @@
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I129" s="9">
         <v>46293</v>
@@ -9036,10 +9036,10 @@
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I130" s="5">
         <v>46293</v>
@@ -9089,10 +9089,10 @@
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I131" s="9">
         <v>46293</v>
@@ -9142,10 +9142,10 @@
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I132" s="5">
         <v>46293</v>
@@ -9195,10 +9195,10 @@
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I133" s="9">
         <v>46293</v>
@@ -9248,10 +9248,10 @@
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I134" s="5">
         <v>46293</v>
@@ -9301,10 +9301,10 @@
         <v>26</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H135" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I135" s="9">
         <v>46293</v>
@@ -9354,10 +9354,10 @@
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I136" s="5">
         <v>46293</v>
@@ -9407,10 +9407,10 @@
         <v>26</v>
       </c>
       <c r="G137" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H137" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I137" s="9">
         <v>46293</v>
@@ -9460,10 +9460,10 @@
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I138" s="5">
         <v>46293</v>
@@ -9513,10 +9513,10 @@
         <v>26</v>
       </c>
       <c r="G139" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H139" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I139" s="9">
         <v>46293</v>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1930" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1930" uniqueCount="394">
   <si>
     <t>50001569 - EUROHINCA</t>
   </si>
@@ -658,9 +658,6 @@
   </si>
   <si>
     <t>Check Planos,Ingenieria y diseño:,Planos Definitivos</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1216218897067253</t>
@@ -4798,7 +4795,7 @@
         <v>46210.52590148148</v>
       </c>
       <c r="D54" s="5">
-        <v>46211.18996762732</v>
+        <v>46219.20085231481</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>175</v>
@@ -4845,8 +4842,8 @@
       <c r="S54" s="6">
         <v>1</v>
       </c>
-      <c r="T54" s="12" t="s">
-        <v>179</v>
+      <c r="T54" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="U54" s="7" t="s">
         <v>27</v>
@@ -4854,7 +4851,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B55" s="9">
         <v>46204.78731518518</v>
@@ -4866,7 +4863,7 @@
         <v>46217.85759137732</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
@@ -4896,10 +4893,10 @@
         <v>172</v>
       </c>
       <c r="O55" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="P55" s="10" t="s">
         <v>182</v>
-      </c>
-      <c r="P55" s="10" t="s">
-        <v>183</v>
       </c>
       <c r="Q55" s="9">
         <v>46239</v>
@@ -4919,7 +4916,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B56" s="5">
         <v>46204.78732028935</v>
@@ -4959,10 +4956,10 @@
         <v>172</v>
       </c>
       <c r="O56" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="P56" s="6" t="s">
         <v>185</v>
-      </c>
-      <c r="P56" s="6" t="s">
-        <v>186</v>
       </c>
       <c r="Q56" s="5">
         <v>46240</v>
@@ -4982,7 +4979,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B57" s="9">
         <v>46204.787326770835</v>
@@ -4992,16 +4989,16 @@
         <v>46206.67498217593</v>
       </c>
       <c r="E57" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G57" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="F57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G57" s="10" t="s">
+      <c r="H57" s="10" t="s">
         <v>189</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>190</v>
       </c>
       <c r="I57" s="9">
         <v>46288</v>
@@ -5022,7 +5019,7 @@
         <v>172</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>172</v>
@@ -5045,7 +5042,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B58" s="5">
         <v>46205.8929956713</v>
@@ -5055,16 +5052,16 @@
         <v>46206.67494384259</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>190</v>
       </c>
       <c r="I58" s="5">
         <v>46288</v>
@@ -5082,13 +5079,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="O58" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="P58" s="6" t="s">
         <v>193</v>
-      </c>
-      <c r="P58" s="6" t="s">
-        <v>194</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5098,7 +5095,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B59" s="9">
         <v>46205.89308850694</v>
@@ -5108,16 +5105,16 @@
         <v>46206.67494135417</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>189</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>190</v>
       </c>
       <c r="I59" s="9">
         <v>46288</v>
@@ -5135,13 +5132,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5151,7 +5148,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B60" s="5">
         <v>46205.89321678241</v>
@@ -5161,16 +5158,16 @@
         <v>46206.67493778935</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>190</v>
       </c>
       <c r="I60" s="5">
         <v>46288</v>
@@ -5188,13 +5185,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="O60" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="P60" s="6" t="s">
         <v>193</v>
-      </c>
-      <c r="P60" s="6" t="s">
-        <v>194</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5204,7 +5201,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B61" s="9">
         <v>46204.787330555555</v>
@@ -5214,7 +5211,7 @@
         <v>46206.65997969908</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>25</v>
@@ -5238,7 +5235,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5251,7 +5248,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B62" s="5">
         <v>46204.78733380787</v>
@@ -5261,16 +5258,16 @@
         <v>46206.67512555556</v>
       </c>
       <c r="E62" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G62" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="F62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G62" s="6" t="s">
+      <c r="H62" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I62" s="5">
         <v>46258</v>
@@ -5288,13 +5285,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>140</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q62" s="5">
         <v>46259</v>
@@ -5314,7 +5311,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B63" s="9">
         <v>46204.78733813658</v>
@@ -5324,7 +5321,7 @@
         <v>46206.67526587963</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
@@ -5351,13 +5348,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Q63" s="9">
         <v>46261</v>
@@ -5377,7 +5374,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B64" s="5">
         <v>46204.79962430555</v>
@@ -5387,16 +5384,16 @@
         <v>46206.67512305555</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I64" s="5">
         <v>46258</v>
@@ -5414,13 +5411,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>146</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q64" s="5">
         <v>46259</v>
@@ -5440,7 +5437,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B65" s="9">
         <v>46204.79970230324</v>
@@ -5450,7 +5447,7 @@
         <v>46206.67526299768</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
@@ -5477,13 +5474,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q65" s="9">
         <v>46261</v>
@@ -5503,7 +5500,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B66" s="5">
         <v>46204.799834722224</v>
@@ -5513,16 +5510,16 @@
         <v>46206.67512025463</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I66" s="5">
         <v>46258</v>
@@ -5540,13 +5537,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>155</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Q66" s="5">
         <v>46259</v>
@@ -5566,7 +5563,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B67" s="9">
         <v>46204.80007783565</v>
@@ -5576,7 +5573,7 @@
         <v>46206.67526012732</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
@@ -5603,13 +5600,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q67" s="9">
         <v>46261</v>
@@ -5629,7 +5626,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B68" s="5">
         <v>46204.787342662035</v>
@@ -5639,7 +5636,7 @@
         <v>46206.66163074074</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5663,7 +5660,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5676,7 +5673,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B69" s="9">
         <v>46204.78734565972</v>
@@ -5686,16 +5683,16 @@
         <v>46206.67535149306</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>222</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>223</v>
       </c>
       <c r="I69" s="9">
         <v>46262</v>
@@ -5713,13 +5710,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O69" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="P69" s="10" t="s">
         <v>224</v>
-      </c>
-      <c r="P69" s="10" t="s">
-        <v>225</v>
       </c>
       <c r="Q69" s="9">
         <v>46266</v>
@@ -5739,7 +5736,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B70" s="5">
         <v>46204.78735021991</v>
@@ -5749,16 +5746,16 @@
         <v>46206.67558131945</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="I70" s="5">
         <v>46267</v>
@@ -5776,13 +5773,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q70" s="5">
         <v>46273</v>
@@ -5802,7 +5799,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B71" s="9">
         <v>46204.83329071759</v>
@@ -5812,16 +5809,16 @@
         <v>46206.67551582176</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="H71" s="10" t="s">
         <v>222</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>223</v>
       </c>
       <c r="I71" s="9">
         <v>46267</v>
@@ -5839,13 +5836,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O71" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="P71" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="P71" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5855,7 +5852,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B72" s="5">
         <v>46204.83348987269</v>
@@ -5865,16 +5862,16 @@
         <v>46206.67551341435</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="I72" s="5">
         <v>46267</v>
@@ -5892,13 +5889,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O72" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="P72" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="P72" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5908,7 +5905,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B73" s="9">
         <v>46204.83350201389</v>
@@ -5918,16 +5915,16 @@
         <v>46206.67551030093</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="H73" s="10" t="s">
         <v>222</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>223</v>
       </c>
       <c r="I73" s="9">
         <v>46267</v>
@@ -5945,13 +5942,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O73" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="P73" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="P73" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -5961,7 +5958,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B74" s="5">
         <v>46204.787355625</v>
@@ -5971,7 +5968,7 @@
         <v>46206.67580866898</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5998,13 +5995,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q74" s="5">
         <v>46274</v>
@@ -6024,7 +6021,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B75" s="9">
         <v>46204.83355802084</v>
@@ -6034,7 +6031,7 @@
         <v>46206.67575559027</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -6059,13 +6056,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6075,7 +6072,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B76" s="5">
         <v>46204.833570069444</v>
@@ -6085,7 +6082,7 @@
         <v>46206.67575268519</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6110,13 +6107,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6126,7 +6123,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B77" s="9">
         <v>46204.833579004626</v>
@@ -6136,7 +6133,7 @@
         <v>46206.67574885416</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -6161,13 +6158,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6177,7 +6174,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B78" s="5">
         <v>46204.78736071759</v>
@@ -6187,7 +6184,7 @@
         <v>46206.67094998843</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>25</v>
@@ -6211,7 +6208,7 @@
         <v>26</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6224,7 +6221,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B79" s="9">
         <v>46204.78736410879</v>
@@ -6234,16 +6231,16 @@
         <v>46213.50330894676</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="H79" s="10" t="s">
         <v>203</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>204</v>
       </c>
       <c r="I79" s="9">
         <v>46210</v>
@@ -6261,13 +6258,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O79" s="10" t="s">
         <v>79</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q79" s="9">
         <v>46210</v>
@@ -6287,7 +6284,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B80" s="5">
         <v>46204.78737366898</v>
@@ -6297,16 +6294,16 @@
         <v>46217.69454351852</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I80" s="5">
         <v>46253</v>
@@ -6324,13 +6321,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>127</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q80" s="5">
         <v>46253</v>
@@ -6350,7 +6347,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B81" s="9">
         <v>46204.78737825232</v>
@@ -6360,16 +6357,16 @@
         <v>46206.67600082176</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="H81" s="10" t="s">
         <v>203</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>204</v>
       </c>
       <c r="I81" s="9">
         <v>46274</v>
@@ -6387,13 +6384,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q81" s="9">
         <v>46274</v>
@@ -6413,7 +6410,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B82" s="5">
         <v>46206.567318657406</v>
@@ -6429,10 +6426,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I82" s="6"/>
       <c r="J82" s="5">
@@ -6448,13 +6445,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>118</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6464,7 +6461,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B83" s="9">
         <v>46206.56766555556</v>
@@ -6480,10 +6477,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="H83" s="10" t="s">
         <v>203</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>204</v>
       </c>
       <c r="I83" s="10"/>
       <c r="J83" s="9">
@@ -6499,13 +6496,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O83" s="10" t="s">
         <v>118</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6515,7 +6512,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B84" s="5">
         <v>46206.56768260417</v>
@@ -6531,10 +6528,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I84" s="6"/>
       <c r="J84" s="5">
@@ -6550,13 +6547,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>118</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6566,7 +6563,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B85" s="9">
         <v>46206.56769806713</v>
@@ -6582,10 +6579,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="H85" s="10" t="s">
         <v>203</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>204</v>
       </c>
       <c r="I85" s="10"/>
       <c r="J85" s="9">
@@ -6601,13 +6598,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O85" s="10" t="s">
         <v>118</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6617,7 +6614,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B86" s="5">
         <v>46206.56771423611</v>
@@ -6633,10 +6630,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I86" s="6"/>
       <c r="J86" s="5">
@@ -6652,13 +6649,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>118</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6668,7 +6665,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B87" s="9">
         <v>46206.56772880787</v>
@@ -6684,10 +6681,10 @@
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="H87" s="10" t="s">
         <v>203</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>204</v>
       </c>
       <c r="I87" s="10"/>
       <c r="J87" s="9">
@@ -6703,13 +6700,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O87" s="10" t="s">
         <v>118</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6719,7 +6716,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B88" s="5">
         <v>46206.567743506945</v>
@@ -6735,10 +6732,10 @@
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I88" s="6"/>
       <c r="J88" s="5">
@@ -6754,13 +6751,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>118</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6770,7 +6767,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B89" s="9">
         <v>46206.56775844908</v>
@@ -6786,10 +6783,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="H89" s="10" t="s">
         <v>203</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>204</v>
       </c>
       <c r="I89" s="10"/>
       <c r="J89" s="9">
@@ -6805,13 +6802,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O89" s="10" t="s">
         <v>118</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6821,7 +6818,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B90" s="5">
         <v>46206.56777289352</v>
@@ -6837,10 +6834,10 @@
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H90" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="I90" s="6"/>
       <c r="J90" s="5">
@@ -6856,13 +6853,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>118</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6872,7 +6869,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B91" s="9">
         <v>46206.67094809028</v>
@@ -6882,16 +6879,16 @@
         <v>46206.67590806713</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="H91" s="10" t="s">
         <v>203</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>204</v>
       </c>
       <c r="I91" s="9">
         <v>46274</v>
@@ -6909,7 +6906,7 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O91" s="10" t="s">
         <v>118</v>
@@ -6929,7 +6926,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B92" s="5">
         <v>46204.78738409722</v>
@@ -6939,7 +6936,7 @@
         <v>46206.66745490741</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>25</v>
@@ -6963,7 +6960,7 @@
         <v>26</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>26</v>
@@ -6976,7 +6973,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B93" s="9">
         <v>46204.787387268516</v>
@@ -6986,7 +6983,7 @@
         <v>46206.676306875</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7011,13 +7008,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q93" s="9">
         <v>46281</v>
@@ -7037,7 +7034,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B94" s="5">
         <v>46204.84491833333</v>
@@ -7047,7 +7044,7 @@
         <v>46206.676259513886</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7072,13 +7069,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7088,7 +7085,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B95" s="9">
         <v>46204.84493530093</v>
@@ -7098,7 +7095,7 @@
         <v>46206.67625695602</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7123,13 +7120,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7139,7 +7136,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B96" s="5">
         <v>46204.84494427084</v>
@@ -7149,7 +7146,7 @@
         <v>46206.67625305556</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7174,13 +7171,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7190,7 +7187,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B97" s="9">
         <v>46204.78739225694</v>
@@ -7200,7 +7197,7 @@
         <v>46206.67641435185</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7225,13 +7222,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q97" s="9">
         <v>46282</v>
@@ -7251,7 +7248,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B98" s="5">
         <v>46204.84497997686</v>
@@ -7261,7 +7258,7 @@
         <v>46206.67651039352</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7286,13 +7283,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="O98" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="P98" s="6" t="s">
         <v>275</v>
-      </c>
-      <c r="P98" s="6" t="s">
-        <v>276</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7302,7 +7299,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B99" s="9">
         <v>46204.84498876157</v>
@@ -7312,7 +7309,7 @@
         <v>46206.67650773148</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7337,13 +7334,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="O99" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="P99" s="10" t="s">
         <v>275</v>
-      </c>
-      <c r="P99" s="10" t="s">
-        <v>276</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7353,7 +7350,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B100" s="5">
         <v>46204.84499563657</v>
@@ -7363,7 +7360,7 @@
         <v>46206.67650460648</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7388,13 +7385,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7404,7 +7401,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B101" s="9">
         <v>46204.78740502315</v>
@@ -7414,7 +7411,7 @@
         <v>46206.676410960645</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7439,13 +7436,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q101" s="9">
         <v>46286</v>
@@ -7465,7 +7462,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B102" s="5">
         <v>46204.84507945602</v>
@@ -7475,7 +7472,7 @@
         <v>46206.67662570602</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7500,13 +7497,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O102" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="P102" s="6" t="s">
         <v>282</v>
-      </c>
-      <c r="P102" s="6" t="s">
-        <v>283</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7516,7 +7513,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B103" s="9">
         <v>46204.84508817129</v>
@@ -7526,7 +7523,7 @@
         <v>46206.676623368054</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7551,13 +7548,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O103" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="P103" s="10" t="s">
         <v>282</v>
-      </c>
-      <c r="P103" s="10" t="s">
-        <v>283</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7567,7 +7564,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B104" s="5">
         <v>46204.845093854165</v>
@@ -7577,7 +7574,7 @@
         <v>46206.676619756945</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7602,13 +7599,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O104" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="P104" s="6" t="s">
         <v>282</v>
-      </c>
-      <c r="P104" s="6" t="s">
-        <v>283</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7618,7 +7615,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B105" s="9">
         <v>46204.78741121528</v>
@@ -7628,7 +7625,7 @@
         <v>46206.67640778935</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7653,13 +7650,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q105" s="9">
         <v>46287</v>
@@ -7679,7 +7676,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B106" s="5">
         <v>46204.84513122685</v>
@@ -7689,7 +7686,7 @@
         <v>46206.67673481481</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7714,13 +7711,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O106" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="P106" s="6" t="s">
         <v>289</v>
-      </c>
-      <c r="P106" s="6" t="s">
-        <v>290</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7730,7 +7727,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B107" s="9">
         <v>46204.84513944444</v>
@@ -7740,7 +7737,7 @@
         <v>46206.67673186342</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7765,13 +7762,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O107" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="P107" s="10" t="s">
         <v>289</v>
-      </c>
-      <c r="P107" s="10" t="s">
-        <v>290</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7781,7 +7778,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B108" s="5">
         <v>46204.8451466088</v>
@@ -7791,7 +7788,7 @@
         <v>46206.67672797454</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7816,13 +7813,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O108" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="P108" s="6" t="s">
         <v>289</v>
-      </c>
-      <c r="P108" s="6" t="s">
-        <v>290</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7832,7 +7829,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B109" s="9">
         <v>46204.787473310185</v>
@@ -7842,7 +7839,7 @@
         <v>46206.676404432874</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -7867,13 +7864,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q109" s="9">
         <v>46289</v>
@@ -7893,7 +7890,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B110" s="5">
         <v>46204.84518325231</v>
@@ -7903,7 +7900,7 @@
         <v>46206.676860590276</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -7928,13 +7925,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -7944,7 +7941,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B111" s="9">
         <v>46204.845191898145</v>
@@ -7954,7 +7951,7 @@
         <v>46206.676858067134</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -7979,13 +7976,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -7995,7 +7992,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B112" s="5">
         <v>46204.84520083333</v>
@@ -8005,7 +8002,7 @@
         <v>46206.676854363424</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8030,13 +8027,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8046,7 +8043,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B113" s="9">
         <v>46204.78748032407</v>
@@ -8056,7 +8053,7 @@
         <v>46206.668344247686</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>25</v>
@@ -8080,7 +8077,7 @@
         <v>26</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>
@@ -8093,7 +8090,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B114" s="5">
         <v>46204.787484155095</v>
@@ -8103,16 +8100,16 @@
         <v>46206.677181631945</v>
       </c>
       <c r="E114" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="F114" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G114" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="F114" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G114" s="6" t="s">
+      <c r="H114" s="6" t="s">
         <v>306</v>
-      </c>
-      <c r="H114" s="6" t="s">
-        <v>307</v>
       </c>
       <c r="I114" s="5">
         <v>46290</v>
@@ -8130,13 +8127,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q114" s="5">
         <v>46290</v>
@@ -8156,7 +8153,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B115" s="9">
         <v>46206.61281571759</v>
@@ -8166,16 +8163,16 @@
         <v>46206.67717564815</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="H115" s="10" t="s">
         <v>306</v>
-      </c>
-      <c r="H115" s="10" t="s">
-        <v>307</v>
       </c>
       <c r="I115" s="9">
         <v>46290</v>
@@ -8193,13 +8190,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8209,7 +8206,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B116" s="5">
         <v>46206.612829722224</v>
@@ -8219,16 +8216,16 @@
         <v>46206.67717299769</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="H116" s="6" t="s">
         <v>306</v>
-      </c>
-      <c r="H116" s="6" t="s">
-        <v>307</v>
       </c>
       <c r="I116" s="5">
         <v>46290</v>
@@ -8246,13 +8243,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8262,7 +8259,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B117" s="9">
         <v>46206.61284180556</v>
@@ -8272,16 +8269,16 @@
         <v>46206.67717023148</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="H117" s="10" t="s">
         <v>306</v>
-      </c>
-      <c r="H117" s="10" t="s">
-        <v>307</v>
       </c>
       <c r="I117" s="9">
         <v>46290</v>
@@ -8299,13 +8296,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8315,7 +8312,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B118" s="5">
         <v>46206.61323981482</v>
@@ -8331,10 +8328,10 @@
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="H118" s="6" t="s">
         <v>306</v>
-      </c>
-      <c r="H118" s="6" t="s">
-        <v>307</v>
       </c>
       <c r="I118" s="5">
         <v>46290</v>
@@ -8352,13 +8349,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8368,7 +8365,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B119" s="9">
         <v>46206.613256446755</v>
@@ -8384,10 +8381,10 @@
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="H119" s="10" t="s">
         <v>306</v>
-      </c>
-      <c r="H119" s="10" t="s">
-        <v>307</v>
       </c>
       <c r="I119" s="9">
         <v>46290</v>
@@ -8405,13 +8402,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O119" s="10" t="s">
         <v>59</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8421,7 +8418,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B120" s="5">
         <v>46206.61328513889</v>
@@ -8437,10 +8434,10 @@
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="H120" s="6" t="s">
         <v>306</v>
-      </c>
-      <c r="H120" s="6" t="s">
-        <v>307</v>
       </c>
       <c r="I120" s="5">
         <v>46290</v>
@@ -8458,13 +8455,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8474,7 +8471,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B121" s="9">
         <v>46206.613270925925</v>
@@ -8490,10 +8487,10 @@
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="H121" s="10" t="s">
         <v>306</v>
-      </c>
-      <c r="H121" s="10" t="s">
-        <v>307</v>
       </c>
       <c r="I121" s="9">
         <v>46290</v>
@@ -8511,13 +8508,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O121" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8527,7 +8524,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B122" s="5">
         <v>46206.6133403125</v>
@@ -8543,10 +8540,10 @@
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="H122" s="6" t="s">
         <v>306</v>
-      </c>
-      <c r="H122" s="6" t="s">
-        <v>307</v>
       </c>
       <c r="I122" s="5">
         <v>46290</v>
@@ -8564,13 +8561,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8580,7 +8577,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B123" s="9">
         <v>46206.613361041665</v>
@@ -8596,10 +8593,10 @@
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="H123" s="10" t="s">
         <v>306</v>
-      </c>
-      <c r="H123" s="10" t="s">
-        <v>307</v>
       </c>
       <c r="I123" s="9">
         <v>46290</v>
@@ -8617,13 +8614,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O123" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8633,7 +8630,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B124" s="5">
         <v>46206.613371493055</v>
@@ -8649,10 +8646,10 @@
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="H124" s="6" t="s">
         <v>306</v>
-      </c>
-      <c r="H124" s="6" t="s">
-        <v>307</v>
       </c>
       <c r="I124" s="5">
         <v>46290</v>
@@ -8670,13 +8667,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8686,7 +8683,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B125" s="9">
         <v>46206.61338284722</v>
@@ -8702,10 +8699,10 @@
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="H125" s="10" t="s">
         <v>306</v>
-      </c>
-      <c r="H125" s="10" t="s">
-        <v>307</v>
       </c>
       <c r="I125" s="9">
         <v>46290</v>
@@ -8723,13 +8720,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O125" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -8739,7 +8736,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B126" s="5">
         <v>46206.61339653935</v>
@@ -8755,10 +8752,10 @@
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="H126" s="6" t="s">
         <v>306</v>
-      </c>
-      <c r="H126" s="6" t="s">
-        <v>307</v>
       </c>
       <c r="I126" s="5">
         <v>46290</v>
@@ -8776,13 +8773,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8792,7 +8789,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B127" s="9">
         <v>46204.78748974537</v>
@@ -8802,7 +8799,7 @@
         <v>46209.580981481486</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
@@ -8821,19 +8818,19 @@
         <v>26</v>
       </c>
       <c r="L127" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="M127" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N127" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="O127" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="M127" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N127" s="10" t="s">
-        <v>302</v>
-      </c>
-      <c r="O127" s="10" t="s">
-        <v>326</v>
-      </c>
       <c r="P127" s="10" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Q127" s="9">
         <v>46293</v>
@@ -8853,7 +8850,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B128" s="5">
         <v>46204.84566665509</v>
@@ -8863,7 +8860,7 @@
         <v>46206.6774368287</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -8888,13 +8885,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -8904,7 +8901,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B129" s="9">
         <v>46204.8456746875</v>
@@ -8914,7 +8911,7 @@
         <v>46206.67743376158</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
@@ -8939,13 +8936,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -8955,7 +8952,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B130" s="5">
         <v>46204.84568395834</v>
@@ -8965,7 +8962,7 @@
         <v>46206.67743099537</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -8990,13 +8987,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9006,7 +9003,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B131" s="9">
         <v>46204.84577770834</v>
@@ -9016,7 +9013,7 @@
         <v>46206.67742784722</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
@@ -9041,13 +9038,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O131" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9057,7 +9054,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B132" s="5">
         <v>46204.845803958335</v>
@@ -9067,7 +9064,7 @@
         <v>46206.677424988426</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9092,13 +9089,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O132" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9108,7 +9105,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B133" s="9">
         <v>46204.8458116088</v>
@@ -9118,7 +9115,7 @@
         <v>46206.67742180555</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
@@ -9143,13 +9140,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O133" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9159,7 +9156,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B134" s="5">
         <v>46204.84582686343</v>
@@ -9169,7 +9166,7 @@
         <v>46206.677418680556</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9194,13 +9191,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9210,7 +9207,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B135" s="9">
         <v>46204.84581974537</v>
@@ -9220,7 +9217,7 @@
         <v>46206.67741584491</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
@@ -9245,13 +9242,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O135" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9261,7 +9258,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B136" s="5">
         <v>46204.84583605324</v>
@@ -9271,7 +9268,7 @@
         <v>46206.67741314815</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9296,13 +9293,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O136" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9312,7 +9309,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B137" s="9">
         <v>46204.84584422453</v>
@@ -9322,7 +9319,7 @@
         <v>46206.67740501158</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
@@ -9347,13 +9344,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O137" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9363,7 +9360,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B138" s="5">
         <v>46204.845850983795</v>
@@ -9373,7 +9370,7 @@
         <v>46206.67740435185</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9398,13 +9395,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O138" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9414,7 +9411,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B139" s="9">
         <v>46204.84585899305</v>
@@ -9424,7 +9421,7 @@
         <v>46206.67740371528</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
@@ -9449,13 +9446,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O139" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q139" s="10"/>
       <c r="R139" s="10"/>
@@ -9465,7 +9462,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B140" s="5">
         <v>46204.78749533565</v>
@@ -9475,16 +9472,16 @@
         <v>46206.67787028935</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="H140" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="H140" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="I140" s="5">
         <v>46294</v>
@@ -9502,13 +9499,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="O140" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="P140" s="6" t="s">
         <v>344</v>
-      </c>
-      <c r="P140" s="6" t="s">
-        <v>345</v>
       </c>
       <c r="Q140" s="5">
         <v>46294</v>
@@ -9528,7 +9525,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B141" s="9">
         <v>46204.84595449074</v>
@@ -9538,16 +9535,16 @@
         <v>46206.67786329861</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="H141" s="10" t="s">
         <v>222</v>
-      </c>
-      <c r="H141" s="10" t="s">
-        <v>223</v>
       </c>
       <c r="I141" s="9">
         <v>46294</v>
@@ -9565,13 +9562,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P141" s="10" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Q141" s="10"/>
       <c r="R141" s="10"/>
@@ -9581,7 +9578,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B142" s="5">
         <v>46204.845964189815</v>
@@ -9591,16 +9588,16 @@
         <v>46206.677860254626</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="H142" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="H142" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="I142" s="5">
         <v>46294</v>
@@ -9618,13 +9615,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9634,7 +9631,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B143" s="9">
         <v>46204.84597238426</v>
@@ -9644,16 +9641,16 @@
         <v>46206.67785763889</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="H143" s="10" t="s">
         <v>222</v>
-      </c>
-      <c r="H143" s="10" t="s">
-        <v>223</v>
       </c>
       <c r="I143" s="9">
         <v>46294</v>
@@ -9671,13 +9668,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Q143" s="10"/>
       <c r="R143" s="10"/>
@@ -9687,7 +9684,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B144" s="5">
         <v>46204.846036469906</v>
@@ -9697,16 +9694,16 @@
         <v>46206.67785519676</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="H144" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="H144" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="I144" s="5">
         <v>46294</v>
@@ -9724,13 +9721,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -9740,7 +9737,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B145" s="9">
         <v>46204.846047893516</v>
@@ -9750,16 +9747,16 @@
         <v>46206.6778525</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="H145" s="10" t="s">
         <v>222</v>
-      </c>
-      <c r="H145" s="10" t="s">
-        <v>223</v>
       </c>
       <c r="I145" s="9">
         <v>46294</v>
@@ -9777,13 +9774,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -9793,7 +9790,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B146" s="5">
         <v>46204.846056724535</v>
@@ -9803,16 +9800,16 @@
         <v>46206.67784956019</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="H146" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="H146" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="I146" s="5">
         <v>46294</v>
@@ -9830,13 +9827,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -9846,7 +9843,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B147" s="9">
         <v>46204.846065578706</v>
@@ -9856,16 +9853,16 @@
         <v>46206.677846921295</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="H147" s="10" t="s">
         <v>222</v>
-      </c>
-      <c r="H147" s="10" t="s">
-        <v>223</v>
       </c>
       <c r="I147" s="9">
         <v>46294</v>
@@ -9883,13 +9880,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="O147" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="Q147" s="10"/>
       <c r="R147" s="10"/>
@@ -9899,7 +9896,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B148" s="5">
         <v>46204.846073252316</v>
@@ -9909,16 +9906,16 @@
         <v>46206.67784445602</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="H148" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="H148" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="I148" s="5">
         <v>46294</v>
@@ -9936,13 +9933,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -9952,7 +9949,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B149" s="9">
         <v>46204.84608019676</v>
@@ -9962,16 +9959,16 @@
         <v>46206.6778419676</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="H149" s="10" t="s">
         <v>222</v>
-      </c>
-      <c r="H149" s="10" t="s">
-        <v>223</v>
       </c>
       <c r="I149" s="9">
         <v>46294</v>
@@ -9989,13 +9986,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="Q149" s="10"/>
       <c r="R149" s="10"/>
@@ -10005,7 +10002,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B150" s="5">
         <v>46204.84608666667</v>
@@ -10015,16 +10012,16 @@
         <v>46206.67783399306</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="H150" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="H150" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="I150" s="5">
         <v>46294</v>
@@ -10042,13 +10039,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10058,7 +10055,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B151" s="9">
         <v>46204.84609472222</v>
@@ -10068,16 +10065,16 @@
         <v>46206.677833344904</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G151" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="H151" s="10" t="s">
         <v>222</v>
-      </c>
-      <c r="H151" s="10" t="s">
-        <v>223</v>
       </c>
       <c r="I151" s="9">
         <v>46294</v>
@@ -10095,13 +10092,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="P151" s="10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="Q151" s="10"/>
       <c r="R151" s="10"/>
@@ -10111,7 +10108,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B152" s="5">
         <v>46204.84610289352</v>
@@ -10121,16 +10118,16 @@
         <v>46206.67783269676</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="H152" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="H152" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="I152" s="5">
         <v>46294</v>
@@ -10148,13 +10145,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10164,7 +10161,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="8" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B153" s="9">
         <v>46204.78749967593</v>
@@ -10174,16 +10171,16 @@
         <v>46206.67812460648</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G153" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="H153" s="10" t="s">
         <v>222</v>
-      </c>
-      <c r="H153" s="10" t="s">
-        <v>223</v>
       </c>
       <c r="I153" s="10"/>
       <c r="J153" s="9">
@@ -10199,13 +10196,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="10" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="O153" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="P153" s="10" t="s">
         <v>364</v>
-      </c>
-      <c r="P153" s="10" t="s">
-        <v>365</v>
       </c>
       <c r="Q153" s="9">
         <v>46295</v>
@@ -10225,7 +10222,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B154" s="5">
         <v>46204.846246076384</v>
@@ -10235,16 +10232,16 @@
         <v>46206.67812013889</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="H154" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="H154" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="I154" s="5">
         <v>46295</v>
@@ -10262,13 +10259,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10278,7 +10275,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="8" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B155" s="9">
         <v>46204.84626494213</v>
@@ -10288,16 +10285,16 @@
         <v>46206.678117118056</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G155" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="H155" s="10" t="s">
         <v>222</v>
-      </c>
-      <c r="H155" s="10" t="s">
-        <v>223</v>
       </c>
       <c r="I155" s="9">
         <v>46295</v>
@@ -10315,13 +10312,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="P155" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="Q155" s="10"/>
       <c r="R155" s="10"/>
@@ -10331,7 +10328,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B156" s="5">
         <v>46204.84627579861</v>
@@ -10341,16 +10338,16 @@
         <v>46206.67810802083</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="H156" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="H156" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="I156" s="5">
         <v>46295</v>
@@ -10368,13 +10365,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -10384,7 +10381,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B157" s="9">
         <v>46204.846348113424</v>
@@ -10394,16 +10391,16 @@
         <v>46206.67810481481</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="H157" s="10" t="s">
         <v>222</v>
-      </c>
-      <c r="H157" s="10" t="s">
-        <v>223</v>
       </c>
       <c r="I157" s="9">
         <v>46295</v>
@@ -10421,13 +10418,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P157" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="Q157" s="10"/>
       <c r="R157" s="10"/>
@@ -10437,7 +10434,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B158" s="5">
         <v>46204.846357789356</v>
@@ -10447,16 +10444,16 @@
         <v>46206.67810172454</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G158" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="H158" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="H158" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="I158" s="5">
         <v>46295</v>
@@ -10474,13 +10471,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -10490,7 +10487,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B159" s="9">
         <v>46204.846365879624</v>
@@ -10500,16 +10497,16 @@
         <v>46206.67809884259</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G159" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="H159" s="10" t="s">
         <v>222</v>
-      </c>
-      <c r="H159" s="10" t="s">
-        <v>223</v>
       </c>
       <c r="I159" s="9">
         <v>46295</v>
@@ -10527,13 +10524,13 @@
         <v>26</v>
       </c>
       <c r="N159" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="O159" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P159" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="Q159" s="10"/>
       <c r="R159" s="10"/>
@@ -10543,7 +10540,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B160" s="5">
         <v>46204.846373692126</v>
@@ -10553,16 +10550,16 @@
         <v>46206.678095509254</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="H160" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="H160" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="I160" s="5">
         <v>46295</v>
@@ -10580,13 +10577,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -10596,7 +10593,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B161" s="9">
         <v>46204.8463796412</v>
@@ -10606,16 +10603,16 @@
         <v>46206.67809255787</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G161" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="H161" s="10" t="s">
         <v>222</v>
-      </c>
-      <c r="H161" s="10" t="s">
-        <v>223</v>
       </c>
       <c r="I161" s="9">
         <v>46295</v>
@@ -10633,13 +10630,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="O161" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P161" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="Q161" s="10"/>
       <c r="R161" s="10"/>
@@ -10649,7 +10646,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B162" s="5">
         <v>46204.846388715276</v>
@@ -10659,16 +10656,16 @@
         <v>46206.678089270834</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="H162" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="H162" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="I162" s="5">
         <v>46295</v>
@@ -10686,13 +10683,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -10702,7 +10699,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B163" s="9">
         <v>46204.84640113426</v>
@@ -10712,16 +10709,16 @@
         <v>46206.67808063657</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F163" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G163" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="H163" s="10" t="s">
         <v>222</v>
-      </c>
-      <c r="H163" s="10" t="s">
-        <v>223</v>
       </c>
       <c r="I163" s="9">
         <v>46295</v>
@@ -10739,13 +10736,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="O163" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P163" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="Q163" s="10"/>
       <c r="R163" s="10"/>
@@ -10755,7 +10752,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B164" s="5">
         <v>46204.84641309028</v>
@@ -10765,16 +10762,16 @@
         <v>46206.67807998843</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G164" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="H164" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="H164" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="I164" s="5">
         <v>46295</v>
@@ -10792,13 +10789,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -10808,7 +10805,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="8" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B165" s="9">
         <v>46204.846406701385</v>
@@ -10818,16 +10815,16 @@
         <v>46206.67807929398</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G165" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="H165" s="10" t="s">
         <v>222</v>
-      </c>
-      <c r="H165" s="10" t="s">
-        <v>223</v>
       </c>
       <c r="I165" s="9">
         <v>46295</v>
@@ -10845,13 +10842,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="O165" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P165" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="Q165" s="10"/>
       <c r="R165" s="10"/>
@@ -10861,7 +10858,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B166" s="5">
         <v>46204.7875055787</v>
@@ -10871,7 +10868,7 @@
         <v>46206.66985314815</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>25</v>
@@ -10895,7 +10892,7 @@
         <v>26</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="P166" s="6" t="s">
         <v>26</v>
@@ -10914,7 +10911,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="8" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B167" s="9">
         <v>46204.787509016205</v>
@@ -10924,16 +10921,16 @@
         <v>46206.67820732639</v>
       </c>
       <c r="E167" s="10" t="s">
+        <v>381</v>
+      </c>
+      <c r="F167" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G167" s="10" t="s">
         <v>382</v>
       </c>
-      <c r="F167" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G167" s="10" t="s">
+      <c r="H167" s="10" t="s">
         <v>383</v>
-      </c>
-      <c r="H167" s="10" t="s">
-        <v>384</v>
       </c>
       <c r="I167" s="9">
         <v>46296</v>
@@ -10951,13 +10948,13 @@
         <v>26</v>
       </c>
       <c r="N167" s="10" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="O167" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="P167" s="10" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="Q167" s="9">
         <v>46304</v>
@@ -10977,7 +10974,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B168" s="5">
         <v>46204.78751333333</v>
@@ -10987,7 +10984,7 @@
         <v>46206.67824334491</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
@@ -11014,13 +11011,13 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="Q168" s="5">
         <v>46304</v>
@@ -11040,7 +11037,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B169" s="9">
         <v>46204.787518564815</v>
@@ -11050,7 +11047,7 @@
         <v>46212.76788890046</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>25</v>
@@ -11074,7 +11071,7 @@
         <v>26</v>
       </c>
       <c r="O169" s="10" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="P169" s="10" t="s">
         <v>26</v>
@@ -11087,7 +11084,7 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B170" s="5">
         <v>46204.78752182871</v>
@@ -11097,7 +11094,7 @@
         <v>46206.67830775463</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
@@ -11124,13 +11121,13 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="P170" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="Q170" s="5">
         <v>46315</v>
@@ -11150,7 +11147,7 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B171" s="9">
         <v>46204.78752627315</v>
@@ -11160,7 +11157,7 @@
         <v>46212.767965266205</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>26</v>
@@ -11187,13 +11184,13 @@
         <v>26</v>
       </c>
       <c r="N171" s="10" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="O171" s="10" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="P171" s="10" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="Q171" s="9">
         <v>46324</v>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1930" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1969" uniqueCount="395">
   <si>
     <t>50001569 - EUROHINCA</t>
   </si>
@@ -358,6 +358,9 @@
   </si>
   <si>
     <t>Reserva produccion</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
   </si>
   <si>
     <t xml:space="preserve">Reserva mono bloque </t>
@@ -3014,7 +3017,7 @@
         <v>46213.50330829861</v>
       </c>
       <c r="D23" s="9">
-        <v>46213.50331935185</v>
+        <v>46223.560216666665</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>78</v>
@@ -3023,9 +3026,11 @@
         <v>25</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H23" s="10"/>
+        <v>79</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>79</v>
+      </c>
       <c r="I23" s="10"/>
       <c r="J23" s="10"/>
       <c r="K23" s="10" t="s">
@@ -3041,7 +3046,7 @@
         <v>26</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P23" s="10" t="s">
         <v>26</v>
@@ -3058,7 +3063,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B24" s="5">
         <v>46204.788881678236</v>
@@ -3067,18 +3072,20 @@
         <v>46213.50328878472</v>
       </c>
       <c r="D24" s="5">
-        <v>46217.187861597224</v>
+        <v>46223.56021195602</v>
       </c>
       <c r="E24" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H24" s="6"/>
+      <c r="H24" s="6" t="s">
+        <v>79</v>
+      </c>
       <c r="I24" s="5">
         <v>46209</v>
       </c>
@@ -3101,7 +3108,7 @@
         <v>38</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q24" s="5">
         <v>46216</v>
@@ -3121,7 +3128,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B25" s="9">
         <v>46204.786945914355</v>
@@ -3131,7 +3138,7 @@
         <v>46209.79230103009</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>25</v>
@@ -3155,10 +3162,10 @@
         <v>26</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -3168,7 +3175,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B26" s="5">
         <v>46204.78715721065</v>
@@ -3180,7 +3187,7 @@
         <v>46213.19381935185</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
@@ -3207,13 +3214,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>72</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q26" s="5">
         <v>46212</v>
@@ -3233,7 +3240,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B27" s="9">
         <v>46204.78716710648</v>
@@ -3245,7 +3252,7 @@
         <v>46214.18292518519</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
@@ -3272,13 +3279,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>44</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q27" s="9">
         <v>46213</v>
@@ -3293,30 +3300,32 @@
         <v>33</v>
       </c>
       <c r="U27" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B28" s="5">
         <v>46204.787177743056</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46206.76986597222</v>
+        <v>46223.56031828704</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H28" s="6"/>
+        <v>79</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>79</v>
+      </c>
       <c r="I28" s="5">
         <v>46241</v>
       </c>
@@ -3333,13 +3342,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q28" s="5">
         <v>46244</v>
@@ -3354,30 +3363,32 @@
         <v>53</v>
       </c>
       <c r="U28" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B29" s="9">
         <v>46204.79158200232</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46206.67314619213</v>
+        <v>46223.560317627314</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H29" s="10"/>
+        <v>79</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>79</v>
+      </c>
       <c r="I29" s="9">
         <v>46241</v>
       </c>
@@ -3394,13 +3405,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q29" s="9">
         <v>46244</v>
@@ -3420,25 +3431,27 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B30" s="5">
         <v>46204.79163886574</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46206.673139039354</v>
+        <v>46223.56031693287</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H30" s="6"/>
+        <v>79</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>79</v>
+      </c>
       <c r="I30" s="5">
         <v>46241</v>
       </c>
@@ -3455,13 +3468,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q30" s="5">
         <v>46244</v>
@@ -3481,25 +3494,27 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B31" s="9">
         <v>46204.7917447338</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46206.67313840278</v>
+        <v>46223.56031626157</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H31" s="10"/>
+        <v>79</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>79</v>
+      </c>
       <c r="I31" s="9">
         <v>46241</v>
       </c>
@@ -3516,13 +3531,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q31" s="9">
         <v>46244</v>
@@ -3542,7 +3557,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B32" s="5">
         <v>46204.78695173611</v>
@@ -3552,7 +3567,7 @@
         <v>46206.65562592592</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>25</v>
@@ -3576,7 +3591,7 @@
         <v>26</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3589,7 +3604,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B33" s="9">
         <v>46204.78719643518</v>
@@ -3599,16 +3614,16 @@
         <v>46206.67332864583</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I33" s="9">
         <v>46216</v>
@@ -3626,13 +3641,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q33" s="9">
         <v>46273</v>
@@ -3652,7 +3667,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B34" s="5">
         <v>46204.7872006713</v>
@@ -3662,16 +3677,16 @@
         <v>46209.792300393514</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I34" s="5">
         <v>46216</v>
@@ -3689,13 +3704,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3711,7 +3726,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B35" s="9">
         <v>46204.787204837965</v>
@@ -3721,16 +3736,16 @@
         <v>46206.67327987269</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I35" s="9">
         <v>46225</v>
@@ -3748,13 +3763,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3770,7 +3785,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B36" s="5">
         <v>46204.78722327546</v>
@@ -3782,16 +3797,16 @@
         <v>46217.69515425926</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I36" s="5">
         <v>46213</v>
@@ -3809,10 +3824,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3835,7 +3850,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B37" s="9">
         <v>46204.78722760417</v>
@@ -3847,16 +3862,16 @@
         <v>46206.769946203705</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I37" s="9">
         <v>46213</v>
@@ -3874,13 +3889,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3890,7 +3905,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B38" s="5">
         <v>46204.787231689814</v>
@@ -3902,16 +3917,16 @@
         <v>46217.69452489584</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I38" s="5">
         <v>46224</v>
@@ -3929,13 +3944,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3945,7 +3960,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B39" s="9">
         <v>46204.78728243055</v>
@@ -3957,16 +3972,16 @@
         <v>46206.769995821756</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I39" s="9">
         <v>46224</v>
@@ -3984,13 +3999,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -4000,7 +4015,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B40" s="5">
         <v>46204.78728729166</v>
@@ -4010,16 +4025,16 @@
         <v>46206.67363866898</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I40" s="5">
         <v>46245</v>
@@ -4037,13 +4052,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q40" s="5">
         <v>46255</v>
@@ -4063,7 +4078,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B41" s="9">
         <v>46204.787292175926</v>
@@ -4073,16 +4088,16 @@
         <v>46206.67358165509</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I41" s="9">
         <v>46245</v>
@@ -4100,13 +4115,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4122,7 +4137,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B42" s="5">
         <v>46204.78730063657</v>
@@ -4132,16 +4147,16 @@
         <v>46206.673579016206</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I42" s="5">
         <v>46247</v>
@@ -4159,13 +4174,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4181,7 +4196,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B43" s="9">
         <v>46204.793668136575</v>
@@ -4191,16 +4206,16 @@
         <v>46209.87015284722</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I43" s="9">
         <v>46245</v>
@@ -4218,10 +4233,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4244,7 +4259,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B44" s="5">
         <v>46204.794818298615</v>
@@ -4254,16 +4269,16 @@
         <v>46206.673746319444</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I44" s="5">
         <v>46245</v>
@@ -4281,13 +4296,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4297,7 +4312,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B45" s="9">
         <v>46204.794902430556</v>
@@ -4307,16 +4322,16 @@
         <v>46206.673743865744</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I45" s="9">
         <v>46247</v>
@@ -4334,13 +4349,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4350,7 +4365,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B46" s="5">
         <v>46204.7938509375</v>
@@ -4360,16 +4375,16 @@
         <v>46206.67393748843</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I46" s="5">
         <v>46245</v>
@@ -4387,10 +4402,10 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4413,7 +4428,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B47" s="9">
         <v>46204.795001412036</v>
@@ -4423,16 +4438,16 @@
         <v>46206.673880648144</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I47" s="9">
         <v>46245</v>
@@ -4450,13 +4465,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
@@ -4466,7 +4481,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B48" s="5">
         <v>46204.795060543984</v>
@@ -4476,16 +4491,16 @@
         <v>46206.67387746528</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I48" s="5">
         <v>46247</v>
@@ -4503,13 +4518,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4519,7 +4534,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B49" s="9">
         <v>46204.7939687037</v>
@@ -4529,16 +4544,16 @@
         <v>46206.67465699074</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I49" s="9">
         <v>46241</v>
@@ -4556,10 +4571,10 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4582,7 +4597,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B50" s="5">
         <v>46204.795132997686</v>
@@ -4592,16 +4607,16 @@
         <v>46206.67409482639</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4619,13 +4634,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4635,7 +4650,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B51" s="9">
         <v>46204.795219293985</v>
@@ -4645,16 +4660,16 @@
         <v>46206.67409221065</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I51" s="9">
         <v>46246</v>
@@ -4672,13 +4687,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4688,7 +4703,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B52" s="5">
         <v>46206.65895994213</v>
@@ -4698,16 +4713,16 @@
         <v>46206.674336111115</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4723,10 +4738,10 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>26</v>
@@ -4739,7 +4754,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B53" s="9">
         <v>46204.787306770835</v>
@@ -4749,7 +4764,7 @@
         <v>46217.8575847801</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>25</v>
@@ -4773,7 +4788,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>26</v>
@@ -4786,7 +4801,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B54" s="5">
         <v>46204.78731047454</v>
@@ -4798,16 +4813,16 @@
         <v>46219.20085231481</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I54" s="5">
         <v>46212</v>
@@ -4825,13 +4840,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>75</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q54" s="5">
         <v>46218</v>
@@ -4851,7 +4866,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B55" s="9">
         <v>46204.78731518518</v>
@@ -4863,16 +4878,16 @@
         <v>46217.85759137732</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I55" s="9">
         <v>46233</v>
@@ -4890,13 +4905,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q55" s="9">
         <v>46239</v>
@@ -4916,7 +4931,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B56" s="5">
         <v>46204.78732028935</v>
@@ -4926,16 +4941,16 @@
         <v>46217.857591875</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I56" s="5">
         <v>46240</v>
@@ -4953,13 +4968,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q56" s="5">
         <v>46240</v>
@@ -4974,12 +4989,12 @@
         <v>53</v>
       </c>
       <c r="U56" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B57" s="9">
         <v>46204.787326770835</v>
@@ -4989,16 +5004,16 @@
         <v>46206.67498217593</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I57" s="9">
         <v>46288</v>
@@ -5016,13 +5031,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q57" s="9">
         <v>46288</v>
@@ -5042,7 +5057,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B58" s="5">
         <v>46205.8929956713</v>
@@ -5052,16 +5067,16 @@
         <v>46206.67494384259</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I58" s="5">
         <v>46288</v>
@@ -5079,13 +5094,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5095,7 +5110,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B59" s="9">
         <v>46205.89308850694</v>
@@ -5105,16 +5120,16 @@
         <v>46206.67494135417</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I59" s="9">
         <v>46288</v>
@@ -5132,13 +5147,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5148,7 +5163,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B60" s="5">
         <v>46205.89321678241</v>
@@ -5158,16 +5173,16 @@
         <v>46206.67493778935</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I60" s="5">
         <v>46288</v>
@@ -5185,13 +5200,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5201,7 +5216,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B61" s="9">
         <v>46204.787330555555</v>
@@ -5211,7 +5226,7 @@
         <v>46206.65997969908</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>25</v>
@@ -5235,7 +5250,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5248,7 +5263,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B62" s="5">
         <v>46204.78733380787</v>
@@ -5258,16 +5273,16 @@
         <v>46206.67512555556</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I62" s="5">
         <v>46258</v>
@@ -5285,13 +5300,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q62" s="5">
         <v>46259</v>
@@ -5311,7 +5326,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B63" s="9">
         <v>46204.78733813658</v>
@@ -5321,16 +5336,16 @@
         <v>46206.67526587963</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I63" s="9">
         <v>46260</v>
@@ -5348,13 +5363,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q63" s="9">
         <v>46261</v>
@@ -5374,7 +5389,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B64" s="5">
         <v>46204.79962430555</v>
@@ -5384,16 +5399,16 @@
         <v>46206.67512305555</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I64" s="5">
         <v>46258</v>
@@ -5411,13 +5426,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q64" s="5">
         <v>46259</v>
@@ -5437,7 +5452,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B65" s="9">
         <v>46204.79970230324</v>
@@ -5447,16 +5462,16 @@
         <v>46206.67526299768</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I65" s="9">
         <v>46260</v>
@@ -5474,13 +5489,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q65" s="9">
         <v>46261</v>
@@ -5500,7 +5515,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B66" s="5">
         <v>46204.799834722224</v>
@@ -5510,16 +5525,16 @@
         <v>46206.67512025463</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I66" s="5">
         <v>46258</v>
@@ -5537,13 +5552,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q66" s="5">
         <v>46259</v>
@@ -5563,7 +5578,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B67" s="9">
         <v>46204.80007783565</v>
@@ -5573,16 +5588,16 @@
         <v>46206.67526012732</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I67" s="9">
         <v>46260</v>
@@ -5600,13 +5615,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q67" s="9">
         <v>46261</v>
@@ -5626,7 +5641,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B68" s="5">
         <v>46204.787342662035</v>
@@ -5636,7 +5651,7 @@
         <v>46206.66163074074</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5660,7 +5675,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5673,7 +5688,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B69" s="9">
         <v>46204.78734565972</v>
@@ -5683,16 +5698,16 @@
         <v>46206.67535149306</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I69" s="9">
         <v>46262</v>
@@ -5710,13 +5725,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q69" s="9">
         <v>46266</v>
@@ -5736,7 +5751,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B70" s="5">
         <v>46204.78735021991</v>
@@ -5746,16 +5761,16 @@
         <v>46206.67558131945</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I70" s="5">
         <v>46267</v>
@@ -5773,13 +5788,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q70" s="5">
         <v>46273</v>
@@ -5799,7 +5814,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B71" s="9">
         <v>46204.83329071759</v>
@@ -5809,16 +5824,16 @@
         <v>46206.67551582176</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I71" s="9">
         <v>46267</v>
@@ -5836,13 +5851,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5852,7 +5867,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B72" s="5">
         <v>46204.83348987269</v>
@@ -5862,16 +5877,16 @@
         <v>46206.67551341435</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I72" s="5">
         <v>46267</v>
@@ -5889,13 +5904,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5905,7 +5920,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B73" s="9">
         <v>46204.83350201389</v>
@@ -5915,16 +5930,16 @@
         <v>46206.67551030093</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I73" s="9">
         <v>46267</v>
@@ -5942,13 +5957,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -5958,7 +5973,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B74" s="5">
         <v>46204.787355625</v>
@@ -5968,16 +5983,16 @@
         <v>46206.67580866898</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I74" s="5">
         <v>46274</v>
@@ -5995,13 +6010,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q74" s="5">
         <v>46274</v>
@@ -6021,7 +6036,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B75" s="9">
         <v>46204.83355802084</v>
@@ -6031,16 +6046,16 @@
         <v>46206.67575559027</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I75" s="10"/>
       <c r="J75" s="9">
@@ -6056,13 +6071,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6072,7 +6087,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B76" s="5">
         <v>46204.833570069444</v>
@@ -6082,16 +6097,16 @@
         <v>46206.67575268519</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I76" s="6"/>
       <c r="J76" s="5">
@@ -6107,13 +6122,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6123,7 +6138,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B77" s="9">
         <v>46204.833579004626</v>
@@ -6133,16 +6148,16 @@
         <v>46206.67574885416</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I77" s="10"/>
       <c r="J77" s="9">
@@ -6158,13 +6173,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6174,7 +6189,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B78" s="5">
         <v>46204.78736071759</v>
@@ -6184,7 +6199,7 @@
         <v>46206.67094998843</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>25</v>
@@ -6208,7 +6223,7 @@
         <v>26</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6221,7 +6236,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B79" s="9">
         <v>46204.78736410879</v>
@@ -6231,16 +6246,16 @@
         <v>46213.50330894676</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I79" s="9">
         <v>46210</v>
@@ -6258,13 +6273,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q79" s="9">
         <v>46210</v>
@@ -6279,12 +6294,12 @@
         <v>33</v>
       </c>
       <c r="U79" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B80" s="5">
         <v>46204.78737366898</v>
@@ -6294,16 +6309,16 @@
         <v>46217.69454351852</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I80" s="5">
         <v>46253</v>
@@ -6321,13 +6336,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q80" s="5">
         <v>46253</v>
@@ -6342,12 +6357,12 @@
         <v>53</v>
       </c>
       <c r="U80" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B81" s="9">
         <v>46204.78737825232</v>
@@ -6357,16 +6372,16 @@
         <v>46206.67600082176</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I81" s="9">
         <v>46274</v>
@@ -6384,13 +6399,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q81" s="9">
         <v>46274</v>
@@ -6410,7 +6425,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B82" s="5">
         <v>46206.567318657406</v>
@@ -6426,10 +6441,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I82" s="6"/>
       <c r="J82" s="5">
@@ -6445,13 +6460,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6461,7 +6476,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B83" s="9">
         <v>46206.56766555556</v>
@@ -6477,10 +6492,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I83" s="10"/>
       <c r="J83" s="9">
@@ -6496,13 +6511,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6512,7 +6527,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B84" s="5">
         <v>46206.56768260417</v>
@@ -6528,10 +6543,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I84" s="6"/>
       <c r="J84" s="5">
@@ -6547,13 +6562,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6563,7 +6578,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B85" s="9">
         <v>46206.56769806713</v>
@@ -6579,10 +6594,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I85" s="10"/>
       <c r="J85" s="9">
@@ -6598,13 +6613,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6614,7 +6629,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B86" s="5">
         <v>46206.56771423611</v>
@@ -6630,10 +6645,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I86" s="6"/>
       <c r="J86" s="5">
@@ -6649,13 +6664,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6665,7 +6680,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B87" s="9">
         <v>46206.56772880787</v>
@@ -6681,10 +6696,10 @@
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I87" s="10"/>
       <c r="J87" s="9">
@@ -6700,13 +6715,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6716,7 +6731,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B88" s="5">
         <v>46206.567743506945</v>
@@ -6732,10 +6747,10 @@
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I88" s="6"/>
       <c r="J88" s="5">
@@ -6751,13 +6766,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6767,7 +6782,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B89" s="9">
         <v>46206.56775844908</v>
@@ -6783,10 +6798,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I89" s="10"/>
       <c r="J89" s="9">
@@ -6802,13 +6817,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6818,7 +6833,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B90" s="5">
         <v>46206.56777289352</v>
@@ -6834,10 +6849,10 @@
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I90" s="6"/>
       <c r="J90" s="5">
@@ -6853,13 +6868,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6869,7 +6884,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B91" s="9">
         <v>46206.67094809028</v>
@@ -6879,16 +6894,16 @@
         <v>46206.67590806713</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I91" s="9">
         <v>46274</v>
@@ -6906,10 +6921,10 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P91" s="10" t="s">
         <v>26</v>
@@ -6926,7 +6941,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B92" s="5">
         <v>46204.78738409722</v>
@@ -6936,7 +6951,7 @@
         <v>46206.66745490741</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>25</v>
@@ -6960,7 +6975,7 @@
         <v>26</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>26</v>
@@ -6973,25 +6988,27 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B93" s="9">
         <v>46204.787387268516</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46206.676306875</v>
+        <v>46223.56188282407</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H93" s="10"/>
+        <v>79</v>
+      </c>
+      <c r="H93" s="10" t="s">
+        <v>79</v>
+      </c>
       <c r="I93" s="9">
         <v>46275</v>
       </c>
@@ -7008,13 +7025,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q93" s="9">
         <v>46281</v>
@@ -7034,25 +7051,27 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B94" s="5">
         <v>46204.84491833333</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46206.676259513886</v>
+        <v>46223.56049512731</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H94" s="6"/>
+        <v>79</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>79</v>
+      </c>
       <c r="I94" s="5">
         <v>46275</v>
       </c>
@@ -7069,13 +7088,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7085,25 +7104,27 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B95" s="9">
         <v>46204.84493530093</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46206.67625695602</v>
+        <v>46223.56049449074</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H95" s="10"/>
+        <v>79</v>
+      </c>
+      <c r="H95" s="10" t="s">
+        <v>79</v>
+      </c>
       <c r="I95" s="9">
         <v>46275</v>
       </c>
@@ -7120,13 +7141,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7136,25 +7157,27 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B96" s="5">
         <v>46204.84494427084</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46206.67625305556</v>
+        <v>46223.56049383101</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H96" s="6"/>
+        <v>79</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>79</v>
+      </c>
       <c r="I96" s="5">
         <v>46275</v>
       </c>
@@ -7171,13 +7194,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7187,25 +7210,27 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B97" s="9">
         <v>46204.78739225694</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46206.67641435185</v>
+        <v>46223.56188216435</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H97" s="10"/>
+        <v>79</v>
+      </c>
+      <c r="H97" s="10" t="s">
+        <v>79</v>
+      </c>
       <c r="I97" s="9">
         <v>46282</v>
       </c>
@@ -7222,13 +7247,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q97" s="9">
         <v>46282</v>
@@ -7248,25 +7273,27 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B98" s="5">
         <v>46204.84497997686</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46206.67651039352</v>
+        <v>46223.560602199075</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H98" s="6"/>
+        <v>79</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>79</v>
+      </c>
       <c r="I98" s="5">
         <v>46282</v>
       </c>
@@ -7283,13 +7310,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7299,25 +7326,27 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B99" s="9">
         <v>46204.84498876157</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46206.67650773148</v>
+        <v>46223.56060143519</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H99" s="10"/>
+        <v>79</v>
+      </c>
+      <c r="H99" s="10" t="s">
+        <v>79</v>
+      </c>
       <c r="I99" s="9">
         <v>46282</v>
       </c>
@@ -7334,13 +7363,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7350,25 +7379,27 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B100" s="5">
         <v>46204.84499563657</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46206.67650460648</v>
+        <v>46223.560600763885</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H100" s="6"/>
+        <v>79</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>79</v>
+      </c>
       <c r="I100" s="5">
         <v>46282</v>
       </c>
@@ -7385,13 +7416,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7401,25 +7432,27 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B101" s="9">
         <v>46204.78740502315</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46206.676410960645</v>
+        <v>46223.56188153935</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H101" s="10"/>
+        <v>79</v>
+      </c>
+      <c r="H101" s="10" t="s">
+        <v>79</v>
+      </c>
       <c r="I101" s="9">
         <v>46286</v>
       </c>
@@ -7436,13 +7469,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q101" s="9">
         <v>46286</v>
@@ -7462,25 +7495,27 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B102" s="5">
         <v>46204.84507945602</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46206.67662570602</v>
+        <v>46223.5607075</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H102" s="6"/>
+        <v>79</v>
+      </c>
+      <c r="H102" s="6" t="s">
+        <v>79</v>
+      </c>
       <c r="I102" s="5">
         <v>46286</v>
       </c>
@@ -7497,13 +7532,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7513,25 +7548,27 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B103" s="9">
         <v>46204.84508817129</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46206.676623368054</v>
+        <v>46223.560706840275</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H103" s="10"/>
+        <v>79</v>
+      </c>
+      <c r="H103" s="10" t="s">
+        <v>79</v>
+      </c>
       <c r="I103" s="9">
         <v>46286</v>
       </c>
@@ -7548,13 +7585,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7564,25 +7601,27 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B104" s="5">
         <v>46204.845093854165</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46206.676619756945</v>
+        <v>46223.56070621528</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H104" s="6"/>
+        <v>79</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>79</v>
+      </c>
       <c r="I104" s="5">
         <v>46286</v>
       </c>
@@ -7599,13 +7638,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7615,25 +7654,27 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B105" s="9">
         <v>46204.78741121528</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46206.67640778935</v>
+        <v>46223.561880925925</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H105" s="10"/>
+        <v>79</v>
+      </c>
+      <c r="H105" s="10" t="s">
+        <v>79</v>
+      </c>
       <c r="I105" s="9">
         <v>46287</v>
       </c>
@@ -7650,13 +7691,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q105" s="9">
         <v>46287</v>
@@ -7676,25 +7717,27 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B106" s="5">
         <v>46204.84513122685</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46206.67673481481</v>
+        <v>46223.56167888889</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H106" s="6"/>
+        <v>79</v>
+      </c>
+      <c r="H106" s="6" t="s">
+        <v>79</v>
+      </c>
       <c r="I106" s="5">
         <v>46287</v>
       </c>
@@ -7711,13 +7754,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7727,25 +7770,27 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B107" s="9">
         <v>46204.84513944444</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46206.67673186342</v>
+        <v>46223.561678287035</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H107" s="10"/>
+        <v>79</v>
+      </c>
+      <c r="H107" s="10" t="s">
+        <v>79</v>
+      </c>
       <c r="I107" s="9">
         <v>46287</v>
       </c>
@@ -7762,13 +7807,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7778,25 +7823,27 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B108" s="5">
         <v>46204.8451466088</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46206.67672797454</v>
+        <v>46223.56167766204</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H108" s="6"/>
+        <v>79</v>
+      </c>
+      <c r="H108" s="6" t="s">
+        <v>79</v>
+      </c>
       <c r="I108" s="5">
         <v>46287</v>
       </c>
@@ -7813,13 +7860,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7829,25 +7876,27 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B109" s="9">
         <v>46204.787473310185</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46206.676404432874</v>
+        <v>46223.56188028935</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H109" s="10"/>
+        <v>79</v>
+      </c>
+      <c r="H109" s="10" t="s">
+        <v>79</v>
+      </c>
       <c r="I109" s="9">
         <v>46289</v>
       </c>
@@ -7864,13 +7913,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q109" s="9">
         <v>46289</v>
@@ -7890,25 +7939,27 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B110" s="5">
         <v>46204.84518325231</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46206.676860590276</v>
+        <v>46223.56179313657</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H110" s="6"/>
+        <v>79</v>
+      </c>
+      <c r="H110" s="6" t="s">
+        <v>79</v>
+      </c>
       <c r="I110" s="5">
         <v>46289</v>
       </c>
@@ -7925,13 +7976,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -7941,25 +7992,27 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B111" s="9">
         <v>46204.845191898145</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46206.676858067134</v>
+        <v>46223.56179228009</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H111" s="10"/>
+        <v>79</v>
+      </c>
+      <c r="H111" s="10" t="s">
+        <v>79</v>
+      </c>
       <c r="I111" s="9">
         <v>46289</v>
       </c>
@@ -7976,13 +8029,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -7992,25 +8045,27 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B112" s="5">
         <v>46204.84520083333</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46206.676854363424</v>
+        <v>46223.56179165509</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H112" s="6"/>
+        <v>79</v>
+      </c>
+      <c r="H112" s="6" t="s">
+        <v>79</v>
+      </c>
       <c r="I112" s="5">
         <v>46289</v>
       </c>
@@ -8027,13 +8082,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8043,7 +8098,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B113" s="9">
         <v>46204.78748032407</v>
@@ -8053,7 +8108,7 @@
         <v>46206.668344247686</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>25</v>
@@ -8077,7 +8132,7 @@
         <v>26</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>
@@ -8090,7 +8145,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B114" s="5">
         <v>46204.787484155095</v>
@@ -8100,16 +8155,16 @@
         <v>46206.677181631945</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I114" s="5">
         <v>46290</v>
@@ -8127,13 +8182,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q114" s="5">
         <v>46290</v>
@@ -8153,7 +8208,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B115" s="9">
         <v>46206.61281571759</v>
@@ -8163,16 +8218,16 @@
         <v>46206.67717564815</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I115" s="9">
         <v>46290</v>
@@ -8190,13 +8245,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8206,7 +8261,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B116" s="5">
         <v>46206.612829722224</v>
@@ -8216,16 +8271,16 @@
         <v>46206.67717299769</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I116" s="5">
         <v>46290</v>
@@ -8243,13 +8298,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8259,7 +8314,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B117" s="9">
         <v>46206.61284180556</v>
@@ -8269,16 +8324,16 @@
         <v>46206.67717023148</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I117" s="9">
         <v>46290</v>
@@ -8296,13 +8351,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8312,7 +8367,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B118" s="5">
         <v>46206.61323981482</v>
@@ -8328,10 +8383,10 @@
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I118" s="5">
         <v>46290</v>
@@ -8349,13 +8404,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8365,7 +8420,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B119" s="9">
         <v>46206.613256446755</v>
@@ -8381,10 +8436,10 @@
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I119" s="9">
         <v>46290</v>
@@ -8402,13 +8457,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O119" s="10" t="s">
         <v>59</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8418,7 +8473,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B120" s="5">
         <v>46206.61328513889</v>
@@ -8434,10 +8489,10 @@
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I120" s="5">
         <v>46290</v>
@@ -8455,13 +8510,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8471,7 +8526,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B121" s="9">
         <v>46206.613270925925</v>
@@ -8487,10 +8542,10 @@
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I121" s="9">
         <v>46290</v>
@@ -8508,13 +8563,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O121" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8524,7 +8579,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B122" s="5">
         <v>46206.6133403125</v>
@@ -8540,10 +8595,10 @@
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I122" s="5">
         <v>46290</v>
@@ -8561,13 +8616,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8577,7 +8632,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B123" s="9">
         <v>46206.613361041665</v>
@@ -8593,10 +8648,10 @@
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I123" s="9">
         <v>46290</v>
@@ -8614,13 +8669,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O123" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8630,7 +8685,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B124" s="5">
         <v>46206.613371493055</v>
@@ -8646,10 +8701,10 @@
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I124" s="5">
         <v>46290</v>
@@ -8667,13 +8722,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8683,7 +8738,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B125" s="9">
         <v>46206.61338284722</v>
@@ -8699,10 +8754,10 @@
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I125" s="9">
         <v>46290</v>
@@ -8720,13 +8775,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O125" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -8736,7 +8791,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B126" s="5">
         <v>46206.61339653935</v>
@@ -8752,10 +8807,10 @@
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I126" s="5">
         <v>46290</v>
@@ -8773,13 +8828,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8789,25 +8844,27 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B127" s="9">
         <v>46204.78748974537</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46209.580981481486</v>
+        <v>46223.56209584491</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H127" s="10"/>
+        <v>79</v>
+      </c>
+      <c r="H127" s="10" t="s">
+        <v>79</v>
+      </c>
       <c r="I127" s="9">
         <v>46293</v>
       </c>
@@ -8818,19 +8875,19 @@
         <v>26</v>
       </c>
       <c r="L127" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q127" s="9">
         <v>46293</v>
@@ -8850,25 +8907,27 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B128" s="5">
         <v>46204.84566665509</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46206.6774368287</v>
+        <v>46223.562056400464</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H128" s="6"/>
+        <v>79</v>
+      </c>
+      <c r="H128" s="6" t="s">
+        <v>79</v>
+      </c>
       <c r="I128" s="5">
         <v>46293</v>
       </c>
@@ -8885,13 +8944,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -8901,25 +8960,27 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B129" s="9">
         <v>46204.8456746875</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46206.67743376158</v>
+        <v>46223.56205577546</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H129" s="10"/>
+        <v>79</v>
+      </c>
+      <c r="H129" s="10" t="s">
+        <v>79</v>
+      </c>
       <c r="I129" s="9">
         <v>46293</v>
       </c>
@@ -8936,13 +8997,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -8952,25 +9013,27 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B130" s="5">
         <v>46204.84568395834</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46206.67743099537</v>
+        <v>46223.56205517361</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H130" s="6"/>
+        <v>79</v>
+      </c>
+      <c r="H130" s="6" t="s">
+        <v>79</v>
+      </c>
       <c r="I130" s="5">
         <v>46293</v>
       </c>
@@ -8987,13 +9050,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9003,25 +9066,27 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B131" s="9">
         <v>46204.84577770834</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46206.67742784722</v>
+        <v>46223.562054548616</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H131" s="10"/>
+        <v>79</v>
+      </c>
+      <c r="H131" s="10" t="s">
+        <v>79</v>
+      </c>
       <c r="I131" s="9">
         <v>46293</v>
       </c>
@@ -9038,13 +9103,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O131" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9054,25 +9119,27 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B132" s="5">
         <v>46204.845803958335</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46206.677424988426</v>
+        <v>46223.56205386574</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H132" s="6"/>
+        <v>79</v>
+      </c>
+      <c r="H132" s="6" t="s">
+        <v>79</v>
+      </c>
       <c r="I132" s="5">
         <v>46293</v>
       </c>
@@ -9089,13 +9156,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O132" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9105,25 +9172,27 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B133" s="9">
         <v>46204.8458116088</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46206.67742180555</v>
+        <v>46223.562053217596</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H133" s="10"/>
+        <v>79</v>
+      </c>
+      <c r="H133" s="10" t="s">
+        <v>79</v>
+      </c>
       <c r="I133" s="9">
         <v>46293</v>
       </c>
@@ -9140,13 +9209,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O133" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9156,25 +9225,27 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B134" s="5">
         <v>46204.84582686343</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46206.677418680556</v>
+        <v>46223.56205256944</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H134" s="6"/>
+        <v>79</v>
+      </c>
+      <c r="H134" s="6" t="s">
+        <v>79</v>
+      </c>
       <c r="I134" s="5">
         <v>46293</v>
       </c>
@@ -9191,13 +9262,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9207,25 +9278,27 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B135" s="9">
         <v>46204.84581974537</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46206.67741584491</v>
+        <v>46223.56205195602</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H135" s="10"/>
+        <v>79</v>
+      </c>
+      <c r="H135" s="10" t="s">
+        <v>79</v>
+      </c>
       <c r="I135" s="9">
         <v>46293</v>
       </c>
@@ -9242,13 +9315,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O135" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9258,25 +9331,27 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B136" s="5">
         <v>46204.84583605324</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46206.67741314815</v>
+        <v>46223.562051354165</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H136" s="6"/>
+        <v>79</v>
+      </c>
+      <c r="H136" s="6" t="s">
+        <v>79</v>
+      </c>
       <c r="I136" s="5">
         <v>46293</v>
       </c>
@@ -9293,13 +9368,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O136" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9309,25 +9384,27 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B137" s="9">
         <v>46204.84584422453</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46206.67740501158</v>
+        <v>46223.562050740744</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H137" s="10"/>
+        <v>79</v>
+      </c>
+      <c r="H137" s="10" t="s">
+        <v>79</v>
+      </c>
       <c r="I137" s="9">
         <v>46293</v>
       </c>
@@ -9344,13 +9421,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O137" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9360,25 +9437,27 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B138" s="5">
         <v>46204.845850983795</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46206.67740435185</v>
+        <v>46223.562050092594</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H138" s="6"/>
+        <v>79</v>
+      </c>
+      <c r="H138" s="6" t="s">
+        <v>79</v>
+      </c>
       <c r="I138" s="5">
         <v>46293</v>
       </c>
@@ -9395,13 +9474,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O138" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9411,25 +9490,27 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B139" s="9">
         <v>46204.84585899305</v>
       </c>
       <c r="C139" s="10"/>
       <c r="D139" s="9">
-        <v>46206.67740371528</v>
+        <v>46223.5620494676</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H139" s="10"/>
+        <v>79</v>
+      </c>
+      <c r="H139" s="10" t="s">
+        <v>79</v>
+      </c>
       <c r="I139" s="9">
         <v>46293</v>
       </c>
@@ -9446,13 +9527,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O139" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q139" s="10"/>
       <c r="R139" s="10"/>
@@ -9462,7 +9543,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B140" s="5">
         <v>46204.78749533565</v>
@@ -9472,16 +9553,16 @@
         <v>46206.67787028935</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I140" s="5">
         <v>46294</v>
@@ -9499,13 +9580,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q140" s="5">
         <v>46294</v>
@@ -9525,7 +9606,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B141" s="9">
         <v>46204.84595449074</v>
@@ -9535,16 +9616,16 @@
         <v>46206.67786329861</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H141" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I141" s="9">
         <v>46294</v>
@@ -9562,13 +9643,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P141" s="10" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q141" s="10"/>
       <c r="R141" s="10"/>
@@ -9578,7 +9659,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B142" s="5">
         <v>46204.845964189815</v>
@@ -9588,16 +9669,16 @@
         <v>46206.677860254626</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I142" s="5">
         <v>46294</v>
@@ -9615,13 +9696,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9631,7 +9712,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B143" s="9">
         <v>46204.84597238426</v>
@@ -9641,16 +9722,16 @@
         <v>46206.67785763889</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H143" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I143" s="9">
         <v>46294</v>
@@ -9668,13 +9749,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q143" s="10"/>
       <c r="R143" s="10"/>
@@ -9684,7 +9765,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B144" s="5">
         <v>46204.846036469906</v>
@@ -9694,16 +9775,16 @@
         <v>46206.67785519676</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I144" s="5">
         <v>46294</v>
@@ -9721,13 +9802,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -9737,7 +9818,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B145" s="9">
         <v>46204.846047893516</v>
@@ -9747,16 +9828,16 @@
         <v>46206.6778525</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H145" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I145" s="9">
         <v>46294</v>
@@ -9774,13 +9855,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -9790,7 +9871,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B146" s="5">
         <v>46204.846056724535</v>
@@ -9800,16 +9881,16 @@
         <v>46206.67784956019</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I146" s="5">
         <v>46294</v>
@@ -9827,13 +9908,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -9843,7 +9924,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B147" s="9">
         <v>46204.846065578706</v>
@@ -9853,16 +9934,16 @@
         <v>46206.677846921295</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H147" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I147" s="9">
         <v>46294</v>
@@ -9880,13 +9961,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O147" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q147" s="10"/>
       <c r="R147" s="10"/>
@@ -9896,7 +9977,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B148" s="5">
         <v>46204.846073252316</v>
@@ -9906,16 +9987,16 @@
         <v>46206.67784445602</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I148" s="5">
         <v>46294</v>
@@ -9933,13 +10014,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -9949,7 +10030,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B149" s="9">
         <v>46204.84608019676</v>
@@ -9959,16 +10040,16 @@
         <v>46206.6778419676</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H149" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I149" s="9">
         <v>46294</v>
@@ -9986,13 +10067,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q149" s="10"/>
       <c r="R149" s="10"/>
@@ -10002,7 +10083,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B150" s="5">
         <v>46204.84608666667</v>
@@ -10012,16 +10093,16 @@
         <v>46206.67783399306</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I150" s="5">
         <v>46294</v>
@@ -10039,13 +10120,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10055,7 +10136,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B151" s="9">
         <v>46204.84609472222</v>
@@ -10065,16 +10146,16 @@
         <v>46206.677833344904</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G151" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H151" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I151" s="9">
         <v>46294</v>
@@ -10092,13 +10173,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P151" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q151" s="10"/>
       <c r="R151" s="10"/>
@@ -10108,7 +10189,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B152" s="5">
         <v>46204.84610289352</v>
@@ -10118,16 +10199,16 @@
         <v>46206.67783269676</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I152" s="5">
         <v>46294</v>
@@ -10145,13 +10226,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10161,7 +10242,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="8" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B153" s="9">
         <v>46204.78749967593</v>
@@ -10171,16 +10252,16 @@
         <v>46206.67812460648</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G153" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H153" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I153" s="10"/>
       <c r="J153" s="9">
@@ -10196,13 +10277,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O153" s="10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P153" s="10" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q153" s="9">
         <v>46295</v>
@@ -10222,7 +10303,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B154" s="5">
         <v>46204.846246076384</v>
@@ -10232,16 +10313,16 @@
         <v>46206.67812013889</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I154" s="5">
         <v>46295</v>
@@ -10259,13 +10340,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10275,7 +10356,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="8" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B155" s="9">
         <v>46204.84626494213</v>
@@ -10285,16 +10366,16 @@
         <v>46206.678117118056</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G155" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H155" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I155" s="9">
         <v>46295</v>
@@ -10312,13 +10393,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P155" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q155" s="10"/>
       <c r="R155" s="10"/>
@@ -10328,7 +10409,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B156" s="5">
         <v>46204.84627579861</v>
@@ -10338,16 +10419,16 @@
         <v>46206.67810802083</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I156" s="5">
         <v>46295</v>
@@ -10365,13 +10446,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -10381,7 +10462,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B157" s="9">
         <v>46204.846348113424</v>
@@ -10391,16 +10472,16 @@
         <v>46206.67810481481</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H157" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I157" s="9">
         <v>46295</v>
@@ -10418,13 +10499,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P157" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q157" s="10"/>
       <c r="R157" s="10"/>
@@ -10434,7 +10515,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B158" s="5">
         <v>46204.846357789356</v>
@@ -10444,16 +10525,16 @@
         <v>46206.67810172454</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H158" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I158" s="5">
         <v>46295</v>
@@ -10471,13 +10552,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -10487,7 +10568,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B159" s="9">
         <v>46204.846365879624</v>
@@ -10497,16 +10578,16 @@
         <v>46206.67809884259</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G159" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H159" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I159" s="9">
         <v>46295</v>
@@ -10524,13 +10605,13 @@
         <v>26</v>
       </c>
       <c r="N159" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O159" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P159" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q159" s="10"/>
       <c r="R159" s="10"/>
@@ -10540,7 +10621,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B160" s="5">
         <v>46204.846373692126</v>
@@ -10550,16 +10631,16 @@
         <v>46206.678095509254</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H160" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I160" s="5">
         <v>46295</v>
@@ -10577,13 +10658,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -10593,7 +10674,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B161" s="9">
         <v>46204.8463796412</v>
@@ -10603,16 +10684,16 @@
         <v>46206.67809255787</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G161" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H161" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I161" s="9">
         <v>46295</v>
@@ -10630,13 +10711,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O161" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P161" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q161" s="10"/>
       <c r="R161" s="10"/>
@@ -10646,7 +10727,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B162" s="5">
         <v>46204.846388715276</v>
@@ -10656,16 +10737,16 @@
         <v>46206.678089270834</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H162" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I162" s="5">
         <v>46295</v>
@@ -10683,13 +10764,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -10699,7 +10780,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B163" s="9">
         <v>46204.84640113426</v>
@@ -10709,16 +10790,16 @@
         <v>46206.67808063657</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F163" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G163" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H163" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I163" s="9">
         <v>46295</v>
@@ -10736,13 +10817,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O163" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P163" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q163" s="10"/>
       <c r="R163" s="10"/>
@@ -10752,7 +10833,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B164" s="5">
         <v>46204.84641309028</v>
@@ -10762,16 +10843,16 @@
         <v>46206.67807998843</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G164" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H164" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I164" s="5">
         <v>46295</v>
@@ -10789,13 +10870,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -10805,7 +10886,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="8" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B165" s="9">
         <v>46204.846406701385</v>
@@ -10815,16 +10896,16 @@
         <v>46206.67807929398</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G165" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H165" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I165" s="9">
         <v>46295</v>
@@ -10842,13 +10923,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O165" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P165" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q165" s="10"/>
       <c r="R165" s="10"/>
@@ -10858,7 +10939,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B166" s="5">
         <v>46204.7875055787</v>
@@ -10868,7 +10949,7 @@
         <v>46206.66985314815</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>25</v>
@@ -10892,7 +10973,7 @@
         <v>26</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P166" s="6" t="s">
         <v>26</v>
@@ -10911,7 +10992,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="8" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B167" s="9">
         <v>46204.787509016205</v>
@@ -10921,16 +11002,16 @@
         <v>46206.67820732639</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G167" s="10" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H167" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="I167" s="9">
         <v>46296</v>
@@ -10948,13 +11029,13 @@
         <v>26</v>
       </c>
       <c r="N167" s="10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O167" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P167" s="10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q167" s="9">
         <v>46304</v>
@@ -10974,7 +11055,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B168" s="5">
         <v>46204.78751333333</v>
@@ -10984,7 +11065,7 @@
         <v>46206.67824334491</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
@@ -11011,13 +11092,13 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q168" s="5">
         <v>46304</v>
@@ -11037,7 +11118,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B169" s="9">
         <v>46204.787518564815</v>
@@ -11047,7 +11128,7 @@
         <v>46212.76788890046</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>25</v>
@@ -11071,7 +11152,7 @@
         <v>26</v>
       </c>
       <c r="O169" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P169" s="10" t="s">
         <v>26</v>
@@ -11084,7 +11165,7 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B170" s="5">
         <v>46204.78752182871</v>
@@ -11094,7 +11175,7 @@
         <v>46206.67830775463</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
@@ -11121,13 +11202,13 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P170" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q170" s="5">
         <v>46315</v>
@@ -11147,7 +11228,7 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B171" s="9">
         <v>46204.78752627315</v>
@@ -11157,7 +11238,7 @@
         <v>46212.767965266205</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>26</v>
@@ -11184,13 +11265,13 @@
         <v>26</v>
       </c>
       <c r="N171" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O171" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="P171" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q171" s="9">
         <v>46324</v>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46209.792300393514</v>
+        <v>46224.170235694444</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>116</v>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1969" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1969" uniqueCount="396">
   <si>
     <t>50001569 - EUROHINCA</t>
   </si>
@@ -441,178 +441,181 @@
     <t xml:space="preserve">propuesta fabricación externa </t>
   </si>
   <si>
+    <t>generacion oc fabricación externa ,Generacion Oc  OT 4375</t>
+  </si>
+  <si>
+    <t>1216208498022048</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tableros 4368,Corte laser 4367 </t>
+  </si>
+  <si>
+    <t>1216219007108859</t>
+  </si>
+  <si>
+    <t>Tableros 4368</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC Tableros,Fabricación Tablero</t>
+  </si>
+  <si>
+    <t>1216218896994060</t>
+  </si>
+  <si>
+    <t>Generación OC Tableros</t>
+  </si>
+  <si>
+    <t>Tableros 4368,Fabricación Tablero</t>
+  </si>
+  <si>
+    <t>1216218897008580</t>
+  </si>
+  <si>
+    <t>Fabricación Tablero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tableros 4368, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 34368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E,RECEPCION FABRICACIÓN EXTERNA </t>
+  </si>
+  <si>
+    <t>1216219007123932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motor 4367 </t>
+  </si>
+  <si>
+    <t>Generación oc Motor,Fabricación motor,Planos motor proveedor</t>
+  </si>
+  <si>
+    <t>1216219007123944</t>
+  </si>
+  <si>
+    <t>Generación oc Motor</t>
+  </si>
+  <si>
+    <t>Motor 4367 ,Fabricación motor,Planos motor proveedor</t>
+  </si>
+  <si>
+    <t>1216218870925196</t>
+  </si>
+  <si>
+    <t>Fabricación motor</t>
+  </si>
+  <si>
+    <t>Motor 4367 ,Recepcion Motor</t>
+  </si>
+  <si>
+    <t>1216218896926045</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor</t>
+  </si>
+  <si>
+    <t>Motor 4367 ,Planos Definitivos</t>
+  </si>
+  <si>
+    <t>1216218897037029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corte laser 4367 </t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC corte laser,Fabricacion  corte laser</t>
+  </si>
+  <si>
+    <t>1216218897037046</t>
+  </si>
+  <si>
+    <t>Corte laser 4367 ,Fabricacion  corte laser</t>
+  </si>
+  <si>
+    <t>1216218897038301</t>
+  </si>
+  <si>
+    <t>Fabricacion  corte laser</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corte laser 4367 ,Recepcion corte laser </t>
+  </si>
+  <si>
+    <t>1216208498022065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corte plasma 4367 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generacion Oc Corte Plasma ,Fabricación corte plasma ,Generacion Oc Corte Plasma </t>
+  </si>
+  <si>
+    <t>1216208498022071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación corte plasma </t>
+  </si>
+  <si>
+    <t>1216208498022072</t>
+  </si>
+  <si>
+    <t>Corte plasma 4367 ,Recepcion corte plasma</t>
+  </si>
+  <si>
+    <t>1216208498022066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mecanizado 4367 </t>
+  </si>
+  <si>
+    <t>generación oc mecanizado,fabricacion mecanizado</t>
+  </si>
+  <si>
+    <t>1216208498022073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fabricacion mecanizado,Mecanizado 4367 </t>
+  </si>
+  <si>
+    <t>1216208498022074</t>
+  </si>
+  <si>
+    <t>fabricacion mecanizado</t>
+  </si>
+  <si>
+    <t>Mecanizado 4367 ,Recepción mecanizado</t>
+  </si>
+  <si>
+    <t>1216208498022067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación externa 4367 </t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">generacion oc fabricación externa ,fabricación material con proveedor externo </t>
+  </si>
+  <si>
+    <t>1216208498022075</t>
+  </si>
+  <si>
     <t xml:space="preserve">generacion oc fabricación externa </t>
-  </si>
-  <si>
-    <t>1216208498022048</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tableros 4368,Corte laser 4367 </t>
-  </si>
-  <si>
-    <t>1216219007108859</t>
-  </si>
-  <si>
-    <t>Tableros 4368</t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC Tableros,Fabricación Tablero</t>
-  </si>
-  <si>
-    <t>1216218896994060</t>
-  </si>
-  <si>
-    <t>Generación OC Tableros</t>
-  </si>
-  <si>
-    <t>Tableros 4368,Fabricación Tablero</t>
-  </si>
-  <si>
-    <t>1216218897008580</t>
-  </si>
-  <si>
-    <t>Fabricación Tablero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tableros 4368, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 34368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E,RECEPCION FABRICACIÓN EXTERNA </t>
-  </si>
-  <si>
-    <t>1216219007123932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motor 4367 </t>
-  </si>
-  <si>
-    <t>Generación oc Motor,Fabricación motor,Planos motor proveedor</t>
-  </si>
-  <si>
-    <t>1216219007123944</t>
-  </si>
-  <si>
-    <t>Generación oc Motor</t>
-  </si>
-  <si>
-    <t>Motor 4367 ,Fabricación motor,Planos motor proveedor</t>
-  </si>
-  <si>
-    <t>1216218870925196</t>
-  </si>
-  <si>
-    <t>Fabricación motor</t>
-  </si>
-  <si>
-    <t>Motor 4367 ,Recepcion Motor</t>
-  </si>
-  <si>
-    <t>1216218896926045</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor</t>
-  </si>
-  <si>
-    <t>Motor 4367 ,Planos Definitivos</t>
-  </si>
-  <si>
-    <t>1216218897037029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corte laser 4367 </t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC corte laser,Fabricacion  corte laser</t>
-  </si>
-  <si>
-    <t>1216218897037046</t>
-  </si>
-  <si>
-    <t>Corte laser 4367 ,Fabricacion  corte laser</t>
-  </si>
-  <si>
-    <t>1216218897038301</t>
-  </si>
-  <si>
-    <t>Fabricacion  corte laser</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corte laser 4367 ,Recepcion corte laser </t>
-  </si>
-  <si>
-    <t>1216208498022065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corte plasma 4367 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generacion Oc Corte Plasma ,Fabricación corte plasma ,Generacion Oc Corte Plasma </t>
-  </si>
-  <si>
-    <t>1216208498022071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación corte plasma </t>
-  </si>
-  <si>
-    <t>1216208498022072</t>
-  </si>
-  <si>
-    <t>Corte plasma 4367 ,Recepcion corte plasma</t>
-  </si>
-  <si>
-    <t>1216208498022066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mecanizado 4367 </t>
-  </si>
-  <si>
-    <t>generación oc mecanizado,fabricacion mecanizado</t>
-  </si>
-  <si>
-    <t>1216208498022073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fabricacion mecanizado,Mecanizado 4367 </t>
-  </si>
-  <si>
-    <t>1216208498022074</t>
-  </si>
-  <si>
-    <t>fabricacion mecanizado</t>
-  </si>
-  <si>
-    <t>Mecanizado 4367 ,Recepción mecanizado</t>
-  </si>
-  <si>
-    <t>1216208498022067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación externa 4367 </t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">generacion oc fabricación externa ,fabricación material con proveedor externo </t>
-  </si>
-  <si>
-    <t>1216208498022075</t>
   </si>
   <si>
     <t xml:space="preserve">fabricación material con proveedor externo ,Fabricación externa 4367 </t>
@@ -3501,7 +3504,7 @@
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46223.56031626157</v>
+        <v>46224.82341019676</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>105</v>
@@ -4607,7 +4610,7 @@
         <v>46206.67409482639</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>106</v>
+        <v>164</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
@@ -4640,7 +4643,7 @@
         <v>105</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4650,7 +4653,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B51" s="9">
         <v>46204.795219293985</v>
@@ -4660,7 +4663,7 @@
         <v>46206.67409221065</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
@@ -4690,10 +4693,10 @@
         <v>159</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>106</v>
+        <v>164</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4703,7 +4706,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B52" s="5">
         <v>46206.65895994213</v>
@@ -4713,16 +4716,16 @@
         <v>46206.674336111115</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4741,7 +4744,7 @@
         <v>159</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>26</v>
@@ -4754,7 +4757,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B53" s="9">
         <v>46204.787306770835</v>
@@ -4764,7 +4767,7 @@
         <v>46217.8575847801</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>25</v>
@@ -4788,7 +4791,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>26</v>
@@ -4801,7 +4804,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B54" s="5">
         <v>46204.78731047454</v>
@@ -4813,16 +4816,16 @@
         <v>46219.20085231481</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I54" s="5">
         <v>46212</v>
@@ -4840,13 +4843,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>75</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q54" s="5">
         <v>46218</v>
@@ -4866,7 +4869,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B55" s="9">
         <v>46204.78731518518</v>
@@ -4878,16 +4881,16 @@
         <v>46217.85759137732</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I55" s="9">
         <v>46233</v>
@@ -4905,13 +4908,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q55" s="9">
         <v>46239</v>
@@ -4931,7 +4934,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B56" s="5">
         <v>46204.78732028935</v>
@@ -4947,10 +4950,10 @@
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I56" s="5">
         <v>46240</v>
@@ -4968,13 +4971,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q56" s="5">
         <v>46240</v>
@@ -4994,7 +4997,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B57" s="9">
         <v>46204.787326770835</v>
@@ -5004,16 +5007,16 @@
         <v>46206.67498217593</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I57" s="9">
         <v>46288</v>
@@ -5031,13 +5034,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q57" s="9">
         <v>46288</v>
@@ -5057,7 +5060,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B58" s="5">
         <v>46205.8929956713</v>
@@ -5067,16 +5070,16 @@
         <v>46206.67494384259</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I58" s="5">
         <v>46288</v>
@@ -5094,13 +5097,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5110,7 +5113,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B59" s="9">
         <v>46205.89308850694</v>
@@ -5120,16 +5123,16 @@
         <v>46206.67494135417</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I59" s="9">
         <v>46288</v>
@@ -5147,13 +5150,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5163,7 +5166,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B60" s="5">
         <v>46205.89321678241</v>
@@ -5173,16 +5176,16 @@
         <v>46206.67493778935</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I60" s="5">
         <v>46288</v>
@@ -5200,13 +5203,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5216,7 +5219,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B61" s="9">
         <v>46204.787330555555</v>
@@ -5226,7 +5229,7 @@
         <v>46206.65997969908</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>25</v>
@@ -5250,7 +5253,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5263,7 +5266,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B62" s="5">
         <v>46204.78733380787</v>
@@ -5273,16 +5276,16 @@
         <v>46206.67512555556</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I62" s="5">
         <v>46258</v>
@@ -5300,13 +5303,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>141</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q62" s="5">
         <v>46259</v>
@@ -5326,7 +5329,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B63" s="9">
         <v>46204.78733813658</v>
@@ -5336,16 +5339,16 @@
         <v>46206.67526587963</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I63" s="9">
         <v>46260</v>
@@ -5363,13 +5366,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q63" s="9">
         <v>46261</v>
@@ -5389,7 +5392,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B64" s="5">
         <v>46204.79962430555</v>
@@ -5399,16 +5402,16 @@
         <v>46206.67512305555</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I64" s="5">
         <v>46258</v>
@@ -5426,13 +5429,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>147</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q64" s="5">
         <v>46259</v>
@@ -5452,7 +5455,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B65" s="9">
         <v>46204.79970230324</v>
@@ -5462,16 +5465,16 @@
         <v>46206.67526299768</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I65" s="9">
         <v>46260</v>
@@ -5489,13 +5492,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q65" s="9">
         <v>46261</v>
@@ -5515,7 +5518,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B66" s="5">
         <v>46204.799834722224</v>
@@ -5525,16 +5528,16 @@
         <v>46206.67512025463</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I66" s="5">
         <v>46258</v>
@@ -5552,13 +5555,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>156</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q66" s="5">
         <v>46259</v>
@@ -5578,7 +5581,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B67" s="9">
         <v>46204.80007783565</v>
@@ -5588,16 +5591,16 @@
         <v>46206.67526012732</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I67" s="9">
         <v>46260</v>
@@ -5615,13 +5618,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q67" s="9">
         <v>46261</v>
@@ -5641,7 +5644,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B68" s="5">
         <v>46204.787342662035</v>
@@ -5651,7 +5654,7 @@
         <v>46206.66163074074</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5675,7 +5678,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5688,7 +5691,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B69" s="9">
         <v>46204.78734565972</v>
@@ -5698,16 +5701,16 @@
         <v>46206.67535149306</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I69" s="9">
         <v>46262</v>
@@ -5725,13 +5728,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q69" s="9">
         <v>46266</v>
@@ -5751,7 +5754,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B70" s="5">
         <v>46204.78735021991</v>
@@ -5761,16 +5764,16 @@
         <v>46206.67558131945</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I70" s="5">
         <v>46267</v>
@@ -5788,13 +5791,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q70" s="5">
         <v>46273</v>
@@ -5814,7 +5817,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B71" s="9">
         <v>46204.83329071759</v>
@@ -5824,16 +5827,16 @@
         <v>46206.67551582176</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I71" s="9">
         <v>46267</v>
@@ -5851,13 +5854,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5867,7 +5870,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B72" s="5">
         <v>46204.83348987269</v>
@@ -5877,16 +5880,16 @@
         <v>46206.67551341435</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I72" s="5">
         <v>46267</v>
@@ -5904,13 +5907,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5920,7 +5923,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B73" s="9">
         <v>46204.83350201389</v>
@@ -5930,16 +5933,16 @@
         <v>46206.67551030093</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I73" s="9">
         <v>46267</v>
@@ -5957,13 +5960,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -5973,7 +5976,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B74" s="5">
         <v>46204.787355625</v>
@@ -5983,16 +5986,16 @@
         <v>46206.67580866898</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I74" s="5">
         <v>46274</v>
@@ -6010,13 +6013,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q74" s="5">
         <v>46274</v>
@@ -6036,7 +6039,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B75" s="9">
         <v>46204.83355802084</v>
@@ -6046,16 +6049,16 @@
         <v>46206.67575559027</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I75" s="10"/>
       <c r="J75" s="9">
@@ -6071,13 +6074,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6087,7 +6090,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B76" s="5">
         <v>46204.833570069444</v>
@@ -6097,16 +6100,16 @@
         <v>46206.67575268519</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I76" s="6"/>
       <c r="J76" s="5">
@@ -6122,13 +6125,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6138,7 +6141,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B77" s="9">
         <v>46204.833579004626</v>
@@ -6148,16 +6151,16 @@
         <v>46206.67574885416</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I77" s="10"/>
       <c r="J77" s="9">
@@ -6173,13 +6176,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6189,7 +6192,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B78" s="5">
         <v>46204.78736071759</v>
@@ -6199,7 +6202,7 @@
         <v>46206.67094998843</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>25</v>
@@ -6223,7 +6226,7 @@
         <v>26</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6236,7 +6239,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B79" s="9">
         <v>46204.78736410879</v>
@@ -6246,16 +6249,16 @@
         <v>46213.50330894676</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I79" s="9">
         <v>46210</v>
@@ -6273,13 +6276,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O79" s="10" t="s">
         <v>80</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q79" s="9">
         <v>46210</v>
@@ -6299,7 +6302,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B80" s="5">
         <v>46204.78737366898</v>
@@ -6309,16 +6312,16 @@
         <v>46217.69454351852</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I80" s="5">
         <v>46253</v>
@@ -6336,13 +6339,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>128</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q80" s="5">
         <v>46253</v>
@@ -6362,7 +6365,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B81" s="9">
         <v>46204.78737825232</v>
@@ -6372,16 +6375,16 @@
         <v>46206.67600082176</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I81" s="9">
         <v>46274</v>
@@ -6399,13 +6402,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q81" s="9">
         <v>46274</v>
@@ -6425,7 +6428,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B82" s="5">
         <v>46206.567318657406</v>
@@ -6441,10 +6444,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I82" s="6"/>
       <c r="J82" s="5">
@@ -6460,13 +6463,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>119</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6476,7 +6479,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B83" s="9">
         <v>46206.56766555556</v>
@@ -6492,10 +6495,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I83" s="10"/>
       <c r="J83" s="9">
@@ -6511,13 +6514,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O83" s="10" t="s">
         <v>119</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6527,7 +6530,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B84" s="5">
         <v>46206.56768260417</v>
@@ -6543,10 +6546,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I84" s="6"/>
       <c r="J84" s="5">
@@ -6562,13 +6565,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>119</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6578,7 +6581,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B85" s="9">
         <v>46206.56769806713</v>
@@ -6594,10 +6597,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I85" s="10"/>
       <c r="J85" s="9">
@@ -6613,13 +6616,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O85" s="10" t="s">
         <v>119</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6629,7 +6632,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B86" s="5">
         <v>46206.56771423611</v>
@@ -6645,10 +6648,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I86" s="6"/>
       <c r="J86" s="5">
@@ -6664,13 +6667,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>119</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6680,7 +6683,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B87" s="9">
         <v>46206.56772880787</v>
@@ -6696,10 +6699,10 @@
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I87" s="10"/>
       <c r="J87" s="9">
@@ -6715,13 +6718,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O87" s="10" t="s">
         <v>119</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6731,7 +6734,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B88" s="5">
         <v>46206.567743506945</v>
@@ -6747,10 +6750,10 @@
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I88" s="6"/>
       <c r="J88" s="5">
@@ -6766,13 +6769,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>119</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6782,7 +6785,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B89" s="9">
         <v>46206.56775844908</v>
@@ -6798,10 +6801,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I89" s="10"/>
       <c r="J89" s="9">
@@ -6817,13 +6820,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O89" s="10" t="s">
         <v>119</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6833,7 +6836,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B90" s="5">
         <v>46206.56777289352</v>
@@ -6849,10 +6852,10 @@
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I90" s="6"/>
       <c r="J90" s="5">
@@ -6868,13 +6871,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>119</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6884,7 +6887,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B91" s="9">
         <v>46206.67094809028</v>
@@ -6894,16 +6897,16 @@
         <v>46206.67590806713</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I91" s="9">
         <v>46274</v>
@@ -6921,7 +6924,7 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O91" s="10" t="s">
         <v>119</v>
@@ -6941,7 +6944,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B92" s="5">
         <v>46204.78738409722</v>
@@ -6951,7 +6954,7 @@
         <v>46206.66745490741</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>25</v>
@@ -6975,7 +6978,7 @@
         <v>26</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>26</v>
@@ -6988,7 +6991,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B93" s="9">
         <v>46204.787387268516</v>
@@ -6998,7 +7001,7 @@
         <v>46223.56188282407</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -7025,13 +7028,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q93" s="9">
         <v>46281</v>
@@ -7051,7 +7054,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B94" s="5">
         <v>46204.84491833333</v>
@@ -7061,7 +7064,7 @@
         <v>46223.56049512731</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7088,13 +7091,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7104,7 +7107,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B95" s="9">
         <v>46204.84493530093</v>
@@ -7114,7 +7117,7 @@
         <v>46223.56049449074</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7141,13 +7144,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7157,7 +7160,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B96" s="5">
         <v>46204.84494427084</v>
@@ -7167,7 +7170,7 @@
         <v>46223.56049383101</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7194,13 +7197,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7210,7 +7213,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B97" s="9">
         <v>46204.78739225694</v>
@@ -7220,7 +7223,7 @@
         <v>46223.56188216435</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
@@ -7247,13 +7250,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q97" s="9">
         <v>46282</v>
@@ -7273,7 +7276,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B98" s="5">
         <v>46204.84497997686</v>
@@ -7283,7 +7286,7 @@
         <v>46223.560602199075</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7310,13 +7313,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7326,7 +7329,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B99" s="9">
         <v>46204.84498876157</v>
@@ -7336,7 +7339,7 @@
         <v>46223.56060143519</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7363,13 +7366,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7379,7 +7382,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B100" s="5">
         <v>46204.84499563657</v>
@@ -7389,7 +7392,7 @@
         <v>46223.560600763885</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7416,13 +7419,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7432,7 +7435,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B101" s="9">
         <v>46204.78740502315</v>
@@ -7442,7 +7445,7 @@
         <v>46223.56188153935</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
@@ -7469,13 +7472,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q101" s="9">
         <v>46286</v>
@@ -7495,7 +7498,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B102" s="5">
         <v>46204.84507945602</v>
@@ -7505,7 +7508,7 @@
         <v>46223.5607075</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7532,13 +7535,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7548,7 +7551,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B103" s="9">
         <v>46204.84508817129</v>
@@ -7558,7 +7561,7 @@
         <v>46223.560706840275</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7585,13 +7588,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7601,7 +7604,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B104" s="5">
         <v>46204.845093854165</v>
@@ -7611,7 +7614,7 @@
         <v>46223.56070621528</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7638,13 +7641,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7654,7 +7657,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B105" s="9">
         <v>46204.78741121528</v>
@@ -7664,7 +7667,7 @@
         <v>46223.561880925925</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7691,13 +7694,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q105" s="9">
         <v>46287</v>
@@ -7717,7 +7720,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B106" s="5">
         <v>46204.84513122685</v>
@@ -7727,7 +7730,7 @@
         <v>46223.56167888889</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7754,13 +7757,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7770,7 +7773,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B107" s="9">
         <v>46204.84513944444</v>
@@ -7780,7 +7783,7 @@
         <v>46223.561678287035</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7807,13 +7810,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7823,7 +7826,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B108" s="5">
         <v>46204.8451466088</v>
@@ -7833,7 +7836,7 @@
         <v>46223.56167766204</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7860,13 +7863,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7876,7 +7879,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B109" s="9">
         <v>46204.787473310185</v>
@@ -7886,7 +7889,7 @@
         <v>46223.56188028935</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
@@ -7913,13 +7916,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q109" s="9">
         <v>46289</v>
@@ -7939,7 +7942,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B110" s="5">
         <v>46204.84518325231</v>
@@ -7949,7 +7952,7 @@
         <v>46223.56179313657</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -7976,13 +7979,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -7992,7 +7995,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B111" s="9">
         <v>46204.845191898145</v>
@@ -8002,7 +8005,7 @@
         <v>46223.56179228009</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
@@ -8029,13 +8032,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -8045,7 +8048,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B112" s="5">
         <v>46204.84520083333</v>
@@ -8055,7 +8058,7 @@
         <v>46223.56179165509</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8082,13 +8085,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8098,7 +8101,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B113" s="9">
         <v>46204.78748032407</v>
@@ -8108,7 +8111,7 @@
         <v>46206.668344247686</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>25</v>
@@ -8132,7 +8135,7 @@
         <v>26</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>
@@ -8145,7 +8148,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B114" s="5">
         <v>46204.787484155095</v>
@@ -8155,16 +8158,16 @@
         <v>46206.677181631945</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I114" s="5">
         <v>46290</v>
@@ -8182,13 +8185,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q114" s="5">
         <v>46290</v>
@@ -8208,7 +8211,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B115" s="9">
         <v>46206.61281571759</v>
@@ -8218,16 +8221,16 @@
         <v>46206.67717564815</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I115" s="9">
         <v>46290</v>
@@ -8245,13 +8248,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8261,7 +8264,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B116" s="5">
         <v>46206.612829722224</v>
@@ -8271,16 +8274,16 @@
         <v>46206.67717299769</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I116" s="5">
         <v>46290</v>
@@ -8298,13 +8301,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8314,7 +8317,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B117" s="9">
         <v>46206.61284180556</v>
@@ -8324,16 +8327,16 @@
         <v>46206.67717023148</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I117" s="9">
         <v>46290</v>
@@ -8351,13 +8354,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8367,7 +8370,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B118" s="5">
         <v>46206.61323981482</v>
@@ -8383,10 +8386,10 @@
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I118" s="5">
         <v>46290</v>
@@ -8404,13 +8407,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8420,7 +8423,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B119" s="9">
         <v>46206.613256446755</v>
@@ -8436,10 +8439,10 @@
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I119" s="9">
         <v>46290</v>
@@ -8457,13 +8460,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O119" s="10" t="s">
         <v>59</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8473,7 +8476,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B120" s="5">
         <v>46206.61328513889</v>
@@ -8489,10 +8492,10 @@
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I120" s="5">
         <v>46290</v>
@@ -8510,13 +8513,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8526,7 +8529,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B121" s="9">
         <v>46206.613270925925</v>
@@ -8542,10 +8545,10 @@
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I121" s="9">
         <v>46290</v>
@@ -8563,13 +8566,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O121" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8579,7 +8582,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B122" s="5">
         <v>46206.6133403125</v>
@@ -8595,10 +8598,10 @@
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I122" s="5">
         <v>46290</v>
@@ -8616,13 +8619,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8632,7 +8635,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B123" s="9">
         <v>46206.613361041665</v>
@@ -8648,10 +8651,10 @@
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I123" s="9">
         <v>46290</v>
@@ -8669,13 +8672,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O123" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8685,7 +8688,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B124" s="5">
         <v>46206.613371493055</v>
@@ -8701,10 +8704,10 @@
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I124" s="5">
         <v>46290</v>
@@ -8722,13 +8725,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8738,7 +8741,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B125" s="9">
         <v>46206.61338284722</v>
@@ -8754,10 +8757,10 @@
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I125" s="9">
         <v>46290</v>
@@ -8775,13 +8778,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O125" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -8791,7 +8794,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B126" s="5">
         <v>46206.61339653935</v>
@@ -8807,10 +8810,10 @@
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I126" s="5">
         <v>46290</v>
@@ -8828,13 +8831,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8844,7 +8847,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B127" s="9">
         <v>46204.78748974537</v>
@@ -8854,7 +8857,7 @@
         <v>46223.56209584491</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
@@ -8875,19 +8878,19 @@
         <v>26</v>
       </c>
       <c r="L127" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q127" s="9">
         <v>46293</v>
@@ -8907,7 +8910,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B128" s="5">
         <v>46204.84566665509</v>
@@ -8917,7 +8920,7 @@
         <v>46223.562056400464</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -8944,13 +8947,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -8960,7 +8963,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B129" s="9">
         <v>46204.8456746875</v>
@@ -8970,7 +8973,7 @@
         <v>46223.56205577546</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
@@ -8997,13 +9000,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -9013,7 +9016,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B130" s="5">
         <v>46204.84568395834</v>
@@ -9023,7 +9026,7 @@
         <v>46223.56205517361</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9050,13 +9053,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9066,7 +9069,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B131" s="9">
         <v>46204.84577770834</v>
@@ -9076,7 +9079,7 @@
         <v>46223.562054548616</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
@@ -9103,13 +9106,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O131" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9119,7 +9122,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B132" s="5">
         <v>46204.845803958335</v>
@@ -9129,7 +9132,7 @@
         <v>46223.56205386574</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9156,13 +9159,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O132" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9172,7 +9175,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B133" s="9">
         <v>46204.8458116088</v>
@@ -9182,7 +9185,7 @@
         <v>46223.562053217596</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
@@ -9209,13 +9212,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O133" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9225,7 +9228,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B134" s="5">
         <v>46204.84582686343</v>
@@ -9235,7 +9238,7 @@
         <v>46223.56205256944</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9262,13 +9265,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9278,7 +9281,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B135" s="9">
         <v>46204.84581974537</v>
@@ -9288,7 +9291,7 @@
         <v>46223.56205195602</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
@@ -9315,13 +9318,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O135" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9331,7 +9334,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B136" s="5">
         <v>46204.84583605324</v>
@@ -9341,7 +9344,7 @@
         <v>46223.562051354165</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9368,13 +9371,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O136" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9384,7 +9387,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B137" s="9">
         <v>46204.84584422453</v>
@@ -9394,7 +9397,7 @@
         <v>46223.562050740744</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
@@ -9421,13 +9424,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O137" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9437,7 +9440,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B138" s="5">
         <v>46204.845850983795</v>
@@ -9447,7 +9450,7 @@
         <v>46223.562050092594</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9474,13 +9477,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O138" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9490,7 +9493,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B139" s="9">
         <v>46204.84585899305</v>
@@ -9500,7 +9503,7 @@
         <v>46223.5620494676</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
@@ -9527,13 +9530,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O139" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q139" s="10"/>
       <c r="R139" s="10"/>
@@ -9543,7 +9546,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B140" s="5">
         <v>46204.78749533565</v>
@@ -9553,16 +9556,16 @@
         <v>46206.67787028935</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I140" s="5">
         <v>46294</v>
@@ -9580,13 +9583,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q140" s="5">
         <v>46294</v>
@@ -9606,7 +9609,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B141" s="9">
         <v>46204.84595449074</v>
@@ -9616,16 +9619,16 @@
         <v>46206.67786329861</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H141" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I141" s="9">
         <v>46294</v>
@@ -9643,13 +9646,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P141" s="10" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q141" s="10"/>
       <c r="R141" s="10"/>
@@ -9659,7 +9662,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B142" s="5">
         <v>46204.845964189815</v>
@@ -9669,16 +9672,16 @@
         <v>46206.677860254626</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I142" s="5">
         <v>46294</v>
@@ -9696,13 +9699,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9712,7 +9715,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B143" s="9">
         <v>46204.84597238426</v>
@@ -9722,16 +9725,16 @@
         <v>46206.67785763889</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H143" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I143" s="9">
         <v>46294</v>
@@ -9749,13 +9752,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q143" s="10"/>
       <c r="R143" s="10"/>
@@ -9765,7 +9768,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B144" s="5">
         <v>46204.846036469906</v>
@@ -9775,16 +9778,16 @@
         <v>46206.67785519676</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I144" s="5">
         <v>46294</v>
@@ -9802,13 +9805,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -9818,7 +9821,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B145" s="9">
         <v>46204.846047893516</v>
@@ -9828,16 +9831,16 @@
         <v>46206.6778525</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H145" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I145" s="9">
         <v>46294</v>
@@ -9855,13 +9858,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -9871,7 +9874,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B146" s="5">
         <v>46204.846056724535</v>
@@ -9881,16 +9884,16 @@
         <v>46206.67784956019</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I146" s="5">
         <v>46294</v>
@@ -9908,13 +9911,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -9924,7 +9927,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B147" s="9">
         <v>46204.846065578706</v>
@@ -9934,16 +9937,16 @@
         <v>46206.677846921295</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H147" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I147" s="9">
         <v>46294</v>
@@ -9961,13 +9964,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O147" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q147" s="10"/>
       <c r="R147" s="10"/>
@@ -9977,7 +9980,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B148" s="5">
         <v>46204.846073252316</v>
@@ -9987,16 +9990,16 @@
         <v>46206.67784445602</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I148" s="5">
         <v>46294</v>
@@ -10014,13 +10017,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10030,7 +10033,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B149" s="9">
         <v>46204.84608019676</v>
@@ -10040,16 +10043,16 @@
         <v>46206.6778419676</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H149" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I149" s="9">
         <v>46294</v>
@@ -10067,13 +10070,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q149" s="10"/>
       <c r="R149" s="10"/>
@@ -10083,7 +10086,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B150" s="5">
         <v>46204.84608666667</v>
@@ -10093,16 +10096,16 @@
         <v>46206.67783399306</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I150" s="5">
         <v>46294</v>
@@ -10120,13 +10123,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10136,7 +10139,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B151" s="9">
         <v>46204.84609472222</v>
@@ -10146,16 +10149,16 @@
         <v>46206.677833344904</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G151" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H151" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I151" s="9">
         <v>46294</v>
@@ -10173,13 +10176,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P151" s="10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q151" s="10"/>
       <c r="R151" s="10"/>
@@ -10189,7 +10192,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B152" s="5">
         <v>46204.84610289352</v>
@@ -10199,16 +10202,16 @@
         <v>46206.67783269676</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I152" s="5">
         <v>46294</v>
@@ -10226,13 +10229,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10242,7 +10245,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="8" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B153" s="9">
         <v>46204.78749967593</v>
@@ -10252,16 +10255,16 @@
         <v>46206.67812460648</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G153" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H153" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I153" s="10"/>
       <c r="J153" s="9">
@@ -10277,13 +10280,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O153" s="10" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P153" s="10" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q153" s="9">
         <v>46295</v>
@@ -10303,7 +10306,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B154" s="5">
         <v>46204.846246076384</v>
@@ -10313,16 +10316,16 @@
         <v>46206.67812013889</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I154" s="5">
         <v>46295</v>
@@ -10340,13 +10343,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10356,7 +10359,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="8" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B155" s="9">
         <v>46204.84626494213</v>
@@ -10366,16 +10369,16 @@
         <v>46206.678117118056</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G155" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H155" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I155" s="9">
         <v>46295</v>
@@ -10393,13 +10396,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="P155" s="10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q155" s="10"/>
       <c r="R155" s="10"/>
@@ -10409,7 +10412,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B156" s="5">
         <v>46204.84627579861</v>
@@ -10419,16 +10422,16 @@
         <v>46206.67810802083</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I156" s="5">
         <v>46295</v>
@@ -10446,13 +10449,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -10462,7 +10465,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B157" s="9">
         <v>46204.846348113424</v>
@@ -10472,16 +10475,16 @@
         <v>46206.67810481481</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H157" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I157" s="9">
         <v>46295</v>
@@ -10499,13 +10502,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P157" s="10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q157" s="10"/>
       <c r="R157" s="10"/>
@@ -10515,7 +10518,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B158" s="5">
         <v>46204.846357789356</v>
@@ -10525,16 +10528,16 @@
         <v>46206.67810172454</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H158" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I158" s="5">
         <v>46295</v>
@@ -10552,13 +10555,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -10568,7 +10571,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B159" s="9">
         <v>46204.846365879624</v>
@@ -10578,16 +10581,16 @@
         <v>46206.67809884259</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G159" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H159" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I159" s="9">
         <v>46295</v>
@@ -10605,13 +10608,13 @@
         <v>26</v>
       </c>
       <c r="N159" s="10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O159" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P159" s="10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q159" s="10"/>
       <c r="R159" s="10"/>
@@ -10621,7 +10624,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B160" s="5">
         <v>46204.846373692126</v>
@@ -10631,16 +10634,16 @@
         <v>46206.678095509254</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H160" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I160" s="5">
         <v>46295</v>
@@ -10658,13 +10661,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -10674,7 +10677,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B161" s="9">
         <v>46204.8463796412</v>
@@ -10684,16 +10687,16 @@
         <v>46206.67809255787</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G161" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H161" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I161" s="9">
         <v>46295</v>
@@ -10711,13 +10714,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O161" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P161" s="10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q161" s="10"/>
       <c r="R161" s="10"/>
@@ -10727,7 +10730,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B162" s="5">
         <v>46204.846388715276</v>
@@ -10737,16 +10740,16 @@
         <v>46206.678089270834</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H162" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I162" s="5">
         <v>46295</v>
@@ -10764,13 +10767,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -10780,7 +10783,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B163" s="9">
         <v>46204.84640113426</v>
@@ -10790,16 +10793,16 @@
         <v>46206.67808063657</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F163" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G163" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H163" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I163" s="9">
         <v>46295</v>
@@ -10817,13 +10820,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O163" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P163" s="10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q163" s="10"/>
       <c r="R163" s="10"/>
@@ -10833,7 +10836,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B164" s="5">
         <v>46204.84641309028</v>
@@ -10843,16 +10846,16 @@
         <v>46206.67807998843</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G164" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H164" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I164" s="5">
         <v>46295</v>
@@ -10870,13 +10873,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -10886,7 +10889,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="8" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B165" s="9">
         <v>46204.846406701385</v>
@@ -10896,16 +10899,16 @@
         <v>46206.67807929398</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G165" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H165" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I165" s="9">
         <v>46295</v>
@@ -10923,13 +10926,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O165" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P165" s="10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q165" s="10"/>
       <c r="R165" s="10"/>
@@ -10939,7 +10942,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B166" s="5">
         <v>46204.7875055787</v>
@@ -10949,7 +10952,7 @@
         <v>46206.66985314815</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>25</v>
@@ -10973,7 +10976,7 @@
         <v>26</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="P166" s="6" t="s">
         <v>26</v>
@@ -10992,7 +10995,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="8" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B167" s="9">
         <v>46204.787509016205</v>
@@ -11002,16 +11005,16 @@
         <v>46206.67820732639</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G167" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H167" s="10" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="I167" s="9">
         <v>46296</v>
@@ -11029,13 +11032,13 @@
         <v>26</v>
       </c>
       <c r="N167" s="10" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O167" s="10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P167" s="10" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q167" s="9">
         <v>46304</v>
@@ -11055,7 +11058,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B168" s="5">
         <v>46204.78751333333</v>
@@ -11065,7 +11068,7 @@
         <v>46206.67824334491</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
@@ -11092,13 +11095,13 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q168" s="5">
         <v>46304</v>
@@ -11118,7 +11121,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B169" s="9">
         <v>46204.787518564815</v>
@@ -11128,7 +11131,7 @@
         <v>46212.76788890046</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>25</v>
@@ -11152,7 +11155,7 @@
         <v>26</v>
       </c>
       <c r="O169" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="P169" s="10" t="s">
         <v>26</v>
@@ -11165,7 +11168,7 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B170" s="5">
         <v>46204.78752182871</v>
@@ -11175,7 +11178,7 @@
         <v>46206.67830775463</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
@@ -11202,13 +11205,13 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P170" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q170" s="5">
         <v>46315</v>
@@ -11228,7 +11231,7 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B171" s="9">
         <v>46204.78752627315</v>
@@ -11238,7 +11241,7 @@
         <v>46212.767965266205</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>26</v>
@@ -11265,13 +11268,13 @@
         <v>26</v>
       </c>
       <c r="N171" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O171" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P171" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q171" s="9">
         <v>46324</v>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -441,7 +441,7 @@
     <t xml:space="preserve">propuesta fabricación externa </t>
   </si>
   <si>
-    <t>generacion oc fabricación externa ,Generacion Oc  OT 4375</t>
+    <t>generacion oc fabricación externa ,Generacion Oc  OT 4375,Generacion Oc  OT 4376 ,Generacion Oc  OT 4377</t>
   </si>
   <si>
     <t>1216208498022048</t>
@@ -3504,7 +3504,7 @@
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46224.82341019676</v>
+        <v>46225.00952798611</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>105</v>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -444,7 +444,7 @@
     <t xml:space="preserve">propuesta fabricación externa </t>
   </si>
   <si>
-    <t xml:space="preserve">generacion oc fabricación externa ,Generacion Oc  OT 4375,Generacion Oc  OT 4376 ,Generacion Oc  OT 4377,Generacion Oc  OT4378,Generacion Oc OT 4376 OT 4381  </t>
+    <t xml:space="preserve">generacion oc fabricación externa ,Generacion Oc  OT 4375,Generacion Oc  OT 4376 ,Generacion Oc  OT 4377,Generacion Oc  OT4378,Generacion Oc OT 4376 OT 4381  ,Generacion Oc OT 4382 - OT 4383 </t>
   </si>
   <si>
     <t>1216208498022048</t>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46225.86179918981</v>
+        <v>46231.56026616898</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>106</v>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1970" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1970" uniqueCount="399">
   <si>
     <t>50001569 - EUROHINCA</t>
   </si>
@@ -342,6 +342,38 @@
     <t>Ingenieria Basica Motor</t>
   </si>
   <si>
+    <t xml:space="preserve">Buen día,
+Para el pedido 1569, se tiene 9 ventiladores ZVN 1-6-15/2 y Tablero VDF en Lógica Maestro-Esclavo para Eurohinca:
+    Planos para fabricación:
+        Estacion de ventilación 3xZVN 1-6-15/2 con motor WEG (3 unidades por cada estación)
+        Incluye: Tobera + Rejilla + 2FAR60/100 con bulbo acústico + Tipo C 600-500mm
+hgutierrez@zitron.com, tu apoyo con los planos.
+    Rodete:
+        Rodete monobloque GEL 6-15  
+        Código 300056
+        Plano mecanizado a confirmar.
+benjamin.bustos@zitron.com, favor realizar reserva de 9 unidades.
+    Tratamiento superficial estándar Zitron:
+        Preparación de superficie: Arenado SSPC-SP10
+        1ª capa imprimación 60 micras Hempadur 15570 Color 12430
+        2ª capa intermedia 40 micras Hempathane HS 55610 Color 20450 RAL 9001
+    Datos eléctricos para el motor:
+        Motor WEG 15 KW, 2 Polos, Frame 160L.
+        380 VAC, 50 Hz, IEC-IE3, IP55, FS 1.0.-
+ecarico@zitron.com, tu apoyo con la compra del motor, propuesta en ZPRO.
+    Datos eléctricos para tableros:
+        Tablero VDF  15KW, 380 VAC, 50 HZ.
+        Integrado en envolvente IP54, HMI en puerta, seccionador de entrada, luces piloto presencia de fases, botones marcha, paro, reset y protección de entrada.
+        Configuración Maestro-Esclavo
+ecarico@zitron.com, tu apoyo con la compra del tablero, propuesta en ZPRO.
+    Fecha de entrega:
+        1° Entrega: 29-07-2026 – 1 Estacion 3x ZVN 1-6-15/2 + 3 Tableros VDF M-E
+        2° Entrega: 23-09-2026 – 2 Estaciones 3x ZVN 1-6-15/2 + 6 Tableros VDF M-E
+hugo.isla@zitron.com, favor notar plazos de entrega.
+Quedo atenta.
+Saludos</t>
+  </si>
+  <si>
     <t>Ingenieria Jefe de proyecto:,Planos Definitivos,propuesta motor</t>
   </si>
   <si>
@@ -679,6 +711,9 @@
   </si>
   <si>
     <t>Check Planos,Ingenieria y diseño:</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1216218870977283</t>
@@ -2893,7 +2928,7 @@
         <v>46206.769487592595</v>
       </c>
       <c r="D21" s="9">
-        <v>46218.18071489583</v>
+        <v>46232.54893075231</v>
       </c>
       <c r="E21" s="10" t="s">
         <v>72</v>
@@ -2917,7 +2952,7 @@
         <v>26</v>
       </c>
       <c r="L21" s="10" t="s">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="M21" s="10" t="s">
         <v>26</v>
@@ -2929,7 +2964,7 @@
         <v>38</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q21" s="9">
         <v>46217</v>
@@ -2949,7 +2984,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B22" s="5">
         <v>46204.787143009264</v>
@@ -2961,7 +2996,7 @@
         <v>46212.19074947917</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -2994,7 +3029,7 @@
         <v>38</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q22" s="5">
         <v>46211</v>
@@ -3014,7 +3049,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B23" s="9">
         <v>46204.78877271991</v>
@@ -3026,16 +3061,16 @@
         <v>46223.560216666665</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>25</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I23" s="10"/>
       <c r="J23" s="10"/>
@@ -3052,7 +3087,7 @@
         <v>26</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P23" s="10" t="s">
         <v>26</v>
@@ -3069,7 +3104,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B24" s="5">
         <v>46204.788881678236</v>
@@ -3081,16 +3116,16 @@
         <v>46223.56021195602</v>
       </c>
       <c r="E24" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>81</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="I24" s="5">
         <v>46209</v>
@@ -3108,13 +3143,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>38</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q24" s="5">
         <v>46216</v>
@@ -3134,7 +3169,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B25" s="9">
         <v>46204.786945914355</v>
@@ -3144,7 +3179,7 @@
         <v>46225.82070921296</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>25</v>
@@ -3168,22 +3203,22 @@
         <v>26</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
       <c r="S25" s="10"/>
       <c r="T25" s="10"/>
       <c r="U25" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B26" s="5">
         <v>46204.78715721065</v>
@@ -3195,7 +3230,7 @@
         <v>46213.19381935185</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
@@ -3222,13 +3257,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>72</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q26" s="5">
         <v>46212</v>
@@ -3248,7 +3283,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B27" s="9">
         <v>46204.78716710648</v>
@@ -3260,7 +3295,7 @@
         <v>46214.18292518519</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
@@ -3287,13 +3322,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>44</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q27" s="9">
         <v>46213</v>
@@ -3308,12 +3343,12 @@
         <v>33</v>
       </c>
       <c r="U27" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B28" s="5">
         <v>46204.787177743056</v>
@@ -3323,16 +3358,16 @@
         <v>46225.82070689814</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I28" s="5">
         <v>46241</v>
@@ -3350,13 +3385,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q28" s="5">
         <v>46244</v>
@@ -3376,7 +3411,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B29" s="9">
         <v>46204.79158200232</v>
@@ -3386,16 +3421,16 @@
         <v>46225.82066863426</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I29" s="9">
         <v>46241</v>
@@ -3413,13 +3448,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P29" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q29" s="9">
         <v>46244</v>
@@ -3439,7 +3474,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B30" s="5">
         <v>46204.79163886574</v>
@@ -3449,16 +3484,16 @@
         <v>46225.82062824074</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I30" s="5">
         <v>46241</v>
@@ -3476,13 +3511,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q30" s="5">
         <v>46244</v>
@@ -3502,7 +3537,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B31" s="9">
         <v>46204.7917447338</v>
@@ -3512,16 +3547,16 @@
         <v>46231.56026616898</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I31" s="9">
         <v>46241</v>
@@ -3539,13 +3574,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q31" s="9">
         <v>46244</v>
@@ -3565,7 +3600,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B32" s="5">
         <v>46204.78695173611</v>
@@ -3575,7 +3610,7 @@
         <v>46206.65562592592</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>25</v>
@@ -3599,7 +3634,7 @@
         <v>26</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3612,7 +3647,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B33" s="9">
         <v>46204.78719643518</v>
@@ -3622,16 +3657,16 @@
         <v>46206.67332864583</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I33" s="9">
         <v>46216</v>
@@ -3649,13 +3684,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q33" s="9">
         <v>46273</v>
@@ -3675,7 +3710,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B34" s="5">
         <v>46204.7872006713</v>
@@ -3685,16 +3720,16 @@
         <v>46224.170235694444</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I34" s="5">
         <v>46216</v>
@@ -3712,13 +3747,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3734,7 +3769,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B35" s="9">
         <v>46204.787204837965</v>
@@ -3744,16 +3779,16 @@
         <v>46206.67327987269</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I35" s="9">
         <v>46225</v>
@@ -3771,13 +3806,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3793,7 +3828,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B36" s="5">
         <v>46204.78722327546</v>
@@ -3805,16 +3840,16 @@
         <v>46217.69515425926</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I36" s="5">
         <v>46213</v>
@@ -3832,10 +3867,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3858,7 +3893,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B37" s="9">
         <v>46204.78722760417</v>
@@ -3870,16 +3905,16 @@
         <v>46206.769946203705</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I37" s="9">
         <v>46213</v>
@@ -3897,13 +3932,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3913,7 +3948,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B38" s="5">
         <v>46204.787231689814</v>
@@ -3925,16 +3960,16 @@
         <v>46217.69452489584</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I38" s="5">
         <v>46224</v>
@@ -3952,13 +3987,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3968,7 +4003,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B39" s="9">
         <v>46204.78728243055</v>
@@ -3980,16 +4015,16 @@
         <v>46206.769995821756</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I39" s="9">
         <v>46224</v>
@@ -4007,13 +4042,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -4023,7 +4058,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B40" s="5">
         <v>46204.78728729166</v>
@@ -4033,16 +4068,16 @@
         <v>46206.67363866898</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I40" s="5">
         <v>46245</v>
@@ -4060,13 +4095,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q40" s="5">
         <v>46255</v>
@@ -4086,7 +4121,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B41" s="9">
         <v>46204.787292175926</v>
@@ -4096,16 +4131,16 @@
         <v>46206.67358165509</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I41" s="9">
         <v>46245</v>
@@ -4123,13 +4158,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4145,7 +4180,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B42" s="5">
         <v>46204.78730063657</v>
@@ -4155,16 +4190,16 @@
         <v>46206.673579016206</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I42" s="5">
         <v>46247</v>
@@ -4182,13 +4217,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4204,7 +4239,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B43" s="9">
         <v>46204.793668136575</v>
@@ -4214,16 +4249,16 @@
         <v>46209.87015284722</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I43" s="9">
         <v>46245</v>
@@ -4241,10 +4276,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4267,7 +4302,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B44" s="5">
         <v>46204.794818298615</v>
@@ -4277,16 +4312,16 @@
         <v>46225.820673090275</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I44" s="5">
         <v>46245</v>
@@ -4304,13 +4339,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4320,7 +4355,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B45" s="9">
         <v>46204.794902430556</v>
@@ -4330,16 +4365,16 @@
         <v>46206.673743865744</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I45" s="9">
         <v>46247</v>
@@ -4357,13 +4392,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4373,7 +4408,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B46" s="5">
         <v>46204.7938509375</v>
@@ -4383,16 +4418,16 @@
         <v>46206.67393748843</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I46" s="5">
         <v>46245</v>
@@ -4410,10 +4445,10 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4436,7 +4471,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B47" s="9">
         <v>46204.795001412036</v>
@@ -4446,16 +4481,16 @@
         <v>46225.82063202546</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I47" s="9">
         <v>46245</v>
@@ -4473,13 +4508,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
@@ -4489,7 +4524,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B48" s="5">
         <v>46204.795060543984</v>
@@ -4499,16 +4534,16 @@
         <v>46206.67387746528</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I48" s="5">
         <v>46247</v>
@@ -4526,13 +4561,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4542,7 +4577,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B49" s="9">
         <v>46204.7939687037</v>
@@ -4552,16 +4587,16 @@
         <v>46206.67465699074</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I49" s="9">
         <v>46241</v>
@@ -4579,10 +4614,10 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4605,7 +4640,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B50" s="5">
         <v>46204.795132997686</v>
@@ -4615,16 +4650,16 @@
         <v>46206.67409482639</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4642,13 +4677,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4658,7 +4693,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B51" s="9">
         <v>46204.795219293985</v>
@@ -4668,16 +4703,16 @@
         <v>46206.67409221065</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I51" s="9">
         <v>46246</v>
@@ -4695,13 +4730,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4711,7 +4746,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B52" s="5">
         <v>46206.65895994213</v>
@@ -4721,16 +4756,16 @@
         <v>46206.674336111115</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4746,10 +4781,10 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>26</v>
@@ -4762,7 +4797,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B53" s="9">
         <v>46204.787306770835</v>
@@ -4772,7 +4807,7 @@
         <v>46217.8575847801</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>25</v>
@@ -4796,7 +4831,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>26</v>
@@ -4809,7 +4844,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B54" s="5">
         <v>46204.78731047454</v>
@@ -4821,16 +4856,16 @@
         <v>46219.20085231481</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I54" s="5">
         <v>46212</v>
@@ -4848,13 +4883,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q54" s="5">
         <v>46218</v>
@@ -4874,7 +4909,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B55" s="9">
         <v>46204.78731518518</v>
@@ -4883,19 +4918,19 @@
         <v>46217.85757222222</v>
       </c>
       <c r="D55" s="9">
-        <v>46217.85759137732</v>
+        <v>46232.20591013889</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I55" s="9">
         <v>46233</v>
@@ -4913,13 +4948,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q55" s="9">
         <v>46239</v>
@@ -4930,8 +4965,8 @@
       <c r="S55" s="10">
         <v>1</v>
       </c>
-      <c r="T55" s="7" t="s">
-        <v>53</v>
+      <c r="T55" s="12" t="s">
+        <v>187</v>
       </c>
       <c r="U55" s="7" t="s">
         <v>27</v>
@@ -4939,7 +4974,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B56" s="5">
         <v>46204.78732028935</v>
@@ -4949,16 +4984,16 @@
         <v>46217.857591875</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I56" s="5">
         <v>46240</v>
@@ -4976,13 +5011,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q56" s="5">
         <v>46240</v>
@@ -4997,12 +5032,12 @@
         <v>53</v>
       </c>
       <c r="U56" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B57" s="9">
         <v>46204.787326770835</v>
@@ -5012,16 +5047,16 @@
         <v>46206.67498217593</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="I57" s="9">
         <v>46288</v>
@@ -5039,13 +5074,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q57" s="9">
         <v>46288</v>
@@ -5065,7 +5100,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B58" s="5">
         <v>46205.8929956713</v>
@@ -5075,16 +5110,16 @@
         <v>46206.67494384259</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="I58" s="5">
         <v>46288</v>
@@ -5102,13 +5137,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5118,7 +5153,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B59" s="9">
         <v>46205.89308850694</v>
@@ -5128,16 +5163,16 @@
         <v>46206.67494135417</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="I59" s="9">
         <v>46288</v>
@@ -5155,13 +5190,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5171,7 +5206,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B60" s="5">
         <v>46205.89321678241</v>
@@ -5181,16 +5216,16 @@
         <v>46206.67493778935</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="I60" s="5">
         <v>46288</v>
@@ -5208,13 +5243,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5224,7 +5259,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B61" s="9">
         <v>46204.787330555555</v>
@@ -5234,7 +5269,7 @@
         <v>46206.65997969908</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>25</v>
@@ -5258,7 +5293,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5271,7 +5306,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B62" s="5">
         <v>46204.78733380787</v>
@@ -5281,16 +5316,16 @@
         <v>46206.67512555556</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I62" s="5">
         <v>46258</v>
@@ -5308,13 +5343,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q62" s="5">
         <v>46259</v>
@@ -5334,7 +5369,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B63" s="9">
         <v>46204.78733813658</v>
@@ -5344,16 +5379,16 @@
         <v>46206.67526587963</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I63" s="9">
         <v>46260</v>
@@ -5371,13 +5406,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q63" s="9">
         <v>46261</v>
@@ -5397,7 +5432,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B64" s="5">
         <v>46204.79962430555</v>
@@ -5407,16 +5442,16 @@
         <v>46206.67512305555</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I64" s="5">
         <v>46258</v>
@@ -5434,13 +5469,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q64" s="5">
         <v>46259</v>
@@ -5460,7 +5495,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B65" s="9">
         <v>46204.79970230324</v>
@@ -5470,16 +5505,16 @@
         <v>46206.67526299768</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I65" s="9">
         <v>46260</v>
@@ -5497,13 +5532,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q65" s="9">
         <v>46261</v>
@@ -5523,7 +5558,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B66" s="5">
         <v>46204.799834722224</v>
@@ -5533,16 +5568,16 @@
         <v>46206.67512025463</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I66" s="5">
         <v>46258</v>
@@ -5560,13 +5595,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q66" s="5">
         <v>46259</v>
@@ -5586,7 +5621,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B67" s="9">
         <v>46204.80007783565</v>
@@ -5596,16 +5631,16 @@
         <v>46206.67526012732</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I67" s="9">
         <v>46260</v>
@@ -5623,13 +5658,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="O67" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="P67" s="10" t="s">
         <v>217</v>
-      </c>
-      <c r="P67" s="10" t="s">
-        <v>215</v>
       </c>
       <c r="Q67" s="9">
         <v>46261</v>
@@ -5649,7 +5684,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B68" s="5">
         <v>46204.787342662035</v>
@@ -5659,7 +5694,7 @@
         <v>46206.66163074074</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5683,7 +5718,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5696,7 +5731,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B69" s="9">
         <v>46204.78734565972</v>
@@ -5706,16 +5741,16 @@
         <v>46206.67535149306</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I69" s="9">
         <v>46262</v>
@@ -5733,13 +5768,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q69" s="9">
         <v>46266</v>
@@ -5759,7 +5794,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B70" s="5">
         <v>46204.78735021991</v>
@@ -5769,16 +5804,16 @@
         <v>46206.67558131945</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I70" s="5">
         <v>46267</v>
@@ -5796,13 +5831,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q70" s="5">
         <v>46273</v>
@@ -5822,7 +5857,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B71" s="9">
         <v>46204.83329071759</v>
@@ -5832,16 +5867,16 @@
         <v>46206.67551582176</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I71" s="9">
         <v>46267</v>
@@ -5859,13 +5894,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q71" s="10"/>
       <c r="R71" s="10"/>
@@ -5875,7 +5910,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B72" s="5">
         <v>46204.83348987269</v>
@@ -5885,16 +5920,16 @@
         <v>46206.67551341435</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I72" s="5">
         <v>46267</v>
@@ -5912,13 +5947,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5928,7 +5963,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B73" s="9">
         <v>46204.83350201389</v>
@@ -5938,16 +5973,16 @@
         <v>46206.67551030093</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I73" s="9">
         <v>46267</v>
@@ -5965,13 +6000,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -5981,7 +6016,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B74" s="5">
         <v>46204.787355625</v>
@@ -5991,16 +6026,16 @@
         <v>46206.67580866898</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I74" s="5">
         <v>46274</v>
@@ -6018,13 +6053,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q74" s="5">
         <v>46274</v>
@@ -6044,7 +6079,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B75" s="9">
         <v>46204.83355802084</v>
@@ -6054,16 +6089,16 @@
         <v>46206.67575559027</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I75" s="10"/>
       <c r="J75" s="9">
@@ -6079,13 +6114,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -6095,7 +6130,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B76" s="5">
         <v>46204.833570069444</v>
@@ -6105,16 +6140,16 @@
         <v>46206.67575268519</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I76" s="6"/>
       <c r="J76" s="5">
@@ -6130,13 +6165,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6146,7 +6181,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B77" s="9">
         <v>46204.833579004626</v>
@@ -6156,16 +6191,16 @@
         <v>46206.67574885416</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I77" s="10"/>
       <c r="J77" s="9">
@@ -6181,13 +6216,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6197,7 +6232,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B78" s="5">
         <v>46204.78736071759</v>
@@ -6207,7 +6242,7 @@
         <v>46206.67094998843</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>25</v>
@@ -6231,7 +6266,7 @@
         <v>26</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6244,7 +6279,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B79" s="9">
         <v>46204.78736410879</v>
@@ -6254,16 +6289,16 @@
         <v>46213.50330894676</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I79" s="9">
         <v>46210</v>
@@ -6281,13 +6316,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q79" s="9">
         <v>46210</v>
@@ -6302,12 +6337,12 @@
         <v>33</v>
       </c>
       <c r="U79" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B80" s="5">
         <v>46204.78737366898</v>
@@ -6317,16 +6352,16 @@
         <v>46217.69454351852</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I80" s="5">
         <v>46253</v>
@@ -6344,13 +6379,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q80" s="5">
         <v>46253</v>
@@ -6365,12 +6400,12 @@
         <v>53</v>
       </c>
       <c r="U80" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B81" s="9">
         <v>46204.78737825232</v>
@@ -6380,16 +6415,16 @@
         <v>46206.67600082176</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I81" s="9">
         <v>46274</v>
@@ -6407,13 +6442,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q81" s="9">
         <v>46274</v>
@@ -6433,7 +6468,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B82" s="5">
         <v>46206.567318657406</v>
@@ -6449,10 +6484,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I82" s="6"/>
       <c r="J82" s="5">
@@ -6468,13 +6503,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6484,7 +6519,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B83" s="9">
         <v>46206.56766555556</v>
@@ -6500,10 +6535,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I83" s="10"/>
       <c r="J83" s="9">
@@ -6519,13 +6554,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6535,7 +6570,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B84" s="5">
         <v>46206.56768260417</v>
@@ -6551,10 +6586,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I84" s="6"/>
       <c r="J84" s="5">
@@ -6570,13 +6605,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6586,7 +6621,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B85" s="9">
         <v>46206.56769806713</v>
@@ -6602,10 +6637,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I85" s="10"/>
       <c r="J85" s="9">
@@ -6621,13 +6656,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6637,7 +6672,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B86" s="5">
         <v>46206.56771423611</v>
@@ -6653,10 +6688,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I86" s="6"/>
       <c r="J86" s="5">
@@ -6672,13 +6707,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6688,7 +6723,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B87" s="9">
         <v>46206.56772880787</v>
@@ -6704,10 +6739,10 @@
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I87" s="10"/>
       <c r="J87" s="9">
@@ -6723,13 +6758,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6739,7 +6774,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B88" s="5">
         <v>46206.567743506945</v>
@@ -6755,10 +6790,10 @@
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I88" s="6"/>
       <c r="J88" s="5">
@@ -6774,13 +6809,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6790,7 +6825,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B89" s="9">
         <v>46206.56775844908</v>
@@ -6806,10 +6841,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I89" s="10"/>
       <c r="J89" s="9">
@@ -6825,13 +6860,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6841,7 +6876,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B90" s="5">
         <v>46206.56777289352</v>
@@ -6857,10 +6892,10 @@
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I90" s="6"/>
       <c r="J90" s="5">
@@ -6876,13 +6911,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6892,7 +6927,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B91" s="9">
         <v>46206.67094809028</v>
@@ -6902,16 +6937,16 @@
         <v>46206.67590806713</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I91" s="9">
         <v>46274</v>
@@ -6929,10 +6964,10 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P91" s="10" t="s">
         <v>26</v>
@@ -6949,7 +6984,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B92" s="5">
         <v>46204.78738409722</v>
@@ -6959,7 +6994,7 @@
         <v>46206.66745490741</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>25</v>
@@ -6983,7 +7018,7 @@
         <v>26</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>26</v>
@@ -6996,7 +7031,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B93" s="9">
         <v>46204.787387268516</v>
@@ -7006,16 +7041,16 @@
         <v>46223.56188282407</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H93" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I93" s="9">
         <v>46275</v>
@@ -7033,13 +7068,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q93" s="9">
         <v>46281</v>
@@ -7059,7 +7094,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B94" s="5">
         <v>46204.84491833333</v>
@@ -7069,16 +7104,16 @@
         <v>46223.56049512731</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I94" s="5">
         <v>46275</v>
@@ -7096,13 +7131,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7112,7 +7147,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B95" s="9">
         <v>46204.84493530093</v>
@@ -7122,16 +7157,16 @@
         <v>46223.56049449074</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I95" s="9">
         <v>46275</v>
@@ -7149,13 +7184,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -7165,7 +7200,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B96" s="5">
         <v>46204.84494427084</v>
@@ -7175,16 +7210,16 @@
         <v>46223.56049383101</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I96" s="5">
         <v>46275</v>
@@ -7202,13 +7237,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7218,26 +7253,26 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B97" s="9">
         <v>46204.78739225694</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46223.56188216435</v>
+        <v>46232.51957259259</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I97" s="9">
         <v>46282</v>
@@ -7255,13 +7290,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q97" s="9">
         <v>46282</v>
@@ -7281,7 +7316,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B98" s="5">
         <v>46204.84497997686</v>
@@ -7291,16 +7326,16 @@
         <v>46223.560602199075</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I98" s="5">
         <v>46282</v>
@@ -7318,13 +7353,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7334,7 +7369,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B99" s="9">
         <v>46204.84498876157</v>
@@ -7344,16 +7379,16 @@
         <v>46223.56060143519</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I99" s="9">
         <v>46282</v>
@@ -7371,13 +7406,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7387,7 +7422,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B100" s="5">
         <v>46204.84499563657</v>
@@ -7397,16 +7432,16 @@
         <v>46223.560600763885</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I100" s="5">
         <v>46282</v>
@@ -7424,13 +7459,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7440,7 +7475,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B101" s="9">
         <v>46204.78740502315</v>
@@ -7450,16 +7485,16 @@
         <v>46223.56188153935</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I101" s="9">
         <v>46286</v>
@@ -7477,13 +7512,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q101" s="9">
         <v>46286</v>
@@ -7503,7 +7538,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B102" s="5">
         <v>46204.84507945602</v>
@@ -7513,16 +7548,16 @@
         <v>46223.5607075</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I102" s="5">
         <v>46286</v>
@@ -7540,13 +7575,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7556,7 +7591,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B103" s="9">
         <v>46204.84508817129</v>
@@ -7566,16 +7601,16 @@
         <v>46223.560706840275</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I103" s="9">
         <v>46286</v>
@@ -7593,13 +7628,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7609,7 +7644,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B104" s="5">
         <v>46204.845093854165</v>
@@ -7619,16 +7654,16 @@
         <v>46223.56070621528</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I104" s="5">
         <v>46286</v>
@@ -7646,13 +7681,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7662,7 +7697,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B105" s="9">
         <v>46204.78741121528</v>
@@ -7672,16 +7707,16 @@
         <v>46223.561880925925</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I105" s="9">
         <v>46287</v>
@@ -7699,13 +7734,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q105" s="9">
         <v>46287</v>
@@ -7725,7 +7760,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B106" s="5">
         <v>46204.84513122685</v>
@@ -7735,16 +7770,16 @@
         <v>46223.56167888889</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I106" s="5">
         <v>46287</v>
@@ -7762,13 +7797,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7778,7 +7813,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B107" s="9">
         <v>46204.84513944444</v>
@@ -7788,16 +7823,16 @@
         <v>46223.561678287035</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I107" s="9">
         <v>46287</v>
@@ -7815,13 +7850,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q107" s="10"/>
       <c r="R107" s="10"/>
@@ -7831,7 +7866,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B108" s="5">
         <v>46204.8451466088</v>
@@ -7841,16 +7876,16 @@
         <v>46223.56167766204</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I108" s="5">
         <v>46287</v>
@@ -7868,13 +7903,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7884,7 +7919,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B109" s="9">
         <v>46204.787473310185</v>
@@ -7894,16 +7929,16 @@
         <v>46223.56188028935</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I109" s="9">
         <v>46289</v>
@@ -7921,13 +7956,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q109" s="9">
         <v>46289</v>
@@ -7947,7 +7982,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B110" s="5">
         <v>46204.84518325231</v>
@@ -7957,16 +7992,16 @@
         <v>46223.56179313657</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I110" s="5">
         <v>46289</v>
@@ -7984,13 +8019,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8000,7 +8035,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B111" s="9">
         <v>46204.845191898145</v>
@@ -8010,16 +8045,16 @@
         <v>46223.56179228009</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I111" s="9">
         <v>46289</v>
@@ -8037,13 +8072,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -8053,7 +8088,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B112" s="5">
         <v>46204.84520083333</v>
@@ -8063,16 +8098,16 @@
         <v>46223.56179165509</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I112" s="5">
         <v>46289</v>
@@ -8090,13 +8125,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8106,7 +8141,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B113" s="9">
         <v>46204.78748032407</v>
@@ -8116,7 +8151,7 @@
         <v>46206.668344247686</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>25</v>
@@ -8140,7 +8175,7 @@
         <v>26</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="P113" s="10" t="s">
         <v>26</v>
@@ -8153,7 +8188,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B114" s="5">
         <v>46204.787484155095</v>
@@ -8163,16 +8198,16 @@
         <v>46206.677181631945</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="I114" s="5">
         <v>46290</v>
@@ -8190,13 +8225,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q114" s="5">
         <v>46290</v>
@@ -8216,7 +8251,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B115" s="9">
         <v>46206.61281571759</v>
@@ -8226,16 +8261,16 @@
         <v>46206.67717564815</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="I115" s="9">
         <v>46290</v>
@@ -8253,13 +8288,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -8269,7 +8304,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B116" s="5">
         <v>46206.612829722224</v>
@@ -8279,16 +8314,16 @@
         <v>46206.67717299769</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="I116" s="5">
         <v>46290</v>
@@ -8306,13 +8341,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8322,7 +8357,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B117" s="9">
         <v>46206.61284180556</v>
@@ -8332,16 +8367,16 @@
         <v>46206.67717023148</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="I117" s="9">
         <v>46290</v>
@@ -8359,13 +8394,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8375,7 +8410,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B118" s="5">
         <v>46206.61323981482</v>
@@ -8391,10 +8426,10 @@
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="I118" s="5">
         <v>46290</v>
@@ -8412,13 +8447,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8428,7 +8463,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B119" s="9">
         <v>46206.613256446755</v>
@@ -8444,10 +8479,10 @@
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="I119" s="9">
         <v>46290</v>
@@ -8465,13 +8500,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="O119" s="10" t="s">
         <v>59</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q119" s="10"/>
       <c r="R119" s="10"/>
@@ -8481,7 +8516,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B120" s="5">
         <v>46206.61328513889</v>
@@ -8497,10 +8532,10 @@
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="I120" s="5">
         <v>46290</v>
@@ -8518,13 +8553,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8534,7 +8569,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B121" s="9">
         <v>46206.613270925925</v>
@@ -8550,10 +8585,10 @@
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="I121" s="9">
         <v>46290</v>
@@ -8571,13 +8606,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="O121" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8587,7 +8622,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B122" s="5">
         <v>46206.6133403125</v>
@@ -8603,10 +8638,10 @@
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="I122" s="5">
         <v>46290</v>
@@ -8624,13 +8659,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8640,7 +8675,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B123" s="9">
         <v>46206.613361041665</v>
@@ -8656,10 +8691,10 @@
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="I123" s="9">
         <v>46290</v>
@@ -8677,13 +8712,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="O123" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P123" s="10" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q123" s="10"/>
       <c r="R123" s="10"/>
@@ -8693,7 +8728,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B124" s="5">
         <v>46206.613371493055</v>
@@ -8709,10 +8744,10 @@
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="I124" s="5">
         <v>46290</v>
@@ -8730,13 +8765,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8746,7 +8781,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B125" s="9">
         <v>46206.61338284722</v>
@@ -8762,10 +8797,10 @@
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="I125" s="9">
         <v>46290</v>
@@ -8783,13 +8818,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="O125" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -8799,7 +8834,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B126" s="5">
         <v>46206.61339653935</v>
@@ -8815,10 +8850,10 @@
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="I126" s="5">
         <v>46290</v>
@@ -8836,13 +8871,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8852,7 +8887,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B127" s="9">
         <v>46204.78748974537</v>
@@ -8862,16 +8897,16 @@
         <v>46223.56209584491</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I127" s="9">
         <v>46293</v>
@@ -8883,19 +8918,19 @@
         <v>26</v>
       </c>
       <c r="L127" s="10" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q127" s="9">
         <v>46293</v>
@@ -8915,7 +8950,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B128" s="5">
         <v>46204.84566665509</v>
@@ -8925,16 +8960,16 @@
         <v>46223.562056400464</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I128" s="5">
         <v>46293</v>
@@ -8952,13 +8987,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -8968,7 +9003,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B129" s="9">
         <v>46204.8456746875</v>
@@ -8978,16 +9013,16 @@
         <v>46223.56205577546</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I129" s="9">
         <v>46293</v>
@@ -9005,13 +9040,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -9021,7 +9056,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B130" s="5">
         <v>46204.84568395834</v>
@@ -9031,16 +9066,16 @@
         <v>46223.56205517361</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I130" s="5">
         <v>46293</v>
@@ -9058,13 +9093,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9074,7 +9109,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B131" s="9">
         <v>46204.84577770834</v>
@@ -9084,16 +9119,16 @@
         <v>46223.562054548616</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I131" s="9">
         <v>46293</v>
@@ -9111,13 +9146,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O131" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P131" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q131" s="10"/>
       <c r="R131" s="10"/>
@@ -9127,7 +9162,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B132" s="5">
         <v>46204.845803958335</v>
@@ -9137,16 +9172,16 @@
         <v>46223.56205386574</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I132" s="5">
         <v>46293</v>
@@ -9164,13 +9199,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O132" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9180,7 +9215,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B133" s="9">
         <v>46204.8458116088</v>
@@ -9190,16 +9225,16 @@
         <v>46223.562053217596</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I133" s="9">
         <v>46293</v>
@@ -9217,13 +9252,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O133" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9233,7 +9268,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B134" s="5">
         <v>46204.84582686343</v>
@@ -9243,16 +9278,16 @@
         <v>46223.56205256944</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I134" s="5">
         <v>46293</v>
@@ -9270,13 +9305,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9286,7 +9321,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B135" s="9">
         <v>46204.84581974537</v>
@@ -9296,16 +9331,16 @@
         <v>46223.56205195602</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H135" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I135" s="9">
         <v>46293</v>
@@ -9323,13 +9358,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O135" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q135" s="10"/>
       <c r="R135" s="10"/>
@@ -9339,7 +9374,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B136" s="5">
         <v>46204.84583605324</v>
@@ -9349,16 +9384,16 @@
         <v>46223.562051354165</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I136" s="5">
         <v>46293</v>
@@ -9376,13 +9411,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O136" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9392,7 +9427,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B137" s="9">
         <v>46204.84584422453</v>
@@ -9402,16 +9437,16 @@
         <v>46223.562050740744</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H137" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I137" s="9">
         <v>46293</v>
@@ -9429,13 +9464,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O137" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9445,7 +9480,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B138" s="5">
         <v>46204.845850983795</v>
@@ -9455,16 +9490,16 @@
         <v>46223.562050092594</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I138" s="5">
         <v>46293</v>
@@ -9482,13 +9517,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O138" s="6" t="s">
         <v>56</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9498,7 +9533,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B139" s="9">
         <v>46204.84585899305</v>
@@ -9508,16 +9543,16 @@
         <v>46223.5620494676</v>
       </c>
       <c r="E139" s="10" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F139" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H139" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I139" s="9">
         <v>46293</v>
@@ -9535,13 +9570,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O139" s="10" t="s">
         <v>56</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q139" s="10"/>
       <c r="R139" s="10"/>
@@ -9551,7 +9586,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B140" s="5">
         <v>46204.78749533565</v>
@@ -9561,16 +9596,16 @@
         <v>46206.67787028935</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I140" s="5">
         <v>46294</v>
@@ -9588,13 +9623,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q140" s="5">
         <v>46294</v>
@@ -9614,7 +9649,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B141" s="9">
         <v>46204.84595449074</v>
@@ -9624,16 +9659,16 @@
         <v>46206.67786329861</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H141" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I141" s="9">
         <v>46294</v>
@@ -9651,13 +9686,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P141" s="10" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q141" s="10"/>
       <c r="R141" s="10"/>
@@ -9667,7 +9702,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B142" s="5">
         <v>46204.845964189815</v>
@@ -9677,16 +9712,16 @@
         <v>46206.677860254626</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I142" s="5">
         <v>46294</v>
@@ -9704,13 +9739,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9720,7 +9755,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B143" s="9">
         <v>46204.84597238426</v>
@@ -9730,16 +9765,16 @@
         <v>46206.67785763889</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H143" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I143" s="9">
         <v>46294</v>
@@ -9757,13 +9792,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q143" s="10"/>
       <c r="R143" s="10"/>
@@ -9773,7 +9808,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B144" s="5">
         <v>46204.846036469906</v>
@@ -9783,16 +9818,16 @@
         <v>46206.67785519676</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I144" s="5">
         <v>46294</v>
@@ -9810,13 +9845,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -9826,7 +9861,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B145" s="9">
         <v>46204.846047893516</v>
@@ -9836,16 +9871,16 @@
         <v>46206.6778525</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H145" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I145" s="9">
         <v>46294</v>
@@ -9863,13 +9898,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -9879,7 +9914,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B146" s="5">
         <v>46204.846056724535</v>
@@ -9889,16 +9924,16 @@
         <v>46206.67784956019</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I146" s="5">
         <v>46294</v>
@@ -9916,13 +9951,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -9932,7 +9967,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B147" s="9">
         <v>46204.846065578706</v>
@@ -9942,16 +9977,16 @@
         <v>46206.677846921295</v>
       </c>
       <c r="E147" s="10" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F147" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H147" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I147" s="9">
         <v>46294</v>
@@ -9969,13 +10004,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="10" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="O147" s="10" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="P147" s="10" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q147" s="10"/>
       <c r="R147" s="10"/>
@@ -9985,7 +10020,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B148" s="5">
         <v>46204.846073252316</v>
@@ -9995,16 +10030,16 @@
         <v>46206.67784445602</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I148" s="5">
         <v>46294</v>
@@ -10022,13 +10057,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10038,7 +10073,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B149" s="9">
         <v>46204.84608019676</v>
@@ -10048,16 +10083,16 @@
         <v>46206.6778419676</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H149" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I149" s="9">
         <v>46294</v>
@@ -10075,13 +10110,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="10" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="P149" s="10" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q149" s="10"/>
       <c r="R149" s="10"/>
@@ -10091,7 +10126,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B150" s="5">
         <v>46204.84608666667</v>
@@ -10101,16 +10136,16 @@
         <v>46206.67783399306</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I150" s="5">
         <v>46294</v>
@@ -10128,13 +10163,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10144,7 +10179,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B151" s="9">
         <v>46204.84609472222</v>
@@ -10154,16 +10189,16 @@
         <v>46206.677833344904</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F151" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G151" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H151" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I151" s="9">
         <v>46294</v>
@@ -10181,13 +10216,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="10" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="P151" s="10" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q151" s="10"/>
       <c r="R151" s="10"/>
@@ -10197,7 +10232,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B152" s="5">
         <v>46204.84610289352</v>
@@ -10207,16 +10242,16 @@
         <v>46206.67783269676</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I152" s="5">
         <v>46294</v>
@@ -10234,13 +10269,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10250,7 +10285,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="8" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B153" s="9">
         <v>46204.78749967593</v>
@@ -10260,16 +10295,16 @@
         <v>46206.67812460648</v>
       </c>
       <c r="E153" s="10" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F153" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G153" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H153" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I153" s="10"/>
       <c r="J153" s="9">
@@ -10285,13 +10320,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="O153" s="10" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="P153" s="10" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q153" s="9">
         <v>46295</v>
@@ -10311,7 +10346,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B154" s="5">
         <v>46204.846246076384</v>
@@ -10321,16 +10356,16 @@
         <v>46206.67812013889</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I154" s="5">
         <v>46295</v>
@@ -10348,13 +10383,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
@@ -10364,7 +10399,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="8" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B155" s="9">
         <v>46204.84626494213</v>
@@ -10374,16 +10409,16 @@
         <v>46206.678117118056</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G155" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H155" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I155" s="9">
         <v>46295</v>
@@ -10401,13 +10436,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="10" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="P155" s="10" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q155" s="10"/>
       <c r="R155" s="10"/>
@@ -10417,7 +10452,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B156" s="5">
         <v>46204.84627579861</v>
@@ -10427,16 +10462,16 @@
         <v>46206.67810802083</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I156" s="5">
         <v>46295</v>
@@ -10454,13 +10489,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -10470,7 +10505,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B157" s="9">
         <v>46204.846348113424</v>
@@ -10480,16 +10515,16 @@
         <v>46206.67810481481</v>
       </c>
       <c r="E157" s="10" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H157" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I157" s="9">
         <v>46295</v>
@@ -10507,13 +10542,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="10" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="O157" s="10" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="P157" s="10" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q157" s="10"/>
       <c r="R157" s="10"/>
@@ -10523,7 +10558,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B158" s="5">
         <v>46204.846357789356</v>
@@ -10533,16 +10568,16 @@
         <v>46206.67810172454</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H158" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I158" s="5">
         <v>46295</v>
@@ -10560,13 +10595,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -10576,7 +10611,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B159" s="9">
         <v>46204.846365879624</v>
@@ -10586,16 +10621,16 @@
         <v>46206.67809884259</v>
       </c>
       <c r="E159" s="10" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F159" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G159" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H159" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I159" s="9">
         <v>46295</v>
@@ -10613,13 +10648,13 @@
         <v>26</v>
       </c>
       <c r="N159" s="10" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="O159" s="10" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="P159" s="10" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q159" s="10"/>
       <c r="R159" s="10"/>
@@ -10629,7 +10664,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B160" s="5">
         <v>46204.846373692126</v>
@@ -10639,16 +10674,16 @@
         <v>46206.678095509254</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H160" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I160" s="5">
         <v>46295</v>
@@ -10666,13 +10701,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -10682,7 +10717,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B161" s="9">
         <v>46204.8463796412</v>
@@ -10692,16 +10727,16 @@
         <v>46206.67809255787</v>
       </c>
       <c r="E161" s="10" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F161" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G161" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H161" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I161" s="9">
         <v>46295</v>
@@ -10719,13 +10754,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="10" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="O161" s="10" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="P161" s="10" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q161" s="10"/>
       <c r="R161" s="10"/>
@@ -10735,7 +10770,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B162" s="5">
         <v>46204.846388715276</v>
@@ -10745,16 +10780,16 @@
         <v>46206.678089270834</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H162" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I162" s="5">
         <v>46295</v>
@@ -10772,13 +10807,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -10788,7 +10823,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B163" s="9">
         <v>46204.84640113426</v>
@@ -10798,16 +10833,16 @@
         <v>46206.67808063657</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F163" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G163" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H163" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I163" s="9">
         <v>46295</v>
@@ -10825,13 +10860,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="10" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="O163" s="10" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="P163" s="10" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q163" s="10"/>
       <c r="R163" s="10"/>
@@ -10841,7 +10876,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B164" s="5">
         <v>46204.84641309028</v>
@@ -10851,16 +10886,16 @@
         <v>46206.67807998843</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G164" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H164" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I164" s="5">
         <v>46295</v>
@@ -10878,13 +10913,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -10894,7 +10929,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="8" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B165" s="9">
         <v>46204.846406701385</v>
@@ -10904,16 +10939,16 @@
         <v>46206.67807929398</v>
       </c>
       <c r="E165" s="10" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G165" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H165" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I165" s="9">
         <v>46295</v>
@@ -10931,13 +10966,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="10" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="O165" s="10" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="P165" s="10" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q165" s="10"/>
       <c r="R165" s="10"/>
@@ -10947,7 +10982,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B166" s="5">
         <v>46204.7875055787</v>
@@ -10957,7 +10992,7 @@
         <v>46206.66985314815</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>25</v>
@@ -10981,7 +11016,7 @@
         <v>26</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="P166" s="6" t="s">
         <v>26</v>
@@ -11000,7 +11035,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="8" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B167" s="9">
         <v>46204.787509016205</v>
@@ -11010,16 +11045,16 @@
         <v>46206.67820732639</v>
       </c>
       <c r="E167" s="10" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F167" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G167" s="10" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="H167" s="10" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="I167" s="9">
         <v>46296</v>
@@ -11037,13 +11072,13 @@
         <v>26</v>
       </c>
       <c r="N167" s="10" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="O167" s="10" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="P167" s="10" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Q167" s="9">
         <v>46304</v>
@@ -11063,7 +11098,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B168" s="5">
         <v>46204.78751333333</v>
@@ -11073,7 +11108,7 @@
         <v>46206.67824334491</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
@@ -11100,13 +11135,13 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Q168" s="5">
         <v>46304</v>
@@ -11126,7 +11161,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B169" s="9">
         <v>46204.787518564815</v>
@@ -11136,7 +11171,7 @@
         <v>46212.76788890046</v>
       </c>
       <c r="E169" s="10" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>25</v>
@@ -11160,7 +11195,7 @@
         <v>26</v>
       </c>
       <c r="O169" s="10" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="P169" s="10" t="s">
         <v>26</v>
@@ -11173,7 +11208,7 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B170" s="5">
         <v>46204.78752182871</v>
@@ -11183,7 +11218,7 @@
         <v>46206.67830775463</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
@@ -11210,13 +11245,13 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="P170" s="6" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="Q170" s="5">
         <v>46315</v>
@@ -11236,7 +11271,7 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B171" s="9">
         <v>46204.78752627315</v>
@@ -11246,7 +11281,7 @@
         <v>46212.767965266205</v>
       </c>
       <c r="E171" s="10" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>26</v>
@@ -11273,13 +11308,13 @@
         <v>26</v>
       </c>
       <c r="N171" s="10" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="O171" s="10" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="P171" s="10" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="Q171" s="9">
         <v>46324</v>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -476,7 +476,7 @@
     <t xml:space="preserve">propuesta fabricación externa </t>
   </si>
   <si>
-    <t xml:space="preserve">generacion oc fabricación externa ,Generacion Oc  OT 4375,Generacion Oc  OT 4376 ,Generacion Oc  OT 4377,Generacion Oc  OT4378,Generacion Oc OT 4376 OT 4381  ,Generacion Oc OT 4382 - OT 4383 </t>
+    <t>generacion oc fabricación externa ,Generacion Oc  OT 4375,Generacion Oc  OT 4376 ,Generacion Oc  OT 4377,Generacion Oc  OT4378,Generacion Oc OT 4376 OT 4381  ,Generacion Oc OT 4382 - OT 4383 ,Generacion Oc ot 4385- 4386</t>
   </si>
   <si>
     <t>1216208498022048</t>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46231.56026616898</v>
+        <v>46232.835847650465</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>107</v>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -4981,7 +4981,7 @@
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46217.857591875</v>
+        <v>46233.199020671294</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>101</v>
@@ -5028,8 +5028,8 @@
       <c r="S56" s="6">
         <v>0</v>
       </c>
-      <c r="T56" s="7" t="s">
-        <v>53</v>
+      <c r="T56" s="12" t="s">
+        <v>187</v>
       </c>
       <c r="U56" s="12" t="s">
         <v>89</v>
@@ -7260,7 +7260,7 @@
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46232.51957259259</v>
+        <v>46233.52674290509</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>277</v>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -4256,9 +4256,11 @@
       <c r="B43" s="9">
         <v>46204.793668136575</v>
       </c>
-      <c r="C43" s="10"/>
+      <c r="C43" s="9">
+        <v>46240.56793090278</v>
+      </c>
       <c r="D43" s="9">
-        <v>46209.87015284722</v>
+        <v>46240.56794395833</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>149</v>
@@ -4303,13 +4305,13 @@
         <v>46245</v>
       </c>
       <c r="S43" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T43" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="U43" s="11" t="s">
-        <v>54</v>
+      <c r="U43" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -4319,9 +4321,11 @@
       <c r="B44" s="5">
         <v>46204.794818298615</v>
       </c>
-      <c r="C44" s="6"/>
+      <c r="C44" s="5">
+        <v>46240.567829039355</v>
+      </c>
       <c r="D44" s="5">
-        <v>46237.606909062495</v>
+        <v>46240.567830925924</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>105</v>
@@ -4372,9 +4376,11 @@
       <c r="B45" s="9">
         <v>46204.794902430556</v>
       </c>
-      <c r="C45" s="10"/>
+      <c r="C45" s="9">
+        <v>46240.5679153588</v>
+      </c>
       <c r="D45" s="9">
-        <v>46206.673743865744</v>
+        <v>46240.56791662037</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>152</v>
@@ -4936,7 +4942,7 @@
         <v>46217.85757222222</v>
       </c>
       <c r="D55" s="9">
-        <v>46238.54260697917</v>
+        <v>46240.20805547453</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>187</v>
@@ -4983,8 +4989,8 @@
       <c r="S55" s="10">
         <v>1</v>
       </c>
-      <c r="T55" s="12" t="s">
-        <v>100</v>
+      <c r="T55" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="U55" s="7" t="s">
         <v>27</v>
@@ -5459,7 +5465,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46206.67512305555</v>
+        <v>46240.56793171296</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>216</v>
@@ -5509,8 +5515,8 @@
       <c r="T64" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="U64" s="11" t="s">
-        <v>54</v>
+      <c r="U64" s="12" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1970" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1934" uniqueCount="393">
   <si>
     <t>50001569 - EUROHINCA</t>
   </si>
@@ -1267,7 +1267,7 @@
     <t>PACKING LIST,ot 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C,ot 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C,ot 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C,ot 4368 - TABLERO VDF 15 KW LOGICA M-E,ot 4368 - TABLERO VDF 15 KW LOGICA M-E,ot 4368 - TABLERO VDF 15 KW LOGICA M-E,ot 4368 - TABLERO VDF 15 KW LOGICA M-E,ot 4368 - TABLERO VDF 15 KW LOGICA M-E,ot 4368 - TABLERO VDF 15 KW LOGICA M-E,ot 4368 - TABLERO VDF 15 KW LOGICA M-E,ot 4368 - TABLERO VDF 15 KW LOGICA M-E,ot 4368 - TABLERO VDF 15 KW LOGICA M-E</t>
   </si>
   <si>
-    <t>Instalación de componentes,Logistica:,Costos,Gestion</t>
+    <t>Logistica:,Costos,Gestion</t>
   </si>
   <si>
     <t>1216208498022194</t>
@@ -1331,30 +1331,6 @@
   </si>
   <si>
     <t>Costos</t>
-  </si>
-  <si>
-    <t>1216219007318996</t>
-  </si>
-  <si>
-    <t>Puesta en marcha Servicios</t>
-  </si>
-  <si>
-    <t>Instalación de componentes,Pruebas de instalación componentes</t>
-  </si>
-  <si>
-    <t>1216218871140128</t>
-  </si>
-  <si>
-    <t>Instalación de componentes</t>
-  </si>
-  <si>
-    <t>Puesta en marcha Servicios,Pruebas de instalación componentes</t>
-  </si>
-  <si>
-    <t>1216218871140150</t>
-  </si>
-  <si>
-    <t>Pruebas de instalación componentes</t>
   </si>
 </sst>
 </file>
@@ -1878,7 +1854,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U171"/>
+  <dimension ref="A1:U168"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -10318,7 +10294,7 @@
       </c>
       <c r="C153" s="10"/>
       <c r="D153" s="9">
-        <v>46206.67812460648</v>
+        <v>46240.71677616898</v>
       </c>
       <c r="E153" s="10" t="s">
         <v>369</v>
@@ -11182,179 +11158,6 @@
         <v>53</v>
       </c>
       <c r="U168" s="11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="169" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A169" s="8" t="s">
-        <v>393</v>
-      </c>
-      <c r="B169" s="9">
-        <v>46204.787518564815</v>
-      </c>
-      <c r="C169" s="10"/>
-      <c r="D169" s="9">
-        <v>46212.76788890046</v>
-      </c>
-      <c r="E169" s="10" t="s">
-        <v>394</v>
-      </c>
-      <c r="F169" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G169" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H169" s="10"/>
-      <c r="I169" s="10"/>
-      <c r="J169" s="10"/>
-      <c r="K169" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L169" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M169" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="N169" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O169" s="10" t="s">
-        <v>395</v>
-      </c>
-      <c r="P169" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q169" s="10"/>
-      <c r="R169" s="10"/>
-      <c r="S169" s="10"/>
-      <c r="T169" s="10"/>
-      <c r="U169" s="10"/>
-    </row>
-    <row r="170" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A170" s="4" t="s">
-        <v>396</v>
-      </c>
-      <c r="B170" s="5">
-        <v>46204.78752182871</v>
-      </c>
-      <c r="C170" s="6"/>
-      <c r="D170" s="5">
-        <v>46206.67830775463</v>
-      </c>
-      <c r="E170" s="6" t="s">
-        <v>397</v>
-      </c>
-      <c r="F170" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G170" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="H170" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="I170" s="5">
-        <v>46307</v>
-      </c>
-      <c r="J170" s="5">
-        <v>46315</v>
-      </c>
-      <c r="K170" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L170" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M170" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N170" s="6" t="s">
-        <v>394</v>
-      </c>
-      <c r="O170" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="P170" s="6" t="s">
-        <v>398</v>
-      </c>
-      <c r="Q170" s="5">
-        <v>46315</v>
-      </c>
-      <c r="R170" s="5">
-        <v>46307</v>
-      </c>
-      <c r="S170" s="6">
-        <v>0</v>
-      </c>
-      <c r="T170" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="U170" s="11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="171" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A171" s="8" t="s">
-        <v>399</v>
-      </c>
-      <c r="B171" s="9">
-        <v>46204.78752627315</v>
-      </c>
-      <c r="C171" s="10"/>
-      <c r="D171" s="9">
-        <v>46212.767965266205</v>
-      </c>
-      <c r="E171" s="10" t="s">
-        <v>400</v>
-      </c>
-      <c r="F171" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G171" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="H171" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="I171" s="9">
-        <v>46316</v>
-      </c>
-      <c r="J171" s="9">
-        <v>46324</v>
-      </c>
-      <c r="K171" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L171" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M171" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N171" s="10" t="s">
-        <v>394</v>
-      </c>
-      <c r="O171" s="10" t="s">
-        <v>397</v>
-      </c>
-      <c r="P171" s="10" t="s">
-        <v>394</v>
-      </c>
-      <c r="Q171" s="9">
-        <v>46324</v>
-      </c>
-      <c r="R171" s="9">
-        <v>46316</v>
-      </c>
-      <c r="S171" s="10">
-        <v>0</v>
-      </c>
-      <c r="T171" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="U171" s="11" t="s">
         <v>54</v>
       </c>
     </row>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -3467,7 +3467,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46238.48979369213</v>
+        <v>46244.16946509259</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>107</v>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -485,7 +485,7 @@
     <t xml:space="preserve">propuesta fabricación externa </t>
   </si>
   <si>
-    <t>generacion oc fabricación externa ,Generacion Oc  OT 4375,Generacion Oc  OT 4376 ,Generacion Oc  OT 4377,Generacion Oc  OT4378,Generacion Oc OT 4376 OT 4381  ,Generacion Oc OT 4382 - OT 4383 ,Generacion Oc ot 4385- 4386,Generacion Oc ot 4385- 4386</t>
+    <t xml:space="preserve">generacion oc fabricación externa ,Generacion Oc  OT 4375,Generacion Oc  OT 4376 ,Generacion Oc  OT 4377,Generacion Oc  OT4378,Generacion Oc OT 4376 OT 4381  ,Generacion Oc OT 4382 - OT 4383 ,Generacion Oc ot 4385- 4386,Generacion Oc OT 4390,Generacion Oc OT 4382 - OT 4383 </t>
   </si>
   <si>
     <t>1216208498022048</t>
@@ -3532,7 +3532,7 @@
         <v>46237.55370259259</v>
       </c>
       <c r="D31" s="9">
-        <v>46238.489794050925</v>
+        <v>46244.816395648144</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>110</v>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -4056,7 +4056,7 @@
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46246.7963303588</v>
+        <v>46248.19978815972</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>139</v>
@@ -4103,8 +4103,8 @@
       <c r="S40" s="6">
         <v>0</v>
       </c>
-      <c r="T40" s="7" t="s">
-        <v>53</v>
+      <c r="T40" s="12" t="s">
+        <v>128</v>
       </c>
       <c r="U40" s="11" t="s">
         <v>54</v>
@@ -4241,7 +4241,7 @@
         <v>46240.56793090278</v>
       </c>
       <c r="D43" s="9">
-        <v>46240.56794395833</v>
+        <v>46248.19978797453</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>150</v>
@@ -4288,8 +4288,8 @@
       <c r="S43" s="10">
         <v>1</v>
       </c>
-      <c r="T43" s="7" t="s">
-        <v>53</v>
+      <c r="T43" s="12" t="s">
+        <v>128</v>
       </c>
       <c r="U43" s="7" t="s">
         <v>27</v>
@@ -4414,7 +4414,7 @@
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46206.67393748843</v>
+        <v>46248.19978818287</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>157</v>
@@ -4461,8 +4461,8 @@
       <c r="S46" s="6">
         <v>0</v>
       </c>
-      <c r="T46" s="7" t="s">
-        <v>53</v>
+      <c r="T46" s="12" t="s">
+        <v>128</v>
       </c>
       <c r="U46" s="11" t="s">
         <v>54</v>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46206.65562592592</v>
+        <v>46251.584816585644</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>112</v>
@@ -4054,9 +4054,11 @@
       <c r="B40" s="5">
         <v>46204.78728729166</v>
       </c>
-      <c r="C40" s="6"/>
+      <c r="C40" s="5">
+        <v>46251.58480644676</v>
+      </c>
       <c r="D40" s="5">
-        <v>46248.19978815972</v>
+        <v>46251.584821909724</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>139</v>
@@ -4101,13 +4103,13 @@
         <v>46245</v>
       </c>
       <c r="S40" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T40" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="U40" s="11" t="s">
-        <v>54</v>
+      <c r="U40" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
@@ -4178,9 +4180,11 @@
       <c r="B42" s="5">
         <v>46204.78730063657</v>
       </c>
-      <c r="C42" s="6"/>
+      <c r="C42" s="5">
+        <v>46251.5847822338</v>
+      </c>
       <c r="D42" s="5">
-        <v>46246.79633084491</v>
+        <v>46251.58478496528</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>147</v>
@@ -5320,7 +5324,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46206.67512555556</v>
+        <v>46251.584806956016</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>209</v>
@@ -5370,8 +5374,8 @@
       <c r="T62" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="U62" s="11" t="s">
-        <v>54</v>
+      <c r="U62" s="12" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -482,7 +482,7 @@
     <t xml:space="preserve">propuesta fabricación externa </t>
   </si>
   <si>
-    <t xml:space="preserve">generacion oc fabricación externa ,Generacion Oc  OT 4375,Generacion Oc  OT 4376 ,Generacion Oc  OT 4377,Generacion Oc  OT4378,Generacion Oc OT 4376 OT 4381  ,Generacion Oc OT 4382 - OT 4383 ,Generacion Oc ot 4385- 4386,Generacion Oc OT 4390,Generacion Oc  OT 4376 </t>
+    <t xml:space="preserve">generacion oc fabricación externa ,Generacion Oc  OT 4375,Generacion Oc  OT 4376 ,Generacion Oc  OT 4377,Generacion Oc  OT4378,Generacion Oc OT 4376 OT 4381  ,Generacion Oc OT 4382 - OT 4383 ,Generacion Oc ot 4385- 4386,Generacion Oc OT 4390,Generacion Oc  OT 4391 </t>
   </si>
   <si>
     <t>1216208498022048</t>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -536,49 +536,49 @@
     <t>Generación oc Motor,Fabricación motor,Planos motor proveedor</t>
   </si>
   <si>
+    <t>1216219007123944</t>
+  </si>
+  <si>
+    <t>Generación oc Motor</t>
+  </si>
+  <si>
+    <t>Motor 4367 ,Fabricación motor,Planos motor proveedor</t>
+  </si>
+  <si>
+    <t>1216218870925196</t>
+  </si>
+  <si>
+    <t>Fabricación motor</t>
+  </si>
+  <si>
+    <t>Motor 4367 ,Recepcion Motor</t>
+  </si>
+  <si>
+    <t>1216218896926045</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor</t>
+  </si>
+  <si>
+    <t>Motor 4367 ,Planos Definitivos</t>
+  </si>
+  <si>
+    <t>1216218897037029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corte laser 4367 </t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC corte laser,Fabricacion  corte laser,propuesta corte laser</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216219007123944</t>
-  </si>
-  <si>
-    <t>Generación oc Motor</t>
-  </si>
-  <si>
-    <t>Motor 4367 ,Fabricación motor,Planos motor proveedor</t>
-  </si>
-  <si>
-    <t>1216218870925196</t>
-  </si>
-  <si>
-    <t>Fabricación motor</t>
-  </si>
-  <si>
-    <t>Motor 4367 ,Recepcion Motor</t>
-  </si>
-  <si>
-    <t>1216218896926045</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor</t>
-  </si>
-  <si>
-    <t>Motor 4367 ,Planos Definitivos</t>
-  </si>
-  <si>
-    <t>1216218897037029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corte laser 4367 </t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC corte laser,Fabricacion  corte laser,propuesta corte laser</t>
   </si>
   <si>
     <t>1216218897037046</t>
@@ -3828,7 +3828,7 @@
         <v>46217.69453972222</v>
       </c>
       <c r="D36" s="5">
-        <v>46245.16703626157</v>
+        <v>46253.18898056713</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>126</v>
@@ -3875,8 +3875,8 @@
       <c r="S36" s="6">
         <v>1</v>
       </c>
-      <c r="T36" s="12" t="s">
-        <v>128</v>
+      <c r="T36" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="U36" s="7" t="s">
         <v>27</v>
@@ -3884,7 +3884,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B37" s="9">
         <v>46204.78722760417</v>
@@ -3896,7 +3896,7 @@
         <v>46206.769946203705</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
@@ -3929,7 +3929,7 @@
         <v>90</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3939,7 +3939,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B38" s="5">
         <v>46204.787231689814</v>
@@ -3951,7 +3951,7 @@
         <v>46217.69452489584</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
@@ -3981,10 +3981,10 @@
         <v>126</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3994,7 +3994,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B39" s="9">
         <v>46204.78728243055</v>
@@ -4006,7 +4006,7 @@
         <v>46206.769995821756</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
@@ -4036,10 +4036,10 @@
         <v>126</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -4049,7 +4049,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B40" s="5">
         <v>46204.78728729166</v>
@@ -4061,16 +4061,16 @@
         <v>46251.584821909724</v>
       </c>
       <c r="E40" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G40" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="F40" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G40" s="6" t="s">
+      <c r="H40" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>141</v>
       </c>
       <c r="I40" s="5">
         <v>46245</v>
@@ -4091,7 +4091,7 @@
         <v>112</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>112</v>
@@ -4106,7 +4106,7 @@
         <v>1</v>
       </c>
       <c r="T40" s="12" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="U40" s="7" t="s">
         <v>27</v>
@@ -4132,10 +4132,10 @@
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="H41" s="10" t="s">
         <v>140</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>141</v>
       </c>
       <c r="I41" s="9">
         <v>46245</v>
@@ -4153,7 +4153,7 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O41" s="10" t="s">
         <v>26</v>
@@ -4193,10 +4193,10 @@
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>141</v>
       </c>
       <c r="I42" s="5">
         <v>46247</v>
@@ -4214,7 +4214,7 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>144</v>
@@ -4254,10 +4254,10 @@
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="H43" s="10" t="s">
         <v>140</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>141</v>
       </c>
       <c r="I43" s="9">
         <v>46245</v>
@@ -4293,7 +4293,7 @@
         <v>1</v>
       </c>
       <c r="T43" s="12" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="U43" s="7" t="s">
         <v>27</v>
@@ -4319,10 +4319,10 @@
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>141</v>
       </c>
       <c r="I44" s="5">
         <v>46245</v>
@@ -4374,10 +4374,10 @@
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="H45" s="10" t="s">
         <v>140</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>141</v>
       </c>
       <c r="I45" s="9">
         <v>46247</v>
@@ -4427,10 +4427,10 @@
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>141</v>
       </c>
       <c r="I46" s="5">
         <v>46245</v>
@@ -4466,7 +4466,7 @@
         <v>0</v>
       </c>
       <c r="T46" s="12" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="U46" s="11" t="s">
         <v>54</v>
@@ -4490,10 +4490,10 @@
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="H47" s="10" t="s">
         <v>140</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>141</v>
       </c>
       <c r="I47" s="9">
         <v>46245</v>
@@ -4543,10 +4543,10 @@
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>141</v>
       </c>
       <c r="I48" s="5">
         <v>46247</v>
@@ -5372,7 +5372,7 @@
         <v>0</v>
       </c>
       <c r="T62" s="12" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="U62" s="12" t="s">
         <v>88</v>
@@ -5498,7 +5498,7 @@
         <v>0</v>
       </c>
       <c r="T64" s="12" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="U64" s="12" t="s">
         <v>88</v>
@@ -5624,7 +5624,7 @@
         <v>0</v>
       </c>
       <c r="T66" s="12" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="U66" s="11" t="s">
         <v>54</v>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46246.16958350694</v>
+        <v>46253.16876418982</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>252</v>
@@ -6393,7 +6393,7 @@
         <v>206</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>250</v>
@@ -6408,7 +6408,7 @@
         <v>0</v>
       </c>
       <c r="T80" s="12" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="U80" s="12" t="s">
         <v>88</v>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -5387,7 +5387,7 @@
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46206.67526587963</v>
+        <v>46254.19498493055</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>214</v>
@@ -5434,8 +5434,8 @@
       <c r="S63" s="10">
         <v>0</v>
       </c>
-      <c r="T63" s="7" t="s">
-        <v>53</v>
+      <c r="T63" s="12" t="s">
+        <v>142</v>
       </c>
       <c r="U63" s="11" t="s">
         <v>54</v>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46206.67526299768</v>
+        <v>46254.194983379624</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>218</v>
@@ -5560,8 +5560,8 @@
       <c r="S65" s="10">
         <v>0</v>
       </c>
-      <c r="T65" s="7" t="s">
-        <v>53</v>
+      <c r="T65" s="12" t="s">
+        <v>142</v>
       </c>
       <c r="U65" s="11" t="s">
         <v>54</v>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46206.67526012732</v>
+        <v>46254.194984016205</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>223</v>
@@ -5686,8 +5686,8 @@
       <c r="S67" s="10">
         <v>0</v>
       </c>
-      <c r="T67" s="7" t="s">
-        <v>53</v>
+      <c r="T67" s="12" t="s">
+        <v>142</v>
       </c>
       <c r="U67" s="11" t="s">
         <v>54</v>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46253.16876418982</v>
+        <v>46254.172617986114</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>252</v>
@@ -6407,8 +6407,8 @@
       <c r="S80" s="6">
         <v>0</v>
       </c>
-      <c r="T80" s="12" t="s">
-        <v>142</v>
+      <c r="T80" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="U80" s="12" t="s">
         <v>88</v>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -4418,7 +4418,7 @@
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46248.19978818287</v>
+        <v>46255.16938028936</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>157</v>
@@ -4534,7 +4534,7 @@
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46206.67387746528</v>
+        <v>46255.16938263889</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>162</v>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -578,217 +578,217 @@
     <t>Generación OC corte laser,Fabricacion  corte laser,propuesta corte laser</t>
   </si>
   <si>
+    <t>1216218897037046</t>
+  </si>
+  <si>
+    <t>Generación OC corte laser</t>
+  </si>
+  <si>
+    <t>Corte laser 4367 ,Fabricacion  corte laser</t>
+  </si>
+  <si>
+    <t>1216218897038301</t>
+  </si>
+  <si>
+    <t>Fabricacion  corte laser</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corte laser 4367 ,Recepcion corte laser </t>
+  </si>
+  <si>
+    <t>1216208498022065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corte plasma 4367 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generacion Oc Corte Plasma ,Fabricación corte plasma ,Generacion Oc Corte Plasma </t>
+  </si>
+  <si>
+    <t>1216208498022071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación corte plasma </t>
+  </si>
+  <si>
+    <t>1216208498022072</t>
+  </si>
+  <si>
+    <t>Corte plasma 4367 ,Recepcion corte plasma</t>
+  </si>
+  <si>
+    <t>1216208498022066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mecanizado 4367 </t>
+  </si>
+  <si>
+    <t>generación oc mecanizado,fabricacion mecanizado</t>
+  </si>
+  <si>
+    <t>1216208498022073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fabricacion mecanizado,Mecanizado 4367 </t>
+  </si>
+  <si>
+    <t>1216208498022074</t>
+  </si>
+  <si>
+    <t>fabricacion mecanizado</t>
+  </si>
+  <si>
+    <t>Mecanizado 4367 ,Recepción mecanizado</t>
+  </si>
+  <si>
+    <t>1216208498022067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación externa 4367 </t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">generacion oc fabricación externa ,fabricación material con proveedor externo </t>
+  </si>
+  <si>
+    <t>1216208498022075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">generacion oc fabricación externa </t>
+  </si>
+  <si>
+    <t xml:space="preserve">fabricación material con proveedor externo ,Fabricación externa 4367 </t>
+  </si>
+  <si>
+    <t>1216208498022076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fabricación material con proveedor externo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación externa 4367 ,CONTROL DE CALIDAD FABRICACIONE XTERNA </t>
+  </si>
+  <si>
+    <t>1216265318483734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTROL DE CALIDAD FABRICACIONE XTERNA </t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1216219007170836</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseño:</t>
+  </si>
+  <si>
+    <t>Check Planos,Planos Preliminar,Planos Definitivos,Check pruebas FAT</t>
+  </si>
+  <si>
+    <t>1216219007170850</t>
+  </si>
+  <si>
+    <t>Planos Preliminar</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>Check Planos,Ingenieria y diseño:,Planos Definitivos</t>
+  </si>
+  <si>
+    <t>1216218897067253</t>
+  </si>
+  <si>
+    <t>Planos Definitivos</t>
+  </si>
+  <si>
+    <t>Ingenieria Basica Motor,Planos motor proveedor,Planos Preliminar</t>
+  </si>
+  <si>
+    <t>Check Planos,Ingenieria y diseño:</t>
+  </si>
+  <si>
+    <t>1216218870977283</t>
+  </si>
+  <si>
+    <t>Planos Preliminar,Planos Definitivos</t>
+  </si>
+  <si>
+    <t>propuesta corte plasma,propuesta mecanizado,propuesta fabricación externa ,OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C,OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C,OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C,Ingenieria y diseño:,OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C,OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C,OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C,OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C,OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C,OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C,propuesta corte laser</t>
+  </si>
+  <si>
+    <t>1216219115200539</t>
+  </si>
+  <si>
+    <t>Check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C,OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C,OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C</t>
+  </si>
+  <si>
+    <t>1216239551129139</t>
+  </si>
+  <si>
+    <t>OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C</t>
+  </si>
+  <si>
+    <t>Check pruebas FAT,OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C</t>
+  </si>
+  <si>
+    <t>1216239551129140</t>
+  </si>
+  <si>
+    <t>Check pruebas FAT,OT  4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C</t>
+  </si>
+  <si>
+    <t>1216239551129141</t>
+  </si>
+  <si>
+    <t>1216219115200556</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">control de calidad corte laser,Recepcion corte laser </t>
+  </si>
+  <si>
+    <t>1216219007202434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion corte laser </t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t>Bodega:,control de calidad corte laser</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216218897037046</t>
-  </si>
-  <si>
-    <t>Generación OC corte laser</t>
-  </si>
-  <si>
-    <t>Corte laser 4367 ,Fabricacion  corte laser</t>
-  </si>
-  <si>
-    <t>1216218897038301</t>
-  </si>
-  <si>
-    <t>Fabricacion  corte laser</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corte laser 4367 ,Recepcion corte laser </t>
-  </si>
-  <si>
-    <t>1216208498022065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corte plasma 4367 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generacion Oc Corte Plasma ,Fabricación corte plasma ,Generacion Oc Corte Plasma </t>
-  </si>
-  <si>
-    <t>1216208498022071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación corte plasma </t>
-  </si>
-  <si>
-    <t>1216208498022072</t>
-  </si>
-  <si>
-    <t>Corte plasma 4367 ,Recepcion corte plasma</t>
-  </si>
-  <si>
-    <t>1216208498022066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mecanizado 4367 </t>
-  </si>
-  <si>
-    <t>generación oc mecanizado,fabricacion mecanizado</t>
-  </si>
-  <si>
-    <t>1216208498022073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fabricacion mecanizado,Mecanizado 4367 </t>
-  </si>
-  <si>
-    <t>1216208498022074</t>
-  </si>
-  <si>
-    <t>fabricacion mecanizado</t>
-  </si>
-  <si>
-    <t>Mecanizado 4367 ,Recepción mecanizado</t>
-  </si>
-  <si>
-    <t>1216208498022067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación externa 4367 </t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">generacion oc fabricación externa ,fabricación material con proveedor externo </t>
-  </si>
-  <si>
-    <t>1216208498022075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">generacion oc fabricación externa </t>
-  </si>
-  <si>
-    <t xml:space="preserve">fabricación material con proveedor externo ,Fabricación externa 4367 </t>
-  </si>
-  <si>
-    <t>1216208498022076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fabricación material con proveedor externo </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación externa 4367 ,CONTROL DE CALIDAD FABRICACIONE XTERNA </t>
-  </si>
-  <si>
-    <t>1216265318483734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTROL DE CALIDAD FABRICACIONE XTERNA </t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1216219007170836</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseño:</t>
-  </si>
-  <si>
-    <t>Check Planos,Planos Preliminar,Planos Definitivos,Check pruebas FAT</t>
-  </si>
-  <si>
-    <t>1216219007170850</t>
-  </si>
-  <si>
-    <t>Planos Preliminar</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Check Planos,Ingenieria y diseño:,Planos Definitivos</t>
-  </si>
-  <si>
-    <t>1216218897067253</t>
-  </si>
-  <si>
-    <t>Planos Definitivos</t>
-  </si>
-  <si>
-    <t>Ingenieria Basica Motor,Planos motor proveedor,Planos Preliminar</t>
-  </si>
-  <si>
-    <t>Check Planos,Ingenieria y diseño:</t>
-  </si>
-  <si>
-    <t>1216218870977283</t>
-  </si>
-  <si>
-    <t>Planos Preliminar,Planos Definitivos</t>
-  </si>
-  <si>
-    <t>propuesta corte plasma,propuesta mecanizado,propuesta fabricación externa ,OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C,OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C,OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C,Ingenieria y diseño:,OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C,OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C,OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C,OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C,OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C,OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C,propuesta corte laser</t>
-  </si>
-  <si>
-    <t>1216219115200539</t>
-  </si>
-  <si>
-    <t>Check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C,OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C,OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C</t>
-  </si>
-  <si>
-    <t>1216239551129139</t>
-  </si>
-  <si>
-    <t>OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C</t>
-  </si>
-  <si>
-    <t>Check pruebas FAT,OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C</t>
-  </si>
-  <si>
-    <t>1216239551129140</t>
-  </si>
-  <si>
-    <t>Check pruebas FAT,OT  4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C</t>
-  </si>
-  <si>
-    <t>1216239551129141</t>
-  </si>
-  <si>
-    <t>1216219115200556</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">control de calidad corte laser,Recepcion corte laser </t>
-  </si>
-  <si>
-    <t>1216219007202434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion corte laser </t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t>Bodega:,control de calidad corte laser</t>
   </si>
   <si>
     <t>1216219007202456</t>
@@ -4058,7 +4058,7 @@
         <v>46251.58480644676</v>
       </c>
       <c r="D40" s="5">
-        <v>46251.584821909724</v>
+        <v>46256.17364127315</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>138</v>
@@ -4105,8 +4105,8 @@
       <c r="S40" s="6">
         <v>1</v>
       </c>
-      <c r="T40" s="12" t="s">
-        <v>142</v>
+      <c r="T40" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="U40" s="7" t="s">
         <v>27</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B41" s="9">
         <v>46204.787292175926</v>
@@ -4126,7 +4126,7 @@
         <v>46246.796326446754</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
@@ -4159,7 +4159,7 @@
         <v>26</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4175,7 +4175,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B42" s="5">
         <v>46204.78730063657</v>
@@ -4187,7 +4187,7 @@
         <v>46251.58478496528</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
@@ -4217,10 +4217,10 @@
         <v>138</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4236,7 +4236,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B43" s="9">
         <v>46204.793668136575</v>
@@ -4245,10 +4245,10 @@
         <v>46240.56793090278</v>
       </c>
       <c r="D43" s="9">
-        <v>46248.19978797453</v>
+        <v>46256.17364498843</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
@@ -4278,7 +4278,7 @@
         <v>112</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4292,8 +4292,8 @@
       <c r="S43" s="10">
         <v>1</v>
       </c>
-      <c r="T43" s="12" t="s">
-        <v>142</v>
+      <c r="T43" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="U43" s="7" t="s">
         <v>27</v>
@@ -4301,7 +4301,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B44" s="5">
         <v>46204.794818298615</v>
@@ -4340,13 +4340,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>101</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4356,7 +4356,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B45" s="9">
         <v>46204.794902430556</v>
@@ -4368,7 +4368,7 @@
         <v>46240.56791662037</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
@@ -4395,13 +4395,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>104</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4411,17 +4411,17 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B46" s="5">
         <v>46204.7938509375</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46255.16938028936</v>
+        <v>46256.173640925925</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
@@ -4451,7 +4451,7 @@
         <v>112</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4465,8 +4465,8 @@
       <c r="S46" s="6">
         <v>0</v>
       </c>
-      <c r="T46" s="12" t="s">
-        <v>142</v>
+      <c r="T46" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="U46" s="11" t="s">
         <v>54</v>
@@ -4474,7 +4474,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B47" s="9">
         <v>46204.795001412036</v>
@@ -4511,13 +4511,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>106</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
@@ -4527,7 +4527,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B48" s="5">
         <v>46204.795060543984</v>
@@ -4537,7 +4537,7 @@
         <v>46255.16938263889</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
@@ -4564,13 +4564,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>107</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4580,7 +4580,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B49" s="9">
         <v>46204.7939687037</v>
@@ -4592,16 +4592,16 @@
         <v>46238.52097420139</v>
       </c>
       <c r="E49" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G49" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="F49" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G49" s="10" t="s">
+      <c r="H49" s="10" t="s">
         <v>166</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>167</v>
       </c>
       <c r="I49" s="9">
         <v>46241</v>
@@ -4622,7 +4622,7 @@
         <v>112</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4645,7 +4645,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B50" s="5">
         <v>46204.795132997686</v>
@@ -4657,16 +4657,16 @@
         <v>46238.52084538194</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>166</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>167</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4684,13 +4684,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>109</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4700,7 +4700,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B51" s="9">
         <v>46204.795219293985</v>
@@ -4712,16 +4712,16 @@
         <v>46238.520887094906</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="H51" s="10" t="s">
         <v>166</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>167</v>
       </c>
       <c r="I51" s="9">
         <v>46246</v>
@@ -4739,13 +4739,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4755,7 +4755,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B52" s="5">
         <v>46206.65895994213</v>
@@ -4765,16 +4765,16 @@
         <v>46238.52089543981</v>
       </c>
       <c r="E52" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="F52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G52" s="6" t="s">
+      <c r="H52" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4790,10 +4790,10 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>26</v>
@@ -4806,7 +4806,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B53" s="9">
         <v>46204.787306770835</v>
@@ -4816,7 +4816,7 @@
         <v>46238.489779490745</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>25</v>
@@ -4840,7 +4840,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>26</v>
@@ -4853,7 +4853,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B54" s="5">
         <v>46204.78731047454</v>
@@ -4865,16 +4865,16 @@
         <v>46219.20085231481</v>
       </c>
       <c r="E54" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G54" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="F54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G54" s="6" t="s">
+      <c r="H54" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="I54" s="5">
         <v>46212</v>
@@ -4892,13 +4892,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>76</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q54" s="5">
         <v>46218</v>
@@ -4918,7 +4918,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B55" s="9">
         <v>46204.78731518518</v>
@@ -4930,16 +4930,16 @@
         <v>46240.20805547453</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="H55" s="10" t="s">
         <v>184</v>
-      </c>
-      <c r="H55" s="10" t="s">
-        <v>185</v>
       </c>
       <c r="I55" s="9">
         <v>46233</v>
@@ -4957,13 +4957,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O55" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="P55" s="10" t="s">
         <v>189</v>
-      </c>
-      <c r="P55" s="10" t="s">
-        <v>190</v>
       </c>
       <c r="Q55" s="9">
         <v>46239</v>
@@ -4983,7 +4983,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B56" s="5">
         <v>46204.78732028935</v>
@@ -5001,10 +5001,10 @@
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="I56" s="5">
         <v>46240</v>
@@ -5022,13 +5022,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O56" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="P56" s="6" t="s">
         <v>192</v>
-      </c>
-      <c r="P56" s="6" t="s">
-        <v>193</v>
       </c>
       <c r="Q56" s="5">
         <v>46240</v>
@@ -5048,7 +5048,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B57" s="9">
         <v>46204.787326770835</v>
@@ -5058,16 +5058,16 @@
         <v>46206.67498217593</v>
       </c>
       <c r="E57" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G57" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="F57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G57" s="10" t="s">
+      <c r="H57" s="10" t="s">
         <v>196</v>
-      </c>
-      <c r="H57" s="10" t="s">
-        <v>197</v>
       </c>
       <c r="I57" s="9">
         <v>46288</v>
@@ -5085,13 +5085,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q57" s="9">
         <v>46288</v>
@@ -5111,7 +5111,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B58" s="5">
         <v>46205.8929956713</v>
@@ -5121,16 +5121,16 @@
         <v>46206.67494384259</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>196</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>197</v>
       </c>
       <c r="I58" s="5">
         <v>46288</v>
@@ -5148,13 +5148,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O58" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="P58" s="6" t="s">
         <v>200</v>
-      </c>
-      <c r="P58" s="6" t="s">
-        <v>201</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5164,7 +5164,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B59" s="9">
         <v>46205.89308850694</v>
@@ -5174,16 +5174,16 @@
         <v>46206.67494135417</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="H59" s="10" t="s">
         <v>196</v>
-      </c>
-      <c r="H59" s="10" t="s">
-        <v>197</v>
       </c>
       <c r="I59" s="9">
         <v>46288</v>
@@ -5201,13 +5201,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5217,7 +5217,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B60" s="5">
         <v>46205.89321678241</v>
@@ -5227,16 +5227,16 @@
         <v>46206.67493778935</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>196</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>197</v>
       </c>
       <c r="I60" s="5">
         <v>46288</v>
@@ -5254,13 +5254,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O60" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="P60" s="6" t="s">
         <v>200</v>
-      </c>
-      <c r="P60" s="6" t="s">
-        <v>201</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5270,7 +5270,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B61" s="9">
         <v>46204.787330555555</v>
@@ -5280,7 +5280,7 @@
         <v>46206.65997969908</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>25</v>
@@ -5304,7 +5304,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5317,7 +5317,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B62" s="5">
         <v>46204.78733380787</v>
@@ -5327,16 +5327,16 @@
         <v>46252.16713914352</v>
       </c>
       <c r="E62" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G62" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="F62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G62" s="6" t="s">
+      <c r="H62" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I62" s="5">
         <v>46258</v>
@@ -5354,13 +5354,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q62" s="5">
         <v>46259</v>
@@ -5372,7 +5372,7 @@
         <v>0</v>
       </c>
       <c r="T62" s="12" t="s">
-        <v>142</v>
+        <v>212</v>
       </c>
       <c r="U62" s="12" t="s">
         <v>88</v>
@@ -5396,10 +5396,10 @@
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="H63" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="H63" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="I63" s="9">
         <v>46260</v>
@@ -5417,10 +5417,10 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P63" s="10" t="s">
         <v>215</v>
@@ -5435,7 +5435,7 @@
         <v>0</v>
       </c>
       <c r="T63" s="12" t="s">
-        <v>142</v>
+        <v>212</v>
       </c>
       <c r="U63" s="11" t="s">
         <v>54</v>
@@ -5459,10 +5459,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I64" s="5">
         <v>46258</v>
@@ -5480,10 +5480,10 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>218</v>
@@ -5498,7 +5498,7 @@
         <v>0</v>
       </c>
       <c r="T64" s="12" t="s">
-        <v>142</v>
+        <v>212</v>
       </c>
       <c r="U64" s="12" t="s">
         <v>88</v>
@@ -5522,10 +5522,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="H65" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="H65" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="I65" s="9">
         <v>46260</v>
@@ -5543,7 +5543,7 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O65" s="10" t="s">
         <v>217</v>
@@ -5561,7 +5561,7 @@
         <v>0</v>
       </c>
       <c r="T65" s="12" t="s">
-        <v>142</v>
+        <v>212</v>
       </c>
       <c r="U65" s="11" t="s">
         <v>54</v>
@@ -5585,10 +5585,10 @@
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I66" s="5">
         <v>46258</v>
@@ -5606,10 +5606,10 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>223</v>
@@ -5624,7 +5624,7 @@
         <v>0</v>
       </c>
       <c r="T66" s="12" t="s">
-        <v>142</v>
+        <v>212</v>
       </c>
       <c r="U66" s="11" t="s">
         <v>54</v>
@@ -5648,10 +5648,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="H67" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="I67" s="9">
         <v>46260</v>
@@ -5669,7 +5669,7 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O67" s="10" t="s">
         <v>222</v>
@@ -5687,7 +5687,7 @@
         <v>0</v>
       </c>
       <c r="T67" s="12" t="s">
-        <v>142</v>
+        <v>212</v>
       </c>
       <c r="U67" s="11" t="s">
         <v>54</v>
@@ -5845,7 +5845,7 @@
         <v>226</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>226</v>
@@ -5878,7 +5878,7 @@
         <v>46238.48977827546</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
@@ -5931,7 +5931,7 @@
         <v>46238.48977881944</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5984,7 +5984,7 @@
         <v>46238.48977920139</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -6043,10 +6043,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I74" s="5">
         <v>46274</v>
@@ -6067,7 +6067,7 @@
         <v>226</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>226</v>
@@ -6100,16 +6100,16 @@
         <v>46206.67575559027</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="H75" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="I75" s="10"/>
       <c r="J75" s="9">
@@ -6128,7 +6128,7 @@
         <v>241</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P75" s="10" t="s">
         <v>243</v>
@@ -6151,16 +6151,16 @@
         <v>46206.67575268519</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I76" s="6"/>
       <c r="J76" s="5">
@@ -6179,7 +6179,7 @@
         <v>241</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>243</v>
@@ -6202,16 +6202,16 @@
         <v>46206.67574885416</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="H77" s="10" t="s">
         <v>177</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>178</v>
       </c>
       <c r="I77" s="10"/>
       <c r="J77" s="9">
@@ -6230,7 +6230,7 @@
         <v>241</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>243</v>
@@ -6253,7 +6253,7 @@
         <v>46206.67094998843</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>25</v>
@@ -6306,10 +6306,10 @@
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H79" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I79" s="9">
         <v>46210</v>
@@ -6327,7 +6327,7 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O79" s="10" t="s">
         <v>82</v>
@@ -6369,10 +6369,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I80" s="5">
         <v>46253</v>
@@ -6390,7 +6390,7 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>132</v>
@@ -6432,10 +6432,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H81" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I81" s="9">
         <v>46274</v>
@@ -6453,13 +6453,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>255</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="Q81" s="9">
         <v>46274</v>
@@ -6495,10 +6495,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I82" s="6"/>
       <c r="J82" s="5">
@@ -6546,10 +6546,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H83" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I83" s="10"/>
       <c r="J83" s="9">
@@ -6597,10 +6597,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H84" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I84" s="6"/>
       <c r="J84" s="5">
@@ -6648,10 +6648,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H85" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I85" s="10"/>
       <c r="J85" s="9">
@@ -6699,10 +6699,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I86" s="6"/>
       <c r="J86" s="5">
@@ -6750,10 +6750,10 @@
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H87" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I87" s="10"/>
       <c r="J87" s="9">
@@ -6801,10 +6801,10 @@
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I88" s="6"/>
       <c r="J88" s="5">
@@ -6852,10 +6852,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H89" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I89" s="10"/>
       <c r="J89" s="9">
@@ -6903,10 +6903,10 @@
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="H90" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="I90" s="6"/>
       <c r="J90" s="5">
@@ -6954,10 +6954,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H91" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="I91" s="9">
         <v>46274</v>
@@ -6975,7 +6975,7 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O91" s="10" t="s">
         <v>123</v>
@@ -7082,7 +7082,7 @@
         <v>270</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>270</v>
@@ -7115,7 +7115,7 @@
         <v>46223.56049512731</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7145,7 +7145,7 @@
         <v>273</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>275</v>
@@ -7168,7 +7168,7 @@
         <v>46223.56049449074</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7198,7 +7198,7 @@
         <v>273</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P95" s="10" t="s">
         <v>275</v>
@@ -7221,7 +7221,7 @@
         <v>46223.56049383101</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7251,7 +7251,7 @@
         <v>273</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>278</v>
@@ -7304,7 +7304,7 @@
         <v>270</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P97" s="10" t="s">
         <v>270</v>
@@ -7337,7 +7337,7 @@
         <v>46238.48978042824</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7390,7 +7390,7 @@
         <v>46238.48978101852</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7443,7 +7443,7 @@
         <v>46238.48978153935</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7476,7 +7476,7 @@
         <v>282</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7526,7 +7526,7 @@
         <v>270</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P101" s="10" t="s">
         <v>270</v>
@@ -7559,7 +7559,7 @@
         <v>46238.48978204861</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7612,7 +7612,7 @@
         <v>46238.489782488425</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7665,7 +7665,7 @@
         <v>46238.489782951394</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7748,7 +7748,7 @@
         <v>270</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P105" s="10" t="s">
         <v>270</v>
@@ -7781,7 +7781,7 @@
         <v>46223.56167888889</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7834,7 +7834,7 @@
         <v>46223.561678287035</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7887,7 +7887,7 @@
         <v>46223.56167766204</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8003,7 +8003,7 @@
         <v>46223.56179313657</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8033,7 +8033,7 @@
         <v>301</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>304</v>
@@ -8086,7 +8086,7 @@
         <v>301</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P111" s="10" t="s">
         <v>304</v>
@@ -8109,7 +8109,7 @@
         <v>46223.56179165509</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8139,7 +8139,7 @@
         <v>301</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>304</v>
@@ -8272,7 +8272,7 @@
         <v>46206.67717564815</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -8302,7 +8302,7 @@
         <v>312</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P115" s="10" t="s">
         <v>317</v>
@@ -8325,7 +8325,7 @@
         <v>46206.67717299769</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8378,7 +8378,7 @@
         <v>46206.67717023148</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8408,7 +8408,7 @@
         <v>312</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P117" s="10" t="s">
         <v>317</v>
@@ -8971,7 +8971,7 @@
         <v>46223.562056400464</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9001,7 +9001,7 @@
         <v>331</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>335</v>
@@ -9024,7 +9024,7 @@
         <v>46223.56205577546</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
@@ -9054,7 +9054,7 @@
         <v>331</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P129" s="10" t="s">
         <v>335</v>
@@ -9077,7 +9077,7 @@
         <v>46223.56205517361</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9107,7 +9107,7 @@
         <v>331</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P130" s="6" t="s">
         <v>335</v>
@@ -9700,7 +9700,7 @@
         <v>350</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P141" s="10" t="s">
         <v>355</v>
@@ -9753,7 +9753,7 @@
         <v>350</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P142" s="6" t="s">
         <v>355</v>
@@ -9806,7 +9806,7 @@
         <v>350</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P143" s="10" t="s">
         <v>355</v>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -482,7 +482,7 @@
     <t xml:space="preserve">propuesta fabricación externa </t>
   </si>
   <si>
-    <t xml:space="preserve">generacion oc fabricación externa ,Generacion Oc  OT 4375,Generacion Oc  OT 4376 ,Generacion Oc  OT 4377,Generacion Oc  OT4378,Generacion Oc OT 4376 OT 4381  ,Generacion Oc OT 4382 - OT 4383 ,Generacion Oc ot 4385- 4386,Generacion Oc OT 4390,Generacion Oc  OT 4391 </t>
+    <t>generacion oc fabricación externa ,Generacion Oc  OT 4375,Generacion Oc  OT 4376 ,Generacion Oc  OT 4377,Generacion Oc  OT4378,Generacion Oc OT 4376 OT 4381  ,Generacion Oc OT 4382 - OT 4383 ,Generacion Oc ot 4385- 4386,Generacion Oc OT 4390,Generacion Oc  OT 4391 ,Generacion Oc OT4080</t>
   </si>
   <si>
     <t>1216208498022048</t>
@@ -3535,7 +3535,7 @@
         <v>46237.55370259259</v>
       </c>
       <c r="D31" s="9">
-        <v>46252.55703577546</v>
+        <v>46258.60316413194</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>109</v>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -285,7 +285,7 @@
     <t>Baja</t>
   </si>
   <si>
-    <t>Tarea sin iniciar</t>
+    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1216265318483681</t>
@@ -416,9 +416,6 @@
     <t>propuesta corte laser,propuesta motor,propuesta tableros</t>
   </si>
   <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
     <t>1216219007082142</t>
   </si>
   <si>
@@ -507,6 +504,9 @@
   </si>
   <si>
     <t>Generación OC Tableros,Fabricación Tablero</t>
+  </si>
+  <si>
+    <t>Tarea sin iniciar</t>
   </si>
   <si>
     <t>1216218896994060</t>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46206.67283681713</v>
+        <v>46259.50952912037</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>49</v>
@@ -2363,12 +2363,12 @@
         <v>46275</v>
       </c>
       <c r="S10" s="6">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="T10" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="U10" s="11" t="s">
+      <c r="U10" s="12" t="s">
         <v>54</v>
       </c>
     </row>
@@ -3198,12 +3198,12 @@
       <c r="S25" s="10"/>
       <c r="T25" s="10"/>
       <c r="U25" s="12" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B26" s="5">
         <v>46204.78715721065</v>
@@ -3215,7 +3215,7 @@
         <v>46213.19381935185</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
@@ -3248,7 +3248,7 @@
         <v>72</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q26" s="5">
         <v>46212</v>
@@ -3268,7 +3268,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B27" s="9">
         <v>46204.78716710648</v>
@@ -3280,7 +3280,7 @@
         <v>46214.18292518519</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>26</v>
@@ -3313,7 +3313,7 @@
         <v>44</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q27" s="9">
         <v>46213</v>
@@ -3328,12 +3328,12 @@
         <v>33</v>
       </c>
       <c r="U27" s="12" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B28" s="5">
         <v>46204.787177743056</v>
@@ -3345,7 +3345,7 @@
         <v>46246.796230520835</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
@@ -3366,7 +3366,7 @@
         <v>26</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="M28" s="6" t="s">
         <v>26</v>
@@ -3375,10 +3375,10 @@
         <v>86</v>
       </c>
       <c r="O28" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="P28" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="P28" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="Q28" s="5">
         <v>46244</v>
@@ -3393,12 +3393,12 @@
         <v>33</v>
       </c>
       <c r="U28" s="12" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B29" s="9">
         <v>46204.79158200232</v>
@@ -3410,7 +3410,7 @@
         <v>46245.20020792824</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
@@ -3431,7 +3431,7 @@
         <v>26</v>
       </c>
       <c r="L29" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M29" s="10" t="s">
         <v>26</v>
@@ -3440,10 +3440,10 @@
         <v>86</v>
       </c>
       <c r="O29" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="P29" s="10" t="s">
         <v>103</v>
-      </c>
-      <c r="P29" s="10" t="s">
-        <v>104</v>
       </c>
       <c r="Q29" s="9">
         <v>46244</v>
@@ -3458,12 +3458,12 @@
         <v>33</v>
       </c>
       <c r="U29" s="12" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B30" s="5">
         <v>46204.79163886574</v>
@@ -3473,7 +3473,7 @@
         <v>46245.20020795139</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3503,10 +3503,10 @@
         <v>86</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q30" s="5">
         <v>46244</v>
@@ -3521,12 +3521,12 @@
         <v>33</v>
       </c>
       <c r="U30" s="12" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B31" s="9">
         <v>46204.7917447338</v>
@@ -3538,7 +3538,7 @@
         <v>46258.60316413194</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
@@ -3568,10 +3568,10 @@
         <v>86</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Q31" s="9">
         <v>46244</v>
@@ -3586,12 +3586,12 @@
         <v>33</v>
       </c>
       <c r="U31" s="12" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B32" s="5">
         <v>46204.78695173611</v>
@@ -3601,7 +3601,7 @@
         <v>46251.584816585644</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>25</v>
@@ -3625,7 +3625,7 @@
         <v>26</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3638,7 +3638,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B33" s="9">
         <v>46204.78719643518</v>
@@ -3648,16 +3648,16 @@
         <v>46206.67332864583</v>
       </c>
       <c r="E33" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="F33" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="10" t="s">
+      <c r="H33" s="10" t="s">
         <v>116</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>117</v>
       </c>
       <c r="I33" s="9">
         <v>46216</v>
@@ -3675,13 +3675,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q33" s="9">
         <v>46273</v>
@@ -3696,7 +3696,7 @@
         <v>53</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -3717,10 +3717,10 @@
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>116</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>117</v>
       </c>
       <c r="I34" s="5">
         <v>46216</v>
@@ -3738,10 +3738,10 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>121</v>
@@ -3755,7 +3755,7 @@
         <v>53</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
@@ -3776,10 +3776,10 @@
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="H35" s="10" t="s">
         <v>116</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>117</v>
       </c>
       <c r="I35" s="9">
         <v>46225</v>
@@ -3797,7 +3797,7 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O35" s="10" t="s">
         <v>120</v>
@@ -3814,7 +3814,7 @@
         <v>53</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
@@ -3837,10 +3837,10 @@
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>116</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>117</v>
       </c>
       <c r="I36" s="5">
         <v>46213</v>
@@ -3858,7 +3858,7 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>127</v>
@@ -3902,10 +3902,10 @@
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="H37" s="10" t="s">
         <v>116</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>117</v>
       </c>
       <c r="I37" s="9">
         <v>46213</v>
@@ -3926,7 +3926,7 @@
         <v>126</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P37" s="10" t="s">
         <v>130</v>
@@ -3957,10 +3957,10 @@
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>116</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>117</v>
       </c>
       <c r="I38" s="5">
         <v>46224</v>
@@ -4012,10 +4012,10 @@
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="H39" s="10" t="s">
         <v>116</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>117</v>
       </c>
       <c r="I39" s="9">
         <v>46224</v>
@@ -4088,13 +4088,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>141</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q40" s="5">
         <v>46255</v>
@@ -4170,7 +4170,7 @@
         <v>53</v>
       </c>
       <c r="U41" s="11" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
@@ -4231,7 +4231,7 @@
         <v>53</v>
       </c>
       <c r="U42" s="11" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
@@ -4275,7 +4275,7 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O43" s="10" t="s">
         <v>150</v>
@@ -4313,7 +4313,7 @@
         <v>46240.567830925924</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
@@ -4343,7 +4343,7 @@
         <v>149</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>152</v>
@@ -4398,7 +4398,7 @@
         <v>149</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="P45" s="10" t="s">
         <v>154</v>
@@ -4448,7 +4448,7 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>157</v>
@@ -4469,7 +4469,7 @@
         <v>33</v>
       </c>
       <c r="U46" s="11" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
@@ -4484,7 +4484,7 @@
         <v>46246.16913164352</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
@@ -4514,7 +4514,7 @@
         <v>156</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P47" s="10" t="s">
         <v>159</v>
@@ -4567,7 +4567,7 @@
         <v>156</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>162</v>
@@ -4619,7 +4619,7 @@
         <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O49" s="10" t="s">
         <v>167</v>
@@ -4687,7 +4687,7 @@
         <v>164</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>170</v>
@@ -4995,7 +4995,7 @@
         <v>46241.182524814816</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -5106,7 +5106,7 @@
         <v>53</v>
       </c>
       <c r="U57" s="11" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46252.16713914352</v>
+        <v>46259.16862984953</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>208</v>
@@ -5375,7 +5375,7 @@
         <v>212</v>
       </c>
       <c r="U62" s="12" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
@@ -5438,7 +5438,7 @@
         <v>212</v>
       </c>
       <c r="U63" s="11" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46252.16713934028</v>
+        <v>46259.168638020834</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>217</v>
@@ -5501,7 +5501,7 @@
         <v>212</v>
       </c>
       <c r="U64" s="12" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5564,7 +5564,7 @@
         <v>212</v>
       </c>
       <c r="U65" s="11" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46252.16713929398</v>
+        <v>46259.16863947916</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>222</v>
@@ -5627,7 +5627,7 @@
         <v>212</v>
       </c>
       <c r="U66" s="11" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5690,7 +5690,7 @@
         <v>212</v>
       </c>
       <c r="U67" s="11" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46206.67535149306</v>
+        <v>46259.18246737268</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>220</v>
@@ -5796,11 +5796,11 @@
       <c r="S69" s="10">
         <v>0</v>
       </c>
-      <c r="T69" s="7" t="s">
-        <v>53</v>
+      <c r="T69" s="12" t="s">
+        <v>212</v>
       </c>
       <c r="U69" s="11" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5863,7 +5863,7 @@
         <v>53</v>
       </c>
       <c r="U70" s="11" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -6085,7 +6085,7 @@
         <v>53</v>
       </c>
       <c r="U74" s="11" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -6348,7 +6348,7 @@
         <v>33</v>
       </c>
       <c r="U79" s="12" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
@@ -6411,7 +6411,7 @@
         <v>33</v>
       </c>
       <c r="U80" s="12" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
@@ -6474,7 +6474,7 @@
         <v>53</v>
       </c>
       <c r="U81" s="11" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -7100,7 +7100,7 @@
         <v>53</v>
       </c>
       <c r="U93" s="11" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
@@ -7322,7 +7322,7 @@
         <v>53</v>
       </c>
       <c r="U97" s="11" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
@@ -7544,7 +7544,7 @@
         <v>53</v>
       </c>
       <c r="U101" s="11" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
@@ -7766,7 +7766,7 @@
         <v>53</v>
       </c>
       <c r="U105" s="11" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
@@ -7988,7 +7988,7 @@
         <v>53</v>
       </c>
       <c r="U109" s="11" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
@@ -8257,7 +8257,7 @@
         <v>53</v>
       </c>
       <c r="U114" s="11" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
@@ -8956,7 +8956,7 @@
         <v>53</v>
       </c>
       <c r="U127" s="11" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
@@ -9655,7 +9655,7 @@
         <v>53</v>
       </c>
       <c r="U140" s="11" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
@@ -10352,7 +10352,7 @@
         <v>53</v>
       </c>
       <c r="U153" s="11" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
@@ -11041,7 +11041,7 @@
         <v>53</v>
       </c>
       <c r="U166" s="11" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
@@ -11104,7 +11104,7 @@
         <v>53</v>
       </c>
       <c r="U167" s="11" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
@@ -11167,7 +11167,7 @@
         <v>53</v>
       </c>
       <c r="U168" s="11" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -788,16 +788,16 @@
     <t>Bodega:,control de calidad corte laser</t>
   </si>
   <si>
+    <t>1216219007202456</t>
+  </si>
+  <si>
+    <t>control de calidad corte laser</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,Bodega:</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216219007202456</t>
-  </si>
-  <si>
-    <t>control de calidad corte laser</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,Bodega:</t>
   </si>
   <si>
     <t>1216208498022089</t>
@@ -5324,7 +5324,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46259.16862984953</v>
+        <v>46260.19331711806</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>208</v>
@@ -5371,8 +5371,8 @@
       <c r="S62" s="6">
         <v>0</v>
       </c>
-      <c r="T62" s="12" t="s">
-        <v>212</v>
+      <c r="T62" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="U62" s="12" t="s">
         <v>54</v>
@@ -5380,7 +5380,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B63" s="9">
         <v>46204.78733813658</v>
@@ -5390,7 +5390,7 @@
         <v>46254.19498493055</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
@@ -5423,7 +5423,7 @@
         <v>208</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q63" s="9">
         <v>46261</v>
@@ -5435,7 +5435,7 @@
         <v>0</v>
       </c>
       <c r="T63" s="12" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="U63" s="11" t="s">
         <v>118</v>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46259.168638020834</v>
+        <v>46260.19331650463</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>217</v>
@@ -5497,8 +5497,8 @@
       <c r="S64" s="6">
         <v>0</v>
       </c>
-      <c r="T64" s="12" t="s">
-        <v>212</v>
+      <c r="T64" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="U64" s="12" t="s">
         <v>54</v>
@@ -5561,7 +5561,7 @@
         <v>0</v>
       </c>
       <c r="T65" s="12" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="U65" s="11" t="s">
         <v>118</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46259.16863947916</v>
+        <v>46260.19331664352</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>222</v>
@@ -5623,8 +5623,8 @@
       <c r="S66" s="6">
         <v>0</v>
       </c>
-      <c r="T66" s="12" t="s">
-        <v>212</v>
+      <c r="T66" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="U66" s="11" t="s">
         <v>118</v>
@@ -5687,7 +5687,7 @@
         <v>0</v>
       </c>
       <c r="T67" s="12" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="U67" s="11" t="s">
         <v>118</v>
@@ -5797,7 +5797,7 @@
         <v>0</v>
       </c>
       <c r="T69" s="12" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="U69" s="11" t="s">
         <v>118</v>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -5702,7 +5702,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46206.66163074074</v>
+        <v>46260.58543177083</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>226</v>
@@ -5747,9 +5747,11 @@
       <c r="B69" s="9">
         <v>46204.78734565972</v>
       </c>
-      <c r="C69" s="10"/>
+      <c r="C69" s="9">
+        <v>46260.585420972224</v>
+      </c>
       <c r="D69" s="9">
-        <v>46259.18246737268</v>
+        <v>46260.58543997685</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>220</v>
@@ -5794,13 +5796,13 @@
         <v>46262</v>
       </c>
       <c r="S69" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T69" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="U69" s="11" t="s">
-        <v>118</v>
+      <c r="U69" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5812,7 +5814,7 @@
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46206.67558131945</v>
+        <v>46260.59149064815</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>234</v>
@@ -5862,8 +5864,8 @@
       <c r="T70" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="U70" s="11" t="s">
-        <v>118</v>
+      <c r="U70" s="12" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -5873,9 +5875,11 @@
       <c r="B71" s="9">
         <v>46204.83329071759</v>
       </c>
-      <c r="C71" s="10"/>
+      <c r="C71" s="9">
+        <v>46260.58549899305</v>
+      </c>
       <c r="D71" s="9">
-        <v>46238.48977827546</v>
+        <v>46260.585500416666</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>199</v>
@@ -5926,9 +5930,11 @@
       <c r="B72" s="5">
         <v>46204.83348987269</v>
       </c>
-      <c r="C72" s="6"/>
+      <c r="C72" s="5">
+        <v>46260.58551476852</v>
+      </c>
       <c r="D72" s="5">
-        <v>46238.48977881944</v>
+        <v>46260.58551640046</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>199</v>
@@ -5981,7 +5987,7 @@
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46238.48977920139</v>
+        <v>46260.58543127315</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>199</v>
@@ -6034,7 +6040,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46206.67580866898</v>
+        <v>46260.59151165509</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>241</v>
@@ -6084,8 +6090,8 @@
       <c r="T74" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="U74" s="11" t="s">
-        <v>118</v>
+      <c r="U74" s="12" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -6095,9 +6101,11 @@
       <c r="B75" s="9">
         <v>46204.83355802084</v>
       </c>
-      <c r="C75" s="10"/>
+      <c r="C75" s="9">
+        <v>46260.585716747686</v>
+      </c>
       <c r="D75" s="9">
-        <v>46206.67575559027</v>
+        <v>46260.58571837963</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>199</v>
@@ -6148,7 +6156,7 @@
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46206.67575268519</v>
+        <v>46260.585522106485</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>199</v>
@@ -7049,7 +7057,7 @@
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46223.56188282407</v>
+        <v>46260.59156738426</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>273</v>
@@ -7099,8 +7107,8 @@
       <c r="T93" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="U93" s="11" t="s">
-        <v>118</v>
+      <c r="U93" s="12" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
@@ -7112,7 +7120,7 @@
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46223.56049512731</v>
+        <v>46260.58572372685</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>199</v>
@@ -7271,7 +7279,7 @@
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46233.52674290509</v>
+        <v>46260.59158416667</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>280</v>
@@ -7321,8 +7329,8 @@
       <c r="T97" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="U97" s="11" t="s">
-        <v>118</v>
+      <c r="U97" s="12" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
@@ -7493,7 +7501,7 @@
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46223.56188153935</v>
+        <v>46260.59160833333</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>287</v>
@@ -7543,8 +7551,8 @@
       <c r="T101" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="U101" s="11" t="s">
-        <v>118</v>
+      <c r="U101" s="12" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
@@ -7715,7 +7723,7 @@
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46223.561880925925</v>
+        <v>46260.591631261574</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>294</v>
@@ -7765,8 +7773,8 @@
       <c r="T105" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="U105" s="11" t="s">
-        <v>118</v>
+      <c r="U105" s="12" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="9">
-        <v>46206.65997969908</v>
+        <v>46260.65768583333</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>205</v>
@@ -5385,9 +5385,11 @@
       <c r="B63" s="9">
         <v>46204.78733813658</v>
       </c>
-      <c r="C63" s="10"/>
+      <c r="C63" s="9">
+        <v>46260.65767847223</v>
+      </c>
       <c r="D63" s="9">
-        <v>46254.19498493055</v>
+        <v>46260.657696967595</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>213</v>
@@ -5432,13 +5434,13 @@
         <v>46260</v>
       </c>
       <c r="S63" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T63" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="U63" s="11" t="s">
-        <v>118</v>
+      <c r="U63" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
@@ -5511,9 +5513,11 @@
       <c r="B65" s="9">
         <v>46204.79970230324</v>
       </c>
-      <c r="C65" s="10"/>
+      <c r="C65" s="9">
+        <v>46260.65781908565</v>
+      </c>
       <c r="D65" s="9">
-        <v>46254.194983379624</v>
+        <v>46260.657837349536</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>218</v>
@@ -5558,13 +5562,13 @@
         <v>46260</v>
       </c>
       <c r="S65" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T65" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="U65" s="11" t="s">
-        <v>118</v>
+      <c r="U65" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5637,9 +5641,11 @@
       <c r="B67" s="9">
         <v>46204.80007783565</v>
       </c>
-      <c r="C67" s="10"/>
+      <c r="C67" s="9">
+        <v>46260.65774840278</v>
+      </c>
       <c r="D67" s="9">
-        <v>46254.194984016205</v>
+        <v>46260.65776447917</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>223</v>
@@ -5684,13 +5690,13 @@
         <v>46260</v>
       </c>
       <c r="S67" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T67" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="U67" s="11" t="s">
-        <v>118</v>
+      <c r="U67" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5751,7 +5757,7 @@
         <v>46260.585420972224</v>
       </c>
       <c r="D69" s="9">
-        <v>46260.58543997685</v>
+        <v>46260.65784505787</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>220</v>
@@ -5801,8 +5807,8 @@
       <c r="T69" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="U69" s="7" t="s">
-        <v>27</v>
+      <c r="U69" s="12" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1934" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1935" uniqueCount="394">
   <si>
     <t>50001569 - EUROHINCA</t>
   </si>
@@ -3159,9 +3159,11 @@
       <c r="B25" s="9">
         <v>46204.786945914355</v>
       </c>
-      <c r="C25" s="10"/>
+      <c r="C25" s="9">
+        <v>46260.881508125</v>
+      </c>
       <c r="D25" s="9">
-        <v>46246.7960239699</v>
+        <v>46260.881520740746</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>86</v>
@@ -3195,10 +3197,12 @@
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
-      <c r="S25" s="10"/>
+      <c r="S25" s="10">
+        <v>1</v>
+      </c>
       <c r="T25" s="10"/>
-      <c r="U25" s="12" t="s">
-        <v>54</v>
+      <c r="U25" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
@@ -3277,7 +3281,7 @@
         <v>46209.792292743055</v>
       </c>
       <c r="D27" s="9">
-        <v>46214.18292518519</v>
+        <v>46260.88157532408</v>
       </c>
       <c r="E27" s="10" t="s">
         <v>92</v>
@@ -3327,8 +3331,8 @@
       <c r="T27" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="U27" s="12" t="s">
-        <v>54</v>
+      <c r="U27" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -3342,7 +3346,7 @@
         <v>46237.60690067129</v>
       </c>
       <c r="D28" s="5">
-        <v>46246.796230520835</v>
+        <v>46260.88157600694</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>95</v>
@@ -3392,8 +3396,8 @@
       <c r="T28" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="U28" s="12" t="s">
-        <v>54</v>
+      <c r="U28" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -3407,7 +3411,7 @@
         <v>46237.60690063657</v>
       </c>
       <c r="D29" s="9">
-        <v>46245.20020792824</v>
+        <v>46260.88157712963</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>100</v>
@@ -3457,8 +3461,8 @@
       <c r="T29" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="U29" s="12" t="s">
-        <v>54</v>
+      <c r="U29" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -3468,9 +3472,11 @@
       <c r="B30" s="5">
         <v>46204.79163886574</v>
       </c>
-      <c r="C30" s="6"/>
+      <c r="C30" s="5">
+        <v>46260.88149162037</v>
+      </c>
       <c r="D30" s="5">
-        <v>46245.20020795139</v>
+        <v>46260.88150880787</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>105</v>
@@ -3520,8 +3526,8 @@
       <c r="T30" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="U30" s="12" t="s">
-        <v>54</v>
+      <c r="U30" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -3535,7 +3541,7 @@
         <v>46237.55370259259</v>
       </c>
       <c r="D31" s="9">
-        <v>46258.60316413194</v>
+        <v>46260.8815815625</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>108</v>
@@ -3585,8 +3591,8 @@
       <c r="T31" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="U31" s="12" t="s">
-        <v>54</v>
+      <c r="U31" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
@@ -4416,9 +4422,11 @@
       <c r="B46" s="5">
         <v>46204.7938509375</v>
       </c>
-      <c r="C46" s="6"/>
+      <c r="C46" s="5">
+        <v>46260.881718206016</v>
+      </c>
       <c r="D46" s="5">
-        <v>46256.173640925925</v>
+        <v>46260.88172936343</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>156</v>
@@ -4463,13 +4471,13 @@
         <v>46245</v>
       </c>
       <c r="S46" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T46" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="U46" s="11" t="s">
-        <v>118</v>
+      <c r="U46" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
@@ -4479,9 +4487,11 @@
       <c r="B47" s="9">
         <v>46204.795001412036</v>
       </c>
-      <c r="C47" s="10"/>
+      <c r="C47" s="9">
+        <v>46260.88164706019</v>
+      </c>
       <c r="D47" s="9">
-        <v>46246.16913164352</v>
+        <v>46260.8816484375</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>106</v>
@@ -4532,9 +4542,11 @@
       <c r="B48" s="5">
         <v>46204.795060543984</v>
       </c>
-      <c r="C48" s="6"/>
+      <c r="C48" s="5">
+        <v>46260.88170265046</v>
+      </c>
       <c r="D48" s="5">
-        <v>46255.16938263889</v>
+        <v>46260.88170462963</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>161</v>
@@ -5275,9 +5287,11 @@
       <c r="B61" s="9">
         <v>46204.787330555555</v>
       </c>
-      <c r="C61" s="10"/>
+      <c r="C61" s="9">
+        <v>46260.88177716435</v>
+      </c>
       <c r="D61" s="9">
-        <v>46260.65768583333</v>
+        <v>46260.88179142361</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>205</v>
@@ -5311,9 +5325,13 @@
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
-      <c r="S61" s="10"/>
+      <c r="S61" s="10">
+        <v>1</v>
+      </c>
       <c r="T61" s="10"/>
-      <c r="U61" s="10"/>
+      <c r="U61" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
@@ -5322,9 +5340,11 @@
       <c r="B62" s="5">
         <v>46204.78733380787</v>
       </c>
-      <c r="C62" s="6"/>
+      <c r="C62" s="5">
+        <v>46260.8812824537</v>
+      </c>
       <c r="D62" s="5">
-        <v>46260.19331711806</v>
+        <v>46260.881308842596</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>208</v>
@@ -5369,13 +5389,13 @@
         <v>46258</v>
       </c>
       <c r="S62" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T62" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="U62" s="12" t="s">
-        <v>54</v>
+      <c r="U62" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
@@ -5389,7 +5409,7 @@
         <v>46260.65767847223</v>
       </c>
       <c r="D63" s="9">
-        <v>46260.657696967595</v>
+        <v>46260.88129792824</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>213</v>
@@ -5439,8 +5459,8 @@
       <c r="T63" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="U63" s="7" t="s">
-        <v>27</v>
+      <c r="U63" s="12" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
@@ -5450,9 +5470,11 @@
       <c r="B64" s="5">
         <v>46204.79962430555</v>
       </c>
-      <c r="C64" s="6"/>
+      <c r="C64" s="5">
+        <v>46260.88129210648</v>
+      </c>
       <c r="D64" s="5">
-        <v>46260.19331650463</v>
+        <v>46260.88131162037</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>217</v>
@@ -5497,13 +5519,13 @@
         <v>46258</v>
       </c>
       <c r="S64" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T64" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="U64" s="12" t="s">
-        <v>54</v>
+      <c r="U64" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -5517,7 +5539,7 @@
         <v>46260.65781908565</v>
       </c>
       <c r="D65" s="9">
-        <v>46260.657837349536</v>
+        <v>46260.88131114583</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>218</v>
@@ -5567,8 +5589,8 @@
       <c r="T65" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="U65" s="7" t="s">
-        <v>27</v>
+      <c r="U65" s="12" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -5578,9 +5600,11 @@
       <c r="B66" s="5">
         <v>46204.799834722224</v>
       </c>
-      <c r="C66" s="6"/>
+      <c r="C66" s="5">
+        <v>46260.88176089121</v>
+      </c>
       <c r="D66" s="5">
-        <v>46260.19331664352</v>
+        <v>46260.88178211806</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>222</v>
@@ -5625,13 +5649,13 @@
         <v>46258</v>
       </c>
       <c r="S66" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T66" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="U66" s="11" t="s">
-        <v>118</v>
+      <c r="U66" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -5645,7 +5669,7 @@
         <v>46260.65774840278</v>
       </c>
       <c r="D67" s="9">
-        <v>46260.65776447917</v>
+        <v>46260.881774629626</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>223</v>
@@ -5695,8 +5719,8 @@
       <c r="T67" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="U67" s="7" t="s">
-        <v>27</v>
+      <c r="U67" s="12" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -5708,7 +5732,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46260.58543177083</v>
+        <v>46260.88126811343</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>226</v>
@@ -5818,9 +5842,11 @@
       <c r="B70" s="5">
         <v>46204.78735021991</v>
       </c>
-      <c r="C70" s="6"/>
+      <c r="C70" s="5">
+        <v>46260.88125827546</v>
+      </c>
       <c r="D70" s="5">
-        <v>46260.59149064815</v>
+        <v>46260.88127290509</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>234</v>
@@ -5865,13 +5891,13 @@
         <v>46267</v>
       </c>
       <c r="S70" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T70" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="U70" s="12" t="s">
-        <v>54</v>
+      <c r="U70" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -5991,9 +6017,11 @@
       <c r="B73" s="9">
         <v>46204.83350201389</v>
       </c>
-      <c r="C73" s="10"/>
+      <c r="C73" s="9">
+        <v>46260.8812409838</v>
+      </c>
       <c r="D73" s="9">
-        <v>46260.58543127315</v>
+        <v>46260.88124274305</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>199</v>
@@ -6213,7 +6241,7 @@
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46206.67574885416</v>
+        <v>46260.881249756945</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>199</v>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -479,7 +479,7 @@
     <t xml:space="preserve">propuesta fabricación externa </t>
   </si>
   <si>
-    <t>generacion oc fabricación externa ,Generacion Oc  OT 4375,Generacion Oc  OT 4376 ,Generacion Oc  OT 4377,Generacion Oc  OT4378,Generacion Oc OT 4376 OT 4381  ,Generacion Oc OT 4382 - OT 4383 ,Generacion Oc ot 4385- 4386,Generacion Oc OT 4390,Generacion Oc  OT 4391 ,Generacion Oc OT4080</t>
+    <t>generacion oc fabricación externa ,Generacion Oc  OT 4375,Generacion Oc  OT 4376 ,Generacion Oc  OT 4377,Generacion Oc  OT4378,Generacion Oc OT 4376 OT 4381  ,Generacion Oc OT 4382 - OT 4383 ,Generacion Oc ot 4385- 4386,Generacion Oc OT 4390,Generacion Oc  OT 4391 ,Generacion Oc OT4080,Generacion Oc OT 4075 ,Generacion Oc OT 4413</t>
   </si>
   <si>
     <t>1216208498022048</t>
@@ -3541,7 +3541,7 @@
         <v>46237.55370259259</v>
       </c>
       <c r="D31" s="9">
-        <v>46260.8815815625</v>
+        <v>46261.60066888889</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>108</v>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -797,58 +797,58 @@
     <t>Preparación Materiales,Bodega:</t>
   </si>
   <si>
+    <t>1216208498022089</t>
+  </si>
+  <si>
+    <t>Recepcion corte plasma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte plasma </t>
+  </si>
+  <si>
+    <t>1216208498022090</t>
+  </si>
+  <si>
+    <t>Preparación Materiales</t>
+  </si>
+  <si>
+    <t>1216208498022091</t>
+  </si>
+  <si>
+    <t>Recepción mecanizado</t>
+  </si>
+  <si>
+    <t>Control de calidad mecanizado</t>
+  </si>
+  <si>
+    <t>1216208498022092</t>
+  </si>
+  <si>
+    <t>1216218963174694</t>
+  </si>
+  <si>
+    <t>Caldereria:</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,Armado,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1216218963174707</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>Control de calidad corte plasma ,Control de calidad mecanizado,control de calidad corte laser</t>
+  </si>
+  <si>
+    <t>OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C,OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C,OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C,Caldereria:</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216208498022089</t>
-  </si>
-  <si>
-    <t>Recepcion corte plasma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte plasma </t>
-  </si>
-  <si>
-    <t>1216208498022090</t>
-  </si>
-  <si>
-    <t>Preparación Materiales</t>
-  </si>
-  <si>
-    <t>1216208498022091</t>
-  </si>
-  <si>
-    <t>Recepción mecanizado</t>
-  </si>
-  <si>
-    <t>Control de calidad mecanizado</t>
-  </si>
-  <si>
-    <t>1216208498022092</t>
-  </si>
-  <si>
-    <t>1216218963174694</t>
-  </si>
-  <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,Armado,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1216218963174707</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>Control de calidad corte plasma ,Control de calidad mecanizado,control de calidad corte laser</t>
-  </si>
-  <si>
-    <t>OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C,OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C,OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C,Caldereria:</t>
   </si>
   <si>
     <t>1216218870996249</t>
@@ -5409,7 +5409,7 @@
         <v>46260.65767847223</v>
       </c>
       <c r="D63" s="9">
-        <v>46260.88129792824</v>
+        <v>46262.17177444445</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>213</v>
@@ -5456,8 +5456,8 @@
       <c r="S63" s="10">
         <v>1</v>
       </c>
-      <c r="T63" s="12" t="s">
-        <v>215</v>
+      <c r="T63" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="U63" s="12" t="s">
         <v>54</v>
@@ -5465,7 +5465,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B64" s="5">
         <v>46204.79962430555</v>
@@ -5477,7 +5477,7 @@
         <v>46260.88131162037</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5510,7 +5510,7 @@
         <v>152</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q64" s="5">
         <v>46259</v>
@@ -5530,7 +5530,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B65" s="9">
         <v>46204.79970230324</v>
@@ -5539,10 +5539,10 @@
         <v>46260.65781908565</v>
       </c>
       <c r="D65" s="9">
-        <v>46260.88131114583</v>
+        <v>46262.171774421295</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
@@ -5572,10 +5572,10 @@
         <v>205</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q65" s="9">
         <v>46261</v>
@@ -5586,8 +5586,8 @@
       <c r="S65" s="10">
         <v>1</v>
       </c>
-      <c r="T65" s="12" t="s">
-        <v>215</v>
+      <c r="T65" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="U65" s="12" t="s">
         <v>54</v>
@@ -5595,7 +5595,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B66" s="5">
         <v>46204.799834722224</v>
@@ -5607,7 +5607,7 @@
         <v>46260.88178211806</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5640,7 +5640,7 @@
         <v>161</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="Q66" s="5">
         <v>46259</v>
@@ -5660,7 +5660,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B67" s="9">
         <v>46204.80007783565</v>
@@ -5669,10 +5669,10 @@
         <v>46260.65774840278</v>
       </c>
       <c r="D67" s="9">
-        <v>46260.881774629626</v>
+        <v>46262.171774560185</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
@@ -5702,10 +5702,10 @@
         <v>205</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q67" s="9">
         <v>46261</v>
@@ -5716,8 +5716,8 @@
       <c r="S67" s="10">
         <v>1</v>
       </c>
-      <c r="T67" s="12" t="s">
-        <v>215</v>
+      <c r="T67" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="U67" s="12" t="s">
         <v>54</v>
@@ -5725,7 +5725,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B68" s="5">
         <v>46204.787342662035</v>
@@ -5735,7 +5735,7 @@
         <v>46260.88126811343</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5759,7 +5759,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5772,7 +5772,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B69" s="9">
         <v>46204.78734565972</v>
@@ -5784,16 +5784,16 @@
         <v>46260.65784505787</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H69" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I69" s="9">
         <v>46262</v>
@@ -5811,13 +5811,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O69" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="P69" s="10" t="s">
         <v>231</v>
-      </c>
-      <c r="P69" s="10" t="s">
-        <v>232</v>
       </c>
       <c r="Q69" s="9">
         <v>46266</v>
@@ -5829,7 +5829,7 @@
         <v>1</v>
       </c>
       <c r="T69" s="12" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="U69" s="12" t="s">
         <v>54</v>
@@ -5855,10 +5855,10 @@
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I70" s="5">
         <v>46267</v>
@@ -5876,13 +5876,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>197</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Q70" s="5">
         <v>46273</v>
@@ -5920,10 +5920,10 @@
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H71" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I71" s="9">
         <v>46267</v>
@@ -5975,10 +5975,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I72" s="5">
         <v>46267</v>
@@ -6030,10 +6030,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H73" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I73" s="9">
         <v>46267</v>
@@ -6104,13 +6104,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>197</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Q74" s="5">
         <v>46274</v>
@@ -9655,10 +9655,10 @@
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H140" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H140" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I140" s="5">
         <v>46294</v>
@@ -9718,10 +9718,10 @@
         <v>26</v>
       </c>
       <c r="G141" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H141" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H141" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I141" s="9">
         <v>46294</v>
@@ -9771,10 +9771,10 @@
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H142" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H142" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I142" s="5">
         <v>46294</v>
@@ -9824,10 +9824,10 @@
         <v>26</v>
       </c>
       <c r="G143" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H143" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H143" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I143" s="9">
         <v>46294</v>
@@ -9877,10 +9877,10 @@
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H144" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H144" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I144" s="5">
         <v>46294</v>
@@ -9930,10 +9930,10 @@
         <v>26</v>
       </c>
       <c r="G145" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H145" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H145" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I145" s="9">
         <v>46294</v>
@@ -9983,10 +9983,10 @@
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H146" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H146" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I146" s="5">
         <v>46294</v>
@@ -10036,10 +10036,10 @@
         <v>26</v>
       </c>
       <c r="G147" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H147" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H147" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I147" s="9">
         <v>46294</v>
@@ -10089,10 +10089,10 @@
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H148" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H148" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I148" s="5">
         <v>46294</v>
@@ -10142,10 +10142,10 @@
         <v>26</v>
       </c>
       <c r="G149" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H149" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H149" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I149" s="9">
         <v>46294</v>
@@ -10195,10 +10195,10 @@
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H150" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H150" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I150" s="5">
         <v>46294</v>
@@ -10248,10 +10248,10 @@
         <v>26</v>
       </c>
       <c r="G151" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H151" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H151" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I151" s="9">
         <v>46294</v>
@@ -10301,10 +10301,10 @@
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H152" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H152" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I152" s="5">
         <v>46294</v>
@@ -10354,10 +10354,10 @@
         <v>26</v>
       </c>
       <c r="G153" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H153" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H153" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I153" s="10"/>
       <c r="J153" s="9">
@@ -10415,10 +10415,10 @@
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H154" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H154" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I154" s="5">
         <v>46295</v>
@@ -10468,10 +10468,10 @@
         <v>26</v>
       </c>
       <c r="G155" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H155" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H155" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I155" s="9">
         <v>46295</v>
@@ -10521,10 +10521,10 @@
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H156" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H156" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I156" s="5">
         <v>46295</v>
@@ -10574,10 +10574,10 @@
         <v>26</v>
       </c>
       <c r="G157" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H157" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H157" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I157" s="9">
         <v>46295</v>
@@ -10627,10 +10627,10 @@
         <v>26</v>
       </c>
       <c r="G158" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H158" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H158" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I158" s="5">
         <v>46295</v>
@@ -10680,10 +10680,10 @@
         <v>26</v>
       </c>
       <c r="G159" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H159" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H159" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I159" s="9">
         <v>46295</v>
@@ -10733,10 +10733,10 @@
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H160" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H160" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I160" s="5">
         <v>46295</v>
@@ -10786,10 +10786,10 @@
         <v>26</v>
       </c>
       <c r="G161" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H161" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H161" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I161" s="9">
         <v>46295</v>
@@ -10839,10 +10839,10 @@
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H162" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H162" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I162" s="5">
         <v>46295</v>
@@ -10892,10 +10892,10 @@
         <v>26</v>
       </c>
       <c r="G163" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H163" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H163" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I163" s="9">
         <v>46295</v>
@@ -10945,10 +10945,10 @@
         <v>26</v>
       </c>
       <c r="G164" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="H164" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="H164" s="6" t="s">
-        <v>230</v>
       </c>
       <c r="I164" s="5">
         <v>46295</v>
@@ -10998,10 +10998,10 @@
         <v>26</v>
       </c>
       <c r="G165" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="H165" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="H165" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="I165" s="9">
         <v>46295</v>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -6074,7 +6074,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46260.59151165509</v>
+        <v>46265.86704146991</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>241</v>
@@ -6188,9 +6188,11 @@
       <c r="B76" s="5">
         <v>46204.833570069444</v>
       </c>
-      <c r="C76" s="6"/>
+      <c r="C76" s="5">
+        <v>46265.86703331018</v>
+      </c>
       <c r="D76" s="5">
-        <v>46260.585522106485</v>
+        <v>46265.867035497686</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>199</v>
@@ -7207,7 +7209,7 @@
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46223.56049449074</v>
+        <v>46265.867042303245</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>199</v>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1935" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1936" uniqueCount="394">
   <si>
     <t>50001569 - EUROHINCA</t>
   </si>
@@ -506,6 +506,9 @@
     <t>Generación OC Tableros,Fabricación Tablero</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>Tarea sin iniciar</t>
   </si>
   <si>
@@ -846,9 +849,6 @@
   </si>
   <si>
     <t>OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C,OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C,OT 4367  -  3xZVN 1-6-15/2 + TOB + REJ + 2FAR + TIPO C,Caldereria:</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1216218870996249</t>
@@ -2204,9 +2204,11 @@
       <c r="B8" s="5">
         <v>46204.786935682874</v>
       </c>
-      <c r="C8" s="6"/>
+      <c r="C8" s="5">
+        <v>46266.50848282407</v>
+      </c>
       <c r="D8" s="5">
-        <v>46212.646741226854</v>
+        <v>46266.508496469905</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2240,9 +2242,13 @@
       </c>
       <c r="Q8" s="6"/>
       <c r="R8" s="6"/>
-      <c r="S8" s="6"/>
+      <c r="S8" s="6">
+        <v>1</v>
+      </c>
       <c r="T8" s="6"/>
-      <c r="U8" s="6"/>
+      <c r="U8" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
@@ -2316,9 +2322,11 @@
       <c r="B10" s="5">
         <v>46204.78712133101</v>
       </c>
-      <c r="C10" s="6"/>
+      <c r="C10" s="5">
+        <v>46266.50846133102</v>
+      </c>
       <c r="D10" s="5">
-        <v>46259.50952912037</v>
+        <v>46266.50961439815</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>49</v>
@@ -2363,7 +2371,7 @@
         <v>46275</v>
       </c>
       <c r="S10" s="6">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="T10" s="7" t="s">
         <v>53</v>
@@ -2379,9 +2387,11 @@
       <c r="B11" s="9">
         <v>46206.56956019676</v>
       </c>
-      <c r="C11" s="10"/>
+      <c r="C11" s="9">
+        <v>46266.50904431713</v>
+      </c>
       <c r="D11" s="9">
-        <v>46206.672837025464</v>
+        <v>46266.50904626158</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>56</v>
@@ -2432,9 +2442,11 @@
       <c r="B12" s="5">
         <v>46206.56957760417</v>
       </c>
-      <c r="C12" s="6"/>
+      <c r="C12" s="5">
+        <v>46266.509142800925</v>
+      </c>
       <c r="D12" s="5">
-        <v>46206.67283768518</v>
+        <v>46266.509144456024</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>59</v>
@@ -2485,9 +2497,11 @@
       <c r="B13" s="9">
         <v>46206.56959189815</v>
       </c>
-      <c r="C13" s="10"/>
+      <c r="C13" s="9">
+        <v>46266.50921689815</v>
+      </c>
       <c r="D13" s="9">
-        <v>46206.67283835648</v>
+        <v>46266.50921978009</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>56</v>
@@ -2538,9 +2552,11 @@
       <c r="B14" s="5">
         <v>46206.56960495371</v>
       </c>
-      <c r="C14" s="6"/>
+      <c r="C14" s="5">
+        <v>46266.509276412035</v>
+      </c>
       <c r="D14" s="5">
-        <v>46206.67283899305</v>
+        <v>46266.509278136575</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>56</v>
@@ -2591,9 +2607,11 @@
       <c r="B15" s="9">
         <v>46206.569617824076</v>
       </c>
-      <c r="C15" s="10"/>
+      <c r="C15" s="9">
+        <v>46266.50933530093</v>
+      </c>
       <c r="D15" s="9">
-        <v>46206.67283964121</v>
+        <v>46266.50933714121</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>56</v>
@@ -2644,9 +2662,11 @@
       <c r="B16" s="5">
         <v>46206.56963048611</v>
       </c>
-      <c r="C16" s="6"/>
+      <c r="C16" s="5">
+        <v>46266.50938923611</v>
+      </c>
       <c r="D16" s="5">
-        <v>46206.67284035879</v>
+        <v>46266.50939061343</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>56</v>
@@ -2697,9 +2717,11 @@
       <c r="B17" s="9">
         <v>46206.56964277777</v>
       </c>
-      <c r="C17" s="10"/>
+      <c r="C17" s="9">
+        <v>46266.50945054398</v>
+      </c>
       <c r="D17" s="9">
-        <v>46206.67284105324</v>
+        <v>46266.50945190972</v>
       </c>
       <c r="E17" s="10" t="s">
         <v>56</v>
@@ -2750,9 +2772,11 @@
       <c r="B18" s="5">
         <v>46206.56965513889</v>
       </c>
-      <c r="C18" s="6"/>
+      <c r="C18" s="5">
+        <v>46266.509526354166</v>
+      </c>
       <c r="D18" s="5">
-        <v>46206.67284175926</v>
+        <v>46266.50952775463</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>56</v>
@@ -2803,9 +2827,11 @@
       <c r="B19" s="9">
         <v>46206.569700810185</v>
       </c>
-      <c r="C19" s="10"/>
+      <c r="C19" s="9">
+        <v>46266.50959806713</v>
+      </c>
       <c r="D19" s="9">
-        <v>46206.67284254629</v>
+        <v>46266.50959966435</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>56</v>
@@ -3651,7 +3677,7 @@
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46206.67332864583</v>
+        <v>46266.18744592593</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>114</v>
@@ -3698,16 +3724,16 @@
       <c r="S33" s="10">
         <v>0</v>
       </c>
-      <c r="T33" s="7" t="s">
-        <v>53</v>
+      <c r="T33" s="12" t="s">
+        <v>118</v>
       </c>
       <c r="U33" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B34" s="5">
         <v>46204.7872006713</v>
@@ -3717,7 +3743,7 @@
         <v>46224.170235694444</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
@@ -3750,7 +3776,7 @@
         <v>92</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3761,12 +3787,12 @@
         <v>53</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B35" s="9">
         <v>46204.787204837965</v>
@@ -3776,7 +3802,7 @@
         <v>46206.67327987269</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
@@ -3806,10 +3832,10 @@
         <v>114</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -3820,12 +3846,12 @@
         <v>53</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B36" s="5">
         <v>46204.78722327546</v>
@@ -3837,7 +3863,7 @@
         <v>46253.18898056713</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -3867,7 +3893,7 @@
         <v>111</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3890,7 +3916,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B37" s="9">
         <v>46204.78722760417</v>
@@ -3902,7 +3928,7 @@
         <v>46206.769946203705</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
@@ -3929,13 +3955,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O37" s="10" t="s">
         <v>89</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3945,7 +3971,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B38" s="5">
         <v>46204.787231689814</v>
@@ -3957,7 +3983,7 @@
         <v>46217.69452489584</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
@@ -3984,13 +4010,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -4000,7 +4026,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B39" s="9">
         <v>46204.78728243055</v>
@@ -4012,7 +4038,7 @@
         <v>46206.769995821756</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
@@ -4039,13 +4065,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -4055,7 +4081,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B40" s="5">
         <v>46204.78728729166</v>
@@ -4067,16 +4093,16 @@
         <v>46256.17364127315</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I40" s="5">
         <v>46245</v>
@@ -4097,7 +4123,7 @@
         <v>111</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>111</v>
@@ -4120,7 +4146,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B41" s="9">
         <v>46204.787292175926</v>
@@ -4132,16 +4158,16 @@
         <v>46246.796326446754</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I41" s="9">
         <v>46245</v>
@@ -4159,13 +4185,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -4176,12 +4202,12 @@
         <v>53</v>
       </c>
       <c r="U41" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B42" s="5">
         <v>46204.78730063657</v>
@@ -4193,16 +4219,16 @@
         <v>46251.58478496528</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I42" s="5">
         <v>46247</v>
@@ -4220,13 +4246,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4237,12 +4263,12 @@
         <v>53</v>
       </c>
       <c r="U42" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B43" s="9">
         <v>46204.793668136575</v>
@@ -4254,16 +4280,16 @@
         <v>46256.17364498843</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I43" s="9">
         <v>46245</v>
@@ -4284,7 +4310,7 @@
         <v>111</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P43" s="10" t="s">
         <v>26</v>
@@ -4307,7 +4333,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B44" s="5">
         <v>46204.794818298615</v>
@@ -4325,10 +4351,10 @@
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I44" s="5">
         <v>46245</v>
@@ -4346,13 +4372,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>100</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4362,7 +4388,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B45" s="9">
         <v>46204.794902430556</v>
@@ -4374,16 +4400,16 @@
         <v>46240.56791662037</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I45" s="9">
         <v>46247</v>
@@ -4401,13 +4427,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>103</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
@@ -4417,7 +4443,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B46" s="5">
         <v>46204.7938509375</v>
@@ -4429,16 +4455,16 @@
         <v>46260.88172936343</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I46" s="5">
         <v>46245</v>
@@ -4459,7 +4485,7 @@
         <v>111</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4482,7 +4508,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B47" s="9">
         <v>46204.795001412036</v>
@@ -4500,10 +4526,10 @@
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I47" s="9">
         <v>46245</v>
@@ -4521,13 +4547,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>105</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
@@ -4537,7 +4563,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B48" s="5">
         <v>46204.795060543984</v>
@@ -4549,16 +4575,16 @@
         <v>46260.88170462963</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I48" s="5">
         <v>46247</v>
@@ -4576,13 +4602,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>106</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4592,7 +4618,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B49" s="9">
         <v>46204.7939687037</v>
@@ -4601,19 +4627,19 @@
         <v>46238.52095883102</v>
       </c>
       <c r="D49" s="9">
-        <v>46238.52097420139</v>
+        <v>46266.18744675926</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I49" s="9">
         <v>46241</v>
@@ -4634,7 +4660,7 @@
         <v>111</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4648,8 +4674,8 @@
       <c r="S49" s="10">
         <v>1</v>
       </c>
-      <c r="T49" s="7" t="s">
-        <v>53</v>
+      <c r="T49" s="12" t="s">
+        <v>118</v>
       </c>
       <c r="U49" s="7" t="s">
         <v>27</v>
@@ -4657,7 +4683,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B50" s="5">
         <v>46204.795132997686</v>
@@ -4669,16 +4695,16 @@
         <v>46238.52084538194</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I50" s="5">
         <v>46241</v>
@@ -4696,13 +4722,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>108</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4712,7 +4738,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B51" s="9">
         <v>46204.795219293985</v>
@@ -4724,16 +4750,16 @@
         <v>46238.520887094906</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I51" s="9">
         <v>46246</v>
@@ -4751,13 +4777,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4767,7 +4793,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B52" s="5">
         <v>46206.65895994213</v>
@@ -4777,16 +4803,16 @@
         <v>46238.52089543981</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="5">
@@ -4802,10 +4828,10 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>26</v>
@@ -4818,7 +4844,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B53" s="9">
         <v>46204.787306770835</v>
@@ -4828,7 +4854,7 @@
         <v>46238.489779490745</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>25</v>
@@ -4852,7 +4878,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P53" s="10" t="s">
         <v>26</v>
@@ -4865,7 +4891,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B54" s="5">
         <v>46204.78731047454</v>
@@ -4877,16 +4903,16 @@
         <v>46219.20085231481</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I54" s="5">
         <v>46212</v>
@@ -4904,13 +4930,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>76</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q54" s="5">
         <v>46218</v>
@@ -4930,7 +4956,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B55" s="9">
         <v>46204.78731518518</v>
@@ -4942,16 +4968,16 @@
         <v>46240.20805547453</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I55" s="9">
         <v>46233</v>
@@ -4969,13 +4995,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q55" s="9">
         <v>46239</v>
@@ -4995,7 +5021,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B56" s="5">
         <v>46204.78732028935</v>
@@ -5013,10 +5039,10 @@
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I56" s="5">
         <v>46240</v>
@@ -5034,13 +5060,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q56" s="5">
         <v>46240</v>
@@ -5060,7 +5086,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B57" s="9">
         <v>46204.787326770835</v>
@@ -5070,16 +5096,16 @@
         <v>46206.67498217593</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I57" s="9">
         <v>46288</v>
@@ -5097,13 +5123,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q57" s="9">
         <v>46288</v>
@@ -5118,12 +5144,12 @@
         <v>53</v>
       </c>
       <c r="U57" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B58" s="5">
         <v>46205.8929956713</v>
@@ -5133,16 +5159,16 @@
         <v>46206.67494384259</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I58" s="5">
         <v>46288</v>
@@ -5160,13 +5186,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5176,7 +5202,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B59" s="9">
         <v>46205.89308850694</v>
@@ -5186,16 +5212,16 @@
         <v>46206.67494135417</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I59" s="9">
         <v>46288</v>
@@ -5213,13 +5239,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -5229,7 +5255,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B60" s="5">
         <v>46205.89321678241</v>
@@ -5239,16 +5265,16 @@
         <v>46206.67493778935</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I60" s="5">
         <v>46288</v>
@@ -5266,13 +5292,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5282,7 +5308,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B61" s="9">
         <v>46204.787330555555</v>
@@ -5294,7 +5320,7 @@
         <v>46260.88179142361</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>25</v>
@@ -5318,7 +5344,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -5335,7 +5361,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B62" s="5">
         <v>46204.78733380787</v>
@@ -5347,16 +5373,16 @@
         <v>46260.881308842596</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I62" s="5">
         <v>46258</v>
@@ -5374,13 +5400,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q62" s="5">
         <v>46259</v>
@@ -5400,7 +5426,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B63" s="9">
         <v>46204.78733813658</v>
@@ -5412,16 +5438,16 @@
         <v>46262.17177444445</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I63" s="9">
         <v>46260</v>
@@ -5439,13 +5465,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q63" s="9">
         <v>46261</v>
@@ -5465,7 +5491,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B64" s="5">
         <v>46204.79962430555</v>
@@ -5477,16 +5503,16 @@
         <v>46260.88131162037</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I64" s="5">
         <v>46258</v>
@@ -5504,13 +5530,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q64" s="5">
         <v>46259</v>
@@ -5530,7 +5556,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B65" s="9">
         <v>46204.79970230324</v>
@@ -5542,16 +5568,16 @@
         <v>46262.171774421295</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I65" s="9">
         <v>46260</v>
@@ -5569,13 +5595,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q65" s="9">
         <v>46261</v>
@@ -5595,7 +5621,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B66" s="5">
         <v>46204.799834722224</v>
@@ -5607,16 +5633,16 @@
         <v>46260.88178211806</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I66" s="5">
         <v>46258</v>
@@ -5634,13 +5660,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q66" s="5">
         <v>46259</v>
@@ -5660,7 +5686,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B67" s="9">
         <v>46204.80007783565</v>
@@ -5672,16 +5698,16 @@
         <v>46262.171774560185</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H67" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I67" s="9">
         <v>46260</v>
@@ -5699,13 +5725,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q67" s="9">
         <v>46261</v>
@@ -5725,7 +5751,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B68" s="5">
         <v>46204.787342662035</v>
@@ -5735,7 +5761,7 @@
         <v>46260.88126811343</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5759,7 +5785,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5772,7 +5798,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B69" s="9">
         <v>46204.78734565972</v>
@@ -5784,16 +5810,16 @@
         <v>46260.65784505787</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I69" s="9">
         <v>46262</v>
@@ -5811,13 +5837,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q69" s="9">
         <v>46266</v>
@@ -5829,7 +5855,7 @@
         <v>1</v>
       </c>
       <c r="T69" s="12" t="s">
-        <v>232</v>
+        <v>118</v>
       </c>
       <c r="U69" s="12" t="s">
         <v>54</v>
@@ -5846,7 +5872,7 @@
         <v>46260.88125827546</v>
       </c>
       <c r="D70" s="5">
-        <v>46260.88127290509</v>
+        <v>46266.18744709491</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>234</v>
@@ -5855,10 +5881,10 @@
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I70" s="5">
         <v>46267</v>
@@ -5876,13 +5902,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q70" s="5">
         <v>46273</v>
@@ -5893,8 +5919,8 @@
       <c r="S70" s="6">
         <v>1</v>
       </c>
-      <c r="T70" s="7" t="s">
-        <v>53</v>
+      <c r="T70" s="12" t="s">
+        <v>118</v>
       </c>
       <c r="U70" s="7" t="s">
         <v>27</v>
@@ -5914,16 +5940,16 @@
         <v>46260.585500416666</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I71" s="9">
         <v>46267</v>
@@ -5969,16 +5995,16 @@
         <v>46260.58551640046</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I72" s="5">
         <v>46267</v>
@@ -6024,16 +6050,16 @@
         <v>46260.88124274305</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I73" s="9">
         <v>46267</v>
@@ -6083,10 +6109,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I74" s="5">
         <v>46274</v>
@@ -6104,13 +6130,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q74" s="5">
         <v>46274</v>
@@ -6142,16 +6168,16 @@
         <v>46260.58571837963</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I75" s="10"/>
       <c r="J75" s="9">
@@ -6170,7 +6196,7 @@
         <v>241</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P75" s="10" t="s">
         <v>243</v>
@@ -6195,16 +6221,16 @@
         <v>46265.867035497686</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I76" s="6"/>
       <c r="J76" s="5">
@@ -6223,7 +6249,7 @@
         <v>241</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>243</v>
@@ -6246,16 +6272,16 @@
         <v>46260.881249756945</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I77" s="10"/>
       <c r="J77" s="9">
@@ -6274,7 +6300,7 @@
         <v>241</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P77" s="10" t="s">
         <v>243</v>
@@ -6297,7 +6323,7 @@
         <v>46206.67094998843</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>25</v>
@@ -6350,10 +6376,10 @@
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I79" s="9">
         <v>46210</v>
@@ -6371,7 +6397,7 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O79" s="10" t="s">
         <v>82</v>
@@ -6413,10 +6439,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I80" s="5">
         <v>46253</v>
@@ -6434,10 +6460,10 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>250</v>
@@ -6476,10 +6502,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I81" s="9">
         <v>46274</v>
@@ -6497,13 +6523,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>255</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q81" s="9">
         <v>46274</v>
@@ -6518,7 +6544,7 @@
         <v>53</v>
       </c>
       <c r="U81" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6539,10 +6565,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I82" s="6"/>
       <c r="J82" s="5">
@@ -6561,7 +6587,7 @@
         <v>254</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>257</v>
@@ -6590,10 +6616,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I83" s="10"/>
       <c r="J83" s="9">
@@ -6612,7 +6638,7 @@
         <v>254</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P83" s="10" t="s">
         <v>259</v>
@@ -6641,10 +6667,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I84" s="6"/>
       <c r="J84" s="5">
@@ -6663,7 +6689,7 @@
         <v>254</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>257</v>
@@ -6692,10 +6718,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I85" s="10"/>
       <c r="J85" s="9">
@@ -6714,7 +6740,7 @@
         <v>254</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>257</v>
@@ -6743,10 +6769,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I86" s="6"/>
       <c r="J86" s="5">
@@ -6765,7 +6791,7 @@
         <v>254</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>257</v>
@@ -6794,10 +6820,10 @@
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I87" s="10"/>
       <c r="J87" s="9">
@@ -6816,7 +6842,7 @@
         <v>254</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P87" s="10" t="s">
         <v>257</v>
@@ -6845,10 +6871,10 @@
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I88" s="6"/>
       <c r="J88" s="5">
@@ -6867,7 +6893,7 @@
         <v>254</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>257</v>
@@ -6896,10 +6922,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I89" s="10"/>
       <c r="J89" s="9">
@@ -6918,7 +6944,7 @@
         <v>254</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P89" s="10" t="s">
         <v>257</v>
@@ -6947,10 +6973,10 @@
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I90" s="6"/>
       <c r="J90" s="5">
@@ -6969,7 +6995,7 @@
         <v>254</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>257</v>
@@ -6998,10 +7024,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I91" s="9">
         <v>46274</v>
@@ -7019,10 +7045,10 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P91" s="10" t="s">
         <v>26</v>
@@ -7126,7 +7152,7 @@
         <v>270</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P93" s="10" t="s">
         <v>270</v>
@@ -7159,7 +7185,7 @@
         <v>46260.58572372685</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7189,7 +7215,7 @@
         <v>273</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>275</v>
@@ -7212,7 +7238,7 @@
         <v>46265.867042303245</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -7242,7 +7268,7 @@
         <v>273</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P95" s="10" t="s">
         <v>275</v>
@@ -7265,7 +7291,7 @@
         <v>46223.56049383101</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7295,7 +7321,7 @@
         <v>273</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>278</v>
@@ -7348,7 +7374,7 @@
         <v>270</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P97" s="10" t="s">
         <v>270</v>
@@ -7381,7 +7407,7 @@
         <v>46238.48978042824</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7434,7 +7460,7 @@
         <v>46238.48978101852</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
@@ -7487,7 +7513,7 @@
         <v>46238.48978153935</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7520,7 +7546,7 @@
         <v>282</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7570,7 +7596,7 @@
         <v>270</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P101" s="10" t="s">
         <v>270</v>
@@ -7603,7 +7629,7 @@
         <v>46238.48978204861</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7656,7 +7682,7 @@
         <v>46238.489782488425</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7709,7 +7735,7 @@
         <v>46238.489782951394</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7792,7 +7818,7 @@
         <v>270</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P105" s="10" t="s">
         <v>270</v>
@@ -7825,7 +7851,7 @@
         <v>46223.56167888889</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7878,7 +7904,7 @@
         <v>46223.561678287035</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
@@ -7931,7 +7957,7 @@
         <v>46223.56167766204</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8032,7 +8058,7 @@
         <v>53</v>
       </c>
       <c r="U109" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
@@ -8047,7 +8073,7 @@
         <v>46223.56179313657</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8077,7 +8103,7 @@
         <v>301</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>304</v>
@@ -8130,7 +8156,7 @@
         <v>301</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P111" s="10" t="s">
         <v>304</v>
@@ -8153,7 +8179,7 @@
         <v>46223.56179165509</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8183,7 +8209,7 @@
         <v>301</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>304</v>
@@ -8301,7 +8327,7 @@
         <v>53</v>
       </c>
       <c r="U114" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
@@ -8316,7 +8342,7 @@
         <v>46206.67717564815</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
@@ -8346,7 +8372,7 @@
         <v>312</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P115" s="10" t="s">
         <v>317</v>
@@ -8369,7 +8395,7 @@
         <v>46206.67717299769</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8422,7 +8448,7 @@
         <v>46206.67717023148</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
@@ -8452,7 +8478,7 @@
         <v>312</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P117" s="10" t="s">
         <v>317</v>
@@ -8472,7 +8498,7 @@
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46206.677167546295</v>
+        <v>46266.509050821754</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>56</v>
@@ -8525,7 +8551,7 @@
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46206.677164733796</v>
+        <v>46266.50914894676</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>56</v>
@@ -8578,7 +8604,7 @@
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46206.67716196759</v>
+        <v>46266.50928239583</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>56</v>
@@ -8631,7 +8657,7 @@
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46206.677158935185</v>
+        <v>46266.50922425926</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>56</v>
@@ -8684,7 +8710,7 @@
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46206.677155868056</v>
+        <v>46266.50934226852</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>56</v>
@@ -8737,7 +8763,7 @@
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46206.67715351852</v>
+        <v>46266.5093941088</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>56</v>
@@ -8790,7 +8816,7 @@
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46206.67715042824</v>
+        <v>46266.50945592593</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>56</v>
@@ -8843,7 +8869,7 @@
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46206.677144120375</v>
+        <v>46266.50953188658</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>56</v>
@@ -8896,7 +8922,7 @@
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46206.67714356481</v>
+        <v>46266.509606238425</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>56</v>
@@ -9000,7 +9026,7 @@
         <v>53</v>
       </c>
       <c r="U127" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
@@ -9015,7 +9041,7 @@
         <v>46223.562056400464</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9045,7 +9071,7 @@
         <v>331</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>335</v>
@@ -9068,7 +9094,7 @@
         <v>46223.56205577546</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
@@ -9098,7 +9124,7 @@
         <v>331</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P129" s="10" t="s">
         <v>335</v>
@@ -9121,7 +9147,7 @@
         <v>46223.56205517361</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9151,7 +9177,7 @@
         <v>331</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P130" s="6" t="s">
         <v>335</v>
@@ -9657,10 +9683,10 @@
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I140" s="5">
         <v>46294</v>
@@ -9699,7 +9725,7 @@
         <v>53</v>
       </c>
       <c r="U140" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
@@ -9720,10 +9746,10 @@
         <v>26</v>
       </c>
       <c r="G141" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H141" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I141" s="9">
         <v>46294</v>
@@ -9744,7 +9770,7 @@
         <v>350</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P141" s="10" t="s">
         <v>355</v>
@@ -9773,10 +9799,10 @@
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I142" s="5">
         <v>46294</v>
@@ -9797,7 +9823,7 @@
         <v>350</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P142" s="6" t="s">
         <v>355</v>
@@ -9826,10 +9852,10 @@
         <v>26</v>
       </c>
       <c r="G143" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H143" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I143" s="9">
         <v>46294</v>
@@ -9850,7 +9876,7 @@
         <v>350</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P143" s="10" t="s">
         <v>355</v>
@@ -9879,10 +9905,10 @@
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I144" s="5">
         <v>46294</v>
@@ -9932,10 +9958,10 @@
         <v>26</v>
       </c>
       <c r="G145" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H145" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I145" s="9">
         <v>46294</v>
@@ -9985,10 +10011,10 @@
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I146" s="5">
         <v>46294</v>
@@ -10038,10 +10064,10 @@
         <v>26</v>
       </c>
       <c r="G147" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H147" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I147" s="9">
         <v>46294</v>
@@ -10091,10 +10117,10 @@
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I148" s="5">
         <v>46294</v>
@@ -10144,10 +10170,10 @@
         <v>26</v>
       </c>
       <c r="G149" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H149" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I149" s="9">
         <v>46294</v>
@@ -10197,10 +10223,10 @@
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I150" s="5">
         <v>46294</v>
@@ -10250,10 +10276,10 @@
         <v>26</v>
       </c>
       <c r="G151" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H151" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I151" s="9">
         <v>46294</v>
@@ -10303,10 +10329,10 @@
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I152" s="5">
         <v>46294</v>
@@ -10356,10 +10382,10 @@
         <v>26</v>
       </c>
       <c r="G153" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H153" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I153" s="10"/>
       <c r="J153" s="9">
@@ -10396,7 +10422,7 @@
         <v>53</v>
       </c>
       <c r="U153" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
@@ -10417,10 +10443,10 @@
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I154" s="5">
         <v>46295</v>
@@ -10470,10 +10496,10 @@
         <v>26</v>
       </c>
       <c r="G155" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H155" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I155" s="9">
         <v>46295</v>
@@ -10523,10 +10549,10 @@
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I156" s="5">
         <v>46295</v>
@@ -10576,10 +10602,10 @@
         <v>26</v>
       </c>
       <c r="G157" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H157" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I157" s="9">
         <v>46295</v>
@@ -10629,10 +10655,10 @@
         <v>26</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H158" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I158" s="5">
         <v>46295</v>
@@ -10682,10 +10708,10 @@
         <v>26</v>
       </c>
       <c r="G159" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H159" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I159" s="9">
         <v>46295</v>
@@ -10735,10 +10761,10 @@
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H160" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I160" s="5">
         <v>46295</v>
@@ -10788,10 +10814,10 @@
         <v>26</v>
       </c>
       <c r="G161" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H161" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I161" s="9">
         <v>46295</v>
@@ -10841,10 +10867,10 @@
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H162" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I162" s="5">
         <v>46295</v>
@@ -10894,10 +10920,10 @@
         <v>26</v>
       </c>
       <c r="G163" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H163" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I163" s="9">
         <v>46295</v>
@@ -10947,10 +10973,10 @@
         <v>26</v>
       </c>
       <c r="G164" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H164" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I164" s="5">
         <v>46295</v>
@@ -11000,10 +11026,10 @@
         <v>26</v>
       </c>
       <c r="G165" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H165" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I165" s="9">
         <v>46295</v>
@@ -11085,7 +11111,7 @@
         <v>53</v>
       </c>
       <c r="U166" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
@@ -11148,7 +11174,7 @@
         <v>53</v>
       </c>
       <c r="U167" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
@@ -11211,7 +11237,7 @@
         <v>53</v>
       </c>
       <c r="U168" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1936" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1937" uniqueCount="394">
   <si>
     <t>50001569 - EUROHINCA</t>
   </si>
@@ -5807,7 +5807,7 @@
         <v>46260.585420972224</v>
       </c>
       <c r="D69" s="9">
-        <v>46260.65784505787</v>
+        <v>46267.18907204861</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>220</v>
@@ -5854,8 +5854,8 @@
       <c r="S69" s="10">
         <v>1</v>
       </c>
-      <c r="T69" s="12" t="s">
-        <v>118</v>
+      <c r="T69" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="U69" s="12" t="s">
         <v>54</v>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46265.86704146991</v>
+        <v>46267.192299490736</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>241</v>
@@ -6147,8 +6147,8 @@
       <c r="S74" s="6">
         <v>0</v>
       </c>
-      <c r="T74" s="7" t="s">
-        <v>53</v>
+      <c r="T74" s="12" t="s">
+        <v>118</v>
       </c>
       <c r="U74" s="12" t="s">
         <v>54</v>
@@ -6493,7 +6493,7 @@
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46206.67600082176</v>
+        <v>46267.19230002315</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>254</v>
@@ -6540,8 +6540,8 @@
       <c r="S81" s="10">
         <v>0</v>
       </c>
-      <c r="T81" s="7" t="s">
-        <v>53</v>
+      <c r="T81" s="12" t="s">
+        <v>118</v>
       </c>
       <c r="U81" s="11" t="s">
         <v>119</v>
@@ -7015,7 +7015,7 @@
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46206.67590806713</v>
+        <v>46267.192300208335</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>268</v>
@@ -7060,7 +7060,9 @@
         <v>46274</v>
       </c>
       <c r="S91" s="10"/>
-      <c r="T91" s="10"/>
+      <c r="T91" s="12" t="s">
+        <v>118</v>
+      </c>
       <c r="U91" s="10"/>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -5156,7 +5156,7 @@
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46206.67494384259</v>
+        <v>46268.82877184028</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>200</v>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46260.59156738426</v>
+        <v>46268.82897829861</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>273</v>
@@ -7182,9 +7182,11 @@
       <c r="B94" s="5">
         <v>46204.84491833333</v>
       </c>
-      <c r="C94" s="6"/>
+      <c r="C94" s="5">
+        <v>46268.82897179398</v>
+      </c>
       <c r="D94" s="5">
-        <v>46260.58572372685</v>
+        <v>46268.82897372685</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>200</v>
@@ -7343,7 +7345,7 @@
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46260.59158416667</v>
+        <v>46268.82912527778</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>280</v>
@@ -7404,9 +7406,11 @@
       <c r="B98" s="5">
         <v>46204.84497997686</v>
       </c>
-      <c r="C98" s="6"/>
+      <c r="C98" s="5">
+        <v>46268.82911924769</v>
+      </c>
       <c r="D98" s="5">
-        <v>46238.48978042824</v>
+        <v>46268.82912079861</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>200</v>
@@ -7565,7 +7569,7 @@
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46260.59160833333</v>
+        <v>46268.83232275463</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>287</v>
@@ -7626,9 +7630,11 @@
       <c r="B102" s="5">
         <v>46204.84507945602</v>
       </c>
-      <c r="C102" s="6"/>
+      <c r="C102" s="5">
+        <v>46268.832316493055</v>
+      </c>
       <c r="D102" s="5">
-        <v>46238.48978204861</v>
+        <v>46268.83231840278</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>200</v>
@@ -7787,7 +7793,7 @@
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46260.591631261574</v>
+        <v>46268.82877262731</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>294</v>
@@ -7848,9 +7854,11 @@
       <c r="B106" s="5">
         <v>46204.84513122685</v>
       </c>
-      <c r="C106" s="6"/>
+      <c r="C106" s="5">
+        <v>46268.828764652775</v>
+      </c>
       <c r="D106" s="5">
-        <v>46223.56167888889</v>
+        <v>46268.8323234375</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>200</v>
@@ -8009,7 +8017,7 @@
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46223.56188028935</v>
+        <v>46268.83245050926</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>301</v>
@@ -8070,9 +8078,11 @@
       <c r="B110" s="5">
         <v>46204.84518325231</v>
       </c>
-      <c r="C110" s="6"/>
+      <c r="C110" s="5">
+        <v>46268.83244546296</v>
+      </c>
       <c r="D110" s="5">
-        <v>46223.56179313657</v>
+        <v>46268.832447175926</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>200</v>
@@ -8341,7 +8351,7 @@
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46206.67717564815</v>
+        <v>46268.83245145834</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>200</v>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -1966,7 +1966,7 @@
         <v>46206.67847994213</v>
       </c>
       <c r="D4" s="5">
-        <v>46206.6784915162</v>
+        <v>46270.90847643519</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2886,7 +2886,7 @@
         <v>46206.76952165509</v>
       </c>
       <c r="D20" s="5">
-        <v>46206.76953472222</v>
+        <v>46270.90897929398</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>69</v>
@@ -3189,7 +3189,7 @@
         <v>46260.881508125</v>
       </c>
       <c r="D25" s="9">
-        <v>46260.881520740746</v>
+        <v>46270.90921540509</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>86</v>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46251.584816585644</v>
+        <v>46270.9090384375</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>111</v>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46206.67094998843</v>
+        <v>46270.9214584838</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>206</v>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -2886,7 +2886,7 @@
         <v>46206.76952165509</v>
       </c>
       <c r="D20" s="5">
-        <v>46270.90897929398</v>
+        <v>46271.18686240741</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>69</v>
@@ -4851,7 +4851,7 @@
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="9">
-        <v>46238.489779490745</v>
+        <v>46271.30030990741</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>180</v>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46206.66745490741</v>
+        <v>46271.191999675924</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>270</v>
@@ -8241,7 +8241,7 @@
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46206.668344247686</v>
+        <v>46270.93091206018</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>309</v>
@@ -8288,7 +8288,7 @@
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46206.677181631945</v>
+        <v>46271.311724189814</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>312</v>
@@ -10385,7 +10385,7 @@
       </c>
       <c r="C153" s="10"/>
       <c r="D153" s="9">
-        <v>46240.71677616898</v>
+        <v>46270.92687512732</v>
       </c>
       <c r="E153" s="10" t="s">
         <v>370</v>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -3677,7 +3677,7 @@
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46266.18744592593</v>
+        <v>46273.16821371528</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>114</v>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46206.67327987269</v>
+        <v>46273.16818572917</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>124</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46238.52089543981</v>
+        <v>46273.16825934028</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>176</v>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -282,7 +282,7 @@
     <t xml:space="preserve"> OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT' 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E, OT 4368 - TABLERO VDF 15 KW LOGICA M-E</t>
   </si>
   <si>
-    <t>Baja</t>
+    <t>Media</t>
   </si>
   <si>
     <t>Tarea en curso</t>
@@ -506,9 +506,6 @@
     <t>Generación OC Tableros,Fabricación Tablero</t>
   </si>
   <si>
-    <t>Media</t>
-  </si>
-  <si>
     <t>Tarea sin iniciar</t>
   </si>
   <si>
@@ -519,6 +516,9 @@
   </si>
   <si>
     <t>Tableros 4368,Fabricación Tablero</t>
+  </si>
+  <si>
+    <t>Baja</t>
   </si>
   <si>
     <t>1216218897008580</t>
@@ -2326,7 +2326,7 @@
         <v>46266.50846133102</v>
       </c>
       <c r="D10" s="5">
-        <v>46266.50961439815</v>
+        <v>46274.16595439815</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>49</v>
@@ -2373,7 +2373,7 @@
       <c r="S10" s="6">
         <v>1</v>
       </c>
-      <c r="T10" s="7" t="s">
+      <c r="T10" s="12" t="s">
         <v>53</v>
       </c>
       <c r="U10" s="12" t="s">
@@ -3677,7 +3677,7 @@
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46273.16821371528</v>
+        <v>46274.15755173611</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>114</v>
@@ -3724,16 +3724,16 @@
       <c r="S33" s="10">
         <v>0</v>
       </c>
-      <c r="T33" s="12" t="s">
+      <c r="T33" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="U33" s="11" t="s">
         <v>118</v>
-      </c>
-      <c r="U33" s="11" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B34" s="5">
         <v>46204.7872006713</v>
@@ -3743,7 +3743,7 @@
         <v>46224.170235694444</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
@@ -3776,7 +3776,7 @@
         <v>92</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3784,10 +3784,10 @@
         <v>0</v>
       </c>
       <c r="T34" s="7" t="s">
-        <v>53</v>
+        <v>122</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
@@ -3832,7 +3832,7 @@
         <v>114</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>125</v>
@@ -3843,10 +3843,10 @@
         <v>0</v>
       </c>
       <c r="T35" s="7" t="s">
-        <v>53</v>
+        <v>122</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
@@ -4199,10 +4199,10 @@
         <v>0</v>
       </c>
       <c r="T41" s="7" t="s">
-        <v>53</v>
+        <v>122</v>
       </c>
       <c r="U41" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
@@ -4260,10 +4260,10 @@
         <v>0</v>
       </c>
       <c r="T42" s="7" t="s">
-        <v>53</v>
+        <v>122</v>
       </c>
       <c r="U42" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
@@ -4627,7 +4627,7 @@
         <v>46238.52095883102</v>
       </c>
       <c r="D49" s="9">
-        <v>46266.18744675926</v>
+        <v>46274.157551620374</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>165</v>
@@ -4674,8 +4674,8 @@
       <c r="S49" s="10">
         <v>1</v>
       </c>
-      <c r="T49" s="12" t="s">
-        <v>118</v>
+      <c r="T49" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="U49" s="7" t="s">
         <v>27</v>
@@ -5141,10 +5141,10 @@
         <v>0</v>
       </c>
       <c r="T57" s="7" t="s">
-        <v>53</v>
+        <v>122</v>
       </c>
       <c r="U57" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -5872,7 +5872,7 @@
         <v>46260.88125827546</v>
       </c>
       <c r="D70" s="5">
-        <v>46266.18744709491</v>
+        <v>46274.157552060184</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>234</v>
@@ -5919,8 +5919,8 @@
       <c r="S70" s="6">
         <v>1</v>
       </c>
-      <c r="T70" s="12" t="s">
-        <v>118</v>
+      <c r="T70" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="U70" s="7" t="s">
         <v>27</v>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46267.192299490736</v>
+        <v>46274.16821466435</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>241</v>
@@ -6148,7 +6148,7 @@
         <v>0</v>
       </c>
       <c r="T74" s="12" t="s">
-        <v>118</v>
+        <v>53</v>
       </c>
       <c r="U74" s="12" t="s">
         <v>54</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46260.881249756945</v>
+        <v>46274.16820373843</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>200</v>
@@ -6493,7 +6493,7 @@
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46267.19230002315</v>
+        <v>46274.16821599537</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>254</v>
@@ -6541,10 +6541,10 @@
         <v>0</v>
       </c>
       <c r="T81" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="U81" s="11" t="s">
         <v>118</v>
-      </c>
-      <c r="U81" s="11" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46206.67610053241</v>
+        <v>46274.16824643518</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>56</v>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46206.676097800926</v>
+        <v>46274.16824774306</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>56</v>
@@ -6658,7 +6658,7 @@
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46206.6760950926</v>
+        <v>46274.1682487037</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>61</v>
@@ -6709,7 +6709,7 @@
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46206.67609248843</v>
+        <v>46274.16824969907</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>56</v>
@@ -6760,7 +6760,7 @@
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46206.67608929398</v>
+        <v>46274.168250601855</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>56</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46206.67608666667</v>
+        <v>46274.16825158565</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>56</v>
@@ -6862,7 +6862,7 @@
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46206.676083935185</v>
+        <v>46274.168252731484</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>56</v>
@@ -6913,7 +6913,7 @@
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46206.676078449076</v>
+        <v>46274.168253807875</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>56</v>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46206.67607780093</v>
+        <v>46274.1682546875</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>56</v>
@@ -7015,7 +7015,7 @@
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46267.192300208335</v>
+        <v>46274.16825564815</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>268</v>
@@ -7061,7 +7061,7 @@
       </c>
       <c r="S91" s="10"/>
       <c r="T91" s="12" t="s">
-        <v>118</v>
+        <v>53</v>
       </c>
       <c r="U91" s="10"/>
     </row>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46268.82897829861</v>
+        <v>46274.165954375</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>273</v>
@@ -7168,7 +7168,7 @@
       <c r="S93" s="10">
         <v>0</v>
       </c>
-      <c r="T93" s="7" t="s">
+      <c r="T93" s="12" t="s">
         <v>53</v>
       </c>
       <c r="U93" s="12" t="s">
@@ -7393,7 +7393,7 @@
         <v>0</v>
       </c>
       <c r="T97" s="7" t="s">
-        <v>53</v>
+        <v>122</v>
       </c>
       <c r="U97" s="12" t="s">
         <v>54</v>
@@ -7617,7 +7617,7 @@
         <v>0</v>
       </c>
       <c r="T101" s="7" t="s">
-        <v>53</v>
+        <v>122</v>
       </c>
       <c r="U101" s="12" t="s">
         <v>54</v>
@@ -7841,7 +7841,7 @@
         <v>0</v>
       </c>
       <c r="T105" s="7" t="s">
-        <v>53</v>
+        <v>122</v>
       </c>
       <c r="U105" s="12" t="s">
         <v>54</v>
@@ -8065,10 +8065,10 @@
         <v>0</v>
       </c>
       <c r="T109" s="7" t="s">
-        <v>53</v>
+        <v>122</v>
       </c>
       <c r="U109" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
@@ -8336,10 +8336,10 @@
         <v>0</v>
       </c>
       <c r="T114" s="7" t="s">
-        <v>53</v>
+        <v>122</v>
       </c>
       <c r="U114" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
@@ -9035,10 +9035,10 @@
         <v>0</v>
       </c>
       <c r="T127" s="7" t="s">
-        <v>53</v>
+        <v>122</v>
       </c>
       <c r="U127" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
@@ -9734,10 +9734,10 @@
         <v>0</v>
       </c>
       <c r="T140" s="7" t="s">
-        <v>53</v>
+        <v>122</v>
       </c>
       <c r="U140" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
@@ -10431,10 +10431,10 @@
         <v>0</v>
       </c>
       <c r="T153" s="7" t="s">
-        <v>53</v>
+        <v>122</v>
       </c>
       <c r="U153" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
@@ -11120,10 +11120,10 @@
         <v>0</v>
       </c>
       <c r="T166" s="7" t="s">
-        <v>53</v>
+        <v>122</v>
       </c>
       <c r="U166" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
@@ -11183,10 +11183,10 @@
         <v>0</v>
       </c>
       <c r="T167" s="7" t="s">
-        <v>53</v>
+        <v>122</v>
       </c>
       <c r="U167" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
@@ -11246,10 +11246,10 @@
         <v>0</v>
       </c>
       <c r="T168" s="7" t="s">
-        <v>53</v>
+        <v>122</v>
       </c>
       <c r="U168" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001569 -  EUROHINCA.xlsx
+++ b/data/50001569 -  EUROHINCA.xlsx
@@ -6100,7 +6100,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46274.16821466435</v>
+        <v>46275.15984197917</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>241</v>
@@ -6147,8 +6147,8 @@
       <c r="S74" s="6">
         <v>0</v>
       </c>
-      <c r="T74" s="12" t="s">
-        <v>53</v>
+      <c r="T74" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="U74" s="12" t="s">
         <v>54</v>
@@ -6493,7 +6493,7 @@
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46274.16821599537</v>
+        <v>46275.15984197917</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>254</v>
@@ -6540,8 +6540,8 @@
       <c r="S81" s="10">
         <v>0</v>
       </c>
-      <c r="T81" s="12" t="s">
-        <v>53</v>
+      <c r="T81" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="U81" s="11" t="s">
         <v>118</v>
@@ -7015,7 +7015,7 @@
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46274.16825564815</v>
+        <v>46275.159843194444</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>268</v>
@@ -7060,8 +7060,8 @@
         <v>46274</v>
       </c>
       <c r="S91" s="10"/>
-      <c r="T91" s="12" t="s">
-        <v>53</v>
+      <c r="T91" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="U91" s="10"/>
     </row>
@@ -7345,7 +7345,7 @@
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46268.82912527778</v>
+        <v>46275.144512893516</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>280</v>
@@ -7392,8 +7392,8 @@
       <c r="S97" s="10">
         <v>0</v>
       </c>
-      <c r="T97" s="7" t="s">
-        <v>122</v>
+      <c r="T97" s="12" t="s">
+        <v>53</v>
       </c>
       <c r="U97" s="12" t="s">
         <v>54</v>
